--- a/xlsx/dre/DRE_02_2026.xlsx
+++ b/xlsx/dre/DRE_02_2026.xlsx
@@ -648,214 +648,214 @@
     <t>R$ 224.680,48</t>
   </si>
   <si>
+    <t>54802/1</t>
+  </si>
+  <si>
     <t>DMP</t>
   </si>
   <si>
+    <t>ITALINEA INDUSTRIA DE MOVEIS LTDA</t>
+  </si>
+  <si>
+    <t>R$  20.126,88</t>
+  </si>
+  <si>
+    <t>PCP</t>
+  </si>
+  <si>
+    <t>DECORA INTERIORES LTDA</t>
+  </si>
+  <si>
+    <t>R$  405,90</t>
+  </si>
+  <si>
+    <t>59401/1</t>
+  </si>
+  <si>
+    <t>DCP</t>
+  </si>
+  <si>
+    <t>R$  39.126,15</t>
+  </si>
+  <si>
+    <t>59601/1</t>
+  </si>
+  <si>
+    <t>R$  37.036,08</t>
+  </si>
+  <si>
+    <t>61401/1</t>
+  </si>
+  <si>
+    <t>R$  5.288,30</t>
+  </si>
+  <si>
+    <t>62301/1</t>
+  </si>
+  <si>
+    <t>R$  11.202,63</t>
+  </si>
+  <si>
+    <t>01/02/26</t>
+  </si>
+  <si>
+    <t>60501/1</t>
+  </si>
+  <si>
+    <t>R$  4.155,65</t>
+  </si>
+  <si>
+    <t>63401/1</t>
+  </si>
+  <si>
+    <t>R$  2.664,41</t>
+  </si>
+  <si>
+    <t>63501/1</t>
+  </si>
+  <si>
+    <t>R$  24.333,46</t>
+  </si>
+  <si>
+    <t>62801/1</t>
+  </si>
+  <si>
+    <t>R$  8.611,10</t>
+  </si>
+  <si>
+    <t>63501/2</t>
+  </si>
+  <si>
+    <t>R$  2.361,24</t>
+  </si>
+  <si>
+    <t>15/06/26</t>
+  </si>
+  <si>
+    <t>Título gerado pela diferença de valor da revisão.</t>
+  </si>
+  <si>
+    <t>61901/1</t>
+  </si>
+  <si>
+    <t>R$  12.309,90</t>
+  </si>
+  <si>
+    <t>64401/2</t>
+  </si>
+  <si>
+    <t>R$  322,96</t>
+  </si>
+  <si>
+    <t>64901/1</t>
+  </si>
+  <si>
+    <t>R$  6.613,24</t>
+  </si>
+  <si>
+    <t>GIR</t>
+  </si>
+  <si>
+    <t>64901FlavioMC</t>
+  </si>
+  <si>
+    <t>63901/1</t>
+  </si>
+  <si>
+    <t>R$  11.869,27</t>
+  </si>
+  <si>
+    <t>63901DeboraCZS</t>
+  </si>
+  <si>
+    <t>64401/1</t>
+  </si>
+  <si>
+    <t>R$  3.001,12</t>
+  </si>
+  <si>
+    <t>R$  1.611,50</t>
+  </si>
+  <si>
+    <t>R$  308,23</t>
+  </si>
+  <si>
+    <t>62901/2</t>
+  </si>
+  <si>
+    <t>R$  1.340,34</t>
+  </si>
+  <si>
+    <t>62901LineuLPA</t>
+  </si>
+  <si>
+    <t>64901/2</t>
+  </si>
+  <si>
+    <t>R$  338,26</t>
+  </si>
+  <si>
+    <t>13/01/26</t>
+  </si>
+  <si>
+    <t>62901/3</t>
+  </si>
+  <si>
+    <t>R$  84,70</t>
+  </si>
+  <si>
+    <t>Antonio Jesus</t>
+  </si>
+  <si>
+    <t>R$  725,71</t>
+  </si>
+  <si>
+    <t>61401/3</t>
+  </si>
+  <si>
+    <t>R$  199,33</t>
+  </si>
+  <si>
+    <t>61901/3</t>
+  </si>
+  <si>
+    <t>R$  2.097,07</t>
+  </si>
+  <si>
+    <t>63901/2</t>
+  </si>
+  <si>
+    <t>R$  932,52</t>
+  </si>
+  <si>
+    <t>64901/3</t>
+  </si>
+  <si>
+    <t>R$  131,04</t>
+  </si>
+  <si>
+    <t>Nail de Senna Cesario</t>
+  </si>
+  <si>
+    <t>R$  5.980,08</t>
+  </si>
+  <si>
     <t>RODAG TRANSPORTES LTDA</t>
   </si>
   <si>
     <t>R$  22,87</t>
   </si>
   <si>
-    <t>PCP</t>
-  </si>
-  <si>
-    <t>DECORA INTERIORES LTDA</t>
-  </si>
-  <si>
-    <t>R$  405,90</t>
-  </si>
-  <si>
-    <t>59401/1</t>
-  </si>
-  <si>
-    <t>DCP</t>
-  </si>
-  <si>
-    <t>ITALINEA INDUSTRIA DE MOVEIS LTDA</t>
-  </si>
-  <si>
-    <t>R$  39.126,15</t>
-  </si>
-  <si>
-    <t>59601/1</t>
-  </si>
-  <si>
-    <t>R$  37.036,08</t>
-  </si>
-  <si>
-    <t>61901/1</t>
-  </si>
-  <si>
-    <t>R$  12.309,90</t>
-  </si>
-  <si>
-    <t>61401/1</t>
-  </si>
-  <si>
-    <t>R$  5.288,30</t>
-  </si>
-  <si>
-    <t>62301/1</t>
-  </si>
-  <si>
-    <t>R$  11.202,63</t>
-  </si>
-  <si>
-    <t>01/02/26</t>
-  </si>
-  <si>
-    <t>60501/1</t>
-  </si>
-  <si>
-    <t>R$  4.155,65</t>
-  </si>
-  <si>
-    <t>63401/1</t>
-  </si>
-  <si>
-    <t>R$  2.664,41</t>
-  </si>
-  <si>
-    <t>63501/1</t>
-  </si>
-  <si>
-    <t>R$  24.333,46</t>
-  </si>
-  <si>
-    <t>62801/1</t>
-  </si>
-  <si>
-    <t>R$  8.611,10</t>
-  </si>
-  <si>
-    <t>63501/2</t>
-  </si>
-  <si>
-    <t>R$  2.361,24</t>
-  </si>
-  <si>
-    <t>15/06/26</t>
-  </si>
-  <si>
-    <t>Título gerado pela diferença de valor da revisão.</t>
-  </si>
-  <si>
-    <t>64401/2</t>
-  </si>
-  <si>
-    <t>R$  322,96</t>
-  </si>
-  <si>
     <t>62901/1</t>
   </si>
   <si>
     <t>R$  14.996,19</t>
   </si>
   <si>
-    <t>GIR</t>
-  </si>
-  <si>
-    <t>62901LineuLPA</t>
-  </si>
-  <si>
-    <t>64901/1</t>
-  </si>
-  <si>
-    <t>R$  6.613,24</t>
-  </si>
-  <si>
-    <t>64901FlavioMC</t>
-  </si>
-  <si>
     <t>57101/1</t>
   </si>
   <si>
     <t>R$  3.613,35</t>
-  </si>
-  <si>
-    <t>63901/1</t>
-  </si>
-  <si>
-    <t>R$  11.869,27</t>
-  </si>
-  <si>
-    <t>63901DeboraCZS</t>
-  </si>
-  <si>
-    <t>64401/1</t>
-  </si>
-  <si>
-    <t>R$  3.001,12</t>
-  </si>
-  <si>
-    <t>R$  1.611,50</t>
-  </si>
-  <si>
-    <t>R$  308,23</t>
-  </si>
-  <si>
-    <t>62901/2</t>
-  </si>
-  <si>
-    <t>R$  1.340,34</t>
-  </si>
-  <si>
-    <t>64901/2</t>
-  </si>
-  <si>
-    <t>R$  338,26</t>
-  </si>
-  <si>
-    <t>13/01/26</t>
-  </si>
-  <si>
-    <t>62901/3</t>
-  </si>
-  <si>
-    <t>R$  84,70</t>
-  </si>
-  <si>
-    <t>Antonio Jesus</t>
-  </si>
-  <si>
-    <t>R$  725,71</t>
-  </si>
-  <si>
-    <t>61401/3</t>
-  </si>
-  <si>
-    <t>R$  199,33</t>
-  </si>
-  <si>
-    <t>61901/3</t>
-  </si>
-  <si>
-    <t>R$  2.097,07</t>
-  </si>
-  <si>
-    <t>63901/2</t>
-  </si>
-  <si>
-    <t>R$  932,52</t>
-  </si>
-  <si>
-    <t>54802/1</t>
-  </si>
-  <si>
-    <t>R$  20.126,88</t>
-  </si>
-  <si>
-    <t>64901/3</t>
-  </si>
-  <si>
-    <t>R$  131,04</t>
-  </si>
-  <si>
-    <t>Nail de Senna Cesario</t>
-  </si>
-  <si>
-    <t>R$  5.980,08</t>
   </si>
   <si>
     <t>59401/4</t>
@@ -5978,25 +5978,25 @@
         <v>33</v>
       </c>
       <c r="E63" t="s">
-        <v>127</v>
+        <v>211</v>
       </c>
       <c r="F63" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G63" t="s">
         <v>41</v>
       </c>
       <c r="H63" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I63" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J63" t="s">
-        <v>119</v>
+        <v>58</v>
       </c>
       <c r="K63" t="s">
-        <v>119</v>
+        <v>58</v>
       </c>
       <c r="L63" t="s">
         <v>34</v>
@@ -6008,10 +6008,10 @@
         <v>47</v>
       </c>
       <c r="O63" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="P63" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q63" t="s">
         <v>47</v>
@@ -6037,16 +6037,16 @@
         <v>157</v>
       </c>
       <c r="F64" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G64" t="s">
         <v>41</v>
       </c>
       <c r="H64" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I64" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J64" t="s">
         <v>134</v>
@@ -6090,16 +6090,16 @@
         <v>34</v>
       </c>
       <c r="E65" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F65" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G65" t="s">
         <v>41</v>
       </c>
       <c r="H65" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="I65" t="s">
         <v>220</v>
@@ -6149,13 +6149,13 @@
         <v>221</v>
       </c>
       <c r="F66" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G66" t="s">
         <v>41</v>
       </c>
       <c r="H66" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="I66" t="s">
         <v>222</v>
@@ -6205,22 +6205,22 @@
         <v>223</v>
       </c>
       <c r="F67" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G67" t="s">
         <v>41</v>
       </c>
       <c r="H67" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="I67" t="s">
         <v>224</v>
       </c>
       <c r="J67" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="K67" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="L67" t="s">
         <v>34</v>
@@ -6232,7 +6232,7 @@
         <v>47</v>
       </c>
       <c r="O67" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="P67" t="s">
         <v>224</v>
@@ -6261,22 +6261,22 @@
         <v>225</v>
       </c>
       <c r="F68" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G68" t="s">
         <v>41</v>
       </c>
       <c r="H68" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="I68" t="s">
         <v>226</v>
       </c>
       <c r="J68" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="K68" t="s">
-        <v>101</v>
+        <v>227</v>
       </c>
       <c r="L68" t="s">
         <v>34</v>
@@ -6288,13 +6288,13 @@
         <v>47</v>
       </c>
       <c r="O68" t="s">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="P68" t="s">
-        <v>226</v>
+        <v>34</v>
       </c>
       <c r="Q68" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R68" t="s">
         <v>34</v>
@@ -6314,25 +6314,25 @@
         <v>34</v>
       </c>
       <c r="E69" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F69" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G69" t="s">
         <v>41</v>
       </c>
       <c r="H69" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="I69" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J69" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="K69" t="s">
-        <v>229</v>
+        <v>101</v>
       </c>
       <c r="L69" t="s">
         <v>34</v>
@@ -6373,22 +6373,22 @@
         <v>230</v>
       </c>
       <c r="F70" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G70" t="s">
         <v>41</v>
       </c>
       <c r="H70" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="I70" t="s">
         <v>231</v>
       </c>
       <c r="J70" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="K70" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="L70" t="s">
         <v>34</v>
@@ -6429,22 +6429,22 @@
         <v>232</v>
       </c>
       <c r="F71" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G71" t="s">
         <v>41</v>
       </c>
       <c r="H71" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="I71" t="s">
         <v>233</v>
       </c>
       <c r="J71" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="K71" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="L71" t="s">
         <v>34</v>
@@ -6456,13 +6456,13 @@
         <v>47</v>
       </c>
       <c r="O71" t="s">
-        <v>34</v>
+        <v>130</v>
       </c>
       <c r="P71" t="s">
-        <v>34</v>
+        <v>233</v>
       </c>
       <c r="Q71" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R71" t="s">
         <v>34</v>
@@ -6485,13 +6485,13 @@
         <v>234</v>
       </c>
       <c r="F72" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G72" t="s">
         <v>41</v>
       </c>
       <c r="H72" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="I72" t="s">
         <v>235</v>
@@ -6512,13 +6512,13 @@
         <v>47</v>
       </c>
       <c r="O72" t="s">
-        <v>130</v>
+        <v>34</v>
       </c>
       <c r="P72" t="s">
-        <v>235</v>
+        <v>34</v>
       </c>
       <c r="Q72" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R72" t="s">
         <v>34</v>
@@ -6541,25 +6541,25 @@
         <v>236</v>
       </c>
       <c r="F73" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G73" t="s">
         <v>41</v>
       </c>
       <c r="H73" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="I73" t="s">
         <v>237</v>
       </c>
       <c r="J73" t="s">
-        <v>119</v>
+        <v>238</v>
       </c>
       <c r="K73" t="s">
         <v>119</v>
       </c>
       <c r="L73" t="s">
-        <v>34</v>
+        <v>239</v>
       </c>
       <c r="M73" t="s">
         <v>209</v>
@@ -6568,13 +6568,13 @@
         <v>47</v>
       </c>
       <c r="O73" t="s">
-        <v>34</v>
+        <v>130</v>
       </c>
       <c r="P73" t="s">
-        <v>34</v>
+        <v>237</v>
       </c>
       <c r="Q73" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R73" t="s">
         <v>34</v>
@@ -6594,28 +6594,28 @@
         <v>34</v>
       </c>
       <c r="E74" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G74" t="s">
         <v>41</v>
       </c>
       <c r="H74" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="I74" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J74" t="s">
-        <v>240</v>
+        <v>113</v>
       </c>
       <c r="K74" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="L74" t="s">
-        <v>241</v>
+        <v>34</v>
       </c>
       <c r="M74" t="s">
         <v>209</v>
@@ -6624,10 +6624,10 @@
         <v>47</v>
       </c>
       <c r="O74" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="P74" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q74" t="s">
         <v>47</v>
@@ -6653,13 +6653,13 @@
         <v>242</v>
       </c>
       <c r="F75" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G75" t="s">
         <v>41</v>
       </c>
       <c r="H75" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="I75" t="s">
         <v>243</v>
@@ -6709,22 +6709,22 @@
         <v>244</v>
       </c>
       <c r="F76" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G76" t="s">
         <v>41</v>
       </c>
       <c r="H76" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="I76" t="s">
         <v>245</v>
       </c>
       <c r="J76" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="K76" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="L76" t="s">
         <v>246</v>
@@ -6765,25 +6765,25 @@
         <v>248</v>
       </c>
       <c r="F77" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G77" t="s">
         <v>41</v>
       </c>
       <c r="H77" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="I77" t="s">
         <v>249</v>
       </c>
       <c r="J77" t="s">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="K77" t="s">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="L77" t="s">
-        <v>246</v>
+        <v>34</v>
       </c>
       <c r="M77" t="s">
         <v>209</v>
@@ -6821,25 +6821,25 @@
         <v>251</v>
       </c>
       <c r="F78" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G78" t="s">
         <v>41</v>
       </c>
       <c r="H78" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="I78" t="s">
         <v>252</v>
       </c>
       <c r="J78" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="K78" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="L78" t="s">
-        <v>246</v>
+        <v>34</v>
       </c>
       <c r="M78" t="s">
         <v>209</v>
@@ -6848,7 +6848,7 @@
         <v>47</v>
       </c>
       <c r="O78" t="s">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="P78" t="s">
         <v>252</v>
@@ -6874,25 +6874,25 @@
         <v>34</v>
       </c>
       <c r="E79" t="s">
+        <v>240</v>
+      </c>
+      <c r="F79" t="s">
+        <v>212</v>
+      </c>
+      <c r="G79" t="s">
+        <v>41</v>
+      </c>
+      <c r="H79" t="s">
+        <v>213</v>
+      </c>
+      <c r="I79" t="s">
         <v>253</v>
       </c>
-      <c r="F79" t="s">
-        <v>211</v>
-      </c>
-      <c r="G79" t="s">
-        <v>41</v>
-      </c>
-      <c r="H79" t="s">
-        <v>219</v>
-      </c>
-      <c r="I79" t="s">
-        <v>254</v>
-      </c>
       <c r="J79" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="K79" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="L79" t="s">
         <v>34</v>
@@ -6904,10 +6904,10 @@
         <v>47</v>
       </c>
       <c r="O79" t="s">
-        <v>255</v>
+        <v>114</v>
       </c>
       <c r="P79" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Q79" t="s">
         <v>47</v>
@@ -6930,25 +6930,25 @@
         <v>34</v>
       </c>
       <c r="E80" t="s">
-        <v>256</v>
+        <v>223</v>
       </c>
       <c r="F80" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G80" t="s">
         <v>41</v>
       </c>
       <c r="H80" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="I80" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="J80" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="K80" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="L80" t="s">
         <v>34</v>
@@ -6960,10 +6960,10 @@
         <v>47</v>
       </c>
       <c r="O80" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="P80" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="Q80" t="s">
         <v>47</v>
@@ -6986,25 +6986,25 @@
         <v>34</v>
       </c>
       <c r="E81" t="s">
-        <v>223</v>
+        <v>255</v>
       </c>
       <c r="F81" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G81" t="s">
         <v>41</v>
       </c>
       <c r="H81" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="I81" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="J81" t="s">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="K81" t="s">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="L81" t="s">
         <v>34</v>
@@ -7016,10 +7016,10 @@
         <v>47</v>
       </c>
       <c r="O81" t="s">
-        <v>114</v>
+        <v>257</v>
       </c>
       <c r="P81" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="Q81" t="s">
         <v>47</v>
@@ -7042,25 +7042,25 @@
         <v>34</v>
       </c>
       <c r="E82" t="s">
-        <v>225</v>
+        <v>258</v>
       </c>
       <c r="F82" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G82" t="s">
         <v>41</v>
       </c>
       <c r="H82" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="I82" t="s">
         <v>259</v>
       </c>
       <c r="J82" t="s">
-        <v>101</v>
+        <v>260</v>
       </c>
       <c r="K82" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="L82" t="s">
         <v>34</v>
@@ -7072,7 +7072,7 @@
         <v>47</v>
       </c>
       <c r="O82" t="s">
-        <v>102</v>
+        <v>247</v>
       </c>
       <c r="P82" t="s">
         <v>259</v>
@@ -7098,19 +7098,19 @@
         <v>34</v>
       </c>
       <c r="E83" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F83" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G83" t="s">
         <v>41</v>
       </c>
       <c r="H83" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="I83" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="J83" t="s">
         <v>80</v>
@@ -7128,10 +7128,10 @@
         <v>47</v>
       </c>
       <c r="O83" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="P83" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q83" t="s">
         <v>47</v>
@@ -7154,22 +7154,22 @@
         <v>34</v>
       </c>
       <c r="E84" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="F84" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G84" t="s">
         <v>41</v>
       </c>
       <c r="H84" t="s">
-        <v>219</v>
+        <v>263</v>
       </c>
       <c r="I84" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="J84" t="s">
-        <v>264</v>
+        <v>119</v>
       </c>
       <c r="K84" t="s">
         <v>119</v>
@@ -7184,10 +7184,10 @@
         <v>47</v>
       </c>
       <c r="O84" t="s">
-        <v>250</v>
+        <v>109</v>
       </c>
       <c r="P84" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q84" t="s">
         <v>47</v>
@@ -7213,22 +7213,22 @@
         <v>265</v>
       </c>
       <c r="F85" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G85" t="s">
         <v>41</v>
       </c>
       <c r="H85" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="I85" t="s">
         <v>266</v>
       </c>
       <c r="J85" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="K85" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="L85" t="s">
         <v>34</v>
@@ -7240,7 +7240,7 @@
         <v>47</v>
       </c>
       <c r="O85" t="s">
-        <v>247</v>
+        <v>102</v>
       </c>
       <c r="P85" t="s">
         <v>266</v>
@@ -7266,25 +7266,25 @@
         <v>34</v>
       </c>
       <c r="E86" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="F86" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G86" t="s">
         <v>41</v>
       </c>
       <c r="H86" t="s">
-        <v>267</v>
+        <v>213</v>
       </c>
       <c r="I86" t="s">
         <v>268</v>
       </c>
       <c r="J86" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="K86" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="L86" t="s">
         <v>34</v>
@@ -7296,7 +7296,7 @@
         <v>47</v>
       </c>
       <c r="O86" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="P86" t="s">
         <v>268</v>
@@ -7325,22 +7325,22 @@
         <v>269</v>
       </c>
       <c r="F87" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G87" t="s">
         <v>41</v>
       </c>
       <c r="H87" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="I87" t="s">
         <v>270</v>
       </c>
       <c r="J87" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="K87" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="L87" t="s">
         <v>34</v>
@@ -7352,7 +7352,7 @@
         <v>47</v>
       </c>
       <c r="O87" t="s">
-        <v>102</v>
+        <v>250</v>
       </c>
       <c r="P87" t="s">
         <v>270</v>
@@ -7381,22 +7381,22 @@
         <v>271</v>
       </c>
       <c r="F88" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G88" t="s">
         <v>41</v>
       </c>
       <c r="H88" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="I88" t="s">
         <v>272</v>
       </c>
       <c r="J88" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="K88" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="L88" t="s">
         <v>34</v>
@@ -7408,7 +7408,7 @@
         <v>47</v>
       </c>
       <c r="O88" t="s">
-        <v>114</v>
+        <v>247</v>
       </c>
       <c r="P88" t="s">
         <v>272</v>
@@ -7434,25 +7434,25 @@
         <v>34</v>
       </c>
       <c r="E89" t="s">
+        <v>127</v>
+      </c>
+      <c r="F89" t="s">
+        <v>212</v>
+      </c>
+      <c r="G89" t="s">
+        <v>41</v>
+      </c>
+      <c r="H89" t="s">
         <v>273</v>
-      </c>
-      <c r="F89" t="s">
-        <v>211</v>
-      </c>
-      <c r="G89" t="s">
-        <v>41</v>
-      </c>
-      <c r="H89" t="s">
-        <v>219</v>
       </c>
       <c r="I89" t="s">
         <v>274</v>
       </c>
       <c r="J89" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="K89" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="L89" t="s">
         <v>34</v>
@@ -7464,7 +7464,7 @@
         <v>47</v>
       </c>
       <c r="O89" t="s">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="P89" t="s">
         <v>274</v>
@@ -7490,25 +7490,25 @@
         <v>34</v>
       </c>
       <c r="E90" t="s">
+        <v>127</v>
+      </c>
+      <c r="F90" t="s">
+        <v>212</v>
+      </c>
+      <c r="G90" t="s">
+        <v>41</v>
+      </c>
+      <c r="H90" t="s">
         <v>275</v>
-      </c>
-      <c r="F90" t="s">
-        <v>211</v>
-      </c>
-      <c r="G90" t="s">
-        <v>41</v>
-      </c>
-      <c r="H90" t="s">
-        <v>219</v>
       </c>
       <c r="I90" t="s">
         <v>276</v>
       </c>
       <c r="J90" t="s">
-        <v>58</v>
+        <v>119</v>
       </c>
       <c r="K90" t="s">
-        <v>58</v>
+        <v>119</v>
       </c>
       <c r="L90" t="s">
         <v>34</v>
@@ -7520,7 +7520,7 @@
         <v>47</v>
       </c>
       <c r="O90" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="P90" t="s">
         <v>276</v>
@@ -7549,25 +7549,25 @@
         <v>277</v>
       </c>
       <c r="F91" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G91" t="s">
         <v>41</v>
       </c>
       <c r="H91" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="I91" t="s">
         <v>278</v>
       </c>
       <c r="J91" t="s">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="K91" t="s">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="L91" t="s">
-        <v>34</v>
+        <v>246</v>
       </c>
       <c r="M91" t="s">
         <v>209</v>
@@ -7576,7 +7576,7 @@
         <v>47</v>
       </c>
       <c r="O91" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="P91" t="s">
         <v>278</v>
@@ -7602,28 +7602,28 @@
         <v>34</v>
       </c>
       <c r="E92" t="s">
-        <v>127</v>
+        <v>279</v>
       </c>
       <c r="F92" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G92" t="s">
         <v>41</v>
       </c>
       <c r="H92" t="s">
-        <v>279</v>
+        <v>213</v>
       </c>
       <c r="I92" t="s">
         <v>280</v>
       </c>
       <c r="J92" t="s">
-        <v>119</v>
+        <v>70</v>
       </c>
       <c r="K92" t="s">
-        <v>119</v>
+        <v>70</v>
       </c>
       <c r="L92" t="s">
-        <v>34</v>
+        <v>246</v>
       </c>
       <c r="M92" t="s">
         <v>209</v>
@@ -7632,7 +7632,7 @@
         <v>47</v>
       </c>
       <c r="O92" t="s">
-        <v>130</v>
+        <v>71</v>
       </c>
       <c r="P92" t="s">
         <v>280</v>
@@ -7661,13 +7661,13 @@
         <v>281</v>
       </c>
       <c r="F93" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G93" t="s">
         <v>41</v>
       </c>
       <c r="H93" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I93" t="s">
         <v>282</v>
@@ -7723,7 +7723,7 @@
         <v>41</v>
       </c>
       <c r="H94" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="I94" t="s">
         <v>286</v>
@@ -7735,7 +7735,7 @@
         <v>134</v>
       </c>
       <c r="L94" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="M94" t="s">
         <v>283</v>
@@ -7779,7 +7779,7 @@
         <v>41</v>
       </c>
       <c r="H95" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="I95" t="s">
         <v>288</v>
@@ -7791,7 +7791,7 @@
         <v>45</v>
       </c>
       <c r="L95" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="M95" t="s">
         <v>283</v>
@@ -7826,10 +7826,10 @@
         <v>33</v>
       </c>
       <c r="E96" t="s">
-        <v>275</v>
+        <v>211</v>
       </c>
       <c r="F96" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G96" t="s">
         <v>41</v>
@@ -7885,7 +7885,7 @@
         <v>293</v>
       </c>
       <c r="F97" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G97" t="s">
         <v>41</v>
@@ -7941,7 +7941,7 @@
         <v>298</v>
       </c>
       <c r="F98" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G98" t="s">
         <v>41</v>
@@ -7997,7 +7997,7 @@
         <v>302</v>
       </c>
       <c r="F99" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G99" t="s">
         <v>41</v>
@@ -8053,7 +8053,7 @@
         <v>306</v>
       </c>
       <c r="F100" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G100" t="s">
         <v>41</v>
@@ -8109,7 +8109,7 @@
         <v>311</v>
       </c>
       <c r="F101" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G101" t="s">
         <v>41</v>
@@ -8165,7 +8165,7 @@
         <v>313</v>
       </c>
       <c r="F102" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G102" t="s">
         <v>41</v>
@@ -8221,7 +8221,7 @@
         <v>315</v>
       </c>
       <c r="F103" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G103" t="s">
         <v>41</v>
@@ -8277,7 +8277,7 @@
         <v>320</v>
       </c>
       <c r="F104" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G104" t="s">
         <v>41</v>
@@ -8333,7 +8333,7 @@
         <v>322</v>
       </c>
       <c r="F105" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G105" t="s">
         <v>41</v>
@@ -8445,7 +8445,7 @@
         <v>327</v>
       </c>
       <c r="F107" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G107" t="s">
         <v>41</v>
@@ -8501,7 +8501,7 @@
         <v>330</v>
       </c>
       <c r="F108" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G108" t="s">
         <v>41</v>
@@ -8613,7 +8613,7 @@
         <v>337</v>
       </c>
       <c r="F110" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G110" t="s">
         <v>41</v>
@@ -8669,7 +8669,7 @@
         <v>339</v>
       </c>
       <c r="F111" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G111" t="s">
         <v>41</v>
@@ -8725,7 +8725,7 @@
         <v>342</v>
       </c>
       <c r="F112" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G112" t="s">
         <v>41</v>
@@ -8893,7 +8893,7 @@
         <v>348</v>
       </c>
       <c r="F115" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G115" t="s">
         <v>41</v>
@@ -8949,7 +8949,7 @@
         <v>352</v>
       </c>
       <c r="F116" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G116" t="s">
         <v>41</v>
@@ -9005,7 +9005,7 @@
         <v>354</v>
       </c>
       <c r="F117" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G117" t="s">
         <v>41</v>
@@ -9020,7 +9020,7 @@
         <v>90</v>
       </c>
       <c r="K117" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L117" t="s">
         <v>351</v>
@@ -9061,7 +9061,7 @@
         <v>356</v>
       </c>
       <c r="F118" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G118" t="s">
         <v>41</v>
@@ -9076,7 +9076,7 @@
         <v>90</v>
       </c>
       <c r="K118" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L118" t="s">
         <v>351</v>
@@ -9117,7 +9117,7 @@
         <v>357</v>
       </c>
       <c r="F119" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G119" t="s">
         <v>41</v>
@@ -9173,7 +9173,7 @@
         <v>359</v>
       </c>
       <c r="F120" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G120" t="s">
         <v>41</v>
@@ -9229,7 +9229,7 @@
         <v>360</v>
       </c>
       <c r="F121" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G121" t="s">
         <v>41</v>
@@ -9285,7 +9285,7 @@
         <v>362</v>
       </c>
       <c r="F122" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G122" t="s">
         <v>41</v>
@@ -9341,7 +9341,7 @@
         <v>363</v>
       </c>
       <c r="F123" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G123" t="s">
         <v>41</v>
@@ -9397,7 +9397,7 @@
         <v>365</v>
       </c>
       <c r="F124" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G124" t="s">
         <v>41</v>
@@ -9453,7 +9453,7 @@
         <v>322</v>
       </c>
       <c r="F125" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G125" t="s">
         <v>41</v>
@@ -9509,7 +9509,7 @@
         <v>367</v>
       </c>
       <c r="F126" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G126" t="s">
         <v>41</v>
@@ -9562,10 +9562,10 @@
         <v>34</v>
       </c>
       <c r="E127" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="F127" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G127" t="s">
         <v>41</v>
@@ -9618,10 +9618,10 @@
         <v>34</v>
       </c>
       <c r="E128" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="F128" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G128" t="s">
         <v>41</v>
@@ -9648,7 +9648,7 @@
         <v>47</v>
       </c>
       <c r="O128" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="P128" t="s">
         <v>370</v>
@@ -9674,10 +9674,10 @@
         <v>34</v>
       </c>
       <c r="E129" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="F129" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G129" t="s">
         <v>41</v>
@@ -9704,7 +9704,7 @@
         <v>47</v>
       </c>
       <c r="O129" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="P129" t="s">
         <v>371</v>
@@ -9730,10 +9730,10 @@
         <v>34</v>
       </c>
       <c r="E130" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="F130" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G130" t="s">
         <v>41</v>
@@ -9760,7 +9760,7 @@
         <v>47</v>
       </c>
       <c r="O130" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="P130" t="s">
         <v>372</v>
@@ -9789,7 +9789,7 @@
         <v>373</v>
       </c>
       <c r="F131" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G131" t="s">
         <v>41</v>
@@ -9842,10 +9842,10 @@
         <v>34</v>
       </c>
       <c r="E132" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="F132" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G132" t="s">
         <v>41</v>
@@ -9901,7 +9901,7 @@
         <v>376</v>
       </c>
       <c r="F133" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G133" t="s">
         <v>41</v>
@@ -9957,7 +9957,7 @@
         <v>327</v>
       </c>
       <c r="F134" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G134" t="s">
         <v>41</v>
@@ -10013,7 +10013,7 @@
         <v>337</v>
       </c>
       <c r="F135" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G135" t="s">
         <v>41</v>
@@ -10069,7 +10069,7 @@
         <v>380</v>
       </c>
       <c r="F136" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G136" t="s">
         <v>41</v>
@@ -10122,10 +10122,10 @@
         <v>34</v>
       </c>
       <c r="E137" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="F137" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G137" t="s">
         <v>41</v>
@@ -10152,7 +10152,7 @@
         <v>47</v>
       </c>
       <c r="O137" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="P137" t="s">
         <v>382</v>
@@ -10181,7 +10181,7 @@
         <v>383</v>
       </c>
       <c r="F138" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G138" t="s">
         <v>41</v>
@@ -10237,7 +10237,7 @@
         <v>242</v>
       </c>
       <c r="F139" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G139" t="s">
         <v>41</v>
@@ -10293,7 +10293,7 @@
         <v>386</v>
       </c>
       <c r="F140" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G140" t="s">
         <v>41</v>
@@ -10320,7 +10320,7 @@
         <v>47</v>
       </c>
       <c r="O140" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="P140" t="s">
         <v>387</v>
@@ -10349,7 +10349,7 @@
         <v>388</v>
       </c>
       <c r="F141" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G141" t="s">
         <v>41</v>
@@ -10402,10 +10402,10 @@
         <v>34</v>
       </c>
       <c r="E142" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="F142" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G142" t="s">
         <v>41</v>
@@ -10432,7 +10432,7 @@
         <v>47</v>
       </c>
       <c r="O142" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="P142" t="s">
         <v>390</v>
@@ -10458,10 +10458,10 @@
         <v>34</v>
       </c>
       <c r="E143" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F143" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G143" t="s">
         <v>41</v>
@@ -10517,7 +10517,7 @@
         <v>103</v>
       </c>
       <c r="F144" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G144" t="s">
         <v>41</v>
@@ -10573,7 +10573,7 @@
         <v>394</v>
       </c>
       <c r="F145" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G145" t="s">
         <v>41</v>
@@ -10600,7 +10600,7 @@
         <v>47</v>
       </c>
       <c r="O145" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="P145" t="s">
         <v>395</v>
@@ -10629,7 +10629,7 @@
         <v>110</v>
       </c>
       <c r="F146" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G146" t="s">
         <v>41</v>
@@ -10685,7 +10685,7 @@
         <v>394</v>
       </c>
       <c r="F147" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G147" t="s">
         <v>41</v>
@@ -10712,7 +10712,7 @@
         <v>47</v>
       </c>
       <c r="O147" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="P147" t="s">
         <v>397</v>
@@ -10741,7 +10741,7 @@
         <v>98</v>
       </c>
       <c r="F148" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G148" t="s">
         <v>41</v>
@@ -10797,7 +10797,7 @@
         <v>110</v>
       </c>
       <c r="F149" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G149" t="s">
         <v>41</v>
@@ -10853,7 +10853,7 @@
         <v>103</v>
       </c>
       <c r="F150" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G150" t="s">
         <v>41</v>
@@ -10909,7 +10909,7 @@
         <v>98</v>
       </c>
       <c r="F151" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G151" t="s">
         <v>41</v>
@@ -10965,7 +10965,7 @@
         <v>402</v>
       </c>
       <c r="F152" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G152" t="s">
         <v>41</v>
@@ -10992,7 +10992,7 @@
         <v>47</v>
       </c>
       <c r="O152" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="P152" t="s">
         <v>374</v>
@@ -11021,7 +11021,7 @@
         <v>403</v>
       </c>
       <c r="F153" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G153" t="s">
         <v>41</v>
@@ -11077,7 +11077,7 @@
         <v>404</v>
       </c>
       <c r="F154" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G154" t="s">
         <v>41</v>
@@ -11104,7 +11104,7 @@
         <v>47</v>
       </c>
       <c r="O154" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="P154" t="s">
         <v>405</v>
@@ -11133,7 +11133,7 @@
         <v>127</v>
       </c>
       <c r="F155" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G155" t="s">
         <v>41</v>
@@ -11189,7 +11189,7 @@
         <v>407</v>
       </c>
       <c r="F156" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G156" t="s">
         <v>41</v>
@@ -11245,7 +11245,7 @@
         <v>409</v>
       </c>
       <c r="F157" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G157" t="s">
         <v>41</v>
@@ -11301,7 +11301,7 @@
         <v>411</v>
       </c>
       <c r="F158" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G158" t="s">
         <v>41</v>
@@ -11328,7 +11328,7 @@
         <v>47</v>
       </c>
       <c r="O158" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="P158" t="s">
         <v>412</v>
@@ -11357,7 +11357,7 @@
         <v>413</v>
       </c>
       <c r="F159" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G159" t="s">
         <v>41</v>
@@ -11384,7 +11384,7 @@
         <v>47</v>
       </c>
       <c r="O159" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="P159" t="s">
         <v>414</v>
@@ -11413,7 +11413,7 @@
         <v>415</v>
       </c>
       <c r="F160" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G160" t="s">
         <v>41</v>
@@ -11690,10 +11690,10 @@
         <v>33</v>
       </c>
       <c r="E165" t="s">
-        <v>275</v>
+        <v>211</v>
       </c>
       <c r="F165" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G165" t="s">
         <v>41</v>
@@ -11746,10 +11746,10 @@
         <v>34</v>
       </c>
       <c r="E166" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F166" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G166" t="s">
         <v>41</v>
@@ -11802,10 +11802,10 @@
         <v>34</v>
       </c>
       <c r="E167" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="F167" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G167" t="s">
         <v>41</v>
@@ -11832,7 +11832,7 @@
         <v>47</v>
       </c>
       <c r="O167" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="P167" t="s">
         <v>428</v>
@@ -11858,10 +11858,10 @@
         <v>34</v>
       </c>
       <c r="E168" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="F168" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G168" t="s">
         <v>41</v>
@@ -11888,7 +11888,7 @@
         <v>47</v>
       </c>
       <c r="O168" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="P168" t="s">
         <v>429</v>
@@ -11914,10 +11914,10 @@
         <v>34</v>
       </c>
       <c r="E169" t="s">
-        <v>251</v>
+        <v>279</v>
       </c>
       <c r="F169" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G169" t="s">
         <v>41</v>
@@ -11970,10 +11970,10 @@
         <v>34</v>
       </c>
       <c r="E170" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F170" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G170" t="s">
         <v>41</v>
@@ -12026,10 +12026,10 @@
         <v>34</v>
       </c>
       <c r="E171" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F171" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G171" t="s">
         <v>41</v>
@@ -12082,10 +12082,10 @@
         <v>34</v>
       </c>
       <c r="E172" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F172" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G172" t="s">
         <v>41</v>
@@ -12100,7 +12100,7 @@
         <v>304</v>
       </c>
       <c r="K172" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L172" t="s">
         <v>34</v>
@@ -12141,7 +12141,7 @@
         <v>221</v>
       </c>
       <c r="F173" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G173" t="s">
         <v>41</v>
@@ -12194,10 +12194,10 @@
         <v>34</v>
       </c>
       <c r="E174" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="F174" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G174" t="s">
         <v>41</v>
@@ -12224,7 +12224,7 @@
         <v>47</v>
       </c>
       <c r="O174" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="P174" t="s">
         <v>437</v>
@@ -12250,10 +12250,10 @@
         <v>34</v>
       </c>
       <c r="E175" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F175" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G175" t="s">
         <v>41</v>
@@ -12306,10 +12306,10 @@
         <v>34</v>
       </c>
       <c r="E176" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="F176" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G176" t="s">
         <v>41</v>
@@ -12362,10 +12362,10 @@
         <v>34</v>
       </c>
       <c r="E177" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F177" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G177" t="s">
         <v>41</v>
@@ -12418,10 +12418,10 @@
         <v>34</v>
       </c>
       <c r="E178" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="F178" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G178" t="s">
         <v>41</v>
@@ -12530,10 +12530,10 @@
         <v>33</v>
       </c>
       <c r="E180" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="F180" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G180" t="s">
         <v>41</v>
@@ -12560,7 +12560,7 @@
         <v>47</v>
       </c>
       <c r="O180" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="P180" t="s">
         <v>446</v>
@@ -12586,10 +12586,10 @@
         <v>34</v>
       </c>
       <c r="E181" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F181" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G181" t="s">
         <v>41</v>
@@ -12642,10 +12642,10 @@
         <v>34</v>
       </c>
       <c r="E182" t="s">
-        <v>251</v>
+        <v>279</v>
       </c>
       <c r="F182" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G182" t="s">
         <v>41</v>
@@ -12698,10 +12698,10 @@
         <v>34</v>
       </c>
       <c r="E183" t="s">
-        <v>251</v>
+        <v>279</v>
       </c>
       <c r="F183" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G183" t="s">
         <v>41</v>
@@ -12754,10 +12754,10 @@
         <v>34</v>
       </c>
       <c r="E184" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F184" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G184" t="s">
         <v>41</v>
@@ -12810,10 +12810,10 @@
         <v>34</v>
       </c>
       <c r="E185" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F185" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G185" t="s">
         <v>41</v>
@@ -12866,10 +12866,10 @@
         <v>34</v>
       </c>
       <c r="E186" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="F186" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G186" t="s">
         <v>41</v>
@@ -12922,10 +12922,10 @@
         <v>34</v>
       </c>
       <c r="E187" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="F187" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G187" t="s">
         <v>41</v>
@@ -12978,10 +12978,10 @@
         <v>34</v>
       </c>
       <c r="E188" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F188" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G188" t="s">
         <v>41</v>
@@ -13034,10 +13034,10 @@
         <v>34</v>
       </c>
       <c r="E189" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F189" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G189" t="s">
         <v>41</v>
@@ -13090,10 +13090,10 @@
         <v>34</v>
       </c>
       <c r="E190" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F190" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G190" t="s">
         <v>41</v>
@@ -13108,7 +13108,7 @@
         <v>304</v>
       </c>
       <c r="K190" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L190" t="s">
         <v>34</v>
@@ -13146,10 +13146,10 @@
         <v>34</v>
       </c>
       <c r="E191" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F191" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G191" t="s">
         <v>41</v>
@@ -13164,7 +13164,7 @@
         <v>304</v>
       </c>
       <c r="K191" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L191" t="s">
         <v>34</v>
@@ -13205,7 +13205,7 @@
         <v>456</v>
       </c>
       <c r="F192" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G192" t="s">
         <v>41</v>
@@ -13261,7 +13261,7 @@
         <v>456</v>
       </c>
       <c r="F193" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G193" t="s">
         <v>41</v>
@@ -13317,7 +13317,7 @@
         <v>157</v>
       </c>
       <c r="F194" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G194" t="s">
         <v>41</v>
@@ -13373,7 +13373,7 @@
         <v>157</v>
       </c>
       <c r="F195" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G195" t="s">
         <v>41</v>
@@ -13426,10 +13426,10 @@
         <v>34</v>
       </c>
       <c r="E196" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F196" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G196" t="s">
         <v>41</v>
@@ -13482,10 +13482,10 @@
         <v>34</v>
       </c>
       <c r="E197" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F197" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G197" t="s">
         <v>41</v>
@@ -13538,10 +13538,10 @@
         <v>34</v>
       </c>
       <c r="E198" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F198" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G198" t="s">
         <v>41</v>
@@ -13594,10 +13594,10 @@
         <v>34</v>
       </c>
       <c r="E199" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="F199" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G199" t="s">
         <v>41</v>
@@ -13650,10 +13650,10 @@
         <v>34</v>
       </c>
       <c r="E200" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="F200" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G200" t="s">
         <v>41</v>
@@ -13706,10 +13706,10 @@
         <v>34</v>
       </c>
       <c r="E201" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F201" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G201" t="s">
         <v>41</v>
@@ -13762,10 +13762,10 @@
         <v>34</v>
       </c>
       <c r="E202" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F202" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G202" t="s">
         <v>41</v>
@@ -13818,10 +13818,10 @@
         <v>34</v>
       </c>
       <c r="E203" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F203" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G203" t="s">
         <v>41</v>
@@ -13877,7 +13877,7 @@
         <v>472</v>
       </c>
       <c r="F204" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G204" t="s">
         <v>41</v>
@@ -13933,7 +13933,7 @@
         <v>472</v>
       </c>
       <c r="F205" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G205" t="s">
         <v>41</v>
@@ -13986,10 +13986,10 @@
         <v>34</v>
       </c>
       <c r="E206" t="s">
-        <v>275</v>
+        <v>211</v>
       </c>
       <c r="F206" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G206" t="s">
         <v>41</v>
@@ -14042,10 +14042,10 @@
         <v>34</v>
       </c>
       <c r="E207" t="s">
-        <v>275</v>
+        <v>211</v>
       </c>
       <c r="F207" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G207" t="s">
         <v>41</v>
@@ -14098,10 +14098,10 @@
         <v>34</v>
       </c>
       <c r="E208" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F208" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G208" t="s">
         <v>41</v>
@@ -14154,10 +14154,10 @@
         <v>34</v>
       </c>
       <c r="E209" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F209" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G209" t="s">
         <v>41</v>
@@ -14210,10 +14210,10 @@
         <v>34</v>
       </c>
       <c r="E210" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="F210" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G210" t="s">
         <v>41</v>
@@ -14266,10 +14266,10 @@
         <v>34</v>
       </c>
       <c r="E211" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="F211" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G211" t="s">
         <v>41</v>
@@ -14296,7 +14296,7 @@
         <v>47</v>
       </c>
       <c r="O211" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="P211" t="s">
         <v>428</v>
@@ -14322,10 +14322,10 @@
         <v>34</v>
       </c>
       <c r="E212" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="F212" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G212" t="s">
         <v>41</v>
@@ -14352,7 +14352,7 @@
         <v>47</v>
       </c>
       <c r="O212" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="P212" t="s">
         <v>480</v>
@@ -14378,10 +14378,10 @@
         <v>34</v>
       </c>
       <c r="E213" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="F213" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G213" t="s">
         <v>41</v>
@@ -14408,7 +14408,7 @@
         <v>47</v>
       </c>
       <c r="O213" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="P213" t="s">
         <v>437</v>
@@ -14434,10 +14434,10 @@
         <v>34</v>
       </c>
       <c r="E214" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="F214" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G214" t="s">
         <v>41</v>
@@ -14464,7 +14464,7 @@
         <v>47</v>
       </c>
       <c r="O214" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="P214" t="s">
         <v>481</v>
@@ -14493,7 +14493,7 @@
         <v>221</v>
       </c>
       <c r="F215" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G215" t="s">
         <v>41</v>
@@ -14549,7 +14549,7 @@
         <v>221</v>
       </c>
       <c r="F216" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G216" t="s">
         <v>41</v>
@@ -14602,10 +14602,10 @@
         <v>34</v>
       </c>
       <c r="E217" t="s">
-        <v>275</v>
+        <v>211</v>
       </c>
       <c r="F217" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G217" t="s">
         <v>41</v>
@@ -14658,10 +14658,10 @@
         <v>34</v>
       </c>
       <c r="E218" t="s">
-        <v>251</v>
+        <v>279</v>
       </c>
       <c r="F218" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G218" t="s">
         <v>41</v>
@@ -14717,7 +14717,7 @@
         <v>221</v>
       </c>
       <c r="F219" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G219" t="s">
         <v>41</v>
@@ -14770,10 +14770,10 @@
         <v>34</v>
       </c>
       <c r="E220" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="F220" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G220" t="s">
         <v>41</v>
@@ -14800,7 +14800,7 @@
         <v>47</v>
       </c>
       <c r="O220" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="P220" t="s">
         <v>486</v>
@@ -14826,10 +14826,10 @@
         <v>34</v>
       </c>
       <c r="E221" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="F221" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G221" t="s">
         <v>41</v>
@@ -14856,7 +14856,7 @@
         <v>47</v>
       </c>
       <c r="O221" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="P221" t="s">
         <v>429</v>
@@ -14882,10 +14882,10 @@
         <v>34</v>
       </c>
       <c r="E222" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="F222" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G222" t="s">
         <v>41</v>
@@ -14912,7 +14912,7 @@
         <v>47</v>
       </c>
       <c r="O222" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="P222" t="s">
         <v>487</v>
@@ -14938,10 +14938,10 @@
         <v>34</v>
       </c>
       <c r="E223" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="F223" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G223" t="s">
         <v>41</v>
@@ -14968,7 +14968,7 @@
         <v>47</v>
       </c>
       <c r="O223" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="P223" t="s">
         <v>488</v>
@@ -14994,10 +14994,10 @@
         <v>34</v>
       </c>
       <c r="E224" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="F224" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G224" t="s">
         <v>41</v>
@@ -15024,7 +15024,7 @@
         <v>47</v>
       </c>
       <c r="O224" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="P224" t="s">
         <v>489</v>
@@ -15050,10 +15050,10 @@
         <v>34</v>
       </c>
       <c r="E225" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F225" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G225" t="s">
         <v>41</v>
@@ -15068,7 +15068,7 @@
         <v>304</v>
       </c>
       <c r="K225" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L225" t="s">
         <v>34</v>
@@ -15106,10 +15106,10 @@
         <v>34</v>
       </c>
       <c r="E226" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F226" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G226" t="s">
         <v>41</v>
@@ -15162,10 +15162,10 @@
         <v>34</v>
       </c>
       <c r="E227" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F227" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G227" t="s">
         <v>41</v>
@@ -15218,10 +15218,10 @@
         <v>34</v>
       </c>
       <c r="E228" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="F228" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G228" t="s">
         <v>41</v>
@@ -15277,7 +15277,7 @@
         <v>494</v>
       </c>
       <c r="F229" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G229" t="s">
         <v>41</v>
@@ -15442,10 +15442,10 @@
         <v>33</v>
       </c>
       <c r="E232" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F232" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G232" t="s">
         <v>41</v>
@@ -15498,10 +15498,10 @@
         <v>34</v>
       </c>
       <c r="E233" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F233" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G233" t="s">
         <v>41</v>
@@ -15554,10 +15554,10 @@
         <v>33</v>
       </c>
       <c r="E234" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="F234" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G234" t="s">
         <v>41</v>
@@ -15584,7 +15584,7 @@
         <v>47</v>
       </c>
       <c r="O234" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="P234" t="s">
         <v>509</v>
@@ -15610,10 +15610,10 @@
         <v>34</v>
       </c>
       <c r="E235" t="s">
-        <v>251</v>
+        <v>279</v>
       </c>
       <c r="F235" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G235" t="s">
         <v>41</v>
@@ -15666,10 +15666,10 @@
         <v>34</v>
       </c>
       <c r="E236" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="F236" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G236" t="s">
         <v>41</v>
@@ -15722,10 +15722,10 @@
         <v>34</v>
       </c>
       <c r="E237" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F237" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G237" t="s">
         <v>41</v>
@@ -15778,10 +15778,10 @@
         <v>34</v>
       </c>
       <c r="E238" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="F238" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G238" t="s">
         <v>41</v>
@@ -15808,7 +15808,7 @@
         <v>47</v>
       </c>
       <c r="O238" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="P238" t="s">
         <v>428</v>
@@ -15834,10 +15834,10 @@
         <v>34</v>
       </c>
       <c r="E239" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="F239" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G239" t="s">
         <v>41</v>
@@ -15864,7 +15864,7 @@
         <v>47</v>
       </c>
       <c r="O239" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="P239" t="s">
         <v>429</v>
@@ -15890,10 +15890,10 @@
         <v>34</v>
       </c>
       <c r="E240" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F240" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G240" t="s">
         <v>41</v>
@@ -15946,10 +15946,10 @@
         <v>34</v>
       </c>
       <c r="E241" t="s">
-        <v>275</v>
+        <v>211</v>
       </c>
       <c r="F241" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G241" t="s">
         <v>41</v>
@@ -16005,7 +16005,7 @@
         <v>472</v>
       </c>
       <c r="F242" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G242" t="s">
         <v>41</v>
@@ -16067,7 +16067,7 @@
         <v>41</v>
       </c>
       <c r="H243" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I243" t="s">
         <v>464</v>
@@ -16123,7 +16123,7 @@
         <v>41</v>
       </c>
       <c r="H244" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I244" t="s">
         <v>517</v>
@@ -16170,10 +16170,10 @@
         <v>34</v>
       </c>
       <c r="E245" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F245" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G245" t="s">
         <v>41</v>
@@ -16235,7 +16235,7 @@
         <v>41</v>
       </c>
       <c r="H246" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I246" t="s">
         <v>519</v>
@@ -16244,7 +16244,7 @@
         <v>90</v>
       </c>
       <c r="K246" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L246" t="s">
         <v>34</v>
@@ -16291,7 +16291,7 @@
         <v>41</v>
       </c>
       <c r="H247" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I247" t="s">
         <v>520</v>
@@ -16347,7 +16347,7 @@
         <v>41</v>
       </c>
       <c r="H248" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I248" t="s">
         <v>521</v>
@@ -16459,7 +16459,7 @@
         <v>41</v>
       </c>
       <c r="H250" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I250" t="s">
         <v>521</v>
@@ -16506,16 +16506,16 @@
         <v>33</v>
       </c>
       <c r="E251" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F251" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G251" t="s">
         <v>41</v>
       </c>
       <c r="H251" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="I251" t="s">
         <v>524</v>
@@ -16562,7 +16562,7 @@
         <v>33</v>
       </c>
       <c r="E252" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F252" t="s">
         <v>499</v>
@@ -16571,7 +16571,7 @@
         <v>41</v>
       </c>
       <c r="H252" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I252" t="s">
         <v>527</v>
@@ -16627,7 +16627,7 @@
         <v>41</v>
       </c>
       <c r="H253" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I253" t="s">
         <v>527</v>
@@ -16683,7 +16683,7 @@
         <v>41</v>
       </c>
       <c r="H254" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I254" t="s">
         <v>528</v>
@@ -16730,7 +16730,7 @@
         <v>34</v>
       </c>
       <c r="E255" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F255" t="s">
         <v>499</v>
@@ -16739,7 +16739,7 @@
         <v>41</v>
       </c>
       <c r="H255" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I255" t="s">
         <v>529</v>
@@ -16786,7 +16786,7 @@
         <v>34</v>
       </c>
       <c r="E256" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F256" t="s">
         <v>499</v>
@@ -16795,7 +16795,7 @@
         <v>41</v>
       </c>
       <c r="H256" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I256" t="s">
         <v>530</v>
@@ -16804,7 +16804,7 @@
         <v>90</v>
       </c>
       <c r="K256" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L256" t="s">
         <v>34</v>
@@ -16842,7 +16842,7 @@
         <v>34</v>
       </c>
       <c r="E257" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F257" t="s">
         <v>499</v>
@@ -16851,7 +16851,7 @@
         <v>41</v>
       </c>
       <c r="H257" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I257" t="s">
         <v>531</v>
@@ -16901,7 +16901,7 @@
         <v>127</v>
       </c>
       <c r="F258" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G258" t="s">
         <v>41</v>
@@ -16957,7 +16957,7 @@
         <v>534</v>
       </c>
       <c r="F259" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G259" t="s">
         <v>41</v>
@@ -16984,7 +16984,7 @@
         <v>47</v>
       </c>
       <c r="O259" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="P259" t="s">
         <v>536</v>
@@ -17013,7 +17013,7 @@
         <v>538</v>
       </c>
       <c r="F260" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G260" t="s">
         <v>41</v>
@@ -17040,7 +17040,7 @@
         <v>47</v>
       </c>
       <c r="O260" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="P260" t="s">
         <v>540</v>
@@ -17069,7 +17069,7 @@
         <v>404</v>
       </c>
       <c r="F261" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G261" t="s">
         <v>41</v>
@@ -17096,7 +17096,7 @@
         <v>47</v>
       </c>
       <c r="O261" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="P261" t="s">
         <v>541</v>
@@ -17131,7 +17131,7 @@
         <v>41</v>
       </c>
       <c r="H262" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I262" t="s">
         <v>543</v>
@@ -17181,7 +17181,7 @@
         <v>103</v>
       </c>
       <c r="F263" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G263" t="s">
         <v>41</v>
@@ -17234,10 +17234,10 @@
         <v>34</v>
       </c>
       <c r="E264" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="F264" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G264" t="s">
         <v>41</v>
@@ -17290,16 +17290,16 @@
         <v>34</v>
       </c>
       <c r="E265" t="s">
-        <v>251</v>
+        <v>279</v>
       </c>
       <c r="F265" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G265" t="s">
         <v>41</v>
       </c>
       <c r="H265" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="I265" t="s">
         <v>548</v>
@@ -17346,10 +17346,10 @@
         <v>34</v>
       </c>
       <c r="E266" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="F266" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G266" t="s">
         <v>41</v>
@@ -17376,7 +17376,7 @@
         <v>47</v>
       </c>
       <c r="O266" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="P266" t="s">
         <v>550</v>
@@ -17405,7 +17405,7 @@
         <v>553</v>
       </c>
       <c r="F267" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G267" t="s">
         <v>41</v>
@@ -17461,7 +17461,7 @@
         <v>555</v>
       </c>
       <c r="F268" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G268" t="s">
         <v>41</v>
@@ -17517,7 +17517,7 @@
         <v>558</v>
       </c>
       <c r="F269" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G269" t="s">
         <v>41</v>
@@ -17573,7 +17573,7 @@
         <v>553</v>
       </c>
       <c r="F270" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G270" t="s">
         <v>41</v>
@@ -17738,10 +17738,10 @@
         <v>33</v>
       </c>
       <c r="E273" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F273" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G273" t="s">
         <v>41</v>
@@ -17756,7 +17756,7 @@
         <v>96</v>
       </c>
       <c r="K273" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L273" t="s">
         <v>566</v>
@@ -17909,7 +17909,7 @@
         <v>572</v>
       </c>
       <c r="F276" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G276" t="s">
         <v>41</v>
@@ -17965,7 +17965,7 @@
         <v>576</v>
       </c>
       <c r="F277" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G277" t="s">
         <v>41</v>
@@ -17992,7 +17992,7 @@
         <v>47</v>
       </c>
       <c r="O277" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="P277" t="s">
         <v>577</v>
@@ -18021,7 +18021,7 @@
         <v>579</v>
       </c>
       <c r="F278" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G278" t="s">
         <v>41</v>
@@ -18077,7 +18077,7 @@
         <v>582</v>
       </c>
       <c r="F279" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G279" t="s">
         <v>41</v>
@@ -18133,7 +18133,7 @@
         <v>585</v>
       </c>
       <c r="F280" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G280" t="s">
         <v>41</v>
@@ -18189,7 +18189,7 @@
         <v>588</v>
       </c>
       <c r="F281" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G281" t="s">
         <v>41</v>
@@ -18245,7 +18245,7 @@
         <v>591</v>
       </c>
       <c r="F282" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G282" t="s">
         <v>41</v>
@@ -18301,7 +18301,7 @@
         <v>594</v>
       </c>
       <c r="F283" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G283" t="s">
         <v>41</v>
@@ -18357,7 +18357,7 @@
         <v>597</v>
       </c>
       <c r="F284" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G284" t="s">
         <v>41</v>
@@ -18413,7 +18413,7 @@
         <v>600</v>
       </c>
       <c r="F285" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G285" t="s">
         <v>41</v>
@@ -18469,7 +18469,7 @@
         <v>603</v>
       </c>
       <c r="F286" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G286" t="s">
         <v>41</v>
@@ -18525,7 +18525,7 @@
         <v>606</v>
       </c>
       <c r="F287" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G287" t="s">
         <v>41</v>
@@ -18581,7 +18581,7 @@
         <v>608</v>
       </c>
       <c r="F288" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G288" t="s">
         <v>41</v>
@@ -18637,7 +18637,7 @@
         <v>611</v>
       </c>
       <c r="F289" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G289" t="s">
         <v>41</v>
@@ -18693,7 +18693,7 @@
         <v>614</v>
       </c>
       <c r="F290" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G290" t="s">
         <v>41</v>
@@ -18749,7 +18749,7 @@
         <v>616</v>
       </c>
       <c r="F291" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G291" t="s">
         <v>41</v>
@@ -18805,7 +18805,7 @@
         <v>618</v>
       </c>
       <c r="F292" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G292" t="s">
         <v>41</v>
@@ -18861,7 +18861,7 @@
         <v>620</v>
       </c>
       <c r="F293" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G293" t="s">
         <v>41</v>
@@ -18917,7 +18917,7 @@
         <v>623</v>
       </c>
       <c r="F294" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G294" t="s">
         <v>41</v>
@@ -18973,7 +18973,7 @@
         <v>626</v>
       </c>
       <c r="F295" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G295" t="s">
         <v>41</v>
@@ -19029,7 +19029,7 @@
         <v>629</v>
       </c>
       <c r="F296" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G296" t="s">
         <v>41</v>
@@ -19085,7 +19085,7 @@
         <v>631</v>
       </c>
       <c r="F297" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G297" t="s">
         <v>41</v>
@@ -19141,7 +19141,7 @@
         <v>634</v>
       </c>
       <c r="F298" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G298" t="s">
         <v>41</v>
@@ -19197,7 +19197,7 @@
         <v>636</v>
       </c>
       <c r="F299" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G299" t="s">
         <v>41</v>
@@ -19253,7 +19253,7 @@
         <v>82</v>
       </c>
       <c r="F300" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G300" t="s">
         <v>41</v>
@@ -19309,7 +19309,7 @@
         <v>110</v>
       </c>
       <c r="F301" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G301" t="s">
         <v>41</v>
@@ -19365,7 +19365,7 @@
         <v>103</v>
       </c>
       <c r="F302" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G302" t="s">
         <v>41</v>
@@ -19421,7 +19421,7 @@
         <v>394</v>
       </c>
       <c r="F303" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G303" t="s">
         <v>41</v>
@@ -19448,7 +19448,7 @@
         <v>47</v>
       </c>
       <c r="O303" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="P303" t="s">
         <v>644</v>
@@ -19477,7 +19477,7 @@
         <v>66</v>
       </c>
       <c r="F304" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G304" t="s">
         <v>41</v>
@@ -19533,7 +19533,7 @@
         <v>98</v>
       </c>
       <c r="F305" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G305" t="s">
         <v>41</v>
@@ -19589,7 +19589,7 @@
         <v>648</v>
       </c>
       <c r="F306" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G306" t="s">
         <v>41</v>
@@ -19645,7 +19645,7 @@
         <v>650</v>
       </c>
       <c r="F307" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G307" t="s">
         <v>41</v>
@@ -19701,7 +19701,7 @@
         <v>652</v>
       </c>
       <c r="F308" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G308" t="s">
         <v>41</v>
@@ -19757,7 +19757,7 @@
         <v>654</v>
       </c>
       <c r="F309" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G309" t="s">
         <v>41</v>
@@ -19813,7 +19813,7 @@
         <v>656</v>
       </c>
       <c r="F310" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G310" t="s">
         <v>41</v>
@@ -19869,7 +19869,7 @@
         <v>534</v>
       </c>
       <c r="F311" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G311" t="s">
         <v>41</v>
@@ -19896,7 +19896,7 @@
         <v>47</v>
       </c>
       <c r="O311" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="P311" t="s">
         <v>658</v>
@@ -19925,7 +19925,7 @@
         <v>659</v>
       </c>
       <c r="F312" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G312" t="s">
         <v>41</v>
@@ -20090,7 +20090,7 @@
         <v>33</v>
       </c>
       <c r="E315" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F315" t="s">
         <v>40</v>
@@ -20146,7 +20146,7 @@
         <v>34</v>
       </c>
       <c r="E316" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="F316" t="s">
         <v>40</v>
@@ -20176,7 +20176,7 @@
         <v>47</v>
       </c>
       <c r="O316" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="P316" t="s">
         <v>667</v>
@@ -20202,7 +20202,7 @@
         <v>34</v>
       </c>
       <c r="E317" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="F317" t="s">
         <v>40</v>
@@ -20232,7 +20232,7 @@
         <v>47</v>
       </c>
       <c r="O317" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="P317" t="s">
         <v>667</v>
@@ -20258,7 +20258,7 @@
         <v>34</v>
       </c>
       <c r="E318" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F318" t="s">
         <v>40</v>
@@ -20314,7 +20314,7 @@
         <v>34</v>
       </c>
       <c r="E319" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="F319" t="s">
         <v>40</v>
@@ -20344,7 +20344,7 @@
         <v>47</v>
       </c>
       <c r="O319" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="P319" t="s">
         <v>667</v>
@@ -20370,7 +20370,7 @@
         <v>34</v>
       </c>
       <c r="E320" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F320" t="s">
         <v>668</v>
@@ -20388,7 +20388,7 @@
         <v>90</v>
       </c>
       <c r="K320" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L320" t="s">
         <v>34</v>
@@ -20426,7 +20426,7 @@
         <v>34</v>
       </c>
       <c r="E321" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="F321" t="s">
         <v>668</v>
@@ -20482,7 +20482,7 @@
         <v>34</v>
       </c>
       <c r="E322" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F322" t="s">
         <v>668</v>
@@ -20594,7 +20594,7 @@
         <v>34</v>
       </c>
       <c r="E324" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="F324" t="s">
         <v>40</v>
@@ -20650,7 +20650,7 @@
         <v>34</v>
       </c>
       <c r="E325" t="s">
-        <v>275</v>
+        <v>211</v>
       </c>
       <c r="F325" t="s">
         <v>40</v>
@@ -20762,7 +20762,7 @@
         <v>34</v>
       </c>
       <c r="E327" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F327" t="s">
         <v>668</v>
@@ -20818,7 +20818,7 @@
         <v>34</v>
       </c>
       <c r="E328" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F328" t="s">
         <v>40</v>
@@ -21060,7 +21060,7 @@
         <v>681</v>
       </c>
       <c r="K332" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L332" t="s">
         <v>682</v>
@@ -21101,7 +21101,7 @@
         <v>683</v>
       </c>
       <c r="F333" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G333" t="s">
         <v>41</v>
@@ -21116,7 +21116,7 @@
         <v>686</v>
       </c>
       <c r="K333" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L333" t="s">
         <v>34</v>
@@ -21549,7 +21549,7 @@
         <v>703</v>
       </c>
       <c r="F341" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G341" t="s">
         <v>41</v>
@@ -21605,13 +21605,13 @@
         <v>704</v>
       </c>
       <c r="F342" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G342" t="s">
         <v>41</v>
       </c>
       <c r="H342" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I342" t="s">
         <v>705</v>
@@ -22165,7 +22165,7 @@
         <v>727</v>
       </c>
       <c r="F352" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G352" t="s">
         <v>41</v>
@@ -22675,7 +22675,7 @@
         <v>41</v>
       </c>
       <c r="H361" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I361" t="s">
         <v>748</v>
@@ -22837,7 +22837,7 @@
         <v>753</v>
       </c>
       <c r="F364" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G364" t="s">
         <v>41</v>
@@ -22893,7 +22893,7 @@
         <v>753</v>
       </c>
       <c r="F365" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G365" t="s">
         <v>41</v>
@@ -23076,7 +23076,7 @@
         <v>681</v>
       </c>
       <c r="K368" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L368" t="s">
         <v>765</v>
@@ -23117,7 +23117,7 @@
         <v>768</v>
       </c>
       <c r="F369" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G369" t="s">
         <v>41</v>
@@ -23621,7 +23621,7 @@
         <v>800</v>
       </c>
       <c r="F378" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G378" t="s">
         <v>41</v>
@@ -23677,7 +23677,7 @@
         <v>802</v>
       </c>
       <c r="F379" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G379" t="s">
         <v>41</v>
@@ -23733,7 +23733,7 @@
         <v>806</v>
       </c>
       <c r="F380" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G380" t="s">
         <v>41</v>
@@ -23789,7 +23789,7 @@
         <v>810</v>
       </c>
       <c r="F381" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G381" t="s">
         <v>41</v>
@@ -23845,7 +23845,7 @@
         <v>814</v>
       </c>
       <c r="F382" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G382" t="s">
         <v>41</v>
@@ -23901,7 +23901,7 @@
         <v>818</v>
       </c>
       <c r="F383" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G383" t="s">
         <v>41</v>
@@ -23957,7 +23957,7 @@
         <v>821</v>
       </c>
       <c r="F384" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G384" t="s">
         <v>41</v>
@@ -24013,7 +24013,7 @@
         <v>825</v>
       </c>
       <c r="F385" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G385" t="s">
         <v>41</v>
@@ -24349,7 +24349,7 @@
         <v>850</v>
       </c>
       <c r="F391" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G391" t="s">
         <v>41</v>
@@ -24685,7 +24685,7 @@
         <v>868</v>
       </c>
       <c r="F397" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G397" t="s">
         <v>41</v>
@@ -24853,7 +24853,7 @@
         <v>879</v>
       </c>
       <c r="F400" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G400" t="s">
         <v>41</v>
@@ -24909,7 +24909,7 @@
         <v>883</v>
       </c>
       <c r="F401" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G401" t="s">
         <v>41</v>
@@ -25581,7 +25581,7 @@
         <v>920</v>
       </c>
       <c r="F413" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G413" t="s">
         <v>41</v>
@@ -25802,10 +25802,10 @@
         <v>33</v>
       </c>
       <c r="E417" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F417" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G417" t="s">
         <v>41</v>
@@ -25858,10 +25858,10 @@
         <v>34</v>
       </c>
       <c r="E418" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="F418" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G418" t="s">
         <v>41</v>
@@ -25888,7 +25888,7 @@
         <v>47</v>
       </c>
       <c r="O418" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="P418" t="s">
         <v>932</v>
@@ -25914,10 +25914,10 @@
         <v>34</v>
       </c>
       <c r="E419" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="F419" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G419" t="s">
         <v>41</v>
@@ -25970,10 +25970,10 @@
         <v>34</v>
       </c>
       <c r="E420" t="s">
-        <v>275</v>
+        <v>211</v>
       </c>
       <c r="F420" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G420" t="s">
         <v>41</v>
@@ -26026,10 +26026,10 @@
         <v>34</v>
       </c>
       <c r="E421" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F421" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G421" t="s">
         <v>41</v>
@@ -26082,10 +26082,10 @@
         <v>34</v>
       </c>
       <c r="E422" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="F422" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G422" t="s">
         <v>41</v>
@@ -26112,7 +26112,7 @@
         <v>47</v>
       </c>
       <c r="O422" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="P422" t="s">
         <v>936</v>
@@ -26138,10 +26138,10 @@
         <v>34</v>
       </c>
       <c r="E423" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F423" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G423" t="s">
         <v>41</v>
@@ -26156,7 +26156,7 @@
         <v>90</v>
       </c>
       <c r="K423" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L423" t="s">
         <v>930</v>
@@ -26194,10 +26194,10 @@
         <v>34</v>
       </c>
       <c r="E424" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F424" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G424" t="s">
         <v>41</v>
@@ -26250,10 +26250,10 @@
         <v>34</v>
       </c>
       <c r="E425" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="F425" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G425" t="s">
         <v>41</v>
@@ -26280,7 +26280,7 @@
         <v>47</v>
       </c>
       <c r="O425" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="P425" t="s">
         <v>939</v>
@@ -26306,10 +26306,10 @@
         <v>34</v>
       </c>
       <c r="E426" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F426" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G426" t="s">
         <v>41</v>
@@ -26365,7 +26365,7 @@
         <v>221</v>
       </c>
       <c r="F427" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G427" t="s">
         <v>41</v>
@@ -26418,10 +26418,10 @@
         <v>34</v>
       </c>
       <c r="E428" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F428" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G428" t="s">
         <v>41</v>
@@ -30901,7 +30901,7 @@
         <v>1043</v>
       </c>
       <c r="F508" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G508" t="s">
         <v>41</v>

--- a/xlsx/dre/DRE_02_2026.xlsx
+++ b/xlsx/dre/DRE_02_2026.xlsx
@@ -648,186 +648,204 @@
     <t>R$ 224.680,48</t>
   </si>
   <si>
+    <t>DMP</t>
+  </si>
+  <si>
+    <t>RODAG TRANSPORTES LTDA</t>
+  </si>
+  <si>
+    <t>R$  22,87</t>
+  </si>
+  <si>
+    <t>PCP</t>
+  </si>
+  <si>
+    <t>DECORA INTERIORES LTDA</t>
+  </si>
+  <si>
+    <t>R$  405,90</t>
+  </si>
+  <si>
+    <t>59401/1</t>
+  </si>
+  <si>
+    <t>DCP</t>
+  </si>
+  <si>
+    <t>ITALINEA INDUSTRIA DE MOVEIS LTDA</t>
+  </si>
+  <si>
+    <t>R$  39.126,15</t>
+  </si>
+  <si>
+    <t>59601/1</t>
+  </si>
+  <si>
+    <t>R$  37.036,08</t>
+  </si>
+  <si>
+    <t>61901/1</t>
+  </si>
+  <si>
+    <t>R$  12.309,90</t>
+  </si>
+  <si>
+    <t>61401/1</t>
+  </si>
+  <si>
+    <t>R$  5.288,30</t>
+  </si>
+  <si>
+    <t>62301/1</t>
+  </si>
+  <si>
+    <t>R$  11.202,63</t>
+  </si>
+  <si>
+    <t>01/02/26</t>
+  </si>
+  <si>
+    <t>60501/1</t>
+  </si>
+  <si>
+    <t>R$  4.155,65</t>
+  </si>
+  <si>
+    <t>63401/1</t>
+  </si>
+  <si>
+    <t>R$  2.664,41</t>
+  </si>
+  <si>
+    <t>63501/1</t>
+  </si>
+  <si>
+    <t>R$  24.333,46</t>
+  </si>
+  <si>
+    <t>62801/1</t>
+  </si>
+  <si>
+    <t>R$  8.611,10</t>
+  </si>
+  <si>
+    <t>63501/2</t>
+  </si>
+  <si>
+    <t>R$  2.361,24</t>
+  </si>
+  <si>
+    <t>15/06/26</t>
+  </si>
+  <si>
+    <t>Título gerado pela diferença de valor da revisão.</t>
+  </si>
+  <si>
+    <t>64401/2</t>
+  </si>
+  <si>
+    <t>R$  322,96</t>
+  </si>
+  <si>
+    <t>62901/1</t>
+  </si>
+  <si>
+    <t>R$  14.996,19</t>
+  </si>
+  <si>
+    <t>GIR</t>
+  </si>
+  <si>
+    <t>62901LineuLPA</t>
+  </si>
+  <si>
+    <t>64901/1</t>
+  </si>
+  <si>
+    <t>R$  6.613,24</t>
+  </si>
+  <si>
+    <t>64901FlavioMC</t>
+  </si>
+  <si>
+    <t>57101/1</t>
+  </si>
+  <si>
+    <t>R$  3.613,35</t>
+  </si>
+  <si>
+    <t>63901/1</t>
+  </si>
+  <si>
+    <t>R$  11.869,27</t>
+  </si>
+  <si>
+    <t>63901DeboraCZS</t>
+  </si>
+  <si>
+    <t>64401/1</t>
+  </si>
+  <si>
+    <t>R$  3.001,12</t>
+  </si>
+  <si>
+    <t>R$  1.611,50</t>
+  </si>
+  <si>
+    <t>R$  308,23</t>
+  </si>
+  <si>
+    <t>62901/2</t>
+  </si>
+  <si>
+    <t>R$  1.340,34</t>
+  </si>
+  <si>
+    <t>64901/2</t>
+  </si>
+  <si>
+    <t>R$  338,26</t>
+  </si>
+  <si>
+    <t>13/01/26</t>
+  </si>
+  <si>
+    <t>62901/3</t>
+  </si>
+  <si>
+    <t>R$  84,70</t>
+  </si>
+  <si>
+    <t>Antonio Jesus</t>
+  </si>
+  <si>
+    <t>R$  725,71</t>
+  </si>
+  <si>
+    <t>61401/3</t>
+  </si>
+  <si>
+    <t>R$  199,33</t>
+  </si>
+  <si>
+    <t>61901/3</t>
+  </si>
+  <si>
+    <t>R$  2.097,07</t>
+  </si>
+  <si>
+    <t>63901/2</t>
+  </si>
+  <si>
+    <t>R$  932,52</t>
+  </si>
+  <si>
     <t>54802/1</t>
   </si>
   <si>
-    <t>DMP</t>
-  </si>
-  <si>
-    <t>ITALINEA INDUSTRIA DE MOVEIS LTDA</t>
-  </si>
-  <si>
     <t>R$  20.126,88</t>
   </si>
   <si>
-    <t>PCP</t>
-  </si>
-  <si>
-    <t>DECORA INTERIORES LTDA</t>
-  </si>
-  <si>
-    <t>R$  405,90</t>
-  </si>
-  <si>
-    <t>59401/1</t>
-  </si>
-  <si>
-    <t>DCP</t>
-  </si>
-  <si>
-    <t>R$  39.126,15</t>
-  </si>
-  <si>
-    <t>59601/1</t>
-  </si>
-  <si>
-    <t>R$  37.036,08</t>
-  </si>
-  <si>
-    <t>61401/1</t>
-  </si>
-  <si>
-    <t>R$  5.288,30</t>
-  </si>
-  <si>
-    <t>62301/1</t>
-  </si>
-  <si>
-    <t>R$  11.202,63</t>
-  </si>
-  <si>
-    <t>01/02/26</t>
-  </si>
-  <si>
-    <t>60501/1</t>
-  </si>
-  <si>
-    <t>R$  4.155,65</t>
-  </si>
-  <si>
-    <t>63401/1</t>
-  </si>
-  <si>
-    <t>R$  2.664,41</t>
-  </si>
-  <si>
-    <t>63501/1</t>
-  </si>
-  <si>
-    <t>R$  24.333,46</t>
-  </si>
-  <si>
-    <t>62801/1</t>
-  </si>
-  <si>
-    <t>R$  8.611,10</t>
-  </si>
-  <si>
-    <t>63501/2</t>
-  </si>
-  <si>
-    <t>R$  2.361,24</t>
-  </si>
-  <si>
-    <t>15/06/26</t>
-  </si>
-  <si>
-    <t>Título gerado pela diferença de valor da revisão.</t>
-  </si>
-  <si>
-    <t>61901/1</t>
-  </si>
-  <si>
-    <t>R$  12.309,90</t>
-  </si>
-  <si>
-    <t>64401/2</t>
-  </si>
-  <si>
-    <t>R$  322,96</t>
-  </si>
-  <si>
-    <t>64901/1</t>
-  </si>
-  <si>
-    <t>R$  6.613,24</t>
-  </si>
-  <si>
-    <t>GIR</t>
-  </si>
-  <si>
-    <t>64901FlavioMC</t>
-  </si>
-  <si>
-    <t>63901/1</t>
-  </si>
-  <si>
-    <t>R$  11.869,27</t>
-  </si>
-  <si>
-    <t>63901DeboraCZS</t>
-  </si>
-  <si>
-    <t>64401/1</t>
-  </si>
-  <si>
-    <t>R$  3.001,12</t>
-  </si>
-  <si>
-    <t>R$  1.611,50</t>
-  </si>
-  <si>
-    <t>R$  308,23</t>
-  </si>
-  <si>
-    <t>62901/2</t>
-  </si>
-  <si>
-    <t>R$  1.340,34</t>
-  </si>
-  <si>
-    <t>62901LineuLPA</t>
-  </si>
-  <si>
-    <t>64901/2</t>
-  </si>
-  <si>
-    <t>R$  338,26</t>
-  </si>
-  <si>
-    <t>13/01/26</t>
-  </si>
-  <si>
-    <t>62901/3</t>
-  </si>
-  <si>
-    <t>R$  84,70</t>
-  </si>
-  <si>
-    <t>Antonio Jesus</t>
-  </si>
-  <si>
-    <t>R$  725,71</t>
-  </si>
-  <si>
-    <t>61401/3</t>
-  </si>
-  <si>
-    <t>R$  199,33</t>
-  </si>
-  <si>
-    <t>61901/3</t>
-  </si>
-  <si>
-    <t>R$  2.097,07</t>
-  </si>
-  <si>
-    <t>63901/2</t>
-  </si>
-  <si>
-    <t>R$  932,52</t>
-  </si>
-  <si>
     <t>64901/3</t>
   </si>
   <si>
@@ -838,24 +856,6 @@
   </si>
   <si>
     <t>R$  5.980,08</t>
-  </si>
-  <si>
-    <t>RODAG TRANSPORTES LTDA</t>
-  </si>
-  <si>
-    <t>R$  22,87</t>
-  </si>
-  <si>
-    <t>62901/1</t>
-  </si>
-  <si>
-    <t>R$  14.996,19</t>
-  </si>
-  <si>
-    <t>57101/1</t>
-  </si>
-  <si>
-    <t>R$  3.613,35</t>
   </si>
   <si>
     <t>59401/4</t>
@@ -5978,25 +5978,25 @@
         <v>33</v>
       </c>
       <c r="E63" t="s">
+        <v>127</v>
+      </c>
+      <c r="F63" t="s">
         <v>211</v>
       </c>
-      <c r="F63" t="s">
+      <c r="G63" t="s">
+        <v>41</v>
+      </c>
+      <c r="H63" t="s">
         <v>212</v>
       </c>
-      <c r="G63" t="s">
-        <v>41</v>
-      </c>
-      <c r="H63" t="s">
+      <c r="I63" t="s">
         <v>213</v>
       </c>
-      <c r="I63" t="s">
-        <v>214</v>
-      </c>
       <c r="J63" t="s">
-        <v>58</v>
+        <v>119</v>
       </c>
       <c r="K63" t="s">
-        <v>58</v>
+        <v>119</v>
       </c>
       <c r="L63" t="s">
         <v>34</v>
@@ -6008,10 +6008,10 @@
         <v>47</v>
       </c>
       <c r="O63" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="P63" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q63" t="s">
         <v>47</v>
@@ -6037,16 +6037,16 @@
         <v>157</v>
       </c>
       <c r="F64" t="s">
+        <v>214</v>
+      </c>
+      <c r="G64" t="s">
+        <v>41</v>
+      </c>
+      <c r="H64" t="s">
         <v>215</v>
       </c>
-      <c r="G64" t="s">
-        <v>41</v>
-      </c>
-      <c r="H64" t="s">
+      <c r="I64" t="s">
         <v>216</v>
-      </c>
-      <c r="I64" t="s">
-        <v>217</v>
       </c>
       <c r="J64" t="s">
         <v>134</v>
@@ -6090,16 +6090,16 @@
         <v>34</v>
       </c>
       <c r="E65" t="s">
+        <v>217</v>
+      </c>
+      <c r="F65" t="s">
         <v>218</v>
       </c>
-      <c r="F65" t="s">
+      <c r="G65" t="s">
+        <v>41</v>
+      </c>
+      <c r="H65" t="s">
         <v>219</v>
-      </c>
-      <c r="G65" t="s">
-        <v>41</v>
-      </c>
-      <c r="H65" t="s">
-        <v>213</v>
       </c>
       <c r="I65" t="s">
         <v>220</v>
@@ -6149,13 +6149,13 @@
         <v>221</v>
       </c>
       <c r="F66" t="s">
+        <v>218</v>
+      </c>
+      <c r="G66" t="s">
+        <v>41</v>
+      </c>
+      <c r="H66" t="s">
         <v>219</v>
-      </c>
-      <c r="G66" t="s">
-        <v>41</v>
-      </c>
-      <c r="H66" t="s">
-        <v>213</v>
       </c>
       <c r="I66" t="s">
         <v>222</v>
@@ -6205,22 +6205,22 @@
         <v>223</v>
       </c>
       <c r="F67" t="s">
+        <v>218</v>
+      </c>
+      <c r="G67" t="s">
+        <v>41</v>
+      </c>
+      <c r="H67" t="s">
         <v>219</v>
-      </c>
-      <c r="G67" t="s">
-        <v>41</v>
-      </c>
-      <c r="H67" t="s">
-        <v>213</v>
       </c>
       <c r="I67" t="s">
         <v>224</v>
       </c>
       <c r="J67" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="K67" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="L67" t="s">
         <v>34</v>
@@ -6232,7 +6232,7 @@
         <v>47</v>
       </c>
       <c r="O67" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="P67" t="s">
         <v>224</v>
@@ -6261,22 +6261,22 @@
         <v>225</v>
       </c>
       <c r="F68" t="s">
+        <v>218</v>
+      </c>
+      <c r="G68" t="s">
+        <v>41</v>
+      </c>
+      <c r="H68" t="s">
         <v>219</v>
-      </c>
-      <c r="G68" t="s">
-        <v>41</v>
-      </c>
-      <c r="H68" t="s">
-        <v>213</v>
       </c>
       <c r="I68" t="s">
         <v>226</v>
       </c>
       <c r="J68" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="K68" t="s">
-        <v>227</v>
+        <v>101</v>
       </c>
       <c r="L68" t="s">
         <v>34</v>
@@ -6288,13 +6288,13 @@
         <v>47</v>
       </c>
       <c r="O68" t="s">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="P68" t="s">
-        <v>34</v>
+        <v>226</v>
       </c>
       <c r="Q68" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R68" t="s">
         <v>34</v>
@@ -6314,25 +6314,25 @@
         <v>34</v>
       </c>
       <c r="E69" t="s">
+        <v>227</v>
+      </c>
+      <c r="F69" t="s">
+        <v>218</v>
+      </c>
+      <c r="G69" t="s">
+        <v>41</v>
+      </c>
+      <c r="H69" t="s">
+        <v>219</v>
+      </c>
+      <c r="I69" t="s">
         <v>228</v>
       </c>
-      <c r="F69" t="s">
-        <v>219</v>
-      </c>
-      <c r="G69" t="s">
-        <v>41</v>
-      </c>
-      <c r="H69" t="s">
-        <v>213</v>
-      </c>
-      <c r="I69" t="s">
+      <c r="J69" t="s">
+        <v>90</v>
+      </c>
+      <c r="K69" t="s">
         <v>229</v>
-      </c>
-      <c r="J69" t="s">
-        <v>101</v>
-      </c>
-      <c r="K69" t="s">
-        <v>101</v>
       </c>
       <c r="L69" t="s">
         <v>34</v>
@@ -6373,22 +6373,22 @@
         <v>230</v>
       </c>
       <c r="F70" t="s">
+        <v>218</v>
+      </c>
+      <c r="G70" t="s">
+        <v>41</v>
+      </c>
+      <c r="H70" t="s">
         <v>219</v>
-      </c>
-      <c r="G70" t="s">
-        <v>41</v>
-      </c>
-      <c r="H70" t="s">
-        <v>213</v>
       </c>
       <c r="I70" t="s">
         <v>231</v>
       </c>
       <c r="J70" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="K70" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="L70" t="s">
         <v>34</v>
@@ -6429,22 +6429,22 @@
         <v>232</v>
       </c>
       <c r="F71" t="s">
+        <v>218</v>
+      </c>
+      <c r="G71" t="s">
+        <v>41</v>
+      </c>
+      <c r="H71" t="s">
         <v>219</v>
-      </c>
-      <c r="G71" t="s">
-        <v>41</v>
-      </c>
-      <c r="H71" t="s">
-        <v>213</v>
       </c>
       <c r="I71" t="s">
         <v>233</v>
       </c>
       <c r="J71" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="K71" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="L71" t="s">
         <v>34</v>
@@ -6456,13 +6456,13 @@
         <v>47</v>
       </c>
       <c r="O71" t="s">
-        <v>130</v>
+        <v>34</v>
       </c>
       <c r="P71" t="s">
-        <v>233</v>
+        <v>34</v>
       </c>
       <c r="Q71" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R71" t="s">
         <v>34</v>
@@ -6485,13 +6485,13 @@
         <v>234</v>
       </c>
       <c r="F72" t="s">
+        <v>218</v>
+      </c>
+      <c r="G72" t="s">
+        <v>41</v>
+      </c>
+      <c r="H72" t="s">
         <v>219</v>
-      </c>
-      <c r="G72" t="s">
-        <v>41</v>
-      </c>
-      <c r="H72" t="s">
-        <v>213</v>
       </c>
       <c r="I72" t="s">
         <v>235</v>
@@ -6512,13 +6512,13 @@
         <v>47</v>
       </c>
       <c r="O72" t="s">
-        <v>34</v>
+        <v>130</v>
       </c>
       <c r="P72" t="s">
-        <v>34</v>
+        <v>235</v>
       </c>
       <c r="Q72" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R72" t="s">
         <v>34</v>
@@ -6541,25 +6541,25 @@
         <v>236</v>
       </c>
       <c r="F73" t="s">
+        <v>218</v>
+      </c>
+      <c r="G73" t="s">
+        <v>41</v>
+      </c>
+      <c r="H73" t="s">
         <v>219</v>
-      </c>
-      <c r="G73" t="s">
-        <v>41</v>
-      </c>
-      <c r="H73" t="s">
-        <v>213</v>
       </c>
       <c r="I73" t="s">
         <v>237</v>
       </c>
       <c r="J73" t="s">
-        <v>238</v>
+        <v>119</v>
       </c>
       <c r="K73" t="s">
         <v>119</v>
       </c>
       <c r="L73" t="s">
-        <v>239</v>
+        <v>34</v>
       </c>
       <c r="M73" t="s">
         <v>209</v>
@@ -6568,13 +6568,13 @@
         <v>47</v>
       </c>
       <c r="O73" t="s">
-        <v>130</v>
+        <v>34</v>
       </c>
       <c r="P73" t="s">
-        <v>237</v>
+        <v>34</v>
       </c>
       <c r="Q73" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R73" t="s">
         <v>34</v>
@@ -6594,28 +6594,28 @@
         <v>34</v>
       </c>
       <c r="E74" t="s">
+        <v>238</v>
+      </c>
+      <c r="F74" t="s">
+        <v>218</v>
+      </c>
+      <c r="G74" t="s">
+        <v>41</v>
+      </c>
+      <c r="H74" t="s">
+        <v>219</v>
+      </c>
+      <c r="I74" t="s">
+        <v>239</v>
+      </c>
+      <c r="J74" t="s">
         <v>240</v>
       </c>
-      <c r="F74" t="s">
-        <v>219</v>
-      </c>
-      <c r="G74" t="s">
-        <v>41</v>
-      </c>
-      <c r="H74" t="s">
-        <v>213</v>
-      </c>
-      <c r="I74" t="s">
+      <c r="K74" t="s">
+        <v>119</v>
+      </c>
+      <c r="L74" t="s">
         <v>241</v>
-      </c>
-      <c r="J74" t="s">
-        <v>113</v>
-      </c>
-      <c r="K74" t="s">
-        <v>113</v>
-      </c>
-      <c r="L74" t="s">
-        <v>34</v>
       </c>
       <c r="M74" t="s">
         <v>209</v>
@@ -6624,10 +6624,10 @@
         <v>47</v>
       </c>
       <c r="O74" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="P74" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="Q74" t="s">
         <v>47</v>
@@ -6653,13 +6653,13 @@
         <v>242</v>
       </c>
       <c r="F75" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G75" t="s">
         <v>41</v>
       </c>
       <c r="H75" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="I75" t="s">
         <v>243</v>
@@ -6709,22 +6709,22 @@
         <v>244</v>
       </c>
       <c r="F76" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G76" t="s">
         <v>41</v>
       </c>
       <c r="H76" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="I76" t="s">
         <v>245</v>
       </c>
       <c r="J76" t="s">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="K76" t="s">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="L76" t="s">
         <v>246</v>
@@ -6765,25 +6765,25 @@
         <v>248</v>
       </c>
       <c r="F77" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G77" t="s">
         <v>41</v>
       </c>
       <c r="H77" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="I77" t="s">
         <v>249</v>
       </c>
       <c r="J77" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="K77" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="L77" t="s">
-        <v>34</v>
+        <v>246</v>
       </c>
       <c r="M77" t="s">
         <v>209</v>
@@ -6821,25 +6821,25 @@
         <v>251</v>
       </c>
       <c r="F78" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G78" t="s">
         <v>41</v>
       </c>
       <c r="H78" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="I78" t="s">
         <v>252</v>
       </c>
       <c r="J78" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="K78" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="L78" t="s">
-        <v>34</v>
+        <v>246</v>
       </c>
       <c r="M78" t="s">
         <v>209</v>
@@ -6848,7 +6848,7 @@
         <v>47</v>
       </c>
       <c r="O78" t="s">
-        <v>109</v>
+        <v>71</v>
       </c>
       <c r="P78" t="s">
         <v>252</v>
@@ -6874,25 +6874,25 @@
         <v>34</v>
       </c>
       <c r="E79" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="F79" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G79" t="s">
         <v>41</v>
       </c>
       <c r="H79" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="I79" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J79" t="s">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="K79" t="s">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="L79" t="s">
         <v>34</v>
@@ -6904,10 +6904,10 @@
         <v>47</v>
       </c>
       <c r="O79" t="s">
-        <v>114</v>
+        <v>255</v>
       </c>
       <c r="P79" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q79" t="s">
         <v>47</v>
@@ -6930,25 +6930,25 @@
         <v>34</v>
       </c>
       <c r="E80" t="s">
-        <v>223</v>
+        <v>256</v>
       </c>
       <c r="F80" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G80" t="s">
         <v>41</v>
       </c>
       <c r="H80" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="I80" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="J80" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="K80" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="L80" t="s">
         <v>34</v>
@@ -6960,10 +6960,10 @@
         <v>47</v>
       </c>
       <c r="O80" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="P80" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q80" t="s">
         <v>47</v>
@@ -6986,25 +6986,25 @@
         <v>34</v>
       </c>
       <c r="E81" t="s">
-        <v>255</v>
+        <v>223</v>
       </c>
       <c r="F81" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G81" t="s">
         <v>41</v>
       </c>
       <c r="H81" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="I81" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="J81" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="K81" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="L81" t="s">
         <v>34</v>
@@ -7016,10 +7016,10 @@
         <v>47</v>
       </c>
       <c r="O81" t="s">
-        <v>257</v>
+        <v>114</v>
       </c>
       <c r="P81" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q81" t="s">
         <v>47</v>
@@ -7042,25 +7042,25 @@
         <v>34</v>
       </c>
       <c r="E82" t="s">
-        <v>258</v>
+        <v>225</v>
       </c>
       <c r="F82" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G82" t="s">
         <v>41</v>
       </c>
       <c r="H82" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="I82" t="s">
         <v>259</v>
       </c>
       <c r="J82" t="s">
-        <v>260</v>
+        <v>101</v>
       </c>
       <c r="K82" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="L82" t="s">
         <v>34</v>
@@ -7072,7 +7072,7 @@
         <v>47</v>
       </c>
       <c r="O82" t="s">
-        <v>247</v>
+        <v>102</v>
       </c>
       <c r="P82" t="s">
         <v>259</v>
@@ -7098,19 +7098,19 @@
         <v>34</v>
       </c>
       <c r="E83" t="s">
+        <v>260</v>
+      </c>
+      <c r="F83" t="s">
+        <v>211</v>
+      </c>
+      <c r="G83" t="s">
+        <v>41</v>
+      </c>
+      <c r="H83" t="s">
+        <v>219</v>
+      </c>
+      <c r="I83" t="s">
         <v>261</v>
-      </c>
-      <c r="F83" t="s">
-        <v>212</v>
-      </c>
-      <c r="G83" t="s">
-        <v>41</v>
-      </c>
-      <c r="H83" t="s">
-        <v>213</v>
-      </c>
-      <c r="I83" t="s">
-        <v>262</v>
       </c>
       <c r="J83" t="s">
         <v>80</v>
@@ -7128,10 +7128,10 @@
         <v>47</v>
       </c>
       <c r="O83" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="P83" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q83" t="s">
         <v>47</v>
@@ -7154,22 +7154,22 @@
         <v>34</v>
       </c>
       <c r="E84" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="F84" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G84" t="s">
         <v>41</v>
       </c>
       <c r="H84" t="s">
+        <v>219</v>
+      </c>
+      <c r="I84" t="s">
         <v>263</v>
       </c>
-      <c r="I84" t="s">
+      <c r="J84" t="s">
         <v>264</v>
-      </c>
-      <c r="J84" t="s">
-        <v>119</v>
       </c>
       <c r="K84" t="s">
         <v>119</v>
@@ -7184,10 +7184,10 @@
         <v>47</v>
       </c>
       <c r="O84" t="s">
-        <v>109</v>
+        <v>250</v>
       </c>
       <c r="P84" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q84" t="s">
         <v>47</v>
@@ -7213,22 +7213,22 @@
         <v>265</v>
       </c>
       <c r="F85" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G85" t="s">
         <v>41</v>
       </c>
       <c r="H85" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="I85" t="s">
         <v>266</v>
       </c>
       <c r="J85" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="K85" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="L85" t="s">
         <v>34</v>
@@ -7240,7 +7240,7 @@
         <v>47</v>
       </c>
       <c r="O85" t="s">
-        <v>102</v>
+        <v>247</v>
       </c>
       <c r="P85" t="s">
         <v>266</v>
@@ -7266,25 +7266,25 @@
         <v>34</v>
       </c>
       <c r="E86" t="s">
+        <v>256</v>
+      </c>
+      <c r="F86" t="s">
+        <v>211</v>
+      </c>
+      <c r="G86" t="s">
+        <v>41</v>
+      </c>
+      <c r="H86" t="s">
         <v>267</v>
-      </c>
-      <c r="F86" t="s">
-        <v>212</v>
-      </c>
-      <c r="G86" t="s">
-        <v>41</v>
-      </c>
-      <c r="H86" t="s">
-        <v>213</v>
       </c>
       <c r="I86" t="s">
         <v>268</v>
       </c>
       <c r="J86" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="K86" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="L86" t="s">
         <v>34</v>
@@ -7296,7 +7296,7 @@
         <v>47</v>
       </c>
       <c r="O86" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="P86" t="s">
         <v>268</v>
@@ -7325,22 +7325,22 @@
         <v>269</v>
       </c>
       <c r="F87" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G87" t="s">
         <v>41</v>
       </c>
       <c r="H87" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="I87" t="s">
         <v>270</v>
       </c>
       <c r="J87" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="K87" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="L87" t="s">
         <v>34</v>
@@ -7352,7 +7352,7 @@
         <v>47</v>
       </c>
       <c r="O87" t="s">
-        <v>250</v>
+        <v>102</v>
       </c>
       <c r="P87" t="s">
         <v>270</v>
@@ -7381,22 +7381,22 @@
         <v>271</v>
       </c>
       <c r="F88" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G88" t="s">
         <v>41</v>
       </c>
       <c r="H88" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="I88" t="s">
         <v>272</v>
       </c>
       <c r="J88" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="K88" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="L88" t="s">
         <v>34</v>
@@ -7408,7 +7408,7 @@
         <v>47</v>
       </c>
       <c r="O88" t="s">
-        <v>247</v>
+        <v>114</v>
       </c>
       <c r="P88" t="s">
         <v>272</v>
@@ -7434,25 +7434,25 @@
         <v>34</v>
       </c>
       <c r="E89" t="s">
-        <v>127</v>
+        <v>273</v>
       </c>
       <c r="F89" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G89" t="s">
         <v>41</v>
       </c>
       <c r="H89" t="s">
-        <v>273</v>
+        <v>219</v>
       </c>
       <c r="I89" t="s">
         <v>274</v>
       </c>
       <c r="J89" t="s">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="K89" t="s">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="L89" t="s">
         <v>34</v>
@@ -7464,7 +7464,7 @@
         <v>47</v>
       </c>
       <c r="O89" t="s">
-        <v>130</v>
+        <v>255</v>
       </c>
       <c r="P89" t="s">
         <v>274</v>
@@ -7490,25 +7490,25 @@
         <v>34</v>
       </c>
       <c r="E90" t="s">
-        <v>127</v>
+        <v>275</v>
       </c>
       <c r="F90" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G90" t="s">
         <v>41</v>
       </c>
       <c r="H90" t="s">
-        <v>275</v>
+        <v>219</v>
       </c>
       <c r="I90" t="s">
         <v>276</v>
       </c>
       <c r="J90" t="s">
-        <v>119</v>
+        <v>58</v>
       </c>
       <c r="K90" t="s">
-        <v>119</v>
+        <v>58</v>
       </c>
       <c r="L90" t="s">
         <v>34</v>
@@ -7520,7 +7520,7 @@
         <v>47</v>
       </c>
       <c r="O90" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="P90" t="s">
         <v>276</v>
@@ -7549,25 +7549,25 @@
         <v>277</v>
       </c>
       <c r="F91" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G91" t="s">
         <v>41</v>
       </c>
       <c r="H91" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="I91" t="s">
         <v>278</v>
       </c>
       <c r="J91" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="K91" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="L91" t="s">
-        <v>246</v>
+        <v>34</v>
       </c>
       <c r="M91" t="s">
         <v>209</v>
@@ -7576,7 +7576,7 @@
         <v>47</v>
       </c>
       <c r="O91" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="P91" t="s">
         <v>278</v>
@@ -7602,28 +7602,28 @@
         <v>34</v>
       </c>
       <c r="E92" t="s">
+        <v>127</v>
+      </c>
+      <c r="F92" t="s">
+        <v>211</v>
+      </c>
+      <c r="G92" t="s">
+        <v>41</v>
+      </c>
+      <c r="H92" t="s">
         <v>279</v>
-      </c>
-      <c r="F92" t="s">
-        <v>212</v>
-      </c>
-      <c r="G92" t="s">
-        <v>41</v>
-      </c>
-      <c r="H92" t="s">
-        <v>213</v>
       </c>
       <c r="I92" t="s">
         <v>280</v>
       </c>
       <c r="J92" t="s">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="K92" t="s">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="L92" t="s">
-        <v>246</v>
+        <v>34</v>
       </c>
       <c r="M92" t="s">
         <v>209</v>
@@ -7632,7 +7632,7 @@
         <v>47</v>
       </c>
       <c r="O92" t="s">
-        <v>71</v>
+        <v>130</v>
       </c>
       <c r="P92" t="s">
         <v>280</v>
@@ -7661,13 +7661,13 @@
         <v>281</v>
       </c>
       <c r="F93" t="s">
+        <v>214</v>
+      </c>
+      <c r="G93" t="s">
+        <v>41</v>
+      </c>
+      <c r="H93" t="s">
         <v>215</v>
-      </c>
-      <c r="G93" t="s">
-        <v>41</v>
-      </c>
-      <c r="H93" t="s">
-        <v>216</v>
       </c>
       <c r="I93" t="s">
         <v>282</v>
@@ -7723,7 +7723,7 @@
         <v>41</v>
       </c>
       <c r="H94" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="I94" t="s">
         <v>286</v>
@@ -7735,7 +7735,7 @@
         <v>134</v>
       </c>
       <c r="L94" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M94" t="s">
         <v>283</v>
@@ -7779,7 +7779,7 @@
         <v>41</v>
       </c>
       <c r="H95" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="I95" t="s">
         <v>288</v>
@@ -7791,7 +7791,7 @@
         <v>45</v>
       </c>
       <c r="L95" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M95" t="s">
         <v>283</v>
@@ -7826,10 +7826,10 @@
         <v>33</v>
       </c>
       <c r="E96" t="s">
+        <v>275</v>
+      </c>
+      <c r="F96" t="s">
         <v>211</v>
-      </c>
-      <c r="F96" t="s">
-        <v>212</v>
       </c>
       <c r="G96" t="s">
         <v>41</v>
@@ -7885,7 +7885,7 @@
         <v>293</v>
       </c>
       <c r="F97" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G97" t="s">
         <v>41</v>
@@ -7941,7 +7941,7 @@
         <v>298</v>
       </c>
       <c r="F98" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G98" t="s">
         <v>41</v>
@@ -7997,7 +7997,7 @@
         <v>302</v>
       </c>
       <c r="F99" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G99" t="s">
         <v>41</v>
@@ -8053,7 +8053,7 @@
         <v>306</v>
       </c>
       <c r="F100" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G100" t="s">
         <v>41</v>
@@ -8109,7 +8109,7 @@
         <v>311</v>
       </c>
       <c r="F101" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G101" t="s">
         <v>41</v>
@@ -8165,7 +8165,7 @@
         <v>313</v>
       </c>
       <c r="F102" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G102" t="s">
         <v>41</v>
@@ -8221,7 +8221,7 @@
         <v>315</v>
       </c>
       <c r="F103" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G103" t="s">
         <v>41</v>
@@ -8277,7 +8277,7 @@
         <v>320</v>
       </c>
       <c r="F104" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G104" t="s">
         <v>41</v>
@@ -8333,7 +8333,7 @@
         <v>322</v>
       </c>
       <c r="F105" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G105" t="s">
         <v>41</v>
@@ -8445,7 +8445,7 @@
         <v>327</v>
       </c>
       <c r="F107" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G107" t="s">
         <v>41</v>
@@ -8501,7 +8501,7 @@
         <v>330</v>
       </c>
       <c r="F108" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G108" t="s">
         <v>41</v>
@@ -8613,7 +8613,7 @@
         <v>337</v>
       </c>
       <c r="F110" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G110" t="s">
         <v>41</v>
@@ -8669,7 +8669,7 @@
         <v>339</v>
       </c>
       <c r="F111" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G111" t="s">
         <v>41</v>
@@ -8725,7 +8725,7 @@
         <v>342</v>
       </c>
       <c r="F112" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G112" t="s">
         <v>41</v>
@@ -8893,7 +8893,7 @@
         <v>348</v>
       </c>
       <c r="F115" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G115" t="s">
         <v>41</v>
@@ -8949,7 +8949,7 @@
         <v>352</v>
       </c>
       <c r="F116" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G116" t="s">
         <v>41</v>
@@ -9005,7 +9005,7 @@
         <v>354</v>
       </c>
       <c r="F117" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G117" t="s">
         <v>41</v>
@@ -9020,7 +9020,7 @@
         <v>90</v>
       </c>
       <c r="K117" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L117" t="s">
         <v>351</v>
@@ -9061,7 +9061,7 @@
         <v>356</v>
       </c>
       <c r="F118" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G118" t="s">
         <v>41</v>
@@ -9076,7 +9076,7 @@
         <v>90</v>
       </c>
       <c r="K118" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L118" t="s">
         <v>351</v>
@@ -9117,7 +9117,7 @@
         <v>357</v>
       </c>
       <c r="F119" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G119" t="s">
         <v>41</v>
@@ -9173,7 +9173,7 @@
         <v>359</v>
       </c>
       <c r="F120" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G120" t="s">
         <v>41</v>
@@ -9229,7 +9229,7 @@
         <v>360</v>
       </c>
       <c r="F121" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G121" t="s">
         <v>41</v>
@@ -9285,7 +9285,7 @@
         <v>362</v>
       </c>
       <c r="F122" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G122" t="s">
         <v>41</v>
@@ -9341,7 +9341,7 @@
         <v>363</v>
       </c>
       <c r="F123" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G123" t="s">
         <v>41</v>
@@ -9397,7 +9397,7 @@
         <v>365</v>
       </c>
       <c r="F124" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G124" t="s">
         <v>41</v>
@@ -9453,7 +9453,7 @@
         <v>322</v>
       </c>
       <c r="F125" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G125" t="s">
         <v>41</v>
@@ -9509,7 +9509,7 @@
         <v>367</v>
       </c>
       <c r="F126" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G126" t="s">
         <v>41</v>
@@ -9562,10 +9562,10 @@
         <v>34</v>
       </c>
       <c r="E127" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="F127" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G127" t="s">
         <v>41</v>
@@ -9618,10 +9618,10 @@
         <v>34</v>
       </c>
       <c r="E128" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="F128" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G128" t="s">
         <v>41</v>
@@ -9648,7 +9648,7 @@
         <v>47</v>
       </c>
       <c r="O128" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="P128" t="s">
         <v>370</v>
@@ -9674,10 +9674,10 @@
         <v>34</v>
       </c>
       <c r="E129" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="F129" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G129" t="s">
         <v>41</v>
@@ -9704,7 +9704,7 @@
         <v>47</v>
       </c>
       <c r="O129" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="P129" t="s">
         <v>371</v>
@@ -9730,10 +9730,10 @@
         <v>34</v>
       </c>
       <c r="E130" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="F130" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G130" t="s">
         <v>41</v>
@@ -9760,7 +9760,7 @@
         <v>47</v>
       </c>
       <c r="O130" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="P130" t="s">
         <v>372</v>
@@ -9789,7 +9789,7 @@
         <v>373</v>
       </c>
       <c r="F131" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G131" t="s">
         <v>41</v>
@@ -9842,10 +9842,10 @@
         <v>34</v>
       </c>
       <c r="E132" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="F132" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G132" t="s">
         <v>41</v>
@@ -9901,7 +9901,7 @@
         <v>376</v>
       </c>
       <c r="F133" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G133" t="s">
         <v>41</v>
@@ -9957,7 +9957,7 @@
         <v>327</v>
       </c>
       <c r="F134" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G134" t="s">
         <v>41</v>
@@ -10013,7 +10013,7 @@
         <v>337</v>
       </c>
       <c r="F135" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G135" t="s">
         <v>41</v>
@@ -10069,7 +10069,7 @@
         <v>380</v>
       </c>
       <c r="F136" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G136" t="s">
         <v>41</v>
@@ -10122,10 +10122,10 @@
         <v>34</v>
       </c>
       <c r="E137" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="F137" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G137" t="s">
         <v>41</v>
@@ -10152,7 +10152,7 @@
         <v>47</v>
       </c>
       <c r="O137" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="P137" t="s">
         <v>382</v>
@@ -10181,7 +10181,7 @@
         <v>383</v>
       </c>
       <c r="F138" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G138" t="s">
         <v>41</v>
@@ -10237,7 +10237,7 @@
         <v>242</v>
       </c>
       <c r="F139" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G139" t="s">
         <v>41</v>
@@ -10293,7 +10293,7 @@
         <v>386</v>
       </c>
       <c r="F140" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G140" t="s">
         <v>41</v>
@@ -10320,7 +10320,7 @@
         <v>47</v>
       </c>
       <c r="O140" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="P140" t="s">
         <v>387</v>
@@ -10349,7 +10349,7 @@
         <v>388</v>
       </c>
       <c r="F141" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G141" t="s">
         <v>41</v>
@@ -10402,10 +10402,10 @@
         <v>34</v>
       </c>
       <c r="E142" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="F142" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G142" t="s">
         <v>41</v>
@@ -10432,7 +10432,7 @@
         <v>47</v>
       </c>
       <c r="O142" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="P142" t="s">
         <v>390</v>
@@ -10458,10 +10458,10 @@
         <v>34</v>
       </c>
       <c r="E143" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F143" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G143" t="s">
         <v>41</v>
@@ -10517,7 +10517,7 @@
         <v>103</v>
       </c>
       <c r="F144" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G144" t="s">
         <v>41</v>
@@ -10573,7 +10573,7 @@
         <v>394</v>
       </c>
       <c r="F145" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G145" t="s">
         <v>41</v>
@@ -10600,7 +10600,7 @@
         <v>47</v>
       </c>
       <c r="O145" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="P145" t="s">
         <v>395</v>
@@ -10629,7 +10629,7 @@
         <v>110</v>
       </c>
       <c r="F146" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G146" t="s">
         <v>41</v>
@@ -10685,7 +10685,7 @@
         <v>394</v>
       </c>
       <c r="F147" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G147" t="s">
         <v>41</v>
@@ -10712,7 +10712,7 @@
         <v>47</v>
       </c>
       <c r="O147" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="P147" t="s">
         <v>397</v>
@@ -10741,7 +10741,7 @@
         <v>98</v>
       </c>
       <c r="F148" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G148" t="s">
         <v>41</v>
@@ -10797,7 +10797,7 @@
         <v>110</v>
       </c>
       <c r="F149" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G149" t="s">
         <v>41</v>
@@ -10853,7 +10853,7 @@
         <v>103</v>
       </c>
       <c r="F150" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G150" t="s">
         <v>41</v>
@@ -10909,7 +10909,7 @@
         <v>98</v>
       </c>
       <c r="F151" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G151" t="s">
         <v>41</v>
@@ -10965,7 +10965,7 @@
         <v>402</v>
       </c>
       <c r="F152" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G152" t="s">
         <v>41</v>
@@ -10992,7 +10992,7 @@
         <v>47</v>
       </c>
       <c r="O152" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="P152" t="s">
         <v>374</v>
@@ -11021,7 +11021,7 @@
         <v>403</v>
       </c>
       <c r="F153" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G153" t="s">
         <v>41</v>
@@ -11077,7 +11077,7 @@
         <v>404</v>
       </c>
       <c r="F154" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G154" t="s">
         <v>41</v>
@@ -11104,7 +11104,7 @@
         <v>47</v>
       </c>
       <c r="O154" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="P154" t="s">
         <v>405</v>
@@ -11133,7 +11133,7 @@
         <v>127</v>
       </c>
       <c r="F155" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G155" t="s">
         <v>41</v>
@@ -11189,7 +11189,7 @@
         <v>407</v>
       </c>
       <c r="F156" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G156" t="s">
         <v>41</v>
@@ -11245,7 +11245,7 @@
         <v>409</v>
       </c>
       <c r="F157" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G157" t="s">
         <v>41</v>
@@ -11301,7 +11301,7 @@
         <v>411</v>
       </c>
       <c r="F158" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G158" t="s">
         <v>41</v>
@@ -11328,7 +11328,7 @@
         <v>47</v>
       </c>
       <c r="O158" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="P158" t="s">
         <v>412</v>
@@ -11357,7 +11357,7 @@
         <v>413</v>
       </c>
       <c r="F159" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G159" t="s">
         <v>41</v>
@@ -11384,7 +11384,7 @@
         <v>47</v>
       </c>
       <c r="O159" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="P159" t="s">
         <v>414</v>
@@ -11413,7 +11413,7 @@
         <v>415</v>
       </c>
       <c r="F160" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G160" t="s">
         <v>41</v>
@@ -11690,10 +11690,10 @@
         <v>33</v>
       </c>
       <c r="E165" t="s">
-        <v>211</v>
+        <v>275</v>
       </c>
       <c r="F165" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G165" t="s">
         <v>41</v>
@@ -11746,10 +11746,10 @@
         <v>34</v>
       </c>
       <c r="E166" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F166" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G166" t="s">
         <v>41</v>
@@ -11802,10 +11802,10 @@
         <v>34</v>
       </c>
       <c r="E167" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F167" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G167" t="s">
         <v>41</v>
@@ -11832,7 +11832,7 @@
         <v>47</v>
       </c>
       <c r="O167" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="P167" t="s">
         <v>428</v>
@@ -11858,10 +11858,10 @@
         <v>34</v>
       </c>
       <c r="E168" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="F168" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G168" t="s">
         <v>41</v>
@@ -11888,7 +11888,7 @@
         <v>47</v>
       </c>
       <c r="O168" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="P168" t="s">
         <v>429</v>
@@ -11914,10 +11914,10 @@
         <v>34</v>
       </c>
       <c r="E169" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
       <c r="F169" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G169" t="s">
         <v>41</v>
@@ -11970,10 +11970,10 @@
         <v>34</v>
       </c>
       <c r="E170" t="s">
+        <v>217</v>
+      </c>
+      <c r="F170" t="s">
         <v>218</v>
-      </c>
-      <c r="F170" t="s">
-        <v>219</v>
       </c>
       <c r="G170" t="s">
         <v>41</v>
@@ -12026,10 +12026,10 @@
         <v>34</v>
       </c>
       <c r="E171" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F171" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G171" t="s">
         <v>41</v>
@@ -12082,10 +12082,10 @@
         <v>34</v>
       </c>
       <c r="E172" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F172" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G172" t="s">
         <v>41</v>
@@ -12100,7 +12100,7 @@
         <v>304</v>
       </c>
       <c r="K172" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L172" t="s">
         <v>34</v>
@@ -12141,7 +12141,7 @@
         <v>221</v>
       </c>
       <c r="F173" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G173" t="s">
         <v>41</v>
@@ -12194,10 +12194,10 @@
         <v>34</v>
       </c>
       <c r="E174" t="s">
-        <v>277</v>
+        <v>244</v>
       </c>
       <c r="F174" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G174" t="s">
         <v>41</v>
@@ -12224,7 +12224,7 @@
         <v>47</v>
       </c>
       <c r="O174" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="P174" t="s">
         <v>437</v>
@@ -12250,10 +12250,10 @@
         <v>34</v>
       </c>
       <c r="E175" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F175" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G175" t="s">
         <v>41</v>
@@ -12306,10 +12306,10 @@
         <v>34</v>
       </c>
       <c r="E176" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="F176" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G176" t="s">
         <v>41</v>
@@ -12362,10 +12362,10 @@
         <v>34</v>
       </c>
       <c r="E177" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F177" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G177" t="s">
         <v>41</v>
@@ -12418,10 +12418,10 @@
         <v>34</v>
       </c>
       <c r="E178" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="F178" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G178" t="s">
         <v>41</v>
@@ -12530,10 +12530,10 @@
         <v>33</v>
       </c>
       <c r="E180" t="s">
-        <v>277</v>
+        <v>244</v>
       </c>
       <c r="F180" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G180" t="s">
         <v>41</v>
@@ -12560,7 +12560,7 @@
         <v>47</v>
       </c>
       <c r="O180" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="P180" t="s">
         <v>446</v>
@@ -12586,10 +12586,10 @@
         <v>34</v>
       </c>
       <c r="E181" t="s">
+        <v>217</v>
+      </c>
+      <c r="F181" t="s">
         <v>218</v>
-      </c>
-      <c r="F181" t="s">
-        <v>219</v>
       </c>
       <c r="G181" t="s">
         <v>41</v>
@@ -12642,10 +12642,10 @@
         <v>34</v>
       </c>
       <c r="E182" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
       <c r="F182" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G182" t="s">
         <v>41</v>
@@ -12698,10 +12698,10 @@
         <v>34</v>
       </c>
       <c r="E183" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
       <c r="F183" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G183" t="s">
         <v>41</v>
@@ -12754,10 +12754,10 @@
         <v>34</v>
       </c>
       <c r="E184" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F184" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G184" t="s">
         <v>41</v>
@@ -12810,10 +12810,10 @@
         <v>34</v>
       </c>
       <c r="E185" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F185" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G185" t="s">
         <v>41</v>
@@ -12866,10 +12866,10 @@
         <v>34</v>
       </c>
       <c r="E186" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="F186" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G186" t="s">
         <v>41</v>
@@ -12922,10 +12922,10 @@
         <v>34</v>
       </c>
       <c r="E187" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="F187" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G187" t="s">
         <v>41</v>
@@ -12978,10 +12978,10 @@
         <v>34</v>
       </c>
       <c r="E188" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F188" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G188" t="s">
         <v>41</v>
@@ -13034,10 +13034,10 @@
         <v>34</v>
       </c>
       <c r="E189" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F189" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G189" t="s">
         <v>41</v>
@@ -13090,10 +13090,10 @@
         <v>34</v>
       </c>
       <c r="E190" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F190" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G190" t="s">
         <v>41</v>
@@ -13108,7 +13108,7 @@
         <v>304</v>
       </c>
       <c r="K190" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L190" t="s">
         <v>34</v>
@@ -13146,10 +13146,10 @@
         <v>34</v>
       </c>
       <c r="E191" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F191" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G191" t="s">
         <v>41</v>
@@ -13164,7 +13164,7 @@
         <v>304</v>
       </c>
       <c r="K191" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L191" t="s">
         <v>34</v>
@@ -13205,7 +13205,7 @@
         <v>456</v>
       </c>
       <c r="F192" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G192" t="s">
         <v>41</v>
@@ -13261,7 +13261,7 @@
         <v>456</v>
       </c>
       <c r="F193" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G193" t="s">
         <v>41</v>
@@ -13317,7 +13317,7 @@
         <v>157</v>
       </c>
       <c r="F194" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G194" t="s">
         <v>41</v>
@@ -13373,7 +13373,7 @@
         <v>157</v>
       </c>
       <c r="F195" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G195" t="s">
         <v>41</v>
@@ -13426,10 +13426,10 @@
         <v>34</v>
       </c>
       <c r="E196" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F196" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G196" t="s">
         <v>41</v>
@@ -13482,10 +13482,10 @@
         <v>34</v>
       </c>
       <c r="E197" t="s">
+        <v>217</v>
+      </c>
+      <c r="F197" t="s">
         <v>218</v>
-      </c>
-      <c r="F197" t="s">
-        <v>219</v>
       </c>
       <c r="G197" t="s">
         <v>41</v>
@@ -13538,10 +13538,10 @@
         <v>34</v>
       </c>
       <c r="E198" t="s">
+        <v>217</v>
+      </c>
+      <c r="F198" t="s">
         <v>218</v>
-      </c>
-      <c r="F198" t="s">
-        <v>219</v>
       </c>
       <c r="G198" t="s">
         <v>41</v>
@@ -13594,10 +13594,10 @@
         <v>34</v>
       </c>
       <c r="E199" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="F199" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G199" t="s">
         <v>41</v>
@@ -13650,10 +13650,10 @@
         <v>34</v>
       </c>
       <c r="E200" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="F200" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G200" t="s">
         <v>41</v>
@@ -13706,10 +13706,10 @@
         <v>34</v>
       </c>
       <c r="E201" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F201" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G201" t="s">
         <v>41</v>
@@ -13762,10 +13762,10 @@
         <v>34</v>
       </c>
       <c r="E202" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F202" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G202" t="s">
         <v>41</v>
@@ -13818,10 +13818,10 @@
         <v>34</v>
       </c>
       <c r="E203" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F203" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G203" t="s">
         <v>41</v>
@@ -13877,7 +13877,7 @@
         <v>472</v>
       </c>
       <c r="F204" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G204" t="s">
         <v>41</v>
@@ -13933,7 +13933,7 @@
         <v>472</v>
       </c>
       <c r="F205" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G205" t="s">
         <v>41</v>
@@ -13986,10 +13986,10 @@
         <v>34</v>
       </c>
       <c r="E206" t="s">
-        <v>211</v>
+        <v>275</v>
       </c>
       <c r="F206" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G206" t="s">
         <v>41</v>
@@ -14042,10 +14042,10 @@
         <v>34</v>
       </c>
       <c r="E207" t="s">
-        <v>211</v>
+        <v>275</v>
       </c>
       <c r="F207" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G207" t="s">
         <v>41</v>
@@ -14098,10 +14098,10 @@
         <v>34</v>
       </c>
       <c r="E208" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F208" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G208" t="s">
         <v>41</v>
@@ -14154,10 +14154,10 @@
         <v>34</v>
       </c>
       <c r="E209" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F209" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G209" t="s">
         <v>41</v>
@@ -14210,10 +14210,10 @@
         <v>34</v>
       </c>
       <c r="E210" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="F210" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G210" t="s">
         <v>41</v>
@@ -14266,10 +14266,10 @@
         <v>34</v>
       </c>
       <c r="E211" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F211" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G211" t="s">
         <v>41</v>
@@ -14296,7 +14296,7 @@
         <v>47</v>
       </c>
       <c r="O211" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="P211" t="s">
         <v>428</v>
@@ -14322,10 +14322,10 @@
         <v>34</v>
       </c>
       <c r="E212" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F212" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G212" t="s">
         <v>41</v>
@@ -14352,7 +14352,7 @@
         <v>47</v>
       </c>
       <c r="O212" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="P212" t="s">
         <v>480</v>
@@ -14378,10 +14378,10 @@
         <v>34</v>
       </c>
       <c r="E213" t="s">
-        <v>277</v>
+        <v>244</v>
       </c>
       <c r="F213" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G213" t="s">
         <v>41</v>
@@ -14408,7 +14408,7 @@
         <v>47</v>
       </c>
       <c r="O213" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="P213" t="s">
         <v>437</v>
@@ -14434,10 +14434,10 @@
         <v>34</v>
       </c>
       <c r="E214" t="s">
-        <v>277</v>
+        <v>244</v>
       </c>
       <c r="F214" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G214" t="s">
         <v>41</v>
@@ -14464,7 +14464,7 @@
         <v>47</v>
       </c>
       <c r="O214" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="P214" t="s">
         <v>481</v>
@@ -14493,7 +14493,7 @@
         <v>221</v>
       </c>
       <c r="F215" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G215" t="s">
         <v>41</v>
@@ -14549,7 +14549,7 @@
         <v>221</v>
       </c>
       <c r="F216" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G216" t="s">
         <v>41</v>
@@ -14602,10 +14602,10 @@
         <v>34</v>
       </c>
       <c r="E217" t="s">
-        <v>211</v>
+        <v>275</v>
       </c>
       <c r="F217" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G217" t="s">
         <v>41</v>
@@ -14658,10 +14658,10 @@
         <v>34</v>
       </c>
       <c r="E218" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
       <c r="F218" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G218" t="s">
         <v>41</v>
@@ -14717,7 +14717,7 @@
         <v>221</v>
       </c>
       <c r="F219" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G219" t="s">
         <v>41</v>
@@ -14770,10 +14770,10 @@
         <v>34</v>
       </c>
       <c r="E220" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F220" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G220" t="s">
         <v>41</v>
@@ -14800,7 +14800,7 @@
         <v>47</v>
       </c>
       <c r="O220" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="P220" t="s">
         <v>486</v>
@@ -14826,10 +14826,10 @@
         <v>34</v>
       </c>
       <c r="E221" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="F221" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G221" t="s">
         <v>41</v>
@@ -14856,7 +14856,7 @@
         <v>47</v>
       </c>
       <c r="O221" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="P221" t="s">
         <v>429</v>
@@ -14882,10 +14882,10 @@
         <v>34</v>
       </c>
       <c r="E222" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="F222" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G222" t="s">
         <v>41</v>
@@ -14912,7 +14912,7 @@
         <v>47</v>
       </c>
       <c r="O222" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="P222" t="s">
         <v>487</v>
@@ -14938,10 +14938,10 @@
         <v>34</v>
       </c>
       <c r="E223" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F223" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G223" t="s">
         <v>41</v>
@@ -14968,7 +14968,7 @@
         <v>47</v>
       </c>
       <c r="O223" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="P223" t="s">
         <v>488</v>
@@ -14994,10 +14994,10 @@
         <v>34</v>
       </c>
       <c r="E224" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="F224" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G224" t="s">
         <v>41</v>
@@ -15024,7 +15024,7 @@
         <v>47</v>
       </c>
       <c r="O224" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="P224" t="s">
         <v>489</v>
@@ -15050,10 +15050,10 @@
         <v>34</v>
       </c>
       <c r="E225" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F225" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G225" t="s">
         <v>41</v>
@@ -15068,7 +15068,7 @@
         <v>304</v>
       </c>
       <c r="K225" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L225" t="s">
         <v>34</v>
@@ -15106,10 +15106,10 @@
         <v>34</v>
       </c>
       <c r="E226" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F226" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G226" t="s">
         <v>41</v>
@@ -15162,10 +15162,10 @@
         <v>34</v>
       </c>
       <c r="E227" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F227" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G227" t="s">
         <v>41</v>
@@ -15218,10 +15218,10 @@
         <v>34</v>
       </c>
       <c r="E228" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="F228" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G228" t="s">
         <v>41</v>
@@ -15277,7 +15277,7 @@
         <v>494</v>
       </c>
       <c r="F229" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G229" t="s">
         <v>41</v>
@@ -15442,10 +15442,10 @@
         <v>33</v>
       </c>
       <c r="E232" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F232" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G232" t="s">
         <v>41</v>
@@ -15498,10 +15498,10 @@
         <v>34</v>
       </c>
       <c r="E233" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F233" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G233" t="s">
         <v>41</v>
@@ -15554,10 +15554,10 @@
         <v>33</v>
       </c>
       <c r="E234" t="s">
-        <v>277</v>
+        <v>244</v>
       </c>
       <c r="F234" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G234" t="s">
         <v>41</v>
@@ -15584,7 +15584,7 @@
         <v>47</v>
       </c>
       <c r="O234" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="P234" t="s">
         <v>509</v>
@@ -15610,10 +15610,10 @@
         <v>34</v>
       </c>
       <c r="E235" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
       <c r="F235" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G235" t="s">
         <v>41</v>
@@ -15666,10 +15666,10 @@
         <v>34</v>
       </c>
       <c r="E236" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="F236" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G236" t="s">
         <v>41</v>
@@ -15722,10 +15722,10 @@
         <v>34</v>
       </c>
       <c r="E237" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F237" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G237" t="s">
         <v>41</v>
@@ -15778,10 +15778,10 @@
         <v>34</v>
       </c>
       <c r="E238" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F238" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G238" t="s">
         <v>41</v>
@@ -15808,7 +15808,7 @@
         <v>47</v>
       </c>
       <c r="O238" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="P238" t="s">
         <v>428</v>
@@ -15834,10 +15834,10 @@
         <v>34</v>
       </c>
       <c r="E239" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="F239" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G239" t="s">
         <v>41</v>
@@ -15864,7 +15864,7 @@
         <v>47</v>
       </c>
       <c r="O239" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="P239" t="s">
         <v>429</v>
@@ -15890,10 +15890,10 @@
         <v>34</v>
       </c>
       <c r="E240" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F240" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G240" t="s">
         <v>41</v>
@@ -15946,10 +15946,10 @@
         <v>34</v>
       </c>
       <c r="E241" t="s">
-        <v>211</v>
+        <v>275</v>
       </c>
       <c r="F241" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G241" t="s">
         <v>41</v>
@@ -16005,7 +16005,7 @@
         <v>472</v>
       </c>
       <c r="F242" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G242" t="s">
         <v>41</v>
@@ -16067,7 +16067,7 @@
         <v>41</v>
       </c>
       <c r="H243" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I243" t="s">
         <v>464</v>
@@ -16123,7 +16123,7 @@
         <v>41</v>
       </c>
       <c r="H244" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I244" t="s">
         <v>517</v>
@@ -16170,10 +16170,10 @@
         <v>34</v>
       </c>
       <c r="E245" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F245" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G245" t="s">
         <v>41</v>
@@ -16235,7 +16235,7 @@
         <v>41</v>
       </c>
       <c r="H246" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I246" t="s">
         <v>519</v>
@@ -16244,7 +16244,7 @@
         <v>90</v>
       </c>
       <c r="K246" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L246" t="s">
         <v>34</v>
@@ -16291,7 +16291,7 @@
         <v>41</v>
       </c>
       <c r="H247" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I247" t="s">
         <v>520</v>
@@ -16347,7 +16347,7 @@
         <v>41</v>
       </c>
       <c r="H248" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I248" t="s">
         <v>521</v>
@@ -16459,7 +16459,7 @@
         <v>41</v>
       </c>
       <c r="H250" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I250" t="s">
         <v>521</v>
@@ -16506,16 +16506,16 @@
         <v>33</v>
       </c>
       <c r="E251" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F251" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G251" t="s">
         <v>41</v>
       </c>
       <c r="H251" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I251" t="s">
         <v>524</v>
@@ -16562,7 +16562,7 @@
         <v>33</v>
       </c>
       <c r="E252" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F252" t="s">
         <v>499</v>
@@ -16571,7 +16571,7 @@
         <v>41</v>
       </c>
       <c r="H252" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I252" t="s">
         <v>527</v>
@@ -16627,7 +16627,7 @@
         <v>41</v>
       </c>
       <c r="H253" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I253" t="s">
         <v>527</v>
@@ -16683,7 +16683,7 @@
         <v>41</v>
       </c>
       <c r="H254" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I254" t="s">
         <v>528</v>
@@ -16730,7 +16730,7 @@
         <v>34</v>
       </c>
       <c r="E255" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F255" t="s">
         <v>499</v>
@@ -16739,7 +16739,7 @@
         <v>41</v>
       </c>
       <c r="H255" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I255" t="s">
         <v>529</v>
@@ -16786,7 +16786,7 @@
         <v>34</v>
       </c>
       <c r="E256" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F256" t="s">
         <v>499</v>
@@ -16795,7 +16795,7 @@
         <v>41</v>
       </c>
       <c r="H256" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I256" t="s">
         <v>530</v>
@@ -16804,7 +16804,7 @@
         <v>90</v>
       </c>
       <c r="K256" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L256" t="s">
         <v>34</v>
@@ -16842,7 +16842,7 @@
         <v>34</v>
       </c>
       <c r="E257" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F257" t="s">
         <v>499</v>
@@ -16851,7 +16851,7 @@
         <v>41</v>
       </c>
       <c r="H257" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I257" t="s">
         <v>531</v>
@@ -16901,7 +16901,7 @@
         <v>127</v>
       </c>
       <c r="F258" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G258" t="s">
         <v>41</v>
@@ -16957,7 +16957,7 @@
         <v>534</v>
       </c>
       <c r="F259" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G259" t="s">
         <v>41</v>
@@ -16984,7 +16984,7 @@
         <v>47</v>
       </c>
       <c r="O259" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="P259" t="s">
         <v>536</v>
@@ -17013,7 +17013,7 @@
         <v>538</v>
       </c>
       <c r="F260" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G260" t="s">
         <v>41</v>
@@ -17040,7 +17040,7 @@
         <v>47</v>
       </c>
       <c r="O260" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="P260" t="s">
         <v>540</v>
@@ -17069,7 +17069,7 @@
         <v>404</v>
       </c>
       <c r="F261" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G261" t="s">
         <v>41</v>
@@ -17096,7 +17096,7 @@
         <v>47</v>
       </c>
       <c r="O261" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="P261" t="s">
         <v>541</v>
@@ -17131,7 +17131,7 @@
         <v>41</v>
       </c>
       <c r="H262" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I262" t="s">
         <v>543</v>
@@ -17181,7 +17181,7 @@
         <v>103</v>
       </c>
       <c r="F263" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G263" t="s">
         <v>41</v>
@@ -17234,10 +17234,10 @@
         <v>34</v>
       </c>
       <c r="E264" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="F264" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G264" t="s">
         <v>41</v>
@@ -17290,16 +17290,16 @@
         <v>34</v>
       </c>
       <c r="E265" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
       <c r="F265" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G265" t="s">
         <v>41</v>
       </c>
       <c r="H265" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I265" t="s">
         <v>548</v>
@@ -17346,10 +17346,10 @@
         <v>34</v>
       </c>
       <c r="E266" t="s">
-        <v>277</v>
+        <v>244</v>
       </c>
       <c r="F266" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G266" t="s">
         <v>41</v>
@@ -17376,7 +17376,7 @@
         <v>47</v>
       </c>
       <c r="O266" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="P266" t="s">
         <v>550</v>
@@ -17405,7 +17405,7 @@
         <v>553</v>
       </c>
       <c r="F267" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G267" t="s">
         <v>41</v>
@@ -17461,7 +17461,7 @@
         <v>555</v>
       </c>
       <c r="F268" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G268" t="s">
         <v>41</v>
@@ -17517,7 +17517,7 @@
         <v>558</v>
       </c>
       <c r="F269" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G269" t="s">
         <v>41</v>
@@ -17573,7 +17573,7 @@
         <v>553</v>
       </c>
       <c r="F270" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G270" t="s">
         <v>41</v>
@@ -17738,10 +17738,10 @@
         <v>33</v>
       </c>
       <c r="E273" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F273" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G273" t="s">
         <v>41</v>
@@ -17756,7 +17756,7 @@
         <v>96</v>
       </c>
       <c r="K273" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L273" t="s">
         <v>566</v>
@@ -17909,7 +17909,7 @@
         <v>572</v>
       </c>
       <c r="F276" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G276" t="s">
         <v>41</v>
@@ -17965,7 +17965,7 @@
         <v>576</v>
       </c>
       <c r="F277" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G277" t="s">
         <v>41</v>
@@ -17992,7 +17992,7 @@
         <v>47</v>
       </c>
       <c r="O277" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="P277" t="s">
         <v>577</v>
@@ -18021,7 +18021,7 @@
         <v>579</v>
       </c>
       <c r="F278" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G278" t="s">
         <v>41</v>
@@ -18077,7 +18077,7 @@
         <v>582</v>
       </c>
       <c r="F279" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G279" t="s">
         <v>41</v>
@@ -18133,7 +18133,7 @@
         <v>585</v>
       </c>
       <c r="F280" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G280" t="s">
         <v>41</v>
@@ -18189,7 +18189,7 @@
         <v>588</v>
       </c>
       <c r="F281" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G281" t="s">
         <v>41</v>
@@ -18245,7 +18245,7 @@
         <v>591</v>
       </c>
       <c r="F282" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G282" t="s">
         <v>41</v>
@@ -18301,7 +18301,7 @@
         <v>594</v>
       </c>
       <c r="F283" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G283" t="s">
         <v>41</v>
@@ -18357,7 +18357,7 @@
         <v>597</v>
       </c>
       <c r="F284" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G284" t="s">
         <v>41</v>
@@ -18413,7 +18413,7 @@
         <v>600</v>
       </c>
       <c r="F285" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G285" t="s">
         <v>41</v>
@@ -18469,7 +18469,7 @@
         <v>603</v>
       </c>
       <c r="F286" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G286" t="s">
         <v>41</v>
@@ -18525,7 +18525,7 @@
         <v>606</v>
       </c>
       <c r="F287" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G287" t="s">
         <v>41</v>
@@ -18581,7 +18581,7 @@
         <v>608</v>
       </c>
       <c r="F288" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G288" t="s">
         <v>41</v>
@@ -18637,7 +18637,7 @@
         <v>611</v>
       </c>
       <c r="F289" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G289" t="s">
         <v>41</v>
@@ -18693,7 +18693,7 @@
         <v>614</v>
       </c>
       <c r="F290" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G290" t="s">
         <v>41</v>
@@ -18749,7 +18749,7 @@
         <v>616</v>
       </c>
       <c r="F291" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G291" t="s">
         <v>41</v>
@@ -18805,7 +18805,7 @@
         <v>618</v>
       </c>
       <c r="F292" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G292" t="s">
         <v>41</v>
@@ -18861,7 +18861,7 @@
         <v>620</v>
       </c>
       <c r="F293" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G293" t="s">
         <v>41</v>
@@ -18917,7 +18917,7 @@
         <v>623</v>
       </c>
       <c r="F294" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G294" t="s">
         <v>41</v>
@@ -18973,7 +18973,7 @@
         <v>626</v>
       </c>
       <c r="F295" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G295" t="s">
         <v>41</v>
@@ -19029,7 +19029,7 @@
         <v>629</v>
       </c>
       <c r="F296" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G296" t="s">
         <v>41</v>
@@ -19085,7 +19085,7 @@
         <v>631</v>
       </c>
       <c r="F297" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G297" t="s">
         <v>41</v>
@@ -19141,7 +19141,7 @@
         <v>634</v>
       </c>
       <c r="F298" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G298" t="s">
         <v>41</v>
@@ -19197,7 +19197,7 @@
         <v>636</v>
       </c>
       <c r="F299" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G299" t="s">
         <v>41</v>
@@ -19253,7 +19253,7 @@
         <v>82</v>
       </c>
       <c r="F300" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G300" t="s">
         <v>41</v>
@@ -19309,7 +19309,7 @@
         <v>110</v>
       </c>
       <c r="F301" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G301" t="s">
         <v>41</v>
@@ -19365,7 +19365,7 @@
         <v>103</v>
       </c>
       <c r="F302" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G302" t="s">
         <v>41</v>
@@ -19421,7 +19421,7 @@
         <v>394</v>
       </c>
       <c r="F303" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G303" t="s">
         <v>41</v>
@@ -19448,7 +19448,7 @@
         <v>47</v>
       </c>
       <c r="O303" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="P303" t="s">
         <v>644</v>
@@ -19477,7 +19477,7 @@
         <v>66</v>
       </c>
       <c r="F304" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G304" t="s">
         <v>41</v>
@@ -19533,7 +19533,7 @@
         <v>98</v>
       </c>
       <c r="F305" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G305" t="s">
         <v>41</v>
@@ -19589,7 +19589,7 @@
         <v>648</v>
       </c>
       <c r="F306" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G306" t="s">
         <v>41</v>
@@ -19645,7 +19645,7 @@
         <v>650</v>
       </c>
       <c r="F307" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G307" t="s">
         <v>41</v>
@@ -19701,7 +19701,7 @@
         <v>652</v>
       </c>
       <c r="F308" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G308" t="s">
         <v>41</v>
@@ -19757,7 +19757,7 @@
         <v>654</v>
       </c>
       <c r="F309" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G309" t="s">
         <v>41</v>
@@ -19813,7 +19813,7 @@
         <v>656</v>
       </c>
       <c r="F310" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G310" t="s">
         <v>41</v>
@@ -19869,7 +19869,7 @@
         <v>534</v>
       </c>
       <c r="F311" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G311" t="s">
         <v>41</v>
@@ -19896,7 +19896,7 @@
         <v>47</v>
       </c>
       <c r="O311" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="P311" t="s">
         <v>658</v>
@@ -19925,7 +19925,7 @@
         <v>659</v>
       </c>
       <c r="F312" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G312" t="s">
         <v>41</v>
@@ -20090,7 +20090,7 @@
         <v>33</v>
       </c>
       <c r="E315" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F315" t="s">
         <v>40</v>
@@ -20146,7 +20146,7 @@
         <v>34</v>
       </c>
       <c r="E316" t="s">
-        <v>277</v>
+        <v>244</v>
       </c>
       <c r="F316" t="s">
         <v>40</v>
@@ -20176,7 +20176,7 @@
         <v>47</v>
       </c>
       <c r="O316" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="P316" t="s">
         <v>667</v>
@@ -20202,7 +20202,7 @@
         <v>34</v>
       </c>
       <c r="E317" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F317" t="s">
         <v>40</v>
@@ -20232,7 +20232,7 @@
         <v>47</v>
       </c>
       <c r="O317" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="P317" t="s">
         <v>667</v>
@@ -20258,7 +20258,7 @@
         <v>34</v>
       </c>
       <c r="E318" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F318" t="s">
         <v>40</v>
@@ -20314,7 +20314,7 @@
         <v>34</v>
       </c>
       <c r="E319" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="F319" t="s">
         <v>40</v>
@@ -20344,7 +20344,7 @@
         <v>47</v>
       </c>
       <c r="O319" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="P319" t="s">
         <v>667</v>
@@ -20370,7 +20370,7 @@
         <v>34</v>
       </c>
       <c r="E320" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F320" t="s">
         <v>668</v>
@@ -20388,7 +20388,7 @@
         <v>90</v>
       </c>
       <c r="K320" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L320" t="s">
         <v>34</v>
@@ -20426,7 +20426,7 @@
         <v>34</v>
       </c>
       <c r="E321" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="F321" t="s">
         <v>668</v>
@@ -20482,7 +20482,7 @@
         <v>34</v>
       </c>
       <c r="E322" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F322" t="s">
         <v>668</v>
@@ -20594,7 +20594,7 @@
         <v>34</v>
       </c>
       <c r="E324" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="F324" t="s">
         <v>40</v>
@@ -20650,7 +20650,7 @@
         <v>34</v>
       </c>
       <c r="E325" t="s">
-        <v>211</v>
+        <v>275</v>
       </c>
       <c r="F325" t="s">
         <v>40</v>
@@ -20762,7 +20762,7 @@
         <v>34</v>
       </c>
       <c r="E327" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F327" t="s">
         <v>668</v>
@@ -20818,7 +20818,7 @@
         <v>34</v>
       </c>
       <c r="E328" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F328" t="s">
         <v>40</v>
@@ -21060,7 +21060,7 @@
         <v>681</v>
       </c>
       <c r="K332" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L332" t="s">
         <v>682</v>
@@ -21101,7 +21101,7 @@
         <v>683</v>
       </c>
       <c r="F333" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G333" t="s">
         <v>41</v>
@@ -21116,7 +21116,7 @@
         <v>686</v>
       </c>
       <c r="K333" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L333" t="s">
         <v>34</v>
@@ -21549,7 +21549,7 @@
         <v>703</v>
       </c>
       <c r="F341" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G341" t="s">
         <v>41</v>
@@ -21605,13 +21605,13 @@
         <v>704</v>
       </c>
       <c r="F342" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G342" t="s">
         <v>41</v>
       </c>
       <c r="H342" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I342" t="s">
         <v>705</v>
@@ -22165,7 +22165,7 @@
         <v>727</v>
       </c>
       <c r="F352" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G352" t="s">
         <v>41</v>
@@ -22675,7 +22675,7 @@
         <v>41</v>
       </c>
       <c r="H361" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I361" t="s">
         <v>748</v>
@@ -22837,7 +22837,7 @@
         <v>753</v>
       </c>
       <c r="F364" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G364" t="s">
         <v>41</v>
@@ -22893,7 +22893,7 @@
         <v>753</v>
       </c>
       <c r="F365" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G365" t="s">
         <v>41</v>
@@ -23076,7 +23076,7 @@
         <v>681</v>
       </c>
       <c r="K368" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L368" t="s">
         <v>765</v>
@@ -23117,7 +23117,7 @@
         <v>768</v>
       </c>
       <c r="F369" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G369" t="s">
         <v>41</v>
@@ -23621,7 +23621,7 @@
         <v>800</v>
       </c>
       <c r="F378" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G378" t="s">
         <v>41</v>
@@ -23677,7 +23677,7 @@
         <v>802</v>
       </c>
       <c r="F379" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G379" t="s">
         <v>41</v>
@@ -23733,7 +23733,7 @@
         <v>806</v>
       </c>
       <c r="F380" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G380" t="s">
         <v>41</v>
@@ -23789,7 +23789,7 @@
         <v>810</v>
       </c>
       <c r="F381" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G381" t="s">
         <v>41</v>
@@ -23845,7 +23845,7 @@
         <v>814</v>
       </c>
       <c r="F382" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G382" t="s">
         <v>41</v>
@@ -23901,7 +23901,7 @@
         <v>818</v>
       </c>
       <c r="F383" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G383" t="s">
         <v>41</v>
@@ -23957,7 +23957,7 @@
         <v>821</v>
       </c>
       <c r="F384" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G384" t="s">
         <v>41</v>
@@ -24013,7 +24013,7 @@
         <v>825</v>
       </c>
       <c r="F385" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G385" t="s">
         <v>41</v>
@@ -24349,7 +24349,7 @@
         <v>850</v>
       </c>
       <c r="F391" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G391" t="s">
         <v>41</v>
@@ -24685,7 +24685,7 @@
         <v>868</v>
       </c>
       <c r="F397" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G397" t="s">
         <v>41</v>
@@ -24853,7 +24853,7 @@
         <v>879</v>
       </c>
       <c r="F400" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G400" t="s">
         <v>41</v>
@@ -24909,7 +24909,7 @@
         <v>883</v>
       </c>
       <c r="F401" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G401" t="s">
         <v>41</v>
@@ -25581,7 +25581,7 @@
         <v>920</v>
       </c>
       <c r="F413" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G413" t="s">
         <v>41</v>
@@ -25802,10 +25802,10 @@
         <v>33</v>
       </c>
       <c r="E417" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F417" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G417" t="s">
         <v>41</v>
@@ -25858,10 +25858,10 @@
         <v>34</v>
       </c>
       <c r="E418" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="F418" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G418" t="s">
         <v>41</v>
@@ -25888,7 +25888,7 @@
         <v>47</v>
       </c>
       <c r="O418" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="P418" t="s">
         <v>932</v>
@@ -25914,10 +25914,10 @@
         <v>34</v>
       </c>
       <c r="E419" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="F419" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G419" t="s">
         <v>41</v>
@@ -25970,10 +25970,10 @@
         <v>34</v>
       </c>
       <c r="E420" t="s">
-        <v>211</v>
+        <v>275</v>
       </c>
       <c r="F420" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G420" t="s">
         <v>41</v>
@@ -26026,10 +26026,10 @@
         <v>34</v>
       </c>
       <c r="E421" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F421" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G421" t="s">
         <v>41</v>
@@ -26082,10 +26082,10 @@
         <v>34</v>
       </c>
       <c r="E422" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F422" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G422" t="s">
         <v>41</v>
@@ -26112,7 +26112,7 @@
         <v>47</v>
       </c>
       <c r="O422" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="P422" t="s">
         <v>936</v>
@@ -26138,10 +26138,10 @@
         <v>34</v>
       </c>
       <c r="E423" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F423" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G423" t="s">
         <v>41</v>
@@ -26156,7 +26156,7 @@
         <v>90</v>
       </c>
       <c r="K423" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L423" t="s">
         <v>930</v>
@@ -26194,10 +26194,10 @@
         <v>34</v>
       </c>
       <c r="E424" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F424" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G424" t="s">
         <v>41</v>
@@ -26250,10 +26250,10 @@
         <v>34</v>
       </c>
       <c r="E425" t="s">
-        <v>277</v>
+        <v>244</v>
       </c>
       <c r="F425" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G425" t="s">
         <v>41</v>
@@ -26280,7 +26280,7 @@
         <v>47</v>
       </c>
       <c r="O425" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="P425" t="s">
         <v>939</v>
@@ -26306,10 +26306,10 @@
         <v>34</v>
       </c>
       <c r="E426" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F426" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G426" t="s">
         <v>41</v>
@@ -26365,7 +26365,7 @@
         <v>221</v>
       </c>
       <c r="F427" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G427" t="s">
         <v>41</v>
@@ -26418,10 +26418,10 @@
         <v>34</v>
       </c>
       <c r="E428" t="s">
+        <v>217</v>
+      </c>
+      <c r="F428" t="s">
         <v>218</v>
-      </c>
-      <c r="F428" t="s">
-        <v>219</v>
       </c>
       <c r="G428" t="s">
         <v>41</v>
@@ -30901,7 +30901,7 @@
         <v>1043</v>
       </c>
       <c r="F508" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G508" t="s">
         <v>41</v>

--- a/xlsx/dre/DRE_02_2026.xlsx
+++ b/xlsx/dre/DRE_02_2026.xlsx
@@ -1550,6 +1550,12 @@
     <t>R$ 10.123,95</t>
   </si>
   <si>
+    <t>R$  1.108,54</t>
+  </si>
+  <si>
+    <t>R$  1.196,02</t>
+  </si>
+  <si>
     <t>RAYSSA BARBOSA SILVA</t>
   </si>
   <si>
@@ -1562,31 +1568,25 @@
     <t>FERNANDA DOCHVAT SILVA</t>
   </si>
   <si>
+    <t>01/06/26</t>
+  </si>
+  <si>
     <t>01/04/26</t>
   </si>
   <si>
-    <t>R$  1.196,02</t>
-  </si>
-  <si>
-    <t>01/06/26</t>
-  </si>
-  <si>
-    <t>R$  1.108,54</t>
+    <t>R$  438,09</t>
+  </si>
+  <si>
+    <t>R$  3,60</t>
   </si>
   <si>
     <t>63801/2</t>
   </si>
   <si>
-    <t>R$  438,09</t>
+    <t>R$  537,59</t>
   </si>
   <si>
     <t>R$  292,95</t>
-  </si>
-  <si>
-    <t>R$  537,59</t>
-  </si>
-  <si>
-    <t>R$  3,60</t>
   </si>
   <si>
     <t>R$  1.941,34</t>
@@ -2028,15 +2028,15 @@
     <t>4.03.03.02.05.02 Assistência técnica medição</t>
   </si>
   <si>
+    <t>PFP</t>
+  </si>
+  <si>
     <t>L E A Medicoes Tecnicas LTDA</t>
   </si>
   <si>
     <t>R$  180,00</t>
   </si>
   <si>
-    <t>PFP</t>
-  </si>
-  <si>
     <t>4.03.03.09 Marketing - mídias / ações comerciais / outros (CV)</t>
   </si>
   <si>
@@ -2058,6 +2058,18 @@
     <t>Google 2026</t>
   </si>
   <si>
+    <t>498/1</t>
+  </si>
+  <si>
+    <t>Facebook</t>
+  </si>
+  <si>
+    <t>R$  3.750,00</t>
+  </si>
+  <si>
+    <t>30/01/26</t>
+  </si>
+  <si>
     <t>WEBGIGA SOLUCOES DIGITAIS LTDA</t>
   </si>
   <si>
@@ -2079,18 +2091,6 @@
     <t>MHM - Honorários 2026</t>
   </si>
   <si>
-    <t>498/1</t>
-  </si>
-  <si>
-    <t>Facebook</t>
-  </si>
-  <si>
-    <t>R$  3.750,00</t>
-  </si>
-  <si>
-    <t>30/01/26</t>
-  </si>
-  <si>
     <t>4.04 DESPESAS ADMINISTRATIVAS</t>
   </si>
   <si>
@@ -2136,40 +2136,70 @@
     <t>4.04.01.02.01.01 Salário fixo</t>
   </si>
   <si>
+    <t>Bianca Rodrigues - Salário fixo 2026</t>
+  </si>
+  <si>
+    <t>587/1</t>
+  </si>
+  <si>
+    <t>R$  2.075,32</t>
+  </si>
+  <si>
+    <t>Rateio salários Mayara, Rayssa e Efraim</t>
+  </si>
+  <si>
+    <t>Fernanda Dochvat - Fixo 2026</t>
+  </si>
+  <si>
+    <t>Danielle Martins da Silva</t>
+  </si>
+  <si>
+    <t>R$  2.090,00</t>
+  </si>
+  <si>
+    <t>Danielle - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>GUTEMBERG DIAS GOMES</t>
+  </si>
+  <si>
+    <t>R$  6.000,00</t>
+  </si>
+  <si>
+    <t>Gutemberg Dias - Pagamento</t>
+  </si>
+  <si>
+    <t>Leandro Henrique Simoes Campos</t>
+  </si>
+  <si>
+    <t>R$  2.000,00</t>
+  </si>
+  <si>
+    <t>Leandro Henrique Simoes Campos Fixo 2026</t>
+  </si>
+  <si>
+    <t>Carina - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>Denny Lucas do Carmo Pereira</t>
+  </si>
+  <si>
+    <t>R$  2.645,58</t>
+  </si>
+  <si>
+    <t>Denny Lucas - Pagamento 2026</t>
+  </si>
+  <si>
     <t>Rubens - Pagamento 2026</t>
   </si>
   <si>
     <t>579/1</t>
   </si>
   <si>
-    <t>587/1</t>
-  </si>
-  <si>
-    <t>R$  2.075,32</t>
-  </si>
-  <si>
-    <t>Rateio salários Mayara, Rayssa e Efraim</t>
-  </si>
-  <si>
-    <t>Fernanda Dochvat - Fixo 2026</t>
-  </si>
-  <si>
-    <t>GUTEMBERG DIAS GOMES</t>
-  </si>
-  <si>
-    <t>R$  6.000,00</t>
-  </si>
-  <si>
-    <t>Gutemberg Dias - Pagamento</t>
-  </si>
-  <si>
-    <t>Denny Lucas do Carmo Pereira</t>
-  </si>
-  <si>
-    <t>R$  2.645,58</t>
-  </si>
-  <si>
-    <t>Denny Lucas - Pagamento 2026</t>
+    <t>Eric Kevin de Souza Serpa</t>
+  </si>
+  <si>
+    <t>Salário Fixo -Eric Serpa 2026</t>
   </si>
   <si>
     <t>Teresinha Elvira Maximino de Menezes</t>
@@ -2178,6 +2208,12 @@
     <t>Tucha - Fixo 2026</t>
   </si>
   <si>
+    <t>578/1</t>
+  </si>
+  <si>
+    <t>R$  2.219,85</t>
+  </si>
+  <si>
     <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
   </si>
   <si>
@@ -2187,42 +2223,6 @@
     <t>Sabrina Braunbeck - Pagamento 2026</t>
   </si>
   <si>
-    <t>Leandro Henrique Simoes Campos</t>
-  </si>
-  <si>
-    <t>R$  2.000,00</t>
-  </si>
-  <si>
-    <t>Leandro Henrique Simoes Campos Fixo 2026</t>
-  </si>
-  <si>
-    <t>R$  2.090,00</t>
-  </si>
-  <si>
-    <t>Carina - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>Eric Kevin de Souza Serpa</t>
-  </si>
-  <si>
-    <t>Salário Fixo -Eric Serpa 2026</t>
-  </si>
-  <si>
-    <t>Bianca Rodrigues - Salário fixo 2026</t>
-  </si>
-  <si>
-    <t>578/1</t>
-  </si>
-  <si>
-    <t>R$  2.219,85</t>
-  </si>
-  <si>
-    <t>Danielle Martins da Silva</t>
-  </si>
-  <si>
-    <t>Danielle - Pagamento 2026</t>
-  </si>
-  <si>
     <t>4.04.01.02.05 IRRF sobre salários</t>
   </si>
   <si>
@@ -2292,12 +2292,12 @@
     <t>VT fev 26/1</t>
   </si>
   <si>
+    <t>R$  433,98</t>
+  </si>
+  <si>
     <t>R$  313,70</t>
   </si>
   <si>
-    <t>R$  433,98</t>
-  </si>
-  <si>
     <t>4.04.02 GASTOS GERAIS ADMINISTRATIVOS</t>
   </si>
   <si>
@@ -2436,17 +2436,25 @@
     <t>R$  45,00</t>
   </si>
   <si>
-    <t>531/1</t>
-  </si>
-  <si>
-    <t>Shopee</t>
-  </si>
-  <si>
-    <t>R$  65,93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freeco refil
-</t>
+    <t>532/1</t>
+  </si>
+  <si>
+    <t>DIA BRASIL SUPERMERCADO</t>
+  </si>
+  <si>
+    <t>R$  59,96</t>
+  </si>
+  <si>
+    <t>cafés</t>
+  </si>
+  <si>
+    <t>502/1</t>
+  </si>
+  <si>
+    <t>R$  100,00</t>
+  </si>
+  <si>
+    <t>Cópia de chaves</t>
   </si>
   <si>
     <t>533/1</t>
@@ -2459,19 +2467,6 @@
   </si>
   <si>
     <t>material limpeza</t>
-  </si>
-  <si>
-    <t>530/1</t>
-  </si>
-  <si>
-    <t>Marinete</t>
-  </si>
-  <si>
-    <t>R$  17,00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Copo descartável para crianças
-</t>
   </si>
   <si>
     <t>529/1</t>
@@ -2488,27 +2483,6 @@
 </t>
   </si>
   <si>
-    <t>502/1</t>
-  </si>
-  <si>
-    <t>R$  100,00</t>
-  </si>
-  <si>
-    <t>Cópia de chaves</t>
-  </si>
-  <si>
-    <t>532/1</t>
-  </si>
-  <si>
-    <t>DIA BRASIL SUPERMERCADO</t>
-  </si>
-  <si>
-    <t>R$  59,96</t>
-  </si>
-  <si>
-    <t>cafés</t>
-  </si>
-  <si>
     <t>505/1</t>
   </si>
   <si>
@@ -2521,6 +2495,32 @@
     <t>Conserto vidro adega</t>
   </si>
   <si>
+    <t>531/1</t>
+  </si>
+  <si>
+    <t>Shopee</t>
+  </si>
+  <si>
+    <t>R$  65,93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freeco refil
+</t>
+  </si>
+  <si>
+    <t>530/1</t>
+  </si>
+  <si>
+    <t>Marinete</t>
+  </si>
+  <si>
+    <t>R$  17,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copo descartável para crianças
+</t>
+  </si>
+  <si>
     <t>4.04.02.07 Informática</t>
   </si>
   <si>
@@ -2584,6 +2584,15 @@
     <t>4.04.02.08.03 Mensalidades e assinaturas - outros gastos</t>
   </si>
   <si>
+    <t>D4 sign</t>
+  </si>
+  <si>
+    <t>R$  49,95</t>
+  </si>
+  <si>
+    <t>D4 sign 2026</t>
+  </si>
+  <si>
     <t>534/1</t>
   </si>
   <si>
@@ -2593,15 +2602,6 @@
     <t>R$  197,63</t>
   </si>
   <si>
-    <t>D4 sign</t>
-  </si>
-  <si>
-    <t>R$  49,95</t>
-  </si>
-  <si>
-    <t>D4 sign 2026</t>
-  </si>
-  <si>
     <t>10/2</t>
   </si>
   <si>
@@ -2614,6 +2614,12 @@
     <t>Promob 2026-1</t>
   </si>
   <si>
+    <t>R$  599,00</t>
+  </si>
+  <si>
+    <t>Promob 2026</t>
+  </si>
+  <si>
     <t>3/1</t>
   </si>
   <si>
@@ -2621,12 +2627,6 @@
   </si>
   <si>
     <t>Promob 2026/2</t>
-  </si>
-  <si>
-    <t>R$  599,00</t>
-  </si>
-  <si>
-    <t>Promob 2026</t>
   </si>
   <si>
     <t>4.04.02.11 Manutenção de predio e equipamentos</t>
@@ -2723,6 +2723,15 @@
     <t>R$ 400,33</t>
   </si>
   <si>
+    <t>VERISURE</t>
+  </si>
+  <si>
+    <t>R$  250,33</t>
+  </si>
+  <si>
+    <t>Verisure - Alarme 2026</t>
+  </si>
+  <si>
     <t>Jackson Fernando de Araujo</t>
   </si>
   <si>
@@ -2730,15 +2739,6 @@
   </si>
   <si>
     <t>Segurança 2026</t>
-  </si>
-  <si>
-    <t>VERISURE</t>
-  </si>
-  <si>
-    <t>R$  250,33</t>
-  </si>
-  <si>
-    <t>Verisure - Alarme 2026</t>
   </si>
   <si>
     <t>4.04.02.14.08 Site e newsletter da loja</t>
@@ -15554,7 +15554,7 @@
         <v>33</v>
       </c>
       <c r="E234" t="s">
-        <v>244</v>
+        <v>275</v>
       </c>
       <c r="F234" t="s">
         <v>218</v>
@@ -15563,16 +15563,16 @@
         <v>41</v>
       </c>
       <c r="H234" t="s">
+        <v>457</v>
+      </c>
+      <c r="I234" t="s">
         <v>508</v>
       </c>
-      <c r="I234" t="s">
-        <v>509</v>
-      </c>
       <c r="J234" t="s">
-        <v>510</v>
+        <v>304</v>
       </c>
       <c r="K234" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="L234" t="s">
         <v>34</v>
@@ -15584,10 +15584,10 @@
         <v>47</v>
       </c>
       <c r="O234" t="s">
-        <v>247</v>
+        <v>105</v>
       </c>
       <c r="P234" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="Q234" t="s">
         <v>47</v>
@@ -15610,7 +15610,7 @@
         <v>34</v>
       </c>
       <c r="E235" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="F235" t="s">
         <v>218</v>
@@ -15619,16 +15619,16 @@
         <v>41</v>
       </c>
       <c r="H235" t="s">
-        <v>511</v>
+        <v>457</v>
       </c>
       <c r="I235" t="s">
-        <v>430</v>
+        <v>509</v>
       </c>
       <c r="J235" t="s">
-        <v>512</v>
+        <v>300</v>
       </c>
       <c r="K235" t="s">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="L235" t="s">
         <v>34</v>
@@ -15640,10 +15640,10 @@
         <v>47</v>
       </c>
       <c r="O235" t="s">
-        <v>71</v>
+        <v>130</v>
       </c>
       <c r="P235" t="s">
-        <v>430</v>
+        <v>509</v>
       </c>
       <c r="Q235" t="s">
         <v>47</v>
@@ -15666,7 +15666,7 @@
         <v>34</v>
       </c>
       <c r="E236" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="F236" t="s">
         <v>218</v>
@@ -15675,16 +15675,16 @@
         <v>41</v>
       </c>
       <c r="H236" t="s">
+        <v>510</v>
+      </c>
+      <c r="I236" t="s">
         <v>511</v>
-      </c>
-      <c r="I236" t="s">
-        <v>439</v>
       </c>
       <c r="J236" t="s">
         <v>512</v>
       </c>
       <c r="K236" t="s">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="L236" t="s">
         <v>34</v>
@@ -15696,10 +15696,10 @@
         <v>47</v>
       </c>
       <c r="O236" t="s">
-        <v>114</v>
+        <v>247</v>
       </c>
       <c r="P236" t="s">
-        <v>439</v>
+        <v>511</v>
       </c>
       <c r="Q236" t="s">
         <v>47</v>
@@ -15722,7 +15722,7 @@
         <v>34</v>
       </c>
       <c r="E237" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="F237" t="s">
         <v>218</v>
@@ -15731,10 +15731,10 @@
         <v>41</v>
       </c>
       <c r="H237" t="s">
-        <v>457</v>
+        <v>513</v>
       </c>
       <c r="I237" t="s">
-        <v>513</v>
+        <v>428</v>
       </c>
       <c r="J237" t="s">
         <v>300</v>
@@ -15752,10 +15752,10 @@
         <v>47</v>
       </c>
       <c r="O237" t="s">
-        <v>130</v>
+        <v>250</v>
       </c>
       <c r="P237" t="s">
-        <v>513</v>
+        <v>428</v>
       </c>
       <c r="Q237" t="s">
         <v>47</v>
@@ -15778,7 +15778,7 @@
         <v>34</v>
       </c>
       <c r="E238" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="F238" t="s">
         <v>218</v>
@@ -15787,16 +15787,16 @@
         <v>41</v>
       </c>
       <c r="H238" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="I238" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="J238" t="s">
-        <v>300</v>
+        <v>514</v>
       </c>
       <c r="K238" t="s">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="L238" t="s">
         <v>34</v>
@@ -15808,10 +15808,10 @@
         <v>47</v>
       </c>
       <c r="O238" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="P238" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q238" t="s">
         <v>47</v>
@@ -15834,7 +15834,7 @@
         <v>34</v>
       </c>
       <c r="E239" t="s">
-        <v>253</v>
+        <v>223</v>
       </c>
       <c r="F239" t="s">
         <v>218</v>
@@ -15843,16 +15843,16 @@
         <v>41</v>
       </c>
       <c r="H239" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="I239" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="J239" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="K239" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="L239" t="s">
         <v>34</v>
@@ -15864,10 +15864,10 @@
         <v>47</v>
       </c>
       <c r="O239" t="s">
-        <v>255</v>
+        <v>114</v>
       </c>
       <c r="P239" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="Q239" t="s">
         <v>47</v>
@@ -15890,25 +15890,25 @@
         <v>34</v>
       </c>
       <c r="E240" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="F240" t="s">
-        <v>218</v>
+        <v>499</v>
       </c>
       <c r="G240" t="s">
         <v>41</v>
       </c>
       <c r="H240" t="s">
-        <v>511</v>
+        <v>457</v>
       </c>
       <c r="I240" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="J240" t="s">
-        <v>512</v>
+        <v>80</v>
       </c>
       <c r="K240" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L240" t="s">
         <v>34</v>
@@ -15920,13 +15920,13 @@
         <v>47</v>
       </c>
       <c r="O240" t="s">
-        <v>310</v>
+        <v>34</v>
       </c>
       <c r="P240" t="s">
-        <v>438</v>
+        <v>34</v>
       </c>
       <c r="Q240" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R240" t="s">
         <v>34</v>
@@ -15946,25 +15946,25 @@
         <v>34</v>
       </c>
       <c r="E241" t="s">
-        <v>275</v>
+        <v>360</v>
       </c>
       <c r="F241" t="s">
-        <v>218</v>
+        <v>499</v>
       </c>
       <c r="G241" t="s">
         <v>41</v>
       </c>
       <c r="H241" t="s">
-        <v>457</v>
+        <v>215</v>
       </c>
       <c r="I241" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="J241" t="s">
-        <v>304</v>
+        <v>119</v>
       </c>
       <c r="K241" t="s">
-        <v>58</v>
+        <v>119</v>
       </c>
       <c r="L241" t="s">
         <v>34</v>
@@ -15976,13 +15976,13 @@
         <v>47</v>
       </c>
       <c r="O241" t="s">
-        <v>105</v>
+        <v>34</v>
       </c>
       <c r="P241" t="s">
-        <v>515</v>
+        <v>34</v>
       </c>
       <c r="Q241" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R241" t="s">
         <v>34</v>
@@ -16002,25 +16002,25 @@
         <v>34</v>
       </c>
       <c r="E242" t="s">
-        <v>472</v>
+        <v>357</v>
       </c>
       <c r="F242" t="s">
-        <v>218</v>
+        <v>499</v>
       </c>
       <c r="G242" t="s">
         <v>41</v>
       </c>
       <c r="H242" t="s">
-        <v>457</v>
+        <v>215</v>
       </c>
       <c r="I242" t="s">
-        <v>473</v>
+        <v>517</v>
       </c>
       <c r="J242" t="s">
-        <v>461</v>
+        <v>80</v>
       </c>
       <c r="K242" t="s">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="L242" t="s">
         <v>34</v>
@@ -16032,13 +16032,13 @@
         <v>47</v>
       </c>
       <c r="O242" t="s">
-        <v>475</v>
+        <v>34</v>
       </c>
       <c r="P242" t="s">
-        <v>473</v>
+        <v>34</v>
       </c>
       <c r="Q242" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R242" t="s">
         <v>34</v>
@@ -16058,25 +16058,25 @@
         <v>34</v>
       </c>
       <c r="E243" t="s">
-        <v>516</v>
+        <v>251</v>
       </c>
       <c r="F243" t="s">
-        <v>499</v>
+        <v>218</v>
       </c>
       <c r="G243" t="s">
         <v>41</v>
       </c>
       <c r="H243" t="s">
-        <v>215</v>
+        <v>513</v>
       </c>
       <c r="I243" t="s">
-        <v>464</v>
+        <v>430</v>
       </c>
       <c r="J243" t="s">
-        <v>134</v>
+        <v>515</v>
       </c>
       <c r="K243" t="s">
-        <v>134</v>
+        <v>70</v>
       </c>
       <c r="L243" t="s">
         <v>34</v>
@@ -16088,13 +16088,13 @@
         <v>47</v>
       </c>
       <c r="O243" t="s">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="P243" t="s">
-        <v>34</v>
+        <v>430</v>
       </c>
       <c r="Q243" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R243" t="s">
         <v>34</v>
@@ -16114,25 +16114,25 @@
         <v>34</v>
       </c>
       <c r="E244" t="s">
-        <v>360</v>
+        <v>472</v>
       </c>
       <c r="F244" t="s">
-        <v>499</v>
+        <v>218</v>
       </c>
       <c r="G244" t="s">
         <v>41</v>
       </c>
       <c r="H244" t="s">
-        <v>215</v>
+        <v>457</v>
       </c>
       <c r="I244" t="s">
-        <v>517</v>
+        <v>473</v>
       </c>
       <c r="J244" t="s">
-        <v>119</v>
+        <v>461</v>
       </c>
       <c r="K244" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="L244" t="s">
         <v>34</v>
@@ -16144,13 +16144,13 @@
         <v>47</v>
       </c>
       <c r="O244" t="s">
-        <v>34</v>
+        <v>475</v>
       </c>
       <c r="P244" t="s">
-        <v>34</v>
+        <v>473</v>
       </c>
       <c r="Q244" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R244" t="s">
         <v>34</v>
@@ -16170,25 +16170,25 @@
         <v>34</v>
       </c>
       <c r="E245" t="s">
-        <v>225</v>
+        <v>518</v>
       </c>
       <c r="F245" t="s">
-        <v>218</v>
+        <v>499</v>
       </c>
       <c r="G245" t="s">
         <v>41</v>
       </c>
       <c r="H245" t="s">
-        <v>457</v>
+        <v>215</v>
       </c>
       <c r="I245" t="s">
-        <v>518</v>
+        <v>464</v>
       </c>
       <c r="J245" t="s">
-        <v>304</v>
+        <v>134</v>
       </c>
       <c r="K245" t="s">
-        <v>101</v>
+        <v>134</v>
       </c>
       <c r="L245" t="s">
         <v>34</v>
@@ -16200,13 +16200,13 @@
         <v>47</v>
       </c>
       <c r="O245" t="s">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="P245" t="s">
-        <v>518</v>
+        <v>34</v>
       </c>
       <c r="Q245" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R245" t="s">
         <v>34</v>
@@ -16226,25 +16226,25 @@
         <v>34</v>
       </c>
       <c r="E246" t="s">
-        <v>354</v>
+        <v>232</v>
       </c>
       <c r="F246" t="s">
-        <v>499</v>
+        <v>218</v>
       </c>
       <c r="G246" t="s">
         <v>41</v>
       </c>
       <c r="H246" t="s">
-        <v>215</v>
+        <v>513</v>
       </c>
       <c r="I246" t="s">
-        <v>519</v>
+        <v>438</v>
       </c>
       <c r="J246" t="s">
+        <v>515</v>
+      </c>
+      <c r="K246" t="s">
         <v>90</v>
-      </c>
-      <c r="K246" t="s">
-        <v>229</v>
       </c>
       <c r="L246" t="s">
         <v>34</v>
@@ -16256,13 +16256,13 @@
         <v>47</v>
       </c>
       <c r="O246" t="s">
-        <v>34</v>
+        <v>310</v>
       </c>
       <c r="P246" t="s">
-        <v>34</v>
+        <v>438</v>
       </c>
       <c r="Q246" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R246" t="s">
         <v>34</v>
@@ -16282,7 +16282,7 @@
         <v>34</v>
       </c>
       <c r="E247" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="F247" t="s">
         <v>499</v>
@@ -16294,13 +16294,13 @@
         <v>215</v>
       </c>
       <c r="I247" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="J247" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K247" t="s">
-        <v>80</v>
+        <v>229</v>
       </c>
       <c r="L247" t="s">
         <v>34</v>
@@ -16338,25 +16338,25 @@
         <v>34</v>
       </c>
       <c r="E248" t="s">
-        <v>363</v>
+        <v>225</v>
       </c>
       <c r="F248" t="s">
-        <v>499</v>
+        <v>218</v>
       </c>
       <c r="G248" t="s">
         <v>41</v>
       </c>
       <c r="H248" t="s">
-        <v>215</v>
+        <v>457</v>
       </c>
       <c r="I248" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="J248" t="s">
-        <v>126</v>
+        <v>304</v>
       </c>
       <c r="K248" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="L248" t="s">
         <v>34</v>
@@ -16368,13 +16368,13 @@
         <v>47</v>
       </c>
       <c r="O248" t="s">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="P248" t="s">
-        <v>34</v>
+        <v>520</v>
       </c>
       <c r="Q248" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R248" t="s">
         <v>34</v>
@@ -16394,7 +16394,7 @@
         <v>34</v>
       </c>
       <c r="E249" t="s">
-        <v>242</v>
+        <v>348</v>
       </c>
       <c r="F249" t="s">
         <v>499</v>
@@ -16403,16 +16403,16 @@
         <v>41</v>
       </c>
       <c r="H249" t="s">
-        <v>457</v>
+        <v>215</v>
       </c>
       <c r="I249" t="s">
-        <v>441</v>
+        <v>521</v>
       </c>
       <c r="J249" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="K249" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="L249" t="s">
         <v>34</v>
@@ -16450,7 +16450,7 @@
         <v>34</v>
       </c>
       <c r="E250" t="s">
-        <v>348</v>
+        <v>363</v>
       </c>
       <c r="F250" t="s">
         <v>499</v>
@@ -17411,7 +17411,7 @@
         <v>41</v>
       </c>
       <c r="H267" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="I267" t="s">
         <v>554</v>
@@ -20090,25 +20090,25 @@
         <v>33</v>
       </c>
       <c r="E315" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="F315" t="s">
-        <v>40</v>
+        <v>666</v>
       </c>
       <c r="G315" t="s">
         <v>41</v>
       </c>
       <c r="H315" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="I315" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="J315" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="K315" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="L315" t="s">
         <v>34</v>
@@ -20120,13 +20120,13 @@
         <v>47</v>
       </c>
       <c r="O315" t="s">
-        <v>310</v>
+        <v>34</v>
       </c>
       <c r="P315" t="s">
-        <v>667</v>
+        <v>34</v>
       </c>
       <c r="Q315" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R315" t="s">
         <v>34</v>
@@ -20146,7 +20146,7 @@
         <v>34</v>
       </c>
       <c r="E316" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="F316" t="s">
         <v>40</v>
@@ -20155,16 +20155,16 @@
         <v>41</v>
       </c>
       <c r="H316" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="I316" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="J316" t="s">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="K316" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="L316" t="s">
         <v>34</v>
@@ -20176,10 +20176,10 @@
         <v>47</v>
       </c>
       <c r="O316" t="s">
-        <v>247</v>
+        <v>114</v>
       </c>
       <c r="P316" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="Q316" t="s">
         <v>47</v>
@@ -20202,7 +20202,7 @@
         <v>34</v>
       </c>
       <c r="E317" t="s">
-        <v>248</v>
+        <v>275</v>
       </c>
       <c r="F317" t="s">
         <v>40</v>
@@ -20211,16 +20211,16 @@
         <v>41</v>
       </c>
       <c r="H317" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="I317" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="J317" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="K317" t="s">
-        <v>119</v>
+        <v>58</v>
       </c>
       <c r="L317" t="s">
         <v>34</v>
@@ -20232,10 +20232,10 @@
         <v>47</v>
       </c>
       <c r="O317" t="s">
-        <v>250</v>
+        <v>105</v>
       </c>
       <c r="P317" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="Q317" t="s">
         <v>47</v>
@@ -20258,22 +20258,22 @@
         <v>34</v>
       </c>
       <c r="E318" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F318" t="s">
-        <v>40</v>
+        <v>666</v>
       </c>
       <c r="G318" t="s">
         <v>41</v>
       </c>
       <c r="H318" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="I318" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="J318" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K318" t="s">
         <v>119</v>
@@ -20288,13 +20288,13 @@
         <v>47</v>
       </c>
       <c r="O318" t="s">
-        <v>130</v>
+        <v>34</v>
       </c>
       <c r="P318" t="s">
-        <v>667</v>
+        <v>34</v>
       </c>
       <c r="Q318" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R318" t="s">
         <v>34</v>
@@ -20314,7 +20314,7 @@
         <v>34</v>
       </c>
       <c r="E319" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="F319" t="s">
         <v>40</v>
@@ -20323,16 +20323,16 @@
         <v>41</v>
       </c>
       <c r="H319" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="I319" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="J319" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="K319" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="L319" t="s">
         <v>34</v>
@@ -20344,10 +20344,10 @@
         <v>47</v>
       </c>
       <c r="O319" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="P319" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="Q319" t="s">
         <v>47</v>
@@ -20370,25 +20370,25 @@
         <v>34</v>
       </c>
       <c r="E320" t="s">
-        <v>227</v>
+        <v>157</v>
       </c>
       <c r="F320" t="s">
+        <v>40</v>
+      </c>
+      <c r="G320" t="s">
+        <v>41</v>
+      </c>
+      <c r="H320" t="s">
+        <v>667</v>
+      </c>
+      <c r="I320" t="s">
         <v>668</v>
       </c>
-      <c r="G320" t="s">
-        <v>41</v>
-      </c>
-      <c r="H320" t="s">
-        <v>666</v>
-      </c>
-      <c r="I320" t="s">
-        <v>667</v>
-      </c>
       <c r="J320" t="s">
-        <v>90</v>
+        <v>134</v>
       </c>
       <c r="K320" t="s">
-        <v>229</v>
+        <v>134</v>
       </c>
       <c r="L320" t="s">
         <v>34</v>
@@ -20400,13 +20400,13 @@
         <v>47</v>
       </c>
       <c r="O320" t="s">
-        <v>34</v>
+        <v>463</v>
       </c>
       <c r="P320" t="s">
-        <v>34</v>
+        <v>668</v>
       </c>
       <c r="Q320" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R320" t="s">
         <v>34</v>
@@ -20426,25 +20426,25 @@
         <v>34</v>
       </c>
       <c r="E321" t="s">
-        <v>256</v>
+        <v>221</v>
       </c>
       <c r="F321" t="s">
+        <v>666</v>
+      </c>
+      <c r="G321" t="s">
+        <v>41</v>
+      </c>
+      <c r="H321" t="s">
+        <v>667</v>
+      </c>
+      <c r="I321" t="s">
         <v>668</v>
       </c>
-      <c r="G321" t="s">
-        <v>41</v>
-      </c>
-      <c r="H321" t="s">
-        <v>666</v>
-      </c>
-      <c r="I321" t="s">
-        <v>667</v>
-      </c>
       <c r="J321" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K321" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L321" t="s">
         <v>34</v>
@@ -20482,25 +20482,25 @@
         <v>34</v>
       </c>
       <c r="E322" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="F322" t="s">
+        <v>40</v>
+      </c>
+      <c r="G322" t="s">
+        <v>41</v>
+      </c>
+      <c r="H322" t="s">
+        <v>667</v>
+      </c>
+      <c r="I322" t="s">
         <v>668</v>
       </c>
-      <c r="G322" t="s">
-        <v>41</v>
-      </c>
-      <c r="H322" t="s">
-        <v>666</v>
-      </c>
-      <c r="I322" t="s">
-        <v>667</v>
-      </c>
       <c r="J322" t="s">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="K322" t="s">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="L322" t="s">
         <v>34</v>
@@ -20512,13 +20512,13 @@
         <v>47</v>
       </c>
       <c r="O322" t="s">
-        <v>34</v>
+        <v>255</v>
       </c>
       <c r="P322" t="s">
-        <v>34</v>
+        <v>668</v>
       </c>
       <c r="Q322" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R322" t="s">
         <v>34</v>
@@ -20538,7 +20538,7 @@
         <v>34</v>
       </c>
       <c r="E323" t="s">
-        <v>157</v>
+        <v>244</v>
       </c>
       <c r="F323" t="s">
         <v>40</v>
@@ -20547,16 +20547,16 @@
         <v>41</v>
       </c>
       <c r="H323" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="I323" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="J323" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="K323" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="L323" t="s">
         <v>34</v>
@@ -20568,10 +20568,10 @@
         <v>47</v>
       </c>
       <c r="O323" t="s">
-        <v>463</v>
+        <v>247</v>
       </c>
       <c r="P323" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="Q323" t="s">
         <v>47</v>
@@ -20594,7 +20594,7 @@
         <v>34</v>
       </c>
       <c r="E324" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="F324" t="s">
         <v>40</v>
@@ -20603,16 +20603,16 @@
         <v>41</v>
       </c>
       <c r="H324" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="I324" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="J324" t="s">
-        <v>147</v>
+        <v>90</v>
       </c>
       <c r="K324" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="L324" t="s">
         <v>34</v>
@@ -20624,10 +20624,10 @@
         <v>47</v>
       </c>
       <c r="O324" t="s">
-        <v>114</v>
+        <v>310</v>
       </c>
       <c r="P324" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="Q324" t="s">
         <v>47</v>
@@ -20650,7 +20650,7 @@
         <v>34</v>
       </c>
       <c r="E325" t="s">
-        <v>275</v>
+        <v>225</v>
       </c>
       <c r="F325" t="s">
         <v>40</v>
@@ -20659,16 +20659,16 @@
         <v>41</v>
       </c>
       <c r="H325" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="I325" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="J325" t="s">
-        <v>96</v>
+        <v>178</v>
       </c>
       <c r="K325" t="s">
-        <v>58</v>
+        <v>101</v>
       </c>
       <c r="L325" t="s">
         <v>34</v>
@@ -20680,10 +20680,10 @@
         <v>47</v>
       </c>
       <c r="O325" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="P325" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="Q325" t="s">
         <v>47</v>
@@ -20706,25 +20706,25 @@
         <v>34</v>
       </c>
       <c r="E326" t="s">
-        <v>221</v>
+        <v>256</v>
       </c>
       <c r="F326" t="s">
+        <v>666</v>
+      </c>
+      <c r="G326" t="s">
+        <v>41</v>
+      </c>
+      <c r="H326" t="s">
+        <v>667</v>
+      </c>
+      <c r="I326" t="s">
         <v>668</v>
       </c>
-      <c r="G326" t="s">
-        <v>41</v>
-      </c>
-      <c r="H326" t="s">
-        <v>666</v>
-      </c>
-      <c r="I326" t="s">
-        <v>667</v>
-      </c>
       <c r="J326" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K326" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L326" t="s">
         <v>34</v>
@@ -20762,25 +20762,25 @@
         <v>34</v>
       </c>
       <c r="E327" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="F327" t="s">
+        <v>40</v>
+      </c>
+      <c r="G327" t="s">
+        <v>41</v>
+      </c>
+      <c r="H327" t="s">
+        <v>667</v>
+      </c>
+      <c r="I327" t="s">
         <v>668</v>
       </c>
-      <c r="G327" t="s">
-        <v>41</v>
-      </c>
-      <c r="H327" t="s">
-        <v>666</v>
-      </c>
-      <c r="I327" t="s">
-        <v>667</v>
-      </c>
       <c r="J327" t="s">
-        <v>191</v>
+        <v>118</v>
       </c>
       <c r="K327" t="s">
-        <v>191</v>
+        <v>119</v>
       </c>
       <c r="L327" t="s">
         <v>34</v>
@@ -20792,13 +20792,13 @@
         <v>47</v>
       </c>
       <c r="O327" t="s">
-        <v>34</v>
+        <v>130</v>
       </c>
       <c r="P327" t="s">
-        <v>34</v>
+        <v>668</v>
       </c>
       <c r="Q327" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R327" t="s">
         <v>34</v>
@@ -20818,25 +20818,25 @@
         <v>34</v>
       </c>
       <c r="E328" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F328" t="s">
-        <v>40</v>
+        <v>666</v>
       </c>
       <c r="G328" t="s">
         <v>41</v>
       </c>
       <c r="H328" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="I328" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="J328" t="s">
-        <v>178</v>
+        <v>90</v>
       </c>
       <c r="K328" t="s">
-        <v>101</v>
+        <v>229</v>
       </c>
       <c r="L328" t="s">
         <v>34</v>
@@ -20848,13 +20848,13 @@
         <v>47</v>
       </c>
       <c r="O328" t="s">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="P328" t="s">
-        <v>667</v>
+        <v>34</v>
       </c>
       <c r="Q328" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R328" t="s">
         <v>34</v>
@@ -20986,28 +20986,28 @@
         <v>34</v>
       </c>
       <c r="E331" t="s">
-        <v>175</v>
+        <v>676</v>
       </c>
       <c r="F331" t="s">
-        <v>40</v>
+        <v>211</v>
       </c>
       <c r="G331" t="s">
         <v>41</v>
       </c>
       <c r="H331" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="I331" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="J331" t="s">
-        <v>178</v>
+        <v>679</v>
       </c>
       <c r="K331" t="s">
-        <v>178</v>
+        <v>229</v>
       </c>
       <c r="L331" t="s">
-        <v>678</v>
+        <v>34</v>
       </c>
       <c r="M331" t="s">
         <v>671</v>
@@ -21019,7 +21019,7 @@
         <v>48</v>
       </c>
       <c r="P331" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="Q331" t="s">
         <v>47</v>
@@ -21042,7 +21042,7 @@
         <v>34</v>
       </c>
       <c r="E332" t="s">
-        <v>672</v>
+        <v>175</v>
       </c>
       <c r="F332" t="s">
         <v>40</v>
@@ -21051,16 +21051,16 @@
         <v>41</v>
       </c>
       <c r="H332" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="I332" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="J332" t="s">
-        <v>681</v>
+        <v>178</v>
       </c>
       <c r="K332" t="s">
-        <v>229</v>
+        <v>178</v>
       </c>
       <c r="L332" t="s">
         <v>682</v>
@@ -21075,7 +21075,7 @@
         <v>48</v>
       </c>
       <c r="P332" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="Q332" t="s">
         <v>47</v>
@@ -21098,28 +21098,28 @@
         <v>34</v>
       </c>
       <c r="E333" t="s">
+        <v>672</v>
+      </c>
+      <c r="F333" t="s">
+        <v>40</v>
+      </c>
+      <c r="G333" t="s">
+        <v>41</v>
+      </c>
+      <c r="H333" t="s">
         <v>683</v>
       </c>
-      <c r="F333" t="s">
-        <v>211</v>
-      </c>
-      <c r="G333" t="s">
-        <v>41</v>
-      </c>
-      <c r="H333" t="s">
+      <c r="I333" t="s">
         <v>684</v>
       </c>
-      <c r="I333" t="s">
+      <c r="J333" t="s">
         <v>685</v>
-      </c>
-      <c r="J333" t="s">
-        <v>686</v>
       </c>
       <c r="K333" t="s">
         <v>229</v>
       </c>
       <c r="L333" t="s">
-        <v>34</v>
+        <v>686</v>
       </c>
       <c r="M333" t="s">
         <v>671</v>
@@ -21131,7 +21131,7 @@
         <v>48</v>
       </c>
       <c r="P333" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="Q333" t="s">
         <v>47</v>
@@ -21337,7 +21337,7 @@
         <v>694</v>
       </c>
       <c r="J337" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K337" t="s">
         <v>45</v>
@@ -21490,7 +21490,7 @@
         <v>33</v>
       </c>
       <c r="E340" t="s">
-        <v>672</v>
+        <v>175</v>
       </c>
       <c r="F340" t="s">
         <v>40</v>
@@ -21499,13 +21499,13 @@
         <v>41</v>
       </c>
       <c r="H340" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="I340" t="s">
-        <v>694</v>
+        <v>155</v>
       </c>
       <c r="J340" t="s">
-        <v>335</v>
+        <v>122</v>
       </c>
       <c r="K340" t="s">
         <v>45</v>
@@ -21523,7 +21523,7 @@
         <v>48</v>
       </c>
       <c r="P340" t="s">
-        <v>694</v>
+        <v>155</v>
       </c>
       <c r="Q340" t="s">
         <v>47</v>
@@ -21555,19 +21555,19 @@
         <v>41</v>
       </c>
       <c r="H341" t="s">
-        <v>556</v>
+        <v>215</v>
       </c>
       <c r="I341" t="s">
-        <v>694</v>
+        <v>704</v>
       </c>
       <c r="J341" t="s">
         <v>474</v>
       </c>
       <c r="K341" t="s">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="L341" t="s">
-        <v>34</v>
+        <v>705</v>
       </c>
       <c r="M341" t="s">
         <v>701</v>
@@ -21579,7 +21579,7 @@
         <v>48</v>
       </c>
       <c r="P341" t="s">
-        <v>694</v>
+        <v>704</v>
       </c>
       <c r="Q341" t="s">
         <v>47</v>
@@ -21602,25 +21602,25 @@
         <v>34</v>
       </c>
       <c r="E342" t="s">
-        <v>704</v>
+        <v>175</v>
       </c>
       <c r="F342" t="s">
-        <v>211</v>
+        <v>40</v>
       </c>
       <c r="G342" t="s">
         <v>41</v>
       </c>
       <c r="H342" t="s">
-        <v>215</v>
+        <v>513</v>
       </c>
       <c r="I342" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="J342" t="s">
-        <v>474</v>
+        <v>70</v>
       </c>
       <c r="K342" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="L342" t="s">
         <v>706</v>
@@ -21635,7 +21635,7 @@
         <v>48</v>
       </c>
       <c r="P342" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="Q342" t="s">
         <v>47</v>
@@ -21658,7 +21658,7 @@
         <v>34</v>
       </c>
       <c r="E343" t="s">
-        <v>175</v>
+        <v>672</v>
       </c>
       <c r="F343" t="s">
         <v>40</v>
@@ -21667,19 +21667,19 @@
         <v>41</v>
       </c>
       <c r="H343" t="s">
-        <v>511</v>
+        <v>707</v>
       </c>
       <c r="I343" t="s">
-        <v>694</v>
+        <v>708</v>
       </c>
       <c r="J343" t="s">
-        <v>70</v>
+        <v>685</v>
       </c>
       <c r="K343" t="s">
         <v>45</v>
       </c>
       <c r="L343" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="M343" t="s">
         <v>701</v>
@@ -21691,7 +21691,7 @@
         <v>48</v>
       </c>
       <c r="P343" t="s">
-        <v>694</v>
+        <v>708</v>
       </c>
       <c r="Q343" t="s">
         <v>47</v>
@@ -21723,19 +21723,19 @@
         <v>41</v>
       </c>
       <c r="H344" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="I344" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="J344" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K344" t="s">
         <v>45</v>
       </c>
       <c r="L344" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="M344" t="s">
         <v>701</v>
@@ -21747,7 +21747,7 @@
         <v>48</v>
       </c>
       <c r="P344" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="Q344" t="s">
         <v>47</v>
@@ -21779,19 +21779,19 @@
         <v>41</v>
       </c>
       <c r="H345" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="I345" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="J345" t="s">
-        <v>681</v>
+        <v>335</v>
       </c>
       <c r="K345" t="s">
         <v>45</v>
       </c>
       <c r="L345" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="M345" t="s">
         <v>701</v>
@@ -21803,7 +21803,7 @@
         <v>48</v>
       </c>
       <c r="P345" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="Q345" t="s">
         <v>47</v>
@@ -21835,19 +21835,19 @@
         <v>41</v>
       </c>
       <c r="H346" t="s">
-        <v>714</v>
+        <v>459</v>
       </c>
       <c r="I346" t="s">
-        <v>694</v>
+        <v>708</v>
       </c>
       <c r="J346" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K346" t="s">
         <v>45</v>
       </c>
       <c r="L346" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="M346" t="s">
         <v>701</v>
@@ -21859,7 +21859,7 @@
         <v>48</v>
       </c>
       <c r="P346" t="s">
-        <v>694</v>
+        <v>708</v>
       </c>
       <c r="Q346" t="s">
         <v>47</v>
@@ -21891,19 +21891,19 @@
         <v>41</v>
       </c>
       <c r="H347" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="I347" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="J347" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K347" t="s">
         <v>45</v>
       </c>
       <c r="L347" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="M347" t="s">
         <v>701</v>
@@ -21915,7 +21915,7 @@
         <v>48</v>
       </c>
       <c r="P347" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="Q347" t="s">
         <v>47</v>
@@ -21947,10 +21947,10 @@
         <v>41</v>
       </c>
       <c r="H348" t="s">
-        <v>719</v>
+        <v>457</v>
       </c>
       <c r="I348" t="s">
-        <v>720</v>
+        <v>694</v>
       </c>
       <c r="J348" t="s">
         <v>335</v>
@@ -21959,7 +21959,7 @@
         <v>45</v>
       </c>
       <c r="L348" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="M348" t="s">
         <v>701</v>
@@ -21971,7 +21971,7 @@
         <v>48</v>
       </c>
       <c r="P348" t="s">
-        <v>720</v>
+        <v>694</v>
       </c>
       <c r="Q348" t="s">
         <v>47</v>
@@ -21994,28 +21994,28 @@
         <v>34</v>
       </c>
       <c r="E349" t="s">
-        <v>672</v>
+        <v>721</v>
       </c>
       <c r="F349" t="s">
-        <v>40</v>
+        <v>211</v>
       </c>
       <c r="G349" t="s">
         <v>41</v>
       </c>
       <c r="H349" t="s">
-        <v>459</v>
+        <v>556</v>
       </c>
       <c r="I349" t="s">
-        <v>722</v>
+        <v>694</v>
       </c>
       <c r="J349" t="s">
-        <v>681</v>
+        <v>474</v>
       </c>
       <c r="K349" t="s">
-        <v>45</v>
+        <v>122</v>
       </c>
       <c r="L349" t="s">
-        <v>723</v>
+        <v>34</v>
       </c>
       <c r="M349" t="s">
         <v>701</v>
@@ -22027,7 +22027,7 @@
         <v>48</v>
       </c>
       <c r="P349" t="s">
-        <v>722</v>
+        <v>694</v>
       </c>
       <c r="Q349" t="s">
         <v>47</v>
@@ -22059,7 +22059,7 @@
         <v>41</v>
       </c>
       <c r="H350" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="I350" t="s">
         <v>155</v>
@@ -22071,7 +22071,7 @@
         <v>122</v>
       </c>
       <c r="L350" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="M350" t="s">
         <v>701</v>
@@ -22106,7 +22106,7 @@
         <v>34</v>
       </c>
       <c r="E351" t="s">
-        <v>175</v>
+        <v>672</v>
       </c>
       <c r="F351" t="s">
         <v>40</v>
@@ -22115,19 +22115,19 @@
         <v>41</v>
       </c>
       <c r="H351" t="s">
-        <v>447</v>
+        <v>724</v>
       </c>
       <c r="I351" t="s">
-        <v>155</v>
+        <v>694</v>
       </c>
       <c r="J351" t="s">
-        <v>122</v>
+        <v>685</v>
       </c>
       <c r="K351" t="s">
         <v>45</v>
       </c>
       <c r="L351" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="M351" t="s">
         <v>701</v>
@@ -22139,7 +22139,7 @@
         <v>48</v>
       </c>
       <c r="P351" t="s">
-        <v>155</v>
+        <v>694</v>
       </c>
       <c r="Q351" t="s">
         <v>47</v>
@@ -22162,7 +22162,7 @@
         <v>34</v>
       </c>
       <c r="E352" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="F352" t="s">
         <v>211</v>
@@ -22174,7 +22174,7 @@
         <v>425</v>
       </c>
       <c r="I352" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="J352" t="s">
         <v>474</v>
@@ -22195,7 +22195,7 @@
         <v>48</v>
       </c>
       <c r="P352" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="Q352" t="s">
         <v>47</v>
@@ -22227,13 +22227,13 @@
         <v>41</v>
       </c>
       <c r="H353" t="s">
+        <v>728</v>
+      </c>
+      <c r="I353" t="s">
         <v>729</v>
       </c>
-      <c r="I353" t="s">
-        <v>722</v>
-      </c>
       <c r="J353" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K353" t="s">
         <v>45</v>
@@ -22251,7 +22251,7 @@
         <v>48</v>
       </c>
       <c r="P353" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="Q353" t="s">
         <v>47</v>
@@ -22669,7 +22669,7 @@
         <v>187</v>
       </c>
       <c r="F361" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="G361" t="s">
         <v>41</v>
@@ -22843,16 +22843,16 @@
         <v>41</v>
       </c>
       <c r="H364" t="s">
-        <v>425</v>
+        <v>469</v>
       </c>
       <c r="I364" t="s">
         <v>754</v>
       </c>
       <c r="J364" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="K364" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="L364" t="s">
         <v>34</v>
@@ -22899,16 +22899,16 @@
         <v>41</v>
       </c>
       <c r="H365" t="s">
-        <v>469</v>
+        <v>425</v>
       </c>
       <c r="I365" t="s">
         <v>755</v>
       </c>
       <c r="J365" t="s">
-        <v>101</v>
+        <v>178</v>
       </c>
       <c r="K365" t="s">
-        <v>101</v>
+        <v>178</v>
       </c>
       <c r="L365" t="s">
         <v>34</v>
@@ -23073,7 +23073,7 @@
         <v>764</v>
       </c>
       <c r="J368" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K368" t="s">
         <v>229</v>
@@ -23353,7 +23353,7 @@
         <v>782</v>
       </c>
       <c r="J373" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K373" t="s">
         <v>45</v>
@@ -23521,7 +23521,7 @@
         <v>794</v>
       </c>
       <c r="J376" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K376" t="s">
         <v>795</v>
@@ -23692,7 +23692,7 @@
         <v>304</v>
       </c>
       <c r="K379" t="s">
-        <v>122</v>
+        <v>75</v>
       </c>
       <c r="L379" t="s">
         <v>805</v>
@@ -23739,19 +23739,19 @@
         <v>41</v>
       </c>
       <c r="H380" t="s">
+        <v>425</v>
+      </c>
+      <c r="I380" t="s">
         <v>807</v>
       </c>
-      <c r="I380" t="s">
+      <c r="J380" t="s">
+        <v>58</v>
+      </c>
+      <c r="K380" t="s">
+        <v>202</v>
+      </c>
+      <c r="L380" t="s">
         <v>808</v>
-      </c>
-      <c r="J380" t="s">
-        <v>304</v>
-      </c>
-      <c r="K380" t="s">
-        <v>96</v>
-      </c>
-      <c r="L380" t="s">
-        <v>809</v>
       </c>
       <c r="M380" t="s">
         <v>799</v>
@@ -23763,7 +23763,7 @@
         <v>48</v>
       </c>
       <c r="P380" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="Q380" t="s">
         <v>47</v>
@@ -23786,7 +23786,7 @@
         <v>34</v>
       </c>
       <c r="E381" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="F381" t="s">
         <v>211</v>
@@ -23795,10 +23795,10 @@
         <v>41</v>
       </c>
       <c r="H381" t="s">
+        <v>810</v>
+      </c>
+      <c r="I381" t="s">
         <v>811</v>
-      </c>
-      <c r="I381" t="s">
-        <v>812</v>
       </c>
       <c r="J381" t="s">
         <v>304</v>
@@ -23807,7 +23807,7 @@
         <v>96</v>
       </c>
       <c r="L381" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="M381" t="s">
         <v>799</v>
@@ -23819,7 +23819,7 @@
         <v>48</v>
       </c>
       <c r="P381" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="Q381" t="s">
         <v>47</v>
@@ -23842,7 +23842,7 @@
         <v>34</v>
       </c>
       <c r="E382" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="F382" t="s">
         <v>211</v>
@@ -23851,10 +23851,10 @@
         <v>41</v>
       </c>
       <c r="H382" t="s">
+        <v>814</v>
+      </c>
+      <c r="I382" t="s">
         <v>815</v>
-      </c>
-      <c r="I382" t="s">
-        <v>816</v>
       </c>
       <c r="J382" t="s">
         <v>304</v>
@@ -23863,7 +23863,7 @@
         <v>96</v>
       </c>
       <c r="L382" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="M382" t="s">
         <v>799</v>
@@ -23875,7 +23875,7 @@
         <v>48</v>
       </c>
       <c r="P382" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="Q382" t="s">
         <v>47</v>
@@ -23898,7 +23898,7 @@
         <v>34</v>
       </c>
       <c r="E383" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="F383" t="s">
         <v>211</v>
@@ -23907,7 +23907,7 @@
         <v>41</v>
       </c>
       <c r="H383" t="s">
-        <v>425</v>
+        <v>818</v>
       </c>
       <c r="I383" t="s">
         <v>819</v>
@@ -23972,7 +23972,7 @@
         <v>304</v>
       </c>
       <c r="K384" t="s">
-        <v>75</v>
+        <v>122</v>
       </c>
       <c r="L384" t="s">
         <v>824</v>
@@ -24025,10 +24025,10 @@
         <v>827</v>
       </c>
       <c r="J385" t="s">
-        <v>58</v>
+        <v>304</v>
       </c>
       <c r="K385" t="s">
-        <v>202</v>
+        <v>96</v>
       </c>
       <c r="L385" t="s">
         <v>828</v>
@@ -24137,7 +24137,7 @@
         <v>834</v>
       </c>
       <c r="J387" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K387" t="s">
         <v>45</v>
@@ -24346,28 +24346,28 @@
         <v>33</v>
       </c>
       <c r="E391" t="s">
+        <v>672</v>
+      </c>
+      <c r="F391" t="s">
+        <v>40</v>
+      </c>
+      <c r="G391" t="s">
+        <v>41</v>
+      </c>
+      <c r="H391" t="s">
         <v>850</v>
       </c>
-      <c r="F391" t="s">
-        <v>211</v>
-      </c>
-      <c r="G391" t="s">
-        <v>41</v>
-      </c>
-      <c r="H391" t="s">
+      <c r="I391" t="s">
         <v>851</v>
       </c>
-      <c r="I391" t="s">
+      <c r="J391" t="s">
+        <v>335</v>
+      </c>
+      <c r="K391" t="s">
+        <v>45</v>
+      </c>
+      <c r="L391" t="s">
         <v>852</v>
-      </c>
-      <c r="J391" t="s">
-        <v>304</v>
-      </c>
-      <c r="K391" t="s">
-        <v>122</v>
-      </c>
-      <c r="L391" t="s">
-        <v>34</v>
       </c>
       <c r="M391" t="s">
         <v>849</v>
@@ -24379,7 +24379,7 @@
         <v>48</v>
       </c>
       <c r="P391" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="Q391" t="s">
         <v>47</v>
@@ -24402,28 +24402,28 @@
         <v>34</v>
       </c>
       <c r="E392" t="s">
-        <v>672</v>
+        <v>853</v>
       </c>
       <c r="F392" t="s">
-        <v>40</v>
+        <v>211</v>
       </c>
       <c r="G392" t="s">
         <v>41</v>
       </c>
       <c r="H392" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="I392" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="J392" t="s">
-        <v>335</v>
+        <v>304</v>
       </c>
       <c r="K392" t="s">
-        <v>45</v>
+        <v>122</v>
       </c>
       <c r="L392" t="s">
-        <v>855</v>
+        <v>34</v>
       </c>
       <c r="M392" t="s">
         <v>849</v>
@@ -24435,7 +24435,7 @@
         <v>48</v>
       </c>
       <c r="P392" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="Q392" t="s">
         <v>47</v>
@@ -24514,7 +24514,7 @@
         <v>34</v>
       </c>
       <c r="E394" t="s">
-        <v>860</v>
+        <v>672</v>
       </c>
       <c r="F394" t="s">
         <v>40</v>
@@ -24526,16 +24526,16 @@
         <v>845</v>
       </c>
       <c r="I394" t="s">
+        <v>860</v>
+      </c>
+      <c r="J394" t="s">
+        <v>335</v>
+      </c>
+      <c r="K394" t="s">
+        <v>858</v>
+      </c>
+      <c r="L394" t="s">
         <v>861</v>
-      </c>
-      <c r="J394" t="s">
-        <v>101</v>
-      </c>
-      <c r="K394" t="s">
-        <v>45</v>
-      </c>
-      <c r="L394" t="s">
-        <v>862</v>
       </c>
       <c r="M394" t="s">
         <v>849</v>
@@ -24547,7 +24547,7 @@
         <v>48</v>
       </c>
       <c r="P394" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="Q394" t="s">
         <v>47</v>
@@ -24570,7 +24570,7 @@
         <v>34</v>
       </c>
       <c r="E395" t="s">
-        <v>672</v>
+        <v>862</v>
       </c>
       <c r="F395" t="s">
         <v>40</v>
@@ -24585,10 +24585,10 @@
         <v>863</v>
       </c>
       <c r="J395" t="s">
-        <v>335</v>
+        <v>101</v>
       </c>
       <c r="K395" t="s">
-        <v>858</v>
+        <v>45</v>
       </c>
       <c r="L395" t="s">
         <v>864</v>
@@ -24809,7 +24809,7 @@
         <v>877</v>
       </c>
       <c r="J399" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K399" t="s">
         <v>45</v>
@@ -24862,7 +24862,7 @@
         <v>876</v>
       </c>
       <c r="I400" t="s">
-        <v>819</v>
+        <v>807</v>
       </c>
       <c r="J400" t="s">
         <v>58</v>
@@ -24883,7 +24883,7 @@
         <v>48</v>
       </c>
       <c r="P400" t="s">
-        <v>819</v>
+        <v>807</v>
       </c>
       <c r="Q400" t="s">
         <v>47</v>
@@ -25074,7 +25074,7 @@
         <v>33</v>
       </c>
       <c r="E404" t="s">
-        <v>672</v>
+        <v>762</v>
       </c>
       <c r="F404" t="s">
         <v>40</v>
@@ -25089,10 +25089,10 @@
         <v>897</v>
       </c>
       <c r="J404" t="s">
-        <v>681</v>
+        <v>178</v>
       </c>
       <c r="K404" t="s">
-        <v>45</v>
+        <v>178</v>
       </c>
       <c r="L404" t="s">
         <v>898</v>
@@ -25130,7 +25130,7 @@
         <v>34</v>
       </c>
       <c r="E405" t="s">
-        <v>762</v>
+        <v>672</v>
       </c>
       <c r="F405" t="s">
         <v>40</v>
@@ -25145,10 +25145,10 @@
         <v>900</v>
       </c>
       <c r="J405" t="s">
-        <v>178</v>
+        <v>685</v>
       </c>
       <c r="K405" t="s">
-        <v>178</v>
+        <v>45</v>
       </c>
       <c r="L405" t="s">
         <v>901</v>

--- a/xlsx/dre/DRE_02_2026.xlsx
+++ b/xlsx/dre/DRE_02_2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8896" uniqueCount="1045">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8896" uniqueCount="1046">
   <si>
     <t>Movimentações Financeiras</t>
   </si>
@@ -2176,6 +2176,9 @@
   </si>
   <si>
     <t>Leandro Henrique Simoes Campos Fixo 2026</t>
+  </si>
+  <si>
+    <t>CARINA PEREIRA</t>
   </si>
   <si>
     <t>Carina - Pagamento 2026</t>
@@ -21835,7 +21838,7 @@
         <v>41</v>
       </c>
       <c r="H346" t="s">
-        <v>459</v>
+        <v>716</v>
       </c>
       <c r="I346" t="s">
         <v>708</v>
@@ -21847,7 +21850,7 @@
         <v>45</v>
       </c>
       <c r="L346" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="M346" t="s">
         <v>701</v>
@@ -21891,10 +21894,10 @@
         <v>41</v>
       </c>
       <c r="H347" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="I347" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="J347" t="s">
         <v>685</v>
@@ -21903,7 +21906,7 @@
         <v>45</v>
       </c>
       <c r="L347" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="M347" t="s">
         <v>701</v>
@@ -21915,7 +21918,7 @@
         <v>48</v>
       </c>
       <c r="P347" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="Q347" t="s">
         <v>47</v>
@@ -21959,7 +21962,7 @@
         <v>45</v>
       </c>
       <c r="L348" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="M348" t="s">
         <v>701</v>
@@ -21994,7 +21997,7 @@
         <v>34</v>
       </c>
       <c r="E349" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="F349" t="s">
         <v>211</v>
@@ -22059,7 +22062,7 @@
         <v>41</v>
       </c>
       <c r="H350" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="I350" t="s">
         <v>155</v>
@@ -22071,7 +22074,7 @@
         <v>122</v>
       </c>
       <c r="L350" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="M350" t="s">
         <v>701</v>
@@ -22115,7 +22118,7 @@
         <v>41</v>
       </c>
       <c r="H351" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="I351" t="s">
         <v>694</v>
@@ -22127,7 +22130,7 @@
         <v>45</v>
       </c>
       <c r="L351" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="M351" t="s">
         <v>701</v>
@@ -22162,7 +22165,7 @@
         <v>34</v>
       </c>
       <c r="E352" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="F352" t="s">
         <v>211</v>
@@ -22174,7 +22177,7 @@
         <v>425</v>
       </c>
       <c r="I352" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="J352" t="s">
         <v>474</v>
@@ -22195,7 +22198,7 @@
         <v>48</v>
       </c>
       <c r="P352" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="Q352" t="s">
         <v>47</v>
@@ -22227,10 +22230,10 @@
         <v>41</v>
       </c>
       <c r="H353" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="I353" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="J353" t="s">
         <v>685</v>
@@ -22239,7 +22242,7 @@
         <v>45</v>
       </c>
       <c r="L353" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="M353" t="s">
         <v>701</v>
@@ -22251,7 +22254,7 @@
         <v>48</v>
       </c>
       <c r="P353" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="Q353" t="s">
         <v>47</v>
@@ -22262,13 +22265,13 @@
     </row>
     <row r="354">
       <c r="A354" t="s" s="1">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B354" t="s" s="1">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C354" t="s" s="1">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D354" t="s" s="1">
         <v>33</v>
@@ -22318,13 +22321,13 @@
     </row>
     <row r="355">
       <c r="A355" t="s">
+        <v>734</v>
+      </c>
+      <c r="B355" t="s">
         <v>733</v>
       </c>
-      <c r="B355" t="s">
-        <v>732</v>
-      </c>
       <c r="C355" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D355" t="s">
         <v>33</v>
@@ -22351,10 +22354,10 @@
         <v>191</v>
       </c>
       <c r="L355" t="s">
+        <v>735</v>
+      </c>
+      <c r="M355" t="s">
         <v>734</v>
-      </c>
-      <c r="M355" t="s">
-        <v>733</v>
       </c>
       <c r="N355" t="s">
         <v>47</v>
@@ -22374,13 +22377,13 @@
     </row>
     <row r="356">
       <c r="A356" t="s" s="1">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B356" t="s" s="1">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C356" t="s" s="1">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="D356" t="s" s="1">
         <v>33</v>
@@ -22430,13 +22433,13 @@
     </row>
     <row r="357">
       <c r="A357" t="s">
+        <v>738</v>
+      </c>
+      <c r="B357" t="s">
         <v>737</v>
       </c>
-      <c r="B357" t="s">
-        <v>736</v>
-      </c>
       <c r="C357" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="D357" t="s">
         <v>33</v>
@@ -22463,10 +22466,10 @@
         <v>191</v>
       </c>
       <c r="L357" t="s">
+        <v>739</v>
+      </c>
+      <c r="M357" t="s">
         <v>738</v>
-      </c>
-      <c r="M357" t="s">
-        <v>737</v>
       </c>
       <c r="N357" t="s">
         <v>47</v>
@@ -22486,13 +22489,13 @@
     </row>
     <row r="358">
       <c r="A358" t="s" s="1">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B358" t="s" s="1">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C358" t="s" s="1">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D358" t="s" s="1">
         <v>33</v>
@@ -22542,13 +22545,13 @@
     </row>
     <row r="359">
       <c r="A359" t="s">
+        <v>742</v>
+      </c>
+      <c r="B359" t="s">
         <v>741</v>
       </c>
-      <c r="B359" t="s">
-        <v>740</v>
-      </c>
       <c r="C359" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D359" t="s">
         <v>33</v>
@@ -22563,10 +22566,10 @@
         <v>41</v>
       </c>
       <c r="H359" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="I359" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="J359" t="s">
         <v>190</v>
@@ -22575,10 +22578,10 @@
         <v>191</v>
       </c>
       <c r="L359" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="M359" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="N359" t="s">
         <v>47</v>
@@ -22587,7 +22590,7 @@
         <v>48</v>
       </c>
       <c r="P359" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="Q359" t="s">
         <v>47</v>
@@ -22598,13 +22601,13 @@
     </row>
     <row r="360">
       <c r="A360" t="s" s="1">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B360" t="s" s="1">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C360" t="s" s="1">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D360" t="s" s="1">
         <v>33</v>
@@ -22654,13 +22657,13 @@
     </row>
     <row r="361">
       <c r="A361" t="s">
+        <v>748</v>
+      </c>
+      <c r="B361" t="s">
         <v>747</v>
       </c>
-      <c r="B361" t="s">
-        <v>746</v>
-      </c>
       <c r="C361" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D361" t="s">
         <v>33</v>
@@ -22678,7 +22681,7 @@
         <v>215</v>
       </c>
       <c r="I361" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="J361" t="s">
         <v>190</v>
@@ -22690,7 +22693,7 @@
         <v>34</v>
       </c>
       <c r="M361" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="N361" t="s">
         <v>47</v>
@@ -22710,13 +22713,13 @@
     </row>
     <row r="362">
       <c r="A362" t="s" s="1">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B362" t="s" s="1">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C362" t="s" s="1">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="D362" t="s" s="1">
         <v>33</v>
@@ -22766,13 +22769,13 @@
     </row>
     <row r="363">
       <c r="A363" t="s" s="1">
+        <v>752</v>
+      </c>
+      <c r="B363" t="s" s="1">
         <v>751</v>
       </c>
-      <c r="B363" t="s" s="1">
-        <v>750</v>
-      </c>
       <c r="C363" t="s" s="1">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="D363" t="s" s="1">
         <v>33</v>
@@ -22822,19 +22825,19 @@
     </row>
     <row r="364">
       <c r="A364" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B364" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C364" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="D364" t="s">
         <v>33</v>
       </c>
       <c r="E364" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="F364" t="s">
         <v>211</v>
@@ -22846,7 +22849,7 @@
         <v>469</v>
       </c>
       <c r="I364" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="J364" t="s">
         <v>101</v>
@@ -22858,7 +22861,7 @@
         <v>34</v>
       </c>
       <c r="M364" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="N364" t="s">
         <v>47</v>
@@ -22867,7 +22870,7 @@
         <v>48</v>
       </c>
       <c r="P364" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="Q364" t="s">
         <v>47</v>
@@ -22878,7 +22881,7 @@
     </row>
     <row r="365">
       <c r="A365" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B365" t="s">
         <v>34</v>
@@ -22890,7 +22893,7 @@
         <v>34</v>
       </c>
       <c r="E365" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="F365" t="s">
         <v>211</v>
@@ -22902,7 +22905,7 @@
         <v>425</v>
       </c>
       <c r="I365" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="J365" t="s">
         <v>178</v>
@@ -22914,7 +22917,7 @@
         <v>34</v>
       </c>
       <c r="M365" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="N365" t="s">
         <v>47</v>
@@ -22923,7 +22926,7 @@
         <v>48</v>
       </c>
       <c r="P365" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="Q365" t="s">
         <v>47</v>
@@ -22934,13 +22937,13 @@
     </row>
     <row r="366">
       <c r="A366" t="s" s="1">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B366" t="s" s="1">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C366" t="s" s="1">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="D366" t="s" s="1">
         <v>33</v>
@@ -22990,13 +22993,13 @@
     </row>
     <row r="367">
       <c r="A367" t="s" s="1">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B367" t="s" s="1">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C367" t="s" s="1">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="D367" t="s" s="1">
         <v>33</v>
@@ -23046,19 +23049,19 @@
     </row>
     <row r="368">
       <c r="A368" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B368" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C368" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D368" t="s">
         <v>33</v>
       </c>
       <c r="E368" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="F368" t="s">
         <v>40</v>
@@ -23067,10 +23070,10 @@
         <v>41</v>
       </c>
       <c r="H368" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="I368" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="J368" t="s">
         <v>685</v>
@@ -23079,10 +23082,10 @@
         <v>229</v>
       </c>
       <c r="L368" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="M368" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="N368" t="s">
         <v>47</v>
@@ -23091,7 +23094,7 @@
         <v>48</v>
       </c>
       <c r="P368" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="Q368" t="s">
         <v>47</v>
@@ -23102,19 +23105,19 @@
     </row>
     <row r="369">
       <c r="A369" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B369" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C369" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D369" t="s">
         <v>33</v>
       </c>
       <c r="E369" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="F369" t="s">
         <v>211</v>
@@ -23126,7 +23129,7 @@
         <v>172</v>
       </c>
       <c r="I369" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="J369" t="s">
         <v>169</v>
@@ -23138,7 +23141,7 @@
         <v>34</v>
       </c>
       <c r="M369" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="N369" t="s">
         <v>47</v>
@@ -23147,7 +23150,7 @@
         <v>48</v>
       </c>
       <c r="P369" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="Q369" t="s">
         <v>47</v>
@@ -23158,13 +23161,13 @@
     </row>
     <row r="370">
       <c r="A370" t="s" s="1">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B370" t="s" s="1">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C370" t="s" s="1">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="D370" t="s" s="1">
         <v>33</v>
@@ -23214,19 +23217,19 @@
     </row>
     <row r="371">
       <c r="A371" t="s">
+        <v>773</v>
+      </c>
+      <c r="B371" t="s">
         <v>772</v>
       </c>
-      <c r="B371" t="s">
-        <v>771</v>
-      </c>
       <c r="C371" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="D371" t="s">
         <v>33</v>
       </c>
       <c r="E371" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="F371" t="s">
         <v>40</v>
@@ -23235,22 +23238,22 @@
         <v>41</v>
       </c>
       <c r="H371" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="I371" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="J371" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="K371" t="s">
         <v>70</v>
       </c>
       <c r="L371" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="M371" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="N371" t="s">
         <v>47</v>
@@ -23259,7 +23262,7 @@
         <v>48</v>
       </c>
       <c r="P371" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="Q371" t="s">
         <v>47</v>
@@ -23270,13 +23273,13 @@
     </row>
     <row r="372">
       <c r="A372" t="s" s="1">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B372" t="s" s="1">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C372" t="s" s="1">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="D372" t="s" s="1">
         <v>33</v>
@@ -23326,13 +23329,13 @@
     </row>
     <row r="373">
       <c r="A373" t="s">
+        <v>781</v>
+      </c>
+      <c r="B373" t="s">
         <v>780</v>
       </c>
-      <c r="B373" t="s">
-        <v>779</v>
-      </c>
       <c r="C373" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="D373" t="s">
         <v>33</v>
@@ -23347,10 +23350,10 @@
         <v>41</v>
       </c>
       <c r="H373" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="I373" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="J373" t="s">
         <v>685</v>
@@ -23359,10 +23362,10 @@
         <v>45</v>
       </c>
       <c r="L373" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="M373" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="N373" t="s">
         <v>47</v>
@@ -23371,7 +23374,7 @@
         <v>48</v>
       </c>
       <c r="P373" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="Q373" t="s">
         <v>47</v>
@@ -23382,13 +23385,13 @@
     </row>
     <row r="374">
       <c r="A374" t="s" s="1">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B374" t="s" s="1">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C374" t="s" s="1">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="D374" t="s" s="1">
         <v>33</v>
@@ -23438,19 +23441,19 @@
     </row>
     <row r="375">
       <c r="A375" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B375" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C375" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="D375" t="s">
         <v>33</v>
       </c>
       <c r="E375" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="F375" t="s">
         <v>40</v>
@@ -23459,22 +23462,22 @@
         <v>41</v>
       </c>
       <c r="H375" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="I375" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="J375" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="K375" t="s">
         <v>134</v>
       </c>
       <c r="L375" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="M375" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="N375" t="s">
         <v>47</v>
@@ -23483,7 +23486,7 @@
         <v>48</v>
       </c>
       <c r="P375" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="Q375" t="s">
         <v>47</v>
@@ -23494,13 +23497,13 @@
     </row>
     <row r="376">
       <c r="A376" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B376" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C376" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D376" t="s">
         <v>33</v>
@@ -23515,22 +23518,22 @@
         <v>41</v>
       </c>
       <c r="H376" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="I376" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="J376" t="s">
         <v>685</v>
       </c>
       <c r="K376" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="L376" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="M376" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="N376" t="s">
         <v>47</v>
@@ -23539,7 +23542,7 @@
         <v>48</v>
       </c>
       <c r="P376" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="Q376" t="s">
         <v>47</v>
@@ -23550,13 +23553,13 @@
     </row>
     <row r="377">
       <c r="A377" t="s" s="1">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B377" t="s" s="1">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C377" t="s" s="1">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="D377" t="s" s="1">
         <v>33</v>
@@ -23606,19 +23609,19 @@
     </row>
     <row r="378">
       <c r="A378" t="s">
+        <v>800</v>
+      </c>
+      <c r="B378" t="s">
         <v>799</v>
       </c>
-      <c r="B378" t="s">
-        <v>798</v>
-      </c>
       <c r="C378" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="D378" t="s">
         <v>33</v>
       </c>
       <c r="E378" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="F378" t="s">
         <v>211</v>
@@ -23630,7 +23633,7 @@
         <v>425</v>
       </c>
       <c r="I378" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="J378" t="s">
         <v>90</v>
@@ -23642,7 +23645,7 @@
         <v>34</v>
       </c>
       <c r="M378" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="N378" t="s">
         <v>47</v>
@@ -23651,7 +23654,7 @@
         <v>48</v>
       </c>
       <c r="P378" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="Q378" t="s">
         <v>47</v>
@@ -23662,7 +23665,7 @@
     </row>
     <row r="379">
       <c r="A379" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B379" t="s">
         <v>34</v>
@@ -23674,7 +23677,7 @@
         <v>34</v>
       </c>
       <c r="E379" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="F379" t="s">
         <v>211</v>
@@ -23683,10 +23686,10 @@
         <v>41</v>
       </c>
       <c r="H379" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I379" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J379" t="s">
         <v>304</v>
@@ -23695,10 +23698,10 @@
         <v>75</v>
       </c>
       <c r="L379" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="M379" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="N379" t="s">
         <v>47</v>
@@ -23707,7 +23710,7 @@
         <v>48</v>
       </c>
       <c r="P379" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="Q379" t="s">
         <v>47</v>
@@ -23718,7 +23721,7 @@
     </row>
     <row r="380">
       <c r="A380" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B380" t="s">
         <v>34</v>
@@ -23730,7 +23733,7 @@
         <v>34</v>
       </c>
       <c r="E380" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="F380" t="s">
         <v>211</v>
@@ -23742,7 +23745,7 @@
         <v>425</v>
       </c>
       <c r="I380" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="J380" t="s">
         <v>58</v>
@@ -23751,10 +23754,10 @@
         <v>202</v>
       </c>
       <c r="L380" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="M380" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="N380" t="s">
         <v>47</v>
@@ -23763,7 +23766,7 @@
         <v>48</v>
       </c>
       <c r="P380" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="Q380" t="s">
         <v>47</v>
@@ -23774,7 +23777,7 @@
     </row>
     <row r="381">
       <c r="A381" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B381" t="s">
         <v>34</v>
@@ -23786,7 +23789,7 @@
         <v>34</v>
       </c>
       <c r="E381" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="F381" t="s">
         <v>211</v>
@@ -23795,10 +23798,10 @@
         <v>41</v>
       </c>
       <c r="H381" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="I381" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="J381" t="s">
         <v>304</v>
@@ -23807,10 +23810,10 @@
         <v>96</v>
       </c>
       <c r="L381" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="M381" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="N381" t="s">
         <v>47</v>
@@ -23819,7 +23822,7 @@
         <v>48</v>
       </c>
       <c r="P381" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="Q381" t="s">
         <v>47</v>
@@ -23830,7 +23833,7 @@
     </row>
     <row r="382">
       <c r="A382" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B382" t="s">
         <v>34</v>
@@ -23842,7 +23845,7 @@
         <v>34</v>
       </c>
       <c r="E382" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="F382" t="s">
         <v>211</v>
@@ -23851,10 +23854,10 @@
         <v>41</v>
       </c>
       <c r="H382" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="I382" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="J382" t="s">
         <v>304</v>
@@ -23863,10 +23866,10 @@
         <v>96</v>
       </c>
       <c r="L382" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="M382" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="N382" t="s">
         <v>47</v>
@@ -23875,7 +23878,7 @@
         <v>48</v>
       </c>
       <c r="P382" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="Q382" t="s">
         <v>47</v>
@@ -23886,7 +23889,7 @@
     </row>
     <row r="383">
       <c r="A383" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B383" t="s">
         <v>34</v>
@@ -23898,7 +23901,7 @@
         <v>34</v>
       </c>
       <c r="E383" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="F383" t="s">
         <v>211</v>
@@ -23907,10 +23910,10 @@
         <v>41</v>
       </c>
       <c r="H383" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="I383" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="J383" t="s">
         <v>58</v>
@@ -23919,10 +23922,10 @@
         <v>202</v>
       </c>
       <c r="L383" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="M383" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="N383" t="s">
         <v>47</v>
@@ -23931,7 +23934,7 @@
         <v>48</v>
       </c>
       <c r="P383" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="Q383" t="s">
         <v>47</v>
@@ -23942,7 +23945,7 @@
     </row>
     <row r="384">
       <c r="A384" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B384" t="s">
         <v>34</v>
@@ -23954,7 +23957,7 @@
         <v>34</v>
       </c>
       <c r="E384" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="F384" t="s">
         <v>211</v>
@@ -23963,10 +23966,10 @@
         <v>41</v>
       </c>
       <c r="H384" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="I384" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="J384" t="s">
         <v>304</v>
@@ -23975,10 +23978,10 @@
         <v>122</v>
       </c>
       <c r="L384" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="M384" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="N384" t="s">
         <v>47</v>
@@ -23987,7 +23990,7 @@
         <v>48</v>
       </c>
       <c r="P384" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="Q384" t="s">
         <v>47</v>
@@ -23998,7 +24001,7 @@
     </row>
     <row r="385">
       <c r="A385" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B385" t="s">
         <v>34</v>
@@ -24010,7 +24013,7 @@
         <v>34</v>
       </c>
       <c r="E385" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="F385" t="s">
         <v>211</v>
@@ -24019,10 +24022,10 @@
         <v>41</v>
       </c>
       <c r="H385" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="I385" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="J385" t="s">
         <v>304</v>
@@ -24031,10 +24034,10 @@
         <v>96</v>
       </c>
       <c r="L385" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="M385" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="N385" t="s">
         <v>47</v>
@@ -24043,7 +24046,7 @@
         <v>48</v>
       </c>
       <c r="P385" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="Q385" t="s">
         <v>47</v>
@@ -24054,13 +24057,13 @@
     </row>
     <row r="386">
       <c r="A386" t="s" s="1">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B386" t="s" s="1">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C386" t="s" s="1">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="D386" t="s" s="1">
         <v>33</v>
@@ -24110,13 +24113,13 @@
     </row>
     <row r="387">
       <c r="A387" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B387" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C387" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D387" t="s">
         <v>33</v>
@@ -24131,10 +24134,10 @@
         <v>41</v>
       </c>
       <c r="H387" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="I387" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="J387" t="s">
         <v>685</v>
@@ -24143,10 +24146,10 @@
         <v>45</v>
       </c>
       <c r="L387" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="M387" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="N387" t="s">
         <v>47</v>
@@ -24155,7 +24158,7 @@
         <v>48</v>
       </c>
       <c r="P387" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="Q387" t="s">
         <v>47</v>
@@ -24166,19 +24169,19 @@
     </row>
     <row r="388">
       <c r="A388" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B388" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C388" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="D388" t="s">
         <v>33</v>
       </c>
       <c r="E388" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="F388" t="s">
         <v>40</v>
@@ -24187,22 +24190,22 @@
         <v>41</v>
       </c>
       <c r="H388" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="I388" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="J388" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="K388" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="L388" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="M388" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="N388" t="s">
         <v>47</v>
@@ -24211,7 +24214,7 @@
         <v>48</v>
       </c>
       <c r="P388" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="Q388" t="s">
         <v>47</v>
@@ -24222,19 +24225,19 @@
     </row>
     <row r="389">
       <c r="A389" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B389" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C389" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="D389" t="s">
         <v>33</v>
       </c>
       <c r="E389" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="F389" t="s">
         <v>40</v>
@@ -24243,10 +24246,10 @@
         <v>41</v>
       </c>
       <c r="H389" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="I389" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="J389" t="s">
         <v>44</v>
@@ -24255,10 +24258,10 @@
         <v>45</v>
       </c>
       <c r="L389" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="M389" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="N389" t="s">
         <v>47</v>
@@ -24267,7 +24270,7 @@
         <v>48</v>
       </c>
       <c r="P389" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="Q389" t="s">
         <v>47</v>
@@ -24278,13 +24281,13 @@
     </row>
     <row r="390">
       <c r="A390" t="s" s="1">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B390" t="s" s="1">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C390" t="s" s="1">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="D390" t="s" s="1">
         <v>33</v>
@@ -24334,13 +24337,13 @@
     </row>
     <row r="391">
       <c r="A391" t="s">
+        <v>850</v>
+      </c>
+      <c r="B391" t="s">
         <v>849</v>
       </c>
-      <c r="B391" t="s">
-        <v>848</v>
-      </c>
       <c r="C391" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="D391" t="s">
         <v>33</v>
@@ -24355,10 +24358,10 @@
         <v>41</v>
       </c>
       <c r="H391" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="I391" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="J391" t="s">
         <v>335</v>
@@ -24367,10 +24370,10 @@
         <v>45</v>
       </c>
       <c r="L391" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="M391" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="N391" t="s">
         <v>47</v>
@@ -24379,7 +24382,7 @@
         <v>48</v>
       </c>
       <c r="P391" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="Q391" t="s">
         <v>47</v>
@@ -24390,7 +24393,7 @@
     </row>
     <row r="392">
       <c r="A392" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B392" t="s">
         <v>34</v>
@@ -24402,7 +24405,7 @@
         <v>34</v>
       </c>
       <c r="E392" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="F392" t="s">
         <v>211</v>
@@ -24411,10 +24414,10 @@
         <v>41</v>
       </c>
       <c r="H392" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="I392" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="J392" t="s">
         <v>304</v>
@@ -24426,7 +24429,7 @@
         <v>34</v>
       </c>
       <c r="M392" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="N392" t="s">
         <v>47</v>
@@ -24435,7 +24438,7 @@
         <v>48</v>
       </c>
       <c r="P392" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="Q392" t="s">
         <v>47</v>
@@ -24446,7 +24449,7 @@
     </row>
     <row r="393">
       <c r="A393" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B393" t="s">
         <v>34</v>
@@ -24458,7 +24461,7 @@
         <v>34</v>
       </c>
       <c r="E393" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="F393" t="s">
         <v>40</v>
@@ -24467,22 +24470,22 @@
         <v>41</v>
       </c>
       <c r="H393" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="I393" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="J393" t="s">
         <v>335</v>
       </c>
       <c r="K393" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="L393" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="M393" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="N393" t="s">
         <v>47</v>
@@ -24491,7 +24494,7 @@
         <v>48</v>
       </c>
       <c r="P393" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="Q393" t="s">
         <v>47</v>
@@ -24502,7 +24505,7 @@
     </row>
     <row r="394">
       <c r="A394" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B394" t="s">
         <v>34</v>
@@ -24523,22 +24526,22 @@
         <v>41</v>
       </c>
       <c r="H394" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="I394" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="J394" t="s">
         <v>335</v>
       </c>
       <c r="K394" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="L394" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="M394" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="N394" t="s">
         <v>47</v>
@@ -24547,7 +24550,7 @@
         <v>48</v>
       </c>
       <c r="P394" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="Q394" t="s">
         <v>47</v>
@@ -24558,7 +24561,7 @@
     </row>
     <row r="395">
       <c r="A395" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B395" t="s">
         <v>34</v>
@@ -24570,7 +24573,7 @@
         <v>34</v>
       </c>
       <c r="E395" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="F395" t="s">
         <v>40</v>
@@ -24579,10 +24582,10 @@
         <v>41</v>
       </c>
       <c r="H395" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="I395" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="J395" t="s">
         <v>101</v>
@@ -24591,10 +24594,10 @@
         <v>45</v>
       </c>
       <c r="L395" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="M395" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="N395" t="s">
         <v>47</v>
@@ -24603,7 +24606,7 @@
         <v>48</v>
       </c>
       <c r="P395" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="Q395" t="s">
         <v>47</v>
@@ -24614,13 +24617,13 @@
     </row>
     <row r="396">
       <c r="A396" t="s" s="1">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B396" t="s" s="1">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C396" t="s" s="1">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="D396" t="s" s="1">
         <v>33</v>
@@ -24670,19 +24673,19 @@
     </row>
     <row r="397">
       <c r="A397" t="s">
+        <v>868</v>
+      </c>
+      <c r="B397" t="s">
         <v>867</v>
       </c>
-      <c r="B397" t="s">
-        <v>866</v>
-      </c>
       <c r="C397" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="D397" t="s">
         <v>33</v>
       </c>
       <c r="E397" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="F397" t="s">
         <v>211</v>
@@ -24691,22 +24694,22 @@
         <v>41</v>
       </c>
       <c r="H397" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="I397" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="J397" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="K397" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="L397" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="M397" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="N397" t="s">
         <v>47</v>
@@ -24715,7 +24718,7 @@
         <v>48</v>
       </c>
       <c r="P397" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="Q397" t="s">
         <v>47</v>
@@ -24726,13 +24729,13 @@
     </row>
     <row r="398">
       <c r="A398" t="s" s="1">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B398" t="s" s="1">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C398" t="s" s="1">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D398" t="s" s="1">
         <v>33</v>
@@ -24782,13 +24785,13 @@
     </row>
     <row r="399">
       <c r="A399" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B399" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C399" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D399" t="s">
         <v>33</v>
@@ -24803,10 +24806,10 @@
         <v>41</v>
       </c>
       <c r="H399" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="I399" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="J399" t="s">
         <v>685</v>
@@ -24815,10 +24818,10 @@
         <v>45</v>
       </c>
       <c r="L399" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="M399" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="N399" t="s">
         <v>47</v>
@@ -24827,7 +24830,7 @@
         <v>48</v>
       </c>
       <c r="P399" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="Q399" t="s">
         <v>47</v>
@@ -24838,7 +24841,7 @@
     </row>
     <row r="400">
       <c r="A400" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B400" t="s">
         <v>34</v>
@@ -24850,7 +24853,7 @@
         <v>34</v>
       </c>
       <c r="E400" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="F400" t="s">
         <v>211</v>
@@ -24859,10 +24862,10 @@
         <v>41</v>
       </c>
       <c r="H400" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="I400" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="J400" t="s">
         <v>58</v>
@@ -24871,10 +24874,10 @@
         <v>202</v>
       </c>
       <c r="L400" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="M400" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="N400" t="s">
         <v>47</v>
@@ -24883,7 +24886,7 @@
         <v>48</v>
       </c>
       <c r="P400" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="Q400" t="s">
         <v>47</v>
@@ -24894,19 +24897,19 @@
     </row>
     <row r="401">
       <c r="A401" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B401" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="C401" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="D401" t="s">
         <v>33</v>
       </c>
       <c r="E401" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="F401" t="s">
         <v>211</v>
@@ -24915,10 +24918,10 @@
         <v>41</v>
       </c>
       <c r="H401" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="I401" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="J401" t="s">
         <v>85</v>
@@ -24927,10 +24930,10 @@
         <v>202</v>
       </c>
       <c r="L401" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="M401" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="N401" t="s">
         <v>47</v>
@@ -24939,7 +24942,7 @@
         <v>48</v>
       </c>
       <c r="P401" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="Q401" t="s">
         <v>47</v>
@@ -24950,13 +24953,13 @@
     </row>
     <row r="402">
       <c r="A402" t="s" s="1">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B402" t="s" s="1">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C402" t="s" s="1">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="D402" t="s" s="1">
         <v>33</v>
@@ -25006,13 +25009,13 @@
     </row>
     <row r="403">
       <c r="A403" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B403" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C403" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="D403" t="s">
         <v>33</v>
@@ -25027,10 +25030,10 @@
         <v>41</v>
       </c>
       <c r="H403" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="I403" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="J403" t="s">
         <v>190</v>
@@ -25039,10 +25042,10 @@
         <v>202</v>
       </c>
       <c r="L403" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="M403" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="N403" t="s">
         <v>47</v>
@@ -25051,7 +25054,7 @@
         <v>48</v>
       </c>
       <c r="P403" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="Q403" t="s">
         <v>47</v>
@@ -25062,19 +25065,19 @@
     </row>
     <row r="404">
       <c r="A404" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B404" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C404" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="D404" t="s">
         <v>33</v>
       </c>
       <c r="E404" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="F404" t="s">
         <v>40</v>
@@ -25083,10 +25086,10 @@
         <v>41</v>
       </c>
       <c r="H404" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="I404" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="J404" t="s">
         <v>178</v>
@@ -25095,10 +25098,10 @@
         <v>178</v>
       </c>
       <c r="L404" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="M404" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="N404" t="s">
         <v>47</v>
@@ -25107,7 +25110,7 @@
         <v>48</v>
       </c>
       <c r="P404" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="Q404" t="s">
         <v>47</v>
@@ -25118,7 +25121,7 @@
     </row>
     <row r="405">
       <c r="A405" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B405" t="s">
         <v>34</v>
@@ -25139,10 +25142,10 @@
         <v>41</v>
       </c>
       <c r="H405" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="I405" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="J405" t="s">
         <v>685</v>
@@ -25151,10 +25154,10 @@
         <v>45</v>
       </c>
       <c r="L405" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="M405" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="N405" t="s">
         <v>47</v>
@@ -25163,7 +25166,7 @@
         <v>48</v>
       </c>
       <c r="P405" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="Q405" t="s">
         <v>47</v>
@@ -25174,13 +25177,13 @@
     </row>
     <row r="406">
       <c r="A406" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B406" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="C406" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="D406" t="s">
         <v>33</v>
@@ -25195,10 +25198,10 @@
         <v>41</v>
       </c>
       <c r="H406" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="I406" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="J406" t="s">
         <v>101</v>
@@ -25207,10 +25210,10 @@
         <v>45</v>
       </c>
       <c r="L406" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="M406" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="N406" t="s">
         <v>47</v>
@@ -25219,7 +25222,7 @@
         <v>48</v>
       </c>
       <c r="P406" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="Q406" t="s">
         <v>47</v>
@@ -25230,13 +25233,13 @@
     </row>
     <row r="407">
       <c r="A407" t="s" s="1">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B407" t="s" s="1">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C407" t="s" s="1">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="D407" t="s" s="1">
         <v>33</v>
@@ -25286,13 +25289,13 @@
     </row>
     <row r="408">
       <c r="A408" t="s" s="1">
+        <v>910</v>
+      </c>
+      <c r="B408" t="s" s="1">
         <v>909</v>
       </c>
-      <c r="B408" t="s" s="1">
-        <v>908</v>
-      </c>
       <c r="C408" t="s" s="1">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="D408" t="s" s="1">
         <v>33</v>
@@ -25342,19 +25345,19 @@
     </row>
     <row r="409">
       <c r="A409" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B409" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C409" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="D409" t="s">
         <v>33</v>
       </c>
       <c r="E409" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="F409" t="s">
         <v>40</v>
@@ -25363,22 +25366,22 @@
         <v>41</v>
       </c>
       <c r="H409" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="I409" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="J409" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="K409" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="L409" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="M409" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="N409" t="s">
         <v>47</v>
@@ -25387,7 +25390,7 @@
         <v>48</v>
       </c>
       <c r="P409" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="Q409" t="s">
         <v>47</v>
@@ -25398,13 +25401,13 @@
     </row>
     <row r="410">
       <c r="A410" t="s" s="1">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B410" t="s" s="1">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C410" t="s" s="1">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D410" t="s" s="1">
         <v>33</v>
@@ -25454,13 +25457,13 @@
     </row>
     <row r="411">
       <c r="A411" t="s" s="1">
+        <v>918</v>
+      </c>
+      <c r="B411" t="s" s="1">
         <v>917</v>
       </c>
-      <c r="B411" t="s" s="1">
-        <v>916</v>
-      </c>
       <c r="C411" t="s" s="1">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D411" t="s" s="1">
         <v>33</v>
@@ -25510,13 +25513,13 @@
     </row>
     <row r="412">
       <c r="A412" t="s" s="1">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B412" t="s" s="1">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C412" t="s" s="1">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D412" t="s" s="1">
         <v>33</v>
@@ -25566,19 +25569,19 @@
     </row>
     <row r="413">
       <c r="A413" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B413" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C413" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D413" t="s">
         <v>33</v>
       </c>
       <c r="E413" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="F413" t="s">
         <v>211</v>
@@ -25587,10 +25590,10 @@
         <v>41</v>
       </c>
       <c r="H413" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="I413" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="J413" t="s">
         <v>304</v>
@@ -25602,7 +25605,7 @@
         <v>34</v>
       </c>
       <c r="M413" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="N413" t="s">
         <v>47</v>
@@ -25611,7 +25614,7 @@
         <v>48</v>
       </c>
       <c r="P413" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="Q413" t="s">
         <v>47</v>
@@ -25622,13 +25625,13 @@
     </row>
     <row r="414">
       <c r="A414" t="s" s="1">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B414" t="s" s="1">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="C414" t="s" s="1">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D414" t="s" s="1">
         <v>33</v>
@@ -25678,13 +25681,13 @@
     </row>
     <row r="415">
       <c r="A415" t="s" s="1">
+        <v>926</v>
+      </c>
+      <c r="B415" t="s" s="1">
         <v>925</v>
       </c>
-      <c r="B415" t="s" s="1">
-        <v>924</v>
-      </c>
       <c r="C415" t="s" s="1">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D415" t="s" s="1">
         <v>33</v>
@@ -25734,13 +25737,13 @@
     </row>
     <row r="416">
       <c r="A416" t="s" s="1">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B416" t="s" s="1">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="C416" t="s" s="1">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D416" t="s" s="1">
         <v>33</v>
@@ -25790,13 +25793,13 @@
     </row>
     <row r="417">
       <c r="A417" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B417" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="C417" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D417" t="s">
         <v>33</v>
@@ -25811,10 +25814,10 @@
         <v>41</v>
       </c>
       <c r="H417" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="I417" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="J417" t="s">
         <v>119</v>
@@ -25823,10 +25826,10 @@
         <v>119</v>
       </c>
       <c r="L417" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="M417" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="N417" t="s">
         <v>47</v>
@@ -25835,7 +25838,7 @@
         <v>130</v>
       </c>
       <c r="P417" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="Q417" t="s">
         <v>47</v>
@@ -25846,7 +25849,7 @@
     </row>
     <row r="418">
       <c r="A418" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B418" t="s">
         <v>34</v>
@@ -25867,10 +25870,10 @@
         <v>41</v>
       </c>
       <c r="H418" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="I418" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="J418" t="s">
         <v>80</v>
@@ -25879,10 +25882,10 @@
         <v>80</v>
       </c>
       <c r="L418" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="M418" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="N418" t="s">
         <v>47</v>
@@ -25891,7 +25894,7 @@
         <v>255</v>
       </c>
       <c r="P418" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="Q418" t="s">
         <v>47</v>
@@ -25902,7 +25905,7 @@
     </row>
     <row r="419">
       <c r="A419" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B419" t="s">
         <v>34</v>
@@ -25923,10 +25926,10 @@
         <v>41</v>
       </c>
       <c r="H419" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="I419" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="J419" t="s">
         <v>113</v>
@@ -25935,10 +25938,10 @@
         <v>113</v>
       </c>
       <c r="L419" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="M419" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="N419" t="s">
         <v>47</v>
@@ -25947,7 +25950,7 @@
         <v>114</v>
       </c>
       <c r="P419" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="Q419" t="s">
         <v>47</v>
@@ -25958,7 +25961,7 @@
     </row>
     <row r="420">
       <c r="A420" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B420" t="s">
         <v>34</v>
@@ -25979,10 +25982,10 @@
         <v>41</v>
       </c>
       <c r="H420" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="I420" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="J420" t="s">
         <v>58</v>
@@ -25991,10 +25994,10 @@
         <v>58</v>
       </c>
       <c r="L420" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="M420" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="N420" t="s">
         <v>47</v>
@@ -26003,7 +26006,7 @@
         <v>105</v>
       </c>
       <c r="P420" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="Q420" t="s">
         <v>47</v>
@@ -26014,7 +26017,7 @@
     </row>
     <row r="421">
       <c r="A421" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B421" t="s">
         <v>34</v>
@@ -26035,10 +26038,10 @@
         <v>41</v>
       </c>
       <c r="H421" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="I421" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="J421" t="s">
         <v>90</v>
@@ -26047,10 +26050,10 @@
         <v>90</v>
       </c>
       <c r="L421" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="M421" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="N421" t="s">
         <v>47</v>
@@ -26059,7 +26062,7 @@
         <v>310</v>
       </c>
       <c r="P421" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="Q421" t="s">
         <v>47</v>
@@ -26070,7 +26073,7 @@
     </row>
     <row r="422">
       <c r="A422" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B422" t="s">
         <v>34</v>
@@ -26091,10 +26094,10 @@
         <v>41</v>
       </c>
       <c r="H422" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="I422" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="J422" t="s">
         <v>119</v>
@@ -26103,10 +26106,10 @@
         <v>119</v>
       </c>
       <c r="L422" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="M422" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="N422" t="s">
         <v>47</v>
@@ -26115,7 +26118,7 @@
         <v>250</v>
       </c>
       <c r="P422" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="Q422" t="s">
         <v>47</v>
@@ -26126,7 +26129,7 @@
     </row>
     <row r="423">
       <c r="A423" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B423" t="s">
         <v>34</v>
@@ -26147,10 +26150,10 @@
         <v>41</v>
       </c>
       <c r="H423" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="I423" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="J423" t="s">
         <v>90</v>
@@ -26159,10 +26162,10 @@
         <v>229</v>
       </c>
       <c r="L423" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="M423" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="N423" t="s">
         <v>47</v>
@@ -26171,7 +26174,7 @@
         <v>91</v>
       </c>
       <c r="P423" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="Q423" t="s">
         <v>47</v>
@@ -26182,7 +26185,7 @@
     </row>
     <row r="424">
       <c r="A424" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B424" t="s">
         <v>34</v>
@@ -26203,10 +26206,10 @@
         <v>41</v>
       </c>
       <c r="H424" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="I424" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="J424" t="s">
         <v>101</v>
@@ -26215,10 +26218,10 @@
         <v>101</v>
       </c>
       <c r="L424" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="M424" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="N424" t="s">
         <v>47</v>
@@ -26227,7 +26230,7 @@
         <v>102</v>
       </c>
       <c r="P424" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="Q424" t="s">
         <v>47</v>
@@ -26238,7 +26241,7 @@
     </row>
     <row r="425">
       <c r="A425" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B425" t="s">
         <v>34</v>
@@ -26259,10 +26262,10 @@
         <v>41</v>
       </c>
       <c r="H425" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="I425" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="J425" t="s">
         <v>80</v>
@@ -26271,10 +26274,10 @@
         <v>80</v>
       </c>
       <c r="L425" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="M425" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="N425" t="s">
         <v>47</v>
@@ -26283,7 +26286,7 @@
         <v>247</v>
       </c>
       <c r="P425" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="Q425" t="s">
         <v>47</v>
@@ -26294,7 +26297,7 @@
     </row>
     <row r="426">
       <c r="A426" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B426" t="s">
         <v>34</v>
@@ -26315,10 +26318,10 @@
         <v>41</v>
       </c>
       <c r="H426" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="I426" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="J426" t="s">
         <v>119</v>
@@ -26327,10 +26330,10 @@
         <v>119</v>
       </c>
       <c r="L426" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="M426" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="N426" t="s">
         <v>47</v>
@@ -26339,7 +26342,7 @@
         <v>156</v>
       </c>
       <c r="P426" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="Q426" t="s">
         <v>47</v>
@@ -26350,7 +26353,7 @@
     </row>
     <row r="427">
       <c r="A427" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B427" t="s">
         <v>34</v>
@@ -26371,10 +26374,10 @@
         <v>41</v>
       </c>
       <c r="H427" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="I427" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="J427" t="s">
         <v>126</v>
@@ -26383,10 +26386,10 @@
         <v>119</v>
       </c>
       <c r="L427" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="M427" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="N427" t="s">
         <v>47</v>
@@ -26395,7 +26398,7 @@
         <v>436</v>
       </c>
       <c r="P427" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="Q427" t="s">
         <v>47</v>
@@ -26406,7 +26409,7 @@
     </row>
     <row r="428">
       <c r="A428" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B428" t="s">
         <v>34</v>
@@ -26427,10 +26430,10 @@
         <v>41</v>
       </c>
       <c r="H428" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="I428" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="J428" t="s">
         <v>126</v>
@@ -26439,10 +26442,10 @@
         <v>119</v>
       </c>
       <c r="L428" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="M428" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="N428" t="s">
         <v>47</v>
@@ -26451,7 +26454,7 @@
         <v>466</v>
       </c>
       <c r="P428" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="Q428" t="s">
         <v>47</v>
@@ -26462,7 +26465,7 @@
     </row>
     <row r="429">
       <c r="A429" t="s" s="1">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B429" t="s" s="1">
         <v>32</v>
@@ -26518,7 +26521,7 @@
     </row>
     <row r="430">
       <c r="A430" t="s" s="1">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B430" t="s" s="1">
         <v>32</v>
@@ -26574,7 +26577,7 @@
     </row>
     <row r="431">
       <c r="A431" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B431" t="s">
         <v>32</v>
@@ -26630,7 +26633,7 @@
     </row>
     <row r="432">
       <c r="A432" t="s" s="1">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B432" t="s" s="1">
         <v>61</v>
@@ -26686,7 +26689,7 @@
     </row>
     <row r="433">
       <c r="A433" t="s" s="1">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B433" t="s" s="1">
         <v>61</v>
@@ -26742,7 +26745,7 @@
     </row>
     <row r="434">
       <c r="A434" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B434" t="s">
         <v>61</v>
@@ -26798,7 +26801,7 @@
     </row>
     <row r="435">
       <c r="A435" t="s" s="1">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B435" t="s" s="1">
         <v>183</v>
@@ -26854,7 +26857,7 @@
     </row>
     <row r="436">
       <c r="A436" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B436" t="s">
         <v>183</v>
@@ -26910,13 +26913,13 @@
     </row>
     <row r="437">
       <c r="A437" t="s" s="1">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B437" t="s" s="1">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="C437" t="s" s="1">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="D437" t="s" s="1">
         <v>33</v>
@@ -26966,7 +26969,7 @@
     </row>
     <row r="438">
       <c r="A438" t="s" s="1">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B438" t="s" s="1">
         <v>205</v>
@@ -27022,7 +27025,7 @@
     </row>
     <row r="439">
       <c r="A439" t="s" s="1">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B439" t="s" s="1">
         <v>207</v>
@@ -27078,7 +27081,7 @@
     </row>
     <row r="440">
       <c r="A440" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B440" t="s">
         <v>207</v>
@@ -27134,7 +27137,7 @@
     </row>
     <row r="441">
       <c r="A441" t="s" s="1">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B441" t="s" s="1">
         <v>345</v>
@@ -27190,7 +27193,7 @@
     </row>
     <row r="442">
       <c r="A442" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B442" t="s">
         <v>345</v>
@@ -27246,13 +27249,13 @@
     </row>
     <row r="443">
       <c r="A443" t="s" s="1">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B443" t="s" s="1">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="C443" t="s" s="1">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="D443" t="s" s="1">
         <v>33</v>
@@ -27302,13 +27305,13 @@
     </row>
     <row r="444">
       <c r="A444" t="s" s="1">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B444" t="s" s="1">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="C444" t="s" s="1">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="D444" t="s" s="1">
         <v>33</v>
@@ -27358,7 +27361,7 @@
     </row>
     <row r="445">
       <c r="A445" t="s" s="1">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B445" t="s" s="1">
         <v>418</v>
@@ -27414,7 +27417,7 @@
     </row>
     <row r="446">
       <c r="A446" t="s" s="1">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B446" t="s" s="1">
         <v>420</v>
@@ -27470,7 +27473,7 @@
     </row>
     <row r="447">
       <c r="A447" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B447" t="s">
         <v>420</v>
@@ -27526,7 +27529,7 @@
     </row>
     <row r="448">
       <c r="A448" t="s" s="1">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B448" t="s" s="1">
         <v>562</v>
@@ -27582,7 +27585,7 @@
     </row>
     <row r="449">
       <c r="A449" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B449" t="s">
         <v>562</v>
@@ -27638,7 +27641,7 @@
     </row>
     <row r="450">
       <c r="A450" t="s" s="1">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B450" t="s" s="1">
         <v>568</v>
@@ -27694,7 +27697,7 @@
     </row>
     <row r="451">
       <c r="A451" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B451" t="s">
         <v>570</v>
@@ -27750,7 +27753,7 @@
     </row>
     <row r="452">
       <c r="A452" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B452" t="s">
         <v>663</v>
@@ -27806,7 +27809,7 @@
     </row>
     <row r="453">
       <c r="A453" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B453" t="s">
         <v>670</v>
@@ -27862,7 +27865,7 @@
     </row>
     <row r="454">
       <c r="A454" t="s" s="1">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B454" t="s" s="1">
         <v>688</v>
@@ -27918,7 +27921,7 @@
     </row>
     <row r="455">
       <c r="A455" t="s" s="1">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B455" t="s" s="1">
         <v>690</v>
@@ -27974,7 +27977,7 @@
     </row>
     <row r="456">
       <c r="A456" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B456" t="s">
         <v>692</v>
@@ -28030,7 +28033,7 @@
     </row>
     <row r="457">
       <c r="A457" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B457" t="s">
         <v>698</v>
@@ -28086,13 +28089,13 @@
     </row>
     <row r="458">
       <c r="A458" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B458" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C458" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D458" t="s">
         <v>33</v>
@@ -28142,13 +28145,13 @@
     </row>
     <row r="459">
       <c r="A459" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B459" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C459" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D459" t="s">
         <v>33</v>
@@ -28198,13 +28201,13 @@
     </row>
     <row r="460">
       <c r="A460" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B460" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C460" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="D460" t="s">
         <v>33</v>
@@ -28254,13 +28257,13 @@
     </row>
     <row r="461">
       <c r="A461" t="s" s="1">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B461" t="s" s="1">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C461" t="s" s="1">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="D461" t="s" s="1">
         <v>33</v>
@@ -28310,13 +28313,13 @@
     </row>
     <row r="462">
       <c r="A462" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B462" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C462" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="D462" t="s">
         <v>33</v>
@@ -28366,13 +28369,13 @@
     </row>
     <row r="463">
       <c r="A463" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B463" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C463" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="D463" t="s">
         <v>33</v>
@@ -28422,13 +28425,13 @@
     </row>
     <row r="464">
       <c r="A464" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B464" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C464" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="D464" t="s">
         <v>33</v>
@@ -28478,13 +28481,13 @@
     </row>
     <row r="465">
       <c r="A465" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B465" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C465" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="D465" t="s">
         <v>33</v>
@@ -28534,13 +28537,13 @@
     </row>
     <row r="466">
       <c r="A466" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B466" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C466" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="D466" t="s">
         <v>33</v>
@@ -28590,13 +28593,13 @@
     </row>
     <row r="467">
       <c r="A467" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B467" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C467" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="D467" t="s">
         <v>33</v>
@@ -28646,13 +28649,13 @@
     </row>
     <row r="468">
       <c r="A468" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B468" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C468" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="D468" t="s">
         <v>33</v>
@@ -28702,13 +28705,13 @@
     </row>
     <row r="469">
       <c r="A469" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B469" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C469" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="D469" t="s">
         <v>33</v>
@@ -28758,13 +28761,13 @@
     </row>
     <row r="470">
       <c r="A470" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="B470" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C470" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D470" t="s">
         <v>33</v>
@@ -28814,13 +28817,13 @@
     </row>
     <row r="471">
       <c r="A471" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B471" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C471" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="D471" t="s">
         <v>33</v>
@@ -28870,13 +28873,13 @@
     </row>
     <row r="472">
       <c r="A472" t="s" s="1">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B472" t="s" s="1">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C472" t="s" s="1">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="D472" t="s" s="1">
         <v>33</v>
@@ -28926,13 +28929,13 @@
     </row>
     <row r="473">
       <c r="A473" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B473" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C473" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="D473" t="s">
         <v>33</v>
@@ -28982,13 +28985,13 @@
     </row>
     <row r="474">
       <c r="A474" t="s" s="1">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B474" t="s" s="1">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="C474" t="s" s="1">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="D474" t="s" s="1">
         <v>33</v>
@@ -29038,13 +29041,13 @@
     </row>
     <row r="475">
       <c r="A475" t="s" s="1">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B475" t="s" s="1">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="C475" t="s" s="1">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="D475" t="s" s="1">
         <v>33</v>
@@ -29094,13 +29097,13 @@
     </row>
     <row r="476">
       <c r="A476" t="s" s="1">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B476" t="s" s="1">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C476" t="s" s="1">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D476" t="s" s="1">
         <v>33</v>
@@ -29150,13 +29153,13 @@
     </row>
     <row r="477">
       <c r="A477" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B477" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C477" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D477" t="s">
         <v>33</v>
@@ -29206,13 +29209,13 @@
     </row>
     <row r="478">
       <c r="A478" t="s" s="1">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B478" t="s" s="1">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="C478" t="s" s="1">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D478" t="s" s="1">
         <v>33</v>
@@ -29262,13 +29265,13 @@
     </row>
     <row r="479">
       <c r="A479" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B479" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="C479" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D479" t="s">
         <v>33</v>
@@ -29318,13 +29321,13 @@
     </row>
     <row r="480">
       <c r="A480" t="s" s="1">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B480" t="s" s="1">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C480" t="s" s="1">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="D480" t="s" s="1">
         <v>33</v>
@@ -29374,13 +29377,13 @@
     </row>
     <row r="481">
       <c r="A481" t="s" s="1">
+        <v>1002</v>
+      </c>
+      <c r="B481" t="s" s="1">
         <v>1001</v>
       </c>
-      <c r="B481" t="s" s="1">
-        <v>1000</v>
-      </c>
       <c r="C481" t="s" s="1">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="D481" t="s" s="1">
         <v>33</v>
@@ -29430,13 +29433,13 @@
     </row>
     <row r="482">
       <c r="A482" t="s" s="1">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B482" t="s" s="1">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="C482" t="s" s="1">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="D482" t="s" s="1">
         <v>33</v>
@@ -29486,7 +29489,7 @@
     </row>
     <row r="483">
       <c r="A483" t="s" s="1">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B483" t="s" s="1">
         <v>61</v>
@@ -29542,13 +29545,13 @@
     </row>
     <row r="484">
       <c r="A484" t="s" s="1">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B484" t="s" s="1">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C484" t="s" s="1">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="D484" t="s" s="1">
         <v>33</v>
@@ -29598,7 +29601,7 @@
     </row>
     <row r="485">
       <c r="A485" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B485" t="s">
         <v>183</v>
@@ -29654,7 +29657,7 @@
     </row>
     <row r="486">
       <c r="A486" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B486" t="s">
         <v>205</v>
@@ -29710,7 +29713,7 @@
     </row>
     <row r="487">
       <c r="A487" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B487" t="s">
         <v>418</v>
@@ -29766,13 +29769,13 @@
     </row>
     <row r="488">
       <c r="A488" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B488" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="C488" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D488" t="s">
         <v>33</v>
@@ -29822,13 +29825,13 @@
     </row>
     <row r="489">
       <c r="A489" t="s" s="1">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B489" t="s" s="1">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="C489" t="s" s="1">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="D489" t="s" s="1">
         <v>33</v>
@@ -29878,7 +29881,7 @@
     </row>
     <row r="490">
       <c r="A490" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B490" t="s">
         <v>688</v>
@@ -29934,13 +29937,13 @@
     </row>
     <row r="491">
       <c r="A491" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="B491" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C491" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D491" t="s">
         <v>33</v>
@@ -29990,7 +29993,7 @@
     </row>
     <row r="492">
       <c r="A492" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B492" t="s">
         <v>61</v>
@@ -30046,13 +30049,13 @@
     </row>
     <row r="493">
       <c r="A493" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B493" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="C493" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="D493" t="s">
         <v>33</v>
@@ -30102,13 +30105,13 @@
     </row>
     <row r="494">
       <c r="A494" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B494" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="C494" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="D494" t="s">
         <v>33</v>
@@ -30158,7 +30161,7 @@
     </row>
     <row r="495">
       <c r="A495" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="B495" t="s">
         <v>207</v>
@@ -30214,7 +30217,7 @@
     </row>
     <row r="496">
       <c r="A496" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B496" t="s">
         <v>420</v>
@@ -30270,7 +30273,7 @@
     </row>
     <row r="497">
       <c r="A497" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="B497" t="s">
         <v>690</v>
@@ -30326,13 +30329,13 @@
     </row>
     <row r="498">
       <c r="A498" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B498" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C498" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="D498" t="s">
         <v>33</v>
@@ -30382,7 +30385,7 @@
     </row>
     <row r="499">
       <c r="A499" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="B499" t="s">
         <v>183</v>
@@ -30438,13 +30441,13 @@
     </row>
     <row r="500">
       <c r="A500" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B500" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="C500" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="D500" t="s">
         <v>33</v>
@@ -30494,13 +30497,13 @@
     </row>
     <row r="501">
       <c r="A501" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B501" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="C501" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="D501" t="s">
         <v>33</v>
@@ -30550,13 +30553,13 @@
     </row>
     <row r="502">
       <c r="A502" t="s" s="1">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B502" t="s" s="1">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="C502" t="s" s="1">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="D502" t="s" s="1">
         <v>33</v>
@@ -30606,16 +30609,16 @@
     </row>
     <row r="503">
       <c r="A503" t="s" s="1">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B503" t="s" s="1">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="C503" t="s" s="1">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="D503" t="s" s="1">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="E503" t="s" s="1">
         <v>34</v>
@@ -30662,16 +30665,16 @@
     </row>
     <row r="504">
       <c r="A504" t="s" s="1">
+        <v>1032</v>
+      </c>
+      <c r="B504" t="s" s="1">
+        <v>1033</v>
+      </c>
+      <c r="C504" t="s" s="1">
+        <v>1033</v>
+      </c>
+      <c r="D504" t="s" s="1">
         <v>1031</v>
-      </c>
-      <c r="B504" t="s" s="1">
-        <v>1032</v>
-      </c>
-      <c r="C504" t="s" s="1">
-        <v>1032</v>
-      </c>
-      <c r="D504" t="s" s="1">
-        <v>1030</v>
       </c>
       <c r="E504" t="s" s="1">
         <v>34</v>
@@ -30718,16 +30721,16 @@
     </row>
     <row r="505">
       <c r="A505" t="s" s="1">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B505" t="s" s="1">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="C505" t="s" s="1">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="D505" t="s" s="1">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="E505" t="s" s="1">
         <v>34</v>
@@ -30774,13 +30777,13 @@
     </row>
     <row r="506">
       <c r="A506" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B506" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="C506" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="D506" t="s">
         <v>33</v>
@@ -30830,31 +30833,31 @@
     </row>
     <row r="507">
       <c r="A507" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B507" t="s">
         <v>1037</v>
       </c>
-      <c r="B507" t="s">
-        <v>1036</v>
-      </c>
       <c r="C507" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="D507" t="s">
         <v>33</v>
       </c>
       <c r="E507" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="F507" t="s">
         <v>93</v>
       </c>
       <c r="G507" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="H507" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="I507" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="J507" t="s">
         <v>90</v>
@@ -30863,10 +30866,10 @@
         <v>90</v>
       </c>
       <c r="L507" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="M507" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="N507" t="s">
         <v>47</v>
@@ -30875,7 +30878,7 @@
         <v>48</v>
       </c>
       <c r="P507" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="Q507" t="s">
         <v>47</v>
@@ -30886,7 +30889,7 @@
     </row>
     <row r="508">
       <c r="A508" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B508" t="s">
         <v>34</v>
@@ -30898,7 +30901,7 @@
         <v>34</v>
       </c>
       <c r="E508" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="F508" t="s">
         <v>211</v>
@@ -30907,10 +30910,10 @@
         <v>41</v>
       </c>
       <c r="H508" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="I508" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="J508" t="s">
         <v>70</v>
@@ -30922,7 +30925,7 @@
         <v>34</v>
       </c>
       <c r="M508" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="N508" t="s">
         <v>47</v>
@@ -30931,7 +30934,7 @@
         <v>48</v>
       </c>
       <c r="P508" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="Q508" t="s">
         <v>47</v>

--- a/xlsx/dre/DRE_02_2026.xlsx
+++ b/xlsx/dre/DRE_02_2026.xlsx
@@ -888,25 +888,36 @@
     <t>R$ 5.432,14</t>
   </si>
   <si>
-    <t>East Glass- R t de Andrade Comercio E Servicos</t>
-  </si>
-  <si>
-    <t>R$  1.886,73</t>
-  </si>
-  <si>
-    <t>575/1</t>
-  </si>
-  <si>
-    <t>FERRAGENS FLORESTA EIRELI EPP</t>
-  </si>
-  <si>
-    <t>R$  256,50</t>
-  </si>
-  <si>
-    <t>18/03/26</t>
-  </si>
-  <si>
-    <t>estoque</t>
+    <t>9/2</t>
+  </si>
+  <si>
+    <t>R$  91,87</t>
+  </si>
+  <si>
+    <t>09/01/26</t>
+  </si>
+  <si>
+    <t>Grapa</t>
+  </si>
+  <si>
+    <t>2/1</t>
+  </si>
+  <si>
+    <t>R$  106,63</t>
+  </si>
+  <si>
+    <t>Mercado livre - mat aspirador</t>
+  </si>
+  <si>
+    <t>54802/2</t>
+  </si>
+  <si>
+    <t>R$  279,56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155,4	Mercado Livre	 Rodizios cliente Krisdany
+124,16	Mercado Livre	dobradiças invisiveis Krisdany
+</t>
   </si>
   <si>
     <t>641/1</t>
@@ -922,25 +933,37 @@
 </t>
   </si>
   <si>
-    <t>581/1</t>
-  </si>
-  <si>
-    <t>R$  137,93</t>
-  </si>
-  <si>
-    <t>05/03/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor	Fornecedor	Descrição
-35,9	Mercado Livre	5 Pé Pézinho Móveis 18cm Até 23cm (assistencia Carina)
-102,03	Mercado Livre	plafon show room moema
-</t>
+    <t>63401/4</t>
+  </si>
+  <si>
+    <t>R$  100,75</t>
+  </si>
+  <si>
+    <t>mão francesa 4/4</t>
+  </si>
+  <si>
+    <t>63401DANIELAIMM</t>
+  </si>
+  <si>
+    <t>63401/3</t>
+  </si>
+  <si>
+    <t>mao francesa 3 /4</t>
+  </si>
+  <si>
+    <t>63401/2</t>
+  </si>
+  <si>
+    <t>mão francesa 2/4</t>
+  </si>
+  <si>
+    <t>East Glass- R t de Andrade Comercio E Servicos</t>
+  </si>
+  <si>
+    <t>R$  1.886,73</t>
   </si>
   <si>
     <t>608/1</t>
-  </si>
-  <si>
-    <t>R$  100,75</t>
   </si>
   <si>
     <t>06/04/26</t>
@@ -950,25 +973,13 @@
 </t>
   </si>
   <si>
-    <t>63401DANIELAIMM</t>
-  </si>
-  <si>
-    <t>559/1</t>
-  </si>
-  <si>
-    <t>R$  630,00</t>
-  </si>
-  <si>
-    <t>63401/4</t>
-  </si>
-  <si>
-    <t>mão francesa 4/4</t>
-  </si>
-  <si>
     <t>580/1</t>
   </si>
   <si>
     <t>R$  165,83</t>
+  </si>
+  <si>
+    <t>05/03/26</t>
   </si>
   <si>
     <t>17/02/26</t>
@@ -984,78 +995,67 @@
     <t>29901FL8</t>
   </si>
   <si>
+    <t>582/1</t>
+  </si>
+  <si>
+    <t>R$  98,00</t>
+  </si>
+  <si>
+    <t>36902LeticiaOC</t>
+  </si>
+  <si>
+    <t>584/1</t>
+  </si>
+  <si>
+    <t>FERRAGENS FLORESTA EIRELI EPP</t>
+  </si>
+  <si>
+    <t>R$  381,46</t>
+  </si>
+  <si>
+    <t>24/03/26</t>
+  </si>
+  <si>
+    <t>estoque</t>
+  </si>
+  <si>
+    <t>571/1</t>
+  </si>
+  <si>
+    <t>R$  443,00</t>
+  </si>
+  <si>
+    <t>581/1</t>
+  </si>
+  <si>
+    <t>R$  137,93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor	Fornecedor	Descrição
+35,9	Mercado Livre	5 Pé Pézinho Móveis 18cm Até 23cm (assistencia Carina)
+102,03	Mercado Livre	plafon show room moema
+</t>
+  </si>
+  <si>
+    <t>559/1</t>
+  </si>
+  <si>
+    <t>R$  630,00</t>
+  </si>
+  <si>
     <t>560/1</t>
   </si>
   <si>
     <t>R$  330,47</t>
   </si>
   <si>
-    <t>63401/3</t>
-  </si>
-  <si>
-    <t>mao francesa 3 /4</t>
-  </si>
-  <si>
-    <t>2/1</t>
-  </si>
-  <si>
-    <t>R$  106,63</t>
-  </si>
-  <si>
-    <t>Mercado livre - mat aspirador</t>
-  </si>
-  <si>
-    <t>54802/2</t>
-  </si>
-  <si>
-    <t>R$  279,56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155,4	Mercado Livre	 Rodizios cliente Krisdany
-124,16	Mercado Livre	dobradiças invisiveis Krisdany
-</t>
-  </si>
-  <si>
-    <t>582/1</t>
-  </si>
-  <si>
-    <t>R$  98,00</t>
-  </si>
-  <si>
-    <t>36902LeticiaOC</t>
-  </si>
-  <si>
-    <t>9/2</t>
-  </si>
-  <si>
-    <t>R$  91,87</t>
-  </si>
-  <si>
-    <t>09/01/26</t>
-  </si>
-  <si>
-    <t>Grapa</t>
-  </si>
-  <si>
-    <t>63401/2</t>
-  </si>
-  <si>
-    <t>mão francesa 2/4</t>
-  </si>
-  <si>
-    <t>584/1</t>
-  </si>
-  <si>
-    <t>R$  381,46</t>
-  </si>
-  <si>
-    <t>24/03/26</t>
-  </si>
-  <si>
-    <t>571/1</t>
-  </si>
-  <si>
-    <t>R$  443,00</t>
+    <t>575/1</t>
+  </si>
+  <si>
+    <t>R$  256,50</t>
+  </si>
+  <si>
+    <t>18/03/26</t>
   </si>
   <si>
     <t>4.02.02 CUSTO DE TRANSPORTE</t>
@@ -1550,46 +1550,46 @@
     <t>R$ 10.123,95</t>
   </si>
   <si>
+    <t>R$  537,59</t>
+  </si>
+  <si>
+    <t>R$  438,09</t>
+  </si>
+  <si>
+    <t>63801/2</t>
+  </si>
+  <si>
+    <t>R$  3,60</t>
+  </si>
+  <si>
+    <t>R$  1.941,34</t>
+  </si>
+  <si>
+    <t>RAYSSA BARBOSA SILVA</t>
+  </si>
+  <si>
+    <t>01/06/26</t>
+  </si>
+  <si>
+    <t>FERNANDA DOCHVAT SILVA</t>
+  </si>
+  <si>
+    <t>R$  1.196,02</t>
+  </si>
+  <si>
+    <t>01/04/26</t>
+  </si>
+  <si>
+    <t>R$  727,31</t>
+  </si>
+  <si>
+    <t>07/04/26</t>
+  </si>
+  <si>
     <t>R$  1.108,54</t>
   </si>
   <si>
-    <t>R$  1.196,02</t>
-  </si>
-  <si>
-    <t>RAYSSA BARBOSA SILVA</t>
-  </si>
-  <si>
-    <t>R$  727,31</t>
-  </si>
-  <si>
-    <t>07/04/26</t>
-  </si>
-  <si>
-    <t>FERNANDA DOCHVAT SILVA</t>
-  </si>
-  <si>
-    <t>01/06/26</t>
-  </si>
-  <si>
-    <t>01/04/26</t>
-  </si>
-  <si>
-    <t>R$  438,09</t>
-  </si>
-  <si>
-    <t>R$  3,60</t>
-  </si>
-  <si>
-    <t>63801/2</t>
-  </si>
-  <si>
-    <t>R$  537,59</t>
-  </si>
-  <si>
     <t>R$  292,95</t>
-  </si>
-  <si>
-    <t>R$  1.941,34</t>
   </si>
   <si>
     <t>4.03.01.02.07 Comissões montagem - custo efetivo</t>
@@ -2136,6 +2136,72 @@
     <t>4.04.01.02.01.01 Salário fixo</t>
   </si>
   <si>
+    <t>Denny Lucas do Carmo Pereira</t>
+  </si>
+  <si>
+    <t>R$  2.645,58</t>
+  </si>
+  <si>
+    <t>Denny Lucas - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>GUTEMBERG DIAS GOMES</t>
+  </si>
+  <si>
+    <t>R$  6.000,00</t>
+  </si>
+  <si>
+    <t>Gutemberg Dias - Pagamento</t>
+  </si>
+  <si>
+    <t>Fernanda Dochvat - Fixo 2026</t>
+  </si>
+  <si>
+    <t>Teresinha Elvira Maximino de Menezes</t>
+  </si>
+  <si>
+    <t>Tucha - Fixo 2026</t>
+  </si>
+  <si>
+    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
+  </si>
+  <si>
+    <t>R$  4.422,07</t>
+  </si>
+  <si>
+    <t>Sabrina Braunbeck - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>Danielle Martins da Silva</t>
+  </si>
+  <si>
+    <t>R$  2.090,00</t>
+  </si>
+  <si>
+    <t>Danielle - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>Leandro Henrique Simoes Campos</t>
+  </si>
+  <si>
+    <t>R$  2.000,00</t>
+  </si>
+  <si>
+    <t>Leandro Henrique Simoes Campos Fixo 2026</t>
+  </si>
+  <si>
+    <t>CARINA PEREIRA</t>
+  </si>
+  <si>
+    <t>Carina - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>Eric Kevin de Souza Serpa</t>
+  </si>
+  <si>
+    <t>Salário Fixo -Eric Serpa 2026</t>
+  </si>
+  <si>
     <t>Bianca Rodrigues - Salário fixo 2026</t>
   </si>
   <si>
@@ -2148,82 +2214,16 @@
     <t>Rateio salários Mayara, Rayssa e Efraim</t>
   </si>
   <si>
-    <t>Fernanda Dochvat - Fixo 2026</t>
-  </si>
-  <si>
-    <t>Danielle Martins da Silva</t>
-  </si>
-  <si>
-    <t>R$  2.090,00</t>
-  </si>
-  <si>
-    <t>Danielle - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>GUTEMBERG DIAS GOMES</t>
-  </si>
-  <si>
-    <t>R$  6.000,00</t>
-  </si>
-  <si>
-    <t>Gutemberg Dias - Pagamento</t>
-  </si>
-  <si>
-    <t>Leandro Henrique Simoes Campos</t>
-  </si>
-  <si>
-    <t>R$  2.000,00</t>
-  </si>
-  <si>
-    <t>Leandro Henrique Simoes Campos Fixo 2026</t>
-  </si>
-  <si>
-    <t>CARINA PEREIRA</t>
-  </si>
-  <si>
-    <t>Carina - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>Denny Lucas do Carmo Pereira</t>
-  </si>
-  <si>
-    <t>R$  2.645,58</t>
-  </si>
-  <si>
-    <t>Denny Lucas - Pagamento 2026</t>
-  </si>
-  <si>
     <t>Rubens - Pagamento 2026</t>
   </si>
   <si>
+    <t>578/1</t>
+  </si>
+  <si>
+    <t>R$  2.219,85</t>
+  </si>
+  <si>
     <t>579/1</t>
-  </si>
-  <si>
-    <t>Eric Kevin de Souza Serpa</t>
-  </si>
-  <si>
-    <t>Salário Fixo -Eric Serpa 2026</t>
-  </si>
-  <si>
-    <t>Teresinha Elvira Maximino de Menezes</t>
-  </si>
-  <si>
-    <t>Tucha - Fixo 2026</t>
-  </si>
-  <si>
-    <t>578/1</t>
-  </si>
-  <si>
-    <t>R$  2.219,85</t>
-  </si>
-  <si>
-    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
-  </si>
-  <si>
-    <t>R$  4.422,07</t>
-  </si>
-  <si>
-    <t>Sabrina Braunbeck - Pagamento 2026</t>
   </si>
   <si>
     <t>4.04.01.02.05 IRRF sobre salários</t>
@@ -2822,49 +2822,49 @@
     <t>4.07.01.01.01 Operações financeiras - desconto de cheques (financeiras)</t>
   </si>
   <si>
+    <t>PAGSEGURO</t>
+  </si>
+  <si>
+    <t>R$  2.389,60</t>
+  </si>
+  <si>
+    <t>Título referente a Valor da Taxa Financeira</t>
+  </si>
+  <si>
+    <t>R$  1.856,00</t>
+  </si>
+  <si>
     <t>Italíneacredi</t>
   </si>
   <si>
     <t>R$  2.297,09</t>
   </si>
   <si>
-    <t>Título referente a Valor da Taxa Financeira</t>
-  </si>
-  <si>
-    <t>PAGSEGURO</t>
-  </si>
-  <si>
-    <t>R$  1.856,00</t>
+    <t>R$  4.023,17</t>
+  </si>
+  <si>
+    <t>R$  5.371,28</t>
+  </si>
+  <si>
+    <t>R$  389,78</t>
+  </si>
+  <si>
+    <t>R$  20.470,96</t>
+  </si>
+  <si>
+    <t>R$  19.259,44</t>
   </si>
   <si>
     <t>R$  3.337,10</t>
   </si>
   <si>
-    <t>R$  5.371,28</t>
-  </si>
-  <si>
     <t>R$  618,68</t>
   </si>
   <si>
+    <t>R$  8.136,54</t>
+  </si>
+  <si>
     <t>R$  1.084,60</t>
-  </si>
-  <si>
-    <t>R$  4.023,17</t>
-  </si>
-  <si>
-    <t>R$  389,78</t>
-  </si>
-  <si>
-    <t>R$  2.389,60</t>
-  </si>
-  <si>
-    <t>R$  8.136,54</t>
-  </si>
-  <si>
-    <t>R$  20.470,96</t>
-  </si>
-  <si>
-    <t>R$  19.259,44</t>
   </si>
   <si>
     <t>6.01 ATIVO</t>
@@ -7829,28 +7829,28 @@
         <v>33</v>
       </c>
       <c r="E96" t="s">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="F96" t="s">
-        <v>211</v>
+        <v>40</v>
       </c>
       <c r="G96" t="s">
         <v>41</v>
       </c>
       <c r="H96" t="s">
-        <v>291</v>
+        <v>56</v>
       </c>
       <c r="I96" t="s">
         <v>292</v>
       </c>
       <c r="J96" t="s">
-        <v>119</v>
+        <v>293</v>
       </c>
       <c r="K96" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="L96" t="s">
-        <v>34</v>
+        <v>294</v>
       </c>
       <c r="M96" t="s">
         <v>289</v>
@@ -7859,7 +7859,7 @@
         <v>47</v>
       </c>
       <c r="O96" t="s">
-        <v>105</v>
+        <v>48</v>
       </c>
       <c r="P96" t="s">
         <v>292</v>
@@ -7885,25 +7885,25 @@
         <v>34</v>
       </c>
       <c r="E97" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F97" t="s">
-        <v>211</v>
+        <v>40</v>
       </c>
       <c r="G97" t="s">
         <v>41</v>
       </c>
       <c r="H97" t="s">
-        <v>294</v>
+        <v>56</v>
       </c>
       <c r="I97" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J97" t="s">
-        <v>296</v>
+        <v>101</v>
       </c>
       <c r="K97" t="s">
-        <v>96</v>
+        <v>45</v>
       </c>
       <c r="L97" t="s">
         <v>297</v>
@@ -7918,7 +7918,7 @@
         <v>48</v>
       </c>
       <c r="P97" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q97" t="s">
         <v>47</v>
@@ -7956,13 +7956,13 @@
         <v>299</v>
       </c>
       <c r="J98" t="s">
+        <v>119</v>
+      </c>
+      <c r="K98" t="s">
+        <v>58</v>
+      </c>
+      <c r="L98" t="s">
         <v>300</v>
-      </c>
-      <c r="K98" t="s">
-        <v>147</v>
-      </c>
-      <c r="L98" t="s">
-        <v>301</v>
       </c>
       <c r="M98" t="s">
         <v>289</v>
@@ -7971,7 +7971,7 @@
         <v>47</v>
       </c>
       <c r="O98" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="P98" t="s">
         <v>299</v>
@@ -7997,7 +7997,7 @@
         <v>34</v>
       </c>
       <c r="E99" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F99" t="s">
         <v>211</v>
@@ -8009,16 +8009,16 @@
         <v>56</v>
       </c>
       <c r="I99" t="s">
+        <v>302</v>
+      </c>
+      <c r="J99" t="s">
         <v>303</v>
       </c>
-      <c r="J99" t="s">
+      <c r="K99" t="s">
+        <v>147</v>
+      </c>
+      <c r="L99" t="s">
         <v>304</v>
-      </c>
-      <c r="K99" t="s">
-        <v>178</v>
-      </c>
-      <c r="L99" t="s">
-        <v>305</v>
       </c>
       <c r="M99" t="s">
         <v>289</v>
@@ -8027,10 +8027,10 @@
         <v>47</v>
       </c>
       <c r="O99" t="s">
-        <v>48</v>
+        <v>114</v>
       </c>
       <c r="P99" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="Q99" t="s">
         <v>47</v>
@@ -8053,7 +8053,7 @@
         <v>34</v>
       </c>
       <c r="E100" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F100" t="s">
         <v>211</v>
@@ -8065,16 +8065,16 @@
         <v>56</v>
       </c>
       <c r="I100" t="s">
+        <v>306</v>
+      </c>
+      <c r="J100" t="s">
+        <v>178</v>
+      </c>
+      <c r="K100" t="s">
+        <v>90</v>
+      </c>
+      <c r="L100" t="s">
         <v>307</v>
-      </c>
-      <c r="J100" t="s">
-        <v>308</v>
-      </c>
-      <c r="K100" t="s">
-        <v>119</v>
-      </c>
-      <c r="L100" t="s">
-        <v>309</v>
       </c>
       <c r="M100" t="s">
         <v>289</v>
@@ -8083,10 +8083,10 @@
         <v>47</v>
       </c>
       <c r="O100" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="P100" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q100" t="s">
         <v>47</v>
@@ -8109,7 +8109,7 @@
         <v>34</v>
       </c>
       <c r="E101" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F101" t="s">
         <v>211</v>
@@ -8118,19 +8118,19 @@
         <v>41</v>
       </c>
       <c r="H101" t="s">
-        <v>294</v>
+        <v>56</v>
       </c>
       <c r="I101" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J101" t="s">
-        <v>304</v>
+        <v>96</v>
       </c>
       <c r="K101" t="s">
-        <v>134</v>
+        <v>90</v>
       </c>
       <c r="L101" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="M101" t="s">
         <v>289</v>
@@ -8139,10 +8139,10 @@
         <v>47</v>
       </c>
       <c r="O101" t="s">
-        <v>48</v>
+        <v>308</v>
       </c>
       <c r="P101" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="Q101" t="s">
         <v>47</v>
@@ -8165,7 +8165,7 @@
         <v>34</v>
       </c>
       <c r="E102" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F102" t="s">
         <v>211</v>
@@ -8177,16 +8177,16 @@
         <v>56</v>
       </c>
       <c r="I102" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="J102" t="s">
-        <v>178</v>
+        <v>119</v>
       </c>
       <c r="K102" t="s">
         <v>90</v>
       </c>
       <c r="L102" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="M102" t="s">
         <v>289</v>
@@ -8195,10 +8195,10 @@
         <v>47</v>
       </c>
       <c r="O102" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="P102" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q102" t="s">
         <v>47</v>
@@ -8221,7 +8221,7 @@
         <v>34</v>
       </c>
       <c r="E103" t="s">
-        <v>315</v>
+        <v>275</v>
       </c>
       <c r="F103" t="s">
         <v>211</v>
@@ -8230,19 +8230,19 @@
         <v>41</v>
       </c>
       <c r="H103" t="s">
-        <v>56</v>
+        <v>313</v>
       </c>
       <c r="I103" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="J103" t="s">
-        <v>304</v>
+        <v>119</v>
       </c>
       <c r="K103" t="s">
-        <v>317</v>
+        <v>58</v>
       </c>
       <c r="L103" t="s">
-        <v>318</v>
+        <v>34</v>
       </c>
       <c r="M103" t="s">
         <v>289</v>
@@ -8251,10 +8251,10 @@
         <v>47</v>
       </c>
       <c r="O103" t="s">
-        <v>319</v>
+        <v>105</v>
       </c>
       <c r="P103" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="Q103" t="s">
         <v>47</v>
@@ -8277,7 +8277,7 @@
         <v>34</v>
       </c>
       <c r="E104" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="F104" t="s">
         <v>211</v>
@@ -8286,19 +8286,19 @@
         <v>41</v>
       </c>
       <c r="H104" t="s">
-        <v>294</v>
+        <v>56</v>
       </c>
       <c r="I104" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="J104" t="s">
-        <v>138</v>
+        <v>316</v>
       </c>
       <c r="K104" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="L104" t="s">
-        <v>297</v>
+        <v>317</v>
       </c>
       <c r="M104" t="s">
         <v>289</v>
@@ -8307,10 +8307,10 @@
         <v>47</v>
       </c>
       <c r="O104" t="s">
-        <v>48</v>
+        <v>308</v>
       </c>
       <c r="P104" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="Q104" t="s">
         <v>47</v>
@@ -8333,7 +8333,7 @@
         <v>34</v>
       </c>
       <c r="E105" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="F105" t="s">
         <v>211</v>
@@ -8345,16 +8345,16 @@
         <v>56</v>
       </c>
       <c r="I105" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="J105" t="s">
-        <v>96</v>
+        <v>320</v>
       </c>
       <c r="K105" t="s">
-        <v>90</v>
+        <v>321</v>
       </c>
       <c r="L105" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="M105" t="s">
         <v>289</v>
@@ -8363,10 +8363,10 @@
         <v>47</v>
       </c>
       <c r="O105" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="P105" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Q105" t="s">
         <v>47</v>
@@ -8392,7 +8392,7 @@
         <v>324</v>
       </c>
       <c r="F106" t="s">
-        <v>40</v>
+        <v>211</v>
       </c>
       <c r="G106" t="s">
         <v>41</v>
@@ -8404,13 +8404,13 @@
         <v>325</v>
       </c>
       <c r="J106" t="s">
-        <v>101</v>
+        <v>320</v>
       </c>
       <c r="K106" t="s">
-        <v>45</v>
+        <v>191</v>
       </c>
       <c r="L106" t="s">
-        <v>326</v>
+        <v>34</v>
       </c>
       <c r="M106" t="s">
         <v>289</v>
@@ -8419,7 +8419,7 @@
         <v>47</v>
       </c>
       <c r="O106" t="s">
-        <v>48</v>
+        <v>326</v>
       </c>
       <c r="P106" t="s">
         <v>325</v>
@@ -8454,19 +8454,19 @@
         <v>41</v>
       </c>
       <c r="H107" t="s">
-        <v>56</v>
+        <v>328</v>
       </c>
       <c r="I107" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J107" t="s">
-        <v>119</v>
+        <v>330</v>
       </c>
       <c r="K107" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="L107" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="M107" t="s">
         <v>289</v>
@@ -8475,10 +8475,10 @@
         <v>47</v>
       </c>
       <c r="O107" t="s">
-        <v>105</v>
+        <v>48</v>
       </c>
       <c r="P107" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q107" t="s">
         <v>47</v>
@@ -8501,7 +8501,7 @@
         <v>34</v>
       </c>
       <c r="E108" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F108" t="s">
         <v>211</v>
@@ -8510,19 +8510,19 @@
         <v>41</v>
       </c>
       <c r="H108" t="s">
-        <v>56</v>
+        <v>328</v>
       </c>
       <c r="I108" t="s">
+        <v>333</v>
+      </c>
+      <c r="J108" t="s">
+        <v>163</v>
+      </c>
+      <c r="K108" t="s">
+        <v>96</v>
+      </c>
+      <c r="L108" t="s">
         <v>331</v>
-      </c>
-      <c r="J108" t="s">
-        <v>304</v>
-      </c>
-      <c r="K108" t="s">
-        <v>191</v>
-      </c>
-      <c r="L108" t="s">
-        <v>34</v>
       </c>
       <c r="M108" t="s">
         <v>289</v>
@@ -8531,10 +8531,10 @@
         <v>47</v>
       </c>
       <c r="O108" t="s">
-        <v>332</v>
+        <v>48</v>
       </c>
       <c r="P108" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q108" t="s">
         <v>47</v>
@@ -8557,10 +8557,10 @@
         <v>34</v>
       </c>
       <c r="E109" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F109" t="s">
-        <v>40</v>
+        <v>211</v>
       </c>
       <c r="G109" t="s">
         <v>41</v>
@@ -8569,13 +8569,13 @@
         <v>56</v>
       </c>
       <c r="I109" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J109" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="K109" t="s">
-        <v>45</v>
+        <v>178</v>
       </c>
       <c r="L109" t="s">
         <v>336</v>
@@ -8590,7 +8590,7 @@
         <v>48</v>
       </c>
       <c r="P109" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q109" t="s">
         <v>47</v>
@@ -8622,19 +8622,19 @@
         <v>41</v>
       </c>
       <c r="H110" t="s">
-        <v>56</v>
+        <v>328</v>
       </c>
       <c r="I110" t="s">
-        <v>307</v>
+        <v>338</v>
       </c>
       <c r="J110" t="s">
-        <v>119</v>
+        <v>320</v>
       </c>
       <c r="K110" t="s">
-        <v>90</v>
+        <v>134</v>
       </c>
       <c r="L110" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="M110" t="s">
         <v>289</v>
@@ -8643,10 +8643,10 @@
         <v>47</v>
       </c>
       <c r="O110" t="s">
-        <v>310</v>
+        <v>48</v>
       </c>
       <c r="P110" t="s">
-        <v>307</v>
+        <v>338</v>
       </c>
       <c r="Q110" t="s">
         <v>47</v>
@@ -8678,19 +8678,19 @@
         <v>41</v>
       </c>
       <c r="H111" t="s">
-        <v>294</v>
+        <v>328</v>
       </c>
       <c r="I111" t="s">
         <v>340</v>
       </c>
       <c r="J111" t="s">
-        <v>341</v>
+        <v>138</v>
       </c>
       <c r="K111" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="L111" t="s">
-        <v>297</v>
+        <v>331</v>
       </c>
       <c r="M111" t="s">
         <v>289</v>
@@ -8725,7 +8725,7 @@
         <v>34</v>
       </c>
       <c r="E112" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F112" t="s">
         <v>211</v>
@@ -8734,19 +8734,19 @@
         <v>41</v>
       </c>
       <c r="H112" t="s">
-        <v>294</v>
+        <v>328</v>
       </c>
       <c r="I112" t="s">
+        <v>342</v>
+      </c>
+      <c r="J112" t="s">
         <v>343</v>
-      </c>
-      <c r="J112" t="s">
-        <v>163</v>
       </c>
       <c r="K112" t="s">
         <v>96</v>
       </c>
       <c r="L112" t="s">
-        <v>297</v>
+        <v>331</v>
       </c>
       <c r="M112" t="s">
         <v>289</v>
@@ -8758,7 +8758,7 @@
         <v>48</v>
       </c>
       <c r="P112" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="Q112" t="s">
         <v>47</v>
@@ -9453,7 +9453,7 @@
         <v>34</v>
       </c>
       <c r="E125" t="s">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="F125" t="s">
         <v>218</v>
@@ -9483,7 +9483,7 @@
         <v>47</v>
       </c>
       <c r="O125" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="P125" t="s">
         <v>366</v>
@@ -9957,7 +9957,7 @@
         <v>34</v>
       </c>
       <c r="E134" t="s">
-        <v>327</v>
+        <v>298</v>
       </c>
       <c r="F134" t="s">
         <v>218</v>
@@ -10013,7 +10013,7 @@
         <v>34</v>
       </c>
       <c r="E135" t="s">
-        <v>337</v>
+        <v>311</v>
       </c>
       <c r="F135" t="s">
         <v>218</v>
@@ -10043,7 +10043,7 @@
         <v>47</v>
       </c>
       <c r="O135" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="P135" t="s">
         <v>379</v>
@@ -11708,7 +11708,7 @@
         <v>426</v>
       </c>
       <c r="J165" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K165" t="s">
         <v>58</v>
@@ -11764,7 +11764,7 @@
         <v>427</v>
       </c>
       <c r="J166" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K166" t="s">
         <v>119</v>
@@ -11820,7 +11820,7 @@
         <v>428</v>
       </c>
       <c r="J167" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K167" t="s">
         <v>119</v>
@@ -11876,7 +11876,7 @@
         <v>429</v>
       </c>
       <c r="J168" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K168" t="s">
         <v>80</v>
@@ -11932,7 +11932,7 @@
         <v>430</v>
       </c>
       <c r="J169" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K169" t="s">
         <v>70</v>
@@ -11988,7 +11988,7 @@
         <v>431</v>
       </c>
       <c r="J170" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K170" t="s">
         <v>119</v>
@@ -12044,7 +12044,7 @@
         <v>433</v>
       </c>
       <c r="J171" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K171" t="s">
         <v>119</v>
@@ -12100,7 +12100,7 @@
         <v>434</v>
       </c>
       <c r="J172" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K172" t="s">
         <v>229</v>
@@ -12156,7 +12156,7 @@
         <v>435</v>
       </c>
       <c r="J173" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K173" t="s">
         <v>119</v>
@@ -12212,7 +12212,7 @@
         <v>437</v>
       </c>
       <c r="J174" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K174" t="s">
         <v>80</v>
@@ -12268,7 +12268,7 @@
         <v>438</v>
       </c>
       <c r="J175" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K175" t="s">
         <v>90</v>
@@ -12283,7 +12283,7 @@
         <v>47</v>
       </c>
       <c r="O175" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="P175" t="s">
         <v>438</v>
@@ -12324,7 +12324,7 @@
         <v>439</v>
       </c>
       <c r="J176" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K176" t="s">
         <v>113</v>
@@ -12380,7 +12380,7 @@
         <v>440</v>
       </c>
       <c r="J177" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K177" t="s">
         <v>101</v>
@@ -12436,7 +12436,7 @@
         <v>441</v>
       </c>
       <c r="J178" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K178" t="s">
         <v>119</v>
@@ -12548,7 +12548,7 @@
         <v>446</v>
       </c>
       <c r="J180" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K180" t="s">
         <v>80</v>
@@ -12604,7 +12604,7 @@
         <v>448</v>
       </c>
       <c r="J181" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K181" t="s">
         <v>119</v>
@@ -12660,7 +12660,7 @@
         <v>430</v>
       </c>
       <c r="J182" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K182" t="s">
         <v>70</v>
@@ -12716,7 +12716,7 @@
         <v>451</v>
       </c>
       <c r="J183" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K183" t="s">
         <v>70</v>
@@ -12772,7 +12772,7 @@
         <v>427</v>
       </c>
       <c r="J184" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K184" t="s">
         <v>119</v>
@@ -12828,7 +12828,7 @@
         <v>452</v>
       </c>
       <c r="J185" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K185" t="s">
         <v>119</v>
@@ -12884,7 +12884,7 @@
         <v>439</v>
       </c>
       <c r="J186" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K186" t="s">
         <v>113</v>
@@ -12940,7 +12940,7 @@
         <v>453</v>
       </c>
       <c r="J187" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K187" t="s">
         <v>113</v>
@@ -12996,7 +12996,7 @@
         <v>438</v>
       </c>
       <c r="J188" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K188" t="s">
         <v>90</v>
@@ -13011,7 +13011,7 @@
         <v>47</v>
       </c>
       <c r="O188" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="P188" t="s">
         <v>438</v>
@@ -13052,7 +13052,7 @@
         <v>454</v>
       </c>
       <c r="J189" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K189" t="s">
         <v>90</v>
@@ -13067,7 +13067,7 @@
         <v>47</v>
       </c>
       <c r="O189" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="P189" t="s">
         <v>454</v>
@@ -13108,7 +13108,7 @@
         <v>434</v>
       </c>
       <c r="J190" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K190" t="s">
         <v>229</v>
@@ -13164,7 +13164,7 @@
         <v>455</v>
       </c>
       <c r="J191" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K191" t="s">
         <v>229</v>
@@ -13332,7 +13332,7 @@
         <v>462</v>
       </c>
       <c r="J194" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K194" t="s">
         <v>134</v>
@@ -13388,7 +13388,7 @@
         <v>464</v>
       </c>
       <c r="J195" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K195" t="s">
         <v>134</v>
@@ -13444,7 +13444,7 @@
         <v>465</v>
       </c>
       <c r="J196" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K196" t="s">
         <v>101</v>
@@ -13500,7 +13500,7 @@
         <v>431</v>
       </c>
       <c r="J197" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K197" t="s">
         <v>119</v>
@@ -13556,7 +13556,7 @@
         <v>467</v>
       </c>
       <c r="J198" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K198" t="s">
         <v>119</v>
@@ -13612,7 +13612,7 @@
         <v>441</v>
       </c>
       <c r="J199" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K199" t="s">
         <v>119</v>
@@ -13668,7 +13668,7 @@
         <v>468</v>
       </c>
       <c r="J200" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K200" t="s">
         <v>119</v>
@@ -13724,7 +13724,7 @@
         <v>470</v>
       </c>
       <c r="J201" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K201" t="s">
         <v>119</v>
@@ -13780,7 +13780,7 @@
         <v>433</v>
       </c>
       <c r="J202" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K202" t="s">
         <v>119</v>
@@ -13836,7 +13836,7 @@
         <v>471</v>
       </c>
       <c r="J203" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K203" t="s">
         <v>119</v>
@@ -14004,7 +14004,7 @@
         <v>426</v>
       </c>
       <c r="J206" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K206" t="s">
         <v>58</v>
@@ -14060,7 +14060,7 @@
         <v>477</v>
       </c>
       <c r="J207" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K207" t="s">
         <v>58</v>
@@ -14116,7 +14116,7 @@
         <v>440</v>
       </c>
       <c r="J208" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K208" t="s">
         <v>101</v>
@@ -14172,7 +14172,7 @@
         <v>478</v>
       </c>
       <c r="J209" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K209" t="s">
         <v>101</v>
@@ -14228,7 +14228,7 @@
         <v>479</v>
       </c>
       <c r="J210" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K210" t="s">
         <v>119</v>
@@ -14284,7 +14284,7 @@
         <v>428</v>
       </c>
       <c r="J211" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K211" t="s">
         <v>119</v>
@@ -14340,7 +14340,7 @@
         <v>480</v>
       </c>
       <c r="J212" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K212" t="s">
         <v>119</v>
@@ -14396,7 +14396,7 @@
         <v>437</v>
       </c>
       <c r="J213" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K213" t="s">
         <v>80</v>
@@ -14452,7 +14452,7 @@
         <v>481</v>
       </c>
       <c r="J214" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K214" t="s">
         <v>80</v>
@@ -14508,7 +14508,7 @@
         <v>435</v>
       </c>
       <c r="J215" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K215" t="s">
         <v>119</v>
@@ -14564,7 +14564,7 @@
         <v>482</v>
       </c>
       <c r="J216" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K216" t="s">
         <v>119</v>
@@ -14620,7 +14620,7 @@
         <v>483</v>
       </c>
       <c r="J217" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K217" t="s">
         <v>58</v>
@@ -14676,7 +14676,7 @@
         <v>484</v>
       </c>
       <c r="J218" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K218" t="s">
         <v>70</v>
@@ -14732,7 +14732,7 @@
         <v>485</v>
       </c>
       <c r="J219" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K219" t="s">
         <v>119</v>
@@ -14788,7 +14788,7 @@
         <v>486</v>
       </c>
       <c r="J220" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K220" t="s">
         <v>119</v>
@@ -14844,7 +14844,7 @@
         <v>429</v>
       </c>
       <c r="J221" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K221" t="s">
         <v>80</v>
@@ -14900,7 +14900,7 @@
         <v>487</v>
       </c>
       <c r="J222" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K222" t="s">
         <v>80</v>
@@ -14956,7 +14956,7 @@
         <v>488</v>
       </c>
       <c r="J223" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K223" t="s">
         <v>119</v>
@@ -15012,7 +15012,7 @@
         <v>489</v>
       </c>
       <c r="J224" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K224" t="s">
         <v>80</v>
@@ -15068,7 +15068,7 @@
         <v>490</v>
       </c>
       <c r="J225" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K225" t="s">
         <v>229</v>
@@ -15124,7 +15124,7 @@
         <v>491</v>
       </c>
       <c r="J226" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K226" t="s">
         <v>90</v>
@@ -15139,7 +15139,7 @@
         <v>47</v>
       </c>
       <c r="O226" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="P226" t="s">
         <v>491</v>
@@ -15180,7 +15180,7 @@
         <v>492</v>
       </c>
       <c r="J227" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K227" t="s">
         <v>119</v>
@@ -15236,7 +15236,7 @@
         <v>493</v>
       </c>
       <c r="J228" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K228" t="s">
         <v>113</v>
@@ -15460,7 +15460,7 @@
         <v>505</v>
       </c>
       <c r="J232" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K232" t="s">
         <v>119</v>
@@ -15516,7 +15516,7 @@
         <v>471</v>
       </c>
       <c r="J233" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K233" t="s">
         <v>119</v>
@@ -15557,25 +15557,25 @@
         <v>33</v>
       </c>
       <c r="E234" t="s">
-        <v>275</v>
+        <v>354</v>
       </c>
       <c r="F234" t="s">
-        <v>218</v>
+        <v>499</v>
       </c>
       <c r="G234" t="s">
         <v>41</v>
       </c>
       <c r="H234" t="s">
-        <v>457</v>
+        <v>215</v>
       </c>
       <c r="I234" t="s">
         <v>508</v>
       </c>
       <c r="J234" t="s">
-        <v>304</v>
+        <v>90</v>
       </c>
       <c r="K234" t="s">
-        <v>58</v>
+        <v>229</v>
       </c>
       <c r="L234" t="s">
         <v>34</v>
@@ -15587,13 +15587,13 @@
         <v>47</v>
       </c>
       <c r="O234" t="s">
-        <v>105</v>
+        <v>34</v>
       </c>
       <c r="P234" t="s">
-        <v>508</v>
+        <v>34</v>
       </c>
       <c r="Q234" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R234" t="s">
         <v>34</v>
@@ -15613,22 +15613,22 @@
         <v>34</v>
       </c>
       <c r="E235" t="s">
-        <v>234</v>
+        <v>360</v>
       </c>
       <c r="F235" t="s">
-        <v>218</v>
+        <v>499</v>
       </c>
       <c r="G235" t="s">
         <v>41</v>
       </c>
       <c r="H235" t="s">
-        <v>457</v>
+        <v>215</v>
       </c>
       <c r="I235" t="s">
         <v>509</v>
       </c>
       <c r="J235" t="s">
-        <v>300</v>
+        <v>119</v>
       </c>
       <c r="K235" t="s">
         <v>119</v>
@@ -15643,13 +15643,13 @@
         <v>47</v>
       </c>
       <c r="O235" t="s">
-        <v>130</v>
+        <v>34</v>
       </c>
       <c r="P235" t="s">
-        <v>509</v>
+        <v>34</v>
       </c>
       <c r="Q235" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R235" t="s">
         <v>34</v>
@@ -15669,25 +15669,25 @@
         <v>34</v>
       </c>
       <c r="E236" t="s">
-        <v>244</v>
+        <v>510</v>
       </c>
       <c r="F236" t="s">
-        <v>218</v>
+        <v>499</v>
       </c>
       <c r="G236" t="s">
         <v>41</v>
       </c>
       <c r="H236" t="s">
-        <v>510</v>
+        <v>215</v>
       </c>
       <c r="I236" t="s">
-        <v>511</v>
+        <v>464</v>
       </c>
       <c r="J236" t="s">
-        <v>512</v>
+        <v>134</v>
       </c>
       <c r="K236" t="s">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="L236" t="s">
         <v>34</v>
@@ -15699,13 +15699,13 @@
         <v>47</v>
       </c>
       <c r="O236" t="s">
-        <v>247</v>
+        <v>34</v>
       </c>
       <c r="P236" t="s">
-        <v>511</v>
+        <v>34</v>
       </c>
       <c r="Q236" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R236" t="s">
         <v>34</v>
@@ -15725,25 +15725,25 @@
         <v>34</v>
       </c>
       <c r="E237" t="s">
-        <v>248</v>
+        <v>357</v>
       </c>
       <c r="F237" t="s">
-        <v>218</v>
+        <v>499</v>
       </c>
       <c r="G237" t="s">
         <v>41</v>
       </c>
       <c r="H237" t="s">
-        <v>513</v>
+        <v>215</v>
       </c>
       <c r="I237" t="s">
-        <v>428</v>
+        <v>511</v>
       </c>
       <c r="J237" t="s">
-        <v>300</v>
+        <v>80</v>
       </c>
       <c r="K237" t="s">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="L237" t="s">
         <v>34</v>
@@ -15755,13 +15755,13 @@
         <v>47</v>
       </c>
       <c r="O237" t="s">
-        <v>250</v>
+        <v>34</v>
       </c>
       <c r="P237" t="s">
-        <v>428</v>
+        <v>34</v>
       </c>
       <c r="Q237" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R237" t="s">
         <v>34</v>
@@ -15781,25 +15781,25 @@
         <v>34</v>
       </c>
       <c r="E238" t="s">
-        <v>253</v>
+        <v>363</v>
       </c>
       <c r="F238" t="s">
-        <v>218</v>
+        <v>499</v>
       </c>
       <c r="G238" t="s">
         <v>41</v>
       </c>
       <c r="H238" t="s">
-        <v>510</v>
+        <v>215</v>
       </c>
       <c r="I238" t="s">
-        <v>429</v>
+        <v>512</v>
       </c>
       <c r="J238" t="s">
-        <v>514</v>
+        <v>126</v>
       </c>
       <c r="K238" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="L238" t="s">
         <v>34</v>
@@ -15811,13 +15811,13 @@
         <v>47</v>
       </c>
       <c r="O238" t="s">
-        <v>255</v>
+        <v>34</v>
       </c>
       <c r="P238" t="s">
-        <v>429</v>
+        <v>34</v>
       </c>
       <c r="Q238" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R238" t="s">
         <v>34</v>
@@ -15837,25 +15837,25 @@
         <v>34</v>
       </c>
       <c r="E239" t="s">
-        <v>223</v>
+        <v>348</v>
       </c>
       <c r="F239" t="s">
-        <v>218</v>
+        <v>499</v>
       </c>
       <c r="G239" t="s">
         <v>41</v>
       </c>
       <c r="H239" t="s">
-        <v>513</v>
+        <v>215</v>
       </c>
       <c r="I239" t="s">
-        <v>439</v>
+        <v>512</v>
       </c>
       <c r="J239" t="s">
-        <v>515</v>
+        <v>126</v>
       </c>
       <c r="K239" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="L239" t="s">
         <v>34</v>
@@ -15867,13 +15867,13 @@
         <v>47</v>
       </c>
       <c r="O239" t="s">
-        <v>114</v>
+        <v>34</v>
       </c>
       <c r="P239" t="s">
-        <v>439</v>
+        <v>34</v>
       </c>
       <c r="Q239" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R239" t="s">
         <v>34</v>
@@ -15949,25 +15949,25 @@
         <v>34</v>
       </c>
       <c r="E241" t="s">
-        <v>360</v>
+        <v>253</v>
       </c>
       <c r="F241" t="s">
-        <v>499</v>
+        <v>218</v>
       </c>
       <c r="G241" t="s">
         <v>41</v>
       </c>
       <c r="H241" t="s">
-        <v>215</v>
+        <v>513</v>
       </c>
       <c r="I241" t="s">
-        <v>516</v>
+        <v>429</v>
       </c>
       <c r="J241" t="s">
-        <v>119</v>
+        <v>514</v>
       </c>
       <c r="K241" t="s">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="L241" t="s">
         <v>34</v>
@@ -15979,13 +15979,13 @@
         <v>47</v>
       </c>
       <c r="O241" t="s">
-        <v>34</v>
+        <v>255</v>
       </c>
       <c r="P241" t="s">
-        <v>34</v>
+        <v>429</v>
       </c>
       <c r="Q241" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R241" t="s">
         <v>34</v>
@@ -16005,25 +16005,25 @@
         <v>34</v>
       </c>
       <c r="E242" t="s">
-        <v>357</v>
+        <v>248</v>
       </c>
       <c r="F242" t="s">
-        <v>499</v>
+        <v>218</v>
       </c>
       <c r="G242" t="s">
         <v>41</v>
       </c>
       <c r="H242" t="s">
-        <v>215</v>
+        <v>515</v>
       </c>
       <c r="I242" t="s">
-        <v>517</v>
+        <v>428</v>
       </c>
       <c r="J242" t="s">
-        <v>80</v>
+        <v>303</v>
       </c>
       <c r="K242" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="L242" t="s">
         <v>34</v>
@@ -16035,13 +16035,13 @@
         <v>47</v>
       </c>
       <c r="O242" t="s">
-        <v>34</v>
+        <v>250</v>
       </c>
       <c r="P242" t="s">
-        <v>34</v>
+        <v>428</v>
       </c>
       <c r="Q242" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R242" t="s">
         <v>34</v>
@@ -16061,7 +16061,7 @@
         <v>34</v>
       </c>
       <c r="E243" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="F243" t="s">
         <v>218</v>
@@ -16070,16 +16070,16 @@
         <v>41</v>
       </c>
       <c r="H243" t="s">
-        <v>513</v>
+        <v>457</v>
       </c>
       <c r="I243" t="s">
-        <v>430</v>
+        <v>516</v>
       </c>
       <c r="J243" t="s">
-        <v>515</v>
+        <v>303</v>
       </c>
       <c r="K243" t="s">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="L243" t="s">
         <v>34</v>
@@ -16091,10 +16091,10 @@
         <v>47</v>
       </c>
       <c r="O243" t="s">
-        <v>71</v>
+        <v>130</v>
       </c>
       <c r="P243" t="s">
-        <v>430</v>
+        <v>516</v>
       </c>
       <c r="Q243" t="s">
         <v>47</v>
@@ -16117,7 +16117,7 @@
         <v>34</v>
       </c>
       <c r="E244" t="s">
-        <v>472</v>
+        <v>223</v>
       </c>
       <c r="F244" t="s">
         <v>218</v>
@@ -16126,13 +16126,13 @@
         <v>41</v>
       </c>
       <c r="H244" t="s">
-        <v>457</v>
+        <v>515</v>
       </c>
       <c r="I244" t="s">
-        <v>473</v>
+        <v>439</v>
       </c>
       <c r="J244" t="s">
-        <v>461</v>
+        <v>517</v>
       </c>
       <c r="K244" t="s">
         <v>113</v>
@@ -16147,10 +16147,10 @@
         <v>47</v>
       </c>
       <c r="O244" t="s">
-        <v>475</v>
+        <v>114</v>
       </c>
       <c r="P244" t="s">
-        <v>473</v>
+        <v>439</v>
       </c>
       <c r="Q244" t="s">
         <v>47</v>
@@ -16173,25 +16173,25 @@
         <v>34</v>
       </c>
       <c r="E245" t="s">
-        <v>518</v>
+        <v>251</v>
       </c>
       <c r="F245" t="s">
-        <v>499</v>
+        <v>218</v>
       </c>
       <c r="G245" t="s">
         <v>41</v>
       </c>
       <c r="H245" t="s">
-        <v>215</v>
+        <v>515</v>
       </c>
       <c r="I245" t="s">
-        <v>464</v>
+        <v>430</v>
       </c>
       <c r="J245" t="s">
-        <v>134</v>
+        <v>517</v>
       </c>
       <c r="K245" t="s">
-        <v>134</v>
+        <v>70</v>
       </c>
       <c r="L245" t="s">
         <v>34</v>
@@ -16203,13 +16203,13 @@
         <v>47</v>
       </c>
       <c r="O245" t="s">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="P245" t="s">
-        <v>34</v>
+        <v>430</v>
       </c>
       <c r="Q245" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R245" t="s">
         <v>34</v>
@@ -16229,7 +16229,7 @@
         <v>34</v>
       </c>
       <c r="E246" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="F246" t="s">
         <v>218</v>
@@ -16241,13 +16241,13 @@
         <v>513</v>
       </c>
       <c r="I246" t="s">
-        <v>438</v>
+        <v>518</v>
       </c>
       <c r="J246" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="K246" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L246" t="s">
         <v>34</v>
@@ -16259,10 +16259,10 @@
         <v>47</v>
       </c>
       <c r="O246" t="s">
-        <v>310</v>
+        <v>247</v>
       </c>
       <c r="P246" t="s">
-        <v>438</v>
+        <v>518</v>
       </c>
       <c r="Q246" t="s">
         <v>47</v>
@@ -16285,25 +16285,25 @@
         <v>34</v>
       </c>
       <c r="E247" t="s">
-        <v>354</v>
+        <v>275</v>
       </c>
       <c r="F247" t="s">
-        <v>499</v>
+        <v>218</v>
       </c>
       <c r="G247" t="s">
         <v>41</v>
       </c>
       <c r="H247" t="s">
-        <v>215</v>
+        <v>457</v>
       </c>
       <c r="I247" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="J247" t="s">
-        <v>90</v>
+        <v>320</v>
       </c>
       <c r="K247" t="s">
-        <v>229</v>
+        <v>58</v>
       </c>
       <c r="L247" t="s">
         <v>34</v>
@@ -16315,13 +16315,13 @@
         <v>47</v>
       </c>
       <c r="O247" t="s">
-        <v>34</v>
+        <v>105</v>
       </c>
       <c r="P247" t="s">
-        <v>34</v>
+        <v>520</v>
       </c>
       <c r="Q247" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R247" t="s">
         <v>34</v>
@@ -16341,7 +16341,7 @@
         <v>34</v>
       </c>
       <c r="E248" t="s">
-        <v>225</v>
+        <v>472</v>
       </c>
       <c r="F248" t="s">
         <v>218</v>
@@ -16353,13 +16353,13 @@
         <v>457</v>
       </c>
       <c r="I248" t="s">
-        <v>520</v>
+        <v>473</v>
       </c>
       <c r="J248" t="s">
-        <v>304</v>
+        <v>461</v>
       </c>
       <c r="K248" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="L248" t="s">
         <v>34</v>
@@ -16371,10 +16371,10 @@
         <v>47</v>
       </c>
       <c r="O248" t="s">
-        <v>102</v>
+        <v>475</v>
       </c>
       <c r="P248" t="s">
-        <v>520</v>
+        <v>473</v>
       </c>
       <c r="Q248" t="s">
         <v>47</v>
@@ -16397,25 +16397,25 @@
         <v>34</v>
       </c>
       <c r="E249" t="s">
-        <v>348</v>
+        <v>225</v>
       </c>
       <c r="F249" t="s">
-        <v>499</v>
+        <v>218</v>
       </c>
       <c r="G249" t="s">
         <v>41</v>
       </c>
       <c r="H249" t="s">
-        <v>215</v>
+        <v>457</v>
       </c>
       <c r="I249" t="s">
         <v>521</v>
       </c>
       <c r="J249" t="s">
-        <v>126</v>
+        <v>320</v>
       </c>
       <c r="K249" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="L249" t="s">
         <v>34</v>
@@ -16427,13 +16427,13 @@
         <v>47</v>
       </c>
       <c r="O249" t="s">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="P249" t="s">
-        <v>34</v>
+        <v>521</v>
       </c>
       <c r="Q249" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R249" t="s">
         <v>34</v>
@@ -16453,25 +16453,25 @@
         <v>34</v>
       </c>
       <c r="E250" t="s">
-        <v>363</v>
+        <v>232</v>
       </c>
       <c r="F250" t="s">
-        <v>499</v>
+        <v>218</v>
       </c>
       <c r="G250" t="s">
         <v>41</v>
       </c>
       <c r="H250" t="s">
-        <v>215</v>
+        <v>515</v>
       </c>
       <c r="I250" t="s">
-        <v>521</v>
+        <v>438</v>
       </c>
       <c r="J250" t="s">
-        <v>126</v>
+        <v>517</v>
       </c>
       <c r="K250" t="s">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="L250" t="s">
         <v>34</v>
@@ -16483,13 +16483,13 @@
         <v>47</v>
       </c>
       <c r="O250" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="P250" t="s">
-        <v>34</v>
+        <v>438</v>
       </c>
       <c r="Q250" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R250" t="s">
         <v>34</v>
@@ -17414,7 +17414,7 @@
         <v>41</v>
       </c>
       <c r="H267" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="I267" t="s">
         <v>554</v>
@@ -17924,7 +17924,7 @@
         <v>574</v>
       </c>
       <c r="J276" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K276" t="s">
         <v>96</v>
@@ -18036,7 +18036,7 @@
         <v>580</v>
       </c>
       <c r="J278" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K278" t="s">
         <v>96</v>
@@ -18092,7 +18092,7 @@
         <v>583</v>
       </c>
       <c r="J279" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K279" t="s">
         <v>96</v>
@@ -18148,7 +18148,7 @@
         <v>586</v>
       </c>
       <c r="J280" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K280" t="s">
         <v>75</v>
@@ -18260,7 +18260,7 @@
         <v>592</v>
       </c>
       <c r="J282" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K282" t="s">
         <v>96</v>
@@ -18316,7 +18316,7 @@
         <v>595</v>
       </c>
       <c r="J283" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K283" t="s">
         <v>96</v>
@@ -18372,7 +18372,7 @@
         <v>598</v>
       </c>
       <c r="J284" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K284" t="s">
         <v>96</v>
@@ -18428,7 +18428,7 @@
         <v>601</v>
       </c>
       <c r="J285" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K285" t="s">
         <v>96</v>
@@ -18484,7 +18484,7 @@
         <v>604</v>
       </c>
       <c r="J286" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K286" t="s">
         <v>96</v>
@@ -18540,7 +18540,7 @@
         <v>607</v>
       </c>
       <c r="J287" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K287" t="s">
         <v>85</v>
@@ -18596,7 +18596,7 @@
         <v>609</v>
       </c>
       <c r="J288" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K288" t="s">
         <v>96</v>
@@ -18652,7 +18652,7 @@
         <v>612</v>
       </c>
       <c r="J289" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K289" t="s">
         <v>96</v>
@@ -18708,7 +18708,7 @@
         <v>615</v>
       </c>
       <c r="J290" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K290" t="s">
         <v>96</v>
@@ -18764,7 +18764,7 @@
         <v>617</v>
       </c>
       <c r="J291" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K291" t="s">
         <v>96</v>
@@ -18820,7 +18820,7 @@
         <v>619</v>
       </c>
       <c r="J292" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K292" t="s">
         <v>96</v>
@@ -18835,7 +18835,7 @@
         <v>47</v>
       </c>
       <c r="O292" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="P292" t="s">
         <v>619</v>
@@ -18876,7 +18876,7 @@
         <v>621</v>
       </c>
       <c r="J293" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K293" t="s">
         <v>96</v>
@@ -18932,7 +18932,7 @@
         <v>624</v>
       </c>
       <c r="J294" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K294" t="s">
         <v>96</v>
@@ -18988,7 +18988,7 @@
         <v>627</v>
       </c>
       <c r="J295" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K295" t="s">
         <v>96</v>
@@ -19044,7 +19044,7 @@
         <v>630</v>
       </c>
       <c r="J296" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K296" t="s">
         <v>96</v>
@@ -19059,7 +19059,7 @@
         <v>47</v>
       </c>
       <c r="O296" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="P296" t="s">
         <v>630</v>
@@ -19100,7 +19100,7 @@
         <v>632</v>
       </c>
       <c r="J297" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K297" t="s">
         <v>96</v>
@@ -19156,7 +19156,7 @@
         <v>609</v>
       </c>
       <c r="J298" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K298" t="s">
         <v>96</v>
@@ -19940,7 +19940,7 @@
         <v>660</v>
       </c>
       <c r="J312" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K312" t="s">
         <v>96</v>
@@ -20627,7 +20627,7 @@
         <v>47</v>
       </c>
       <c r="O324" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="P324" t="s">
         <v>668</v>
@@ -20948,7 +20948,7 @@
         <v>674</v>
       </c>
       <c r="J330" t="s">
-        <v>335</v>
+        <v>293</v>
       </c>
       <c r="K330" t="s">
         <v>45</v>
@@ -21493,7 +21493,7 @@
         <v>33</v>
       </c>
       <c r="E340" t="s">
-        <v>175</v>
+        <v>672</v>
       </c>
       <c r="F340" t="s">
         <v>40</v>
@@ -21502,19 +21502,19 @@
         <v>41</v>
       </c>
       <c r="H340" t="s">
-        <v>447</v>
+        <v>702</v>
       </c>
       <c r="I340" t="s">
-        <v>155</v>
+        <v>703</v>
       </c>
       <c r="J340" t="s">
-        <v>122</v>
+        <v>685</v>
       </c>
       <c r="K340" t="s">
         <v>45</v>
       </c>
       <c r="L340" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="M340" t="s">
         <v>701</v>
@@ -21526,7 +21526,7 @@
         <v>48</v>
       </c>
       <c r="P340" t="s">
-        <v>155</v>
+        <v>703</v>
       </c>
       <c r="Q340" t="s">
         <v>47</v>
@@ -21549,28 +21549,28 @@
         <v>34</v>
       </c>
       <c r="E341" t="s">
-        <v>703</v>
+        <v>672</v>
       </c>
       <c r="F341" t="s">
-        <v>211</v>
+        <v>40</v>
       </c>
       <c r="G341" t="s">
         <v>41</v>
       </c>
       <c r="H341" t="s">
-        <v>215</v>
+        <v>705</v>
       </c>
       <c r="I341" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="J341" t="s">
-        <v>474</v>
+        <v>685</v>
       </c>
       <c r="K341" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="L341" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="M341" t="s">
         <v>701</v>
@@ -21582,7 +21582,7 @@
         <v>48</v>
       </c>
       <c r="P341" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="Q341" t="s">
         <v>47</v>
@@ -21614,7 +21614,7 @@
         <v>41</v>
       </c>
       <c r="H342" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="I342" t="s">
         <v>694</v>
@@ -21626,7 +21626,7 @@
         <v>45</v>
       </c>
       <c r="L342" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="M342" t="s">
         <v>701</v>
@@ -21670,10 +21670,10 @@
         <v>41</v>
       </c>
       <c r="H343" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="I343" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="J343" t="s">
         <v>685</v>
@@ -21682,7 +21682,7 @@
         <v>45</v>
       </c>
       <c r="L343" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="M343" t="s">
         <v>701</v>
@@ -21694,7 +21694,7 @@
         <v>48</v>
       </c>
       <c r="P343" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="Q343" t="s">
         <v>47</v>
@@ -21726,10 +21726,10 @@
         <v>41</v>
       </c>
       <c r="H344" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="I344" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="J344" t="s">
         <v>685</v>
@@ -21738,7 +21738,7 @@
         <v>45</v>
       </c>
       <c r="L344" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="M344" t="s">
         <v>701</v>
@@ -21750,7 +21750,7 @@
         <v>48</v>
       </c>
       <c r="P344" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="Q344" t="s">
         <v>47</v>
@@ -21782,19 +21782,19 @@
         <v>41</v>
       </c>
       <c r="H345" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="I345" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="J345" t="s">
-        <v>335</v>
+        <v>685</v>
       </c>
       <c r="K345" t="s">
         <v>45</v>
       </c>
       <c r="L345" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="M345" t="s">
         <v>701</v>
@@ -21806,7 +21806,7 @@
         <v>48</v>
       </c>
       <c r="P345" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="Q345" t="s">
         <v>47</v>
@@ -21838,19 +21838,19 @@
         <v>41</v>
       </c>
       <c r="H346" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="I346" t="s">
-        <v>708</v>
+        <v>718</v>
       </c>
       <c r="J346" t="s">
-        <v>685</v>
+        <v>293</v>
       </c>
       <c r="K346" t="s">
         <v>45</v>
       </c>
       <c r="L346" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="M346" t="s">
         <v>701</v>
@@ -21862,7 +21862,7 @@
         <v>48</v>
       </c>
       <c r="P346" t="s">
-        <v>708</v>
+        <v>718</v>
       </c>
       <c r="Q346" t="s">
         <v>47</v>
@@ -21894,10 +21894,10 @@
         <v>41</v>
       </c>
       <c r="H347" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="I347" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="J347" t="s">
         <v>685</v>
@@ -21906,7 +21906,7 @@
         <v>45</v>
       </c>
       <c r="L347" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="M347" t="s">
         <v>701</v>
@@ -21918,7 +21918,7 @@
         <v>48</v>
       </c>
       <c r="P347" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="Q347" t="s">
         <v>47</v>
@@ -21941,7 +21941,7 @@
         <v>34</v>
       </c>
       <c r="E348" t="s">
-        <v>672</v>
+        <v>175</v>
       </c>
       <c r="F348" t="s">
         <v>40</v>
@@ -21950,19 +21950,19 @@
         <v>41</v>
       </c>
       <c r="H348" t="s">
-        <v>457</v>
+        <v>722</v>
       </c>
       <c r="I348" t="s">
-        <v>694</v>
+        <v>155</v>
       </c>
       <c r="J348" t="s">
-        <v>335</v>
+        <v>122</v>
       </c>
       <c r="K348" t="s">
-        <v>45</v>
+        <v>122</v>
       </c>
       <c r="L348" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="M348" t="s">
         <v>701</v>
@@ -21974,7 +21974,7 @@
         <v>48</v>
       </c>
       <c r="P348" t="s">
-        <v>694</v>
+        <v>155</v>
       </c>
       <c r="Q348" t="s">
         <v>47</v>
@@ -21997,28 +21997,28 @@
         <v>34</v>
       </c>
       <c r="E349" t="s">
-        <v>722</v>
+        <v>175</v>
       </c>
       <c r="F349" t="s">
-        <v>211</v>
+        <v>40</v>
       </c>
       <c r="G349" t="s">
         <v>41</v>
       </c>
       <c r="H349" t="s">
-        <v>556</v>
+        <v>447</v>
       </c>
       <c r="I349" t="s">
-        <v>694</v>
+        <v>155</v>
       </c>
       <c r="J349" t="s">
-        <v>474</v>
+        <v>122</v>
       </c>
       <c r="K349" t="s">
-        <v>122</v>
+        <v>45</v>
       </c>
       <c r="L349" t="s">
-        <v>34</v>
+        <v>724</v>
       </c>
       <c r="M349" t="s">
         <v>701</v>
@@ -22030,7 +22030,7 @@
         <v>48</v>
       </c>
       <c r="P349" t="s">
-        <v>694</v>
+        <v>155</v>
       </c>
       <c r="Q349" t="s">
         <v>47</v>
@@ -22053,28 +22053,28 @@
         <v>34</v>
       </c>
       <c r="E350" t="s">
-        <v>175</v>
+        <v>725</v>
       </c>
       <c r="F350" t="s">
-        <v>40</v>
+        <v>211</v>
       </c>
       <c r="G350" t="s">
         <v>41</v>
       </c>
       <c r="H350" t="s">
-        <v>723</v>
+        <v>215</v>
       </c>
       <c r="I350" t="s">
-        <v>155</v>
+        <v>726</v>
       </c>
       <c r="J350" t="s">
-        <v>122</v>
+        <v>474</v>
       </c>
       <c r="K350" t="s">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="L350" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="M350" t="s">
         <v>701</v>
@@ -22086,7 +22086,7 @@
         <v>48</v>
       </c>
       <c r="P350" t="s">
-        <v>155</v>
+        <v>726</v>
       </c>
       <c r="Q350" t="s">
         <v>47</v>
@@ -22118,19 +22118,19 @@
         <v>41</v>
       </c>
       <c r="H351" t="s">
-        <v>725</v>
+        <v>457</v>
       </c>
       <c r="I351" t="s">
         <v>694</v>
       </c>
       <c r="J351" t="s">
-        <v>685</v>
+        <v>293</v>
       </c>
       <c r="K351" t="s">
         <v>45</v>
       </c>
       <c r="L351" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="M351" t="s">
         <v>701</v>
@@ -22165,7 +22165,7 @@
         <v>34</v>
       </c>
       <c r="E352" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="F352" t="s">
         <v>211</v>
@@ -22177,7 +22177,7 @@
         <v>425</v>
       </c>
       <c r="I352" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="J352" t="s">
         <v>474</v>
@@ -22198,7 +22198,7 @@
         <v>48</v>
       </c>
       <c r="P352" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="Q352" t="s">
         <v>47</v>
@@ -22221,28 +22221,28 @@
         <v>34</v>
       </c>
       <c r="E353" t="s">
-        <v>672</v>
+        <v>731</v>
       </c>
       <c r="F353" t="s">
-        <v>40</v>
+        <v>211</v>
       </c>
       <c r="G353" t="s">
         <v>41</v>
       </c>
       <c r="H353" t="s">
-        <v>729</v>
+        <v>556</v>
       </c>
       <c r="I353" t="s">
-        <v>730</v>
+        <v>694</v>
       </c>
       <c r="J353" t="s">
-        <v>685</v>
+        <v>474</v>
       </c>
       <c r="K353" t="s">
-        <v>45</v>
+        <v>122</v>
       </c>
       <c r="L353" t="s">
-        <v>731</v>
+        <v>34</v>
       </c>
       <c r="M353" t="s">
         <v>701</v>
@@ -22254,7 +22254,7 @@
         <v>48</v>
       </c>
       <c r="P353" t="s">
-        <v>730</v>
+        <v>694</v>
       </c>
       <c r="Q353" t="s">
         <v>47</v>
@@ -23692,7 +23692,7 @@
         <v>805</v>
       </c>
       <c r="J379" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K379" t="s">
         <v>75</v>
@@ -23804,7 +23804,7 @@
         <v>812</v>
       </c>
       <c r="J381" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K381" t="s">
         <v>96</v>
@@ -23860,7 +23860,7 @@
         <v>816</v>
       </c>
       <c r="J382" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K382" t="s">
         <v>96</v>
@@ -23972,7 +23972,7 @@
         <v>824</v>
       </c>
       <c r="J384" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K384" t="s">
         <v>122</v>
@@ -24028,7 +24028,7 @@
         <v>828</v>
       </c>
       <c r="J385" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K385" t="s">
         <v>96</v>
@@ -24364,7 +24364,7 @@
         <v>852</v>
       </c>
       <c r="J391" t="s">
-        <v>335</v>
+        <v>293</v>
       </c>
       <c r="K391" t="s">
         <v>45</v>
@@ -24420,7 +24420,7 @@
         <v>856</v>
       </c>
       <c r="J392" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K392" t="s">
         <v>122</v>
@@ -24476,7 +24476,7 @@
         <v>858</v>
       </c>
       <c r="J393" t="s">
-        <v>335</v>
+        <v>293</v>
       </c>
       <c r="K393" t="s">
         <v>859</v>
@@ -24532,7 +24532,7 @@
         <v>861</v>
       </c>
       <c r="J394" t="s">
-        <v>335</v>
+        <v>293</v>
       </c>
       <c r="K394" t="s">
         <v>859</v>
@@ -25596,7 +25596,7 @@
         <v>923</v>
       </c>
       <c r="J413" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K413" t="s">
         <v>96</v>
@@ -25805,7 +25805,7 @@
         <v>33</v>
       </c>
       <c r="E417" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="F417" t="s">
         <v>218</v>
@@ -25820,10 +25820,10 @@
         <v>930</v>
       </c>
       <c r="J417" t="s">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="K417" t="s">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="L417" t="s">
         <v>931</v>
@@ -25835,7 +25835,7 @@
         <v>47</v>
       </c>
       <c r="O417" t="s">
-        <v>130</v>
+        <v>247</v>
       </c>
       <c r="P417" t="s">
         <v>930</v>
@@ -25870,10 +25870,10 @@
         <v>41</v>
       </c>
       <c r="H418" t="s">
+        <v>929</v>
+      </c>
+      <c r="I418" t="s">
         <v>932</v>
-      </c>
-      <c r="I418" t="s">
-        <v>933</v>
       </c>
       <c r="J418" t="s">
         <v>80</v>
@@ -25894,7 +25894,7 @@
         <v>255</v>
       </c>
       <c r="P418" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="Q418" t="s">
         <v>47</v>
@@ -25917,7 +25917,7 @@
         <v>34</v>
       </c>
       <c r="E419" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="F419" t="s">
         <v>218</v>
@@ -25926,16 +25926,16 @@
         <v>41</v>
       </c>
       <c r="H419" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="I419" t="s">
         <v>934</v>
       </c>
       <c r="J419" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="K419" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="L419" t="s">
         <v>931</v>
@@ -25947,7 +25947,7 @@
         <v>47</v>
       </c>
       <c r="O419" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="P419" t="s">
         <v>934</v>
@@ -25973,7 +25973,7 @@
         <v>34</v>
       </c>
       <c r="E420" t="s">
-        <v>275</v>
+        <v>227</v>
       </c>
       <c r="F420" t="s">
         <v>218</v>
@@ -25982,16 +25982,16 @@
         <v>41</v>
       </c>
       <c r="H420" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="I420" t="s">
         <v>935</v>
       </c>
       <c r="J420" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="K420" t="s">
-        <v>58</v>
+        <v>229</v>
       </c>
       <c r="L420" t="s">
         <v>931</v>
@@ -26003,7 +26003,7 @@
         <v>47</v>
       </c>
       <c r="O420" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="P420" t="s">
         <v>935</v>
@@ -26029,7 +26029,7 @@
         <v>34</v>
       </c>
       <c r="E421" t="s">
-        <v>232</v>
+        <v>275</v>
       </c>
       <c r="F421" t="s">
         <v>218</v>
@@ -26038,16 +26038,16 @@
         <v>41</v>
       </c>
       <c r="H421" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="I421" t="s">
         <v>936</v>
       </c>
       <c r="J421" t="s">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="K421" t="s">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="L421" t="s">
         <v>931</v>
@@ -26059,7 +26059,7 @@
         <v>47</v>
       </c>
       <c r="O421" t="s">
-        <v>310</v>
+        <v>105</v>
       </c>
       <c r="P421" t="s">
         <v>936</v>
@@ -26085,7 +26085,7 @@
         <v>34</v>
       </c>
       <c r="E422" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="F422" t="s">
         <v>218</v>
@@ -26094,16 +26094,16 @@
         <v>41</v>
       </c>
       <c r="H422" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="I422" t="s">
         <v>937</v>
       </c>
       <c r="J422" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="K422" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="L422" t="s">
         <v>931</v>
@@ -26115,7 +26115,7 @@
         <v>47</v>
       </c>
       <c r="O422" t="s">
-        <v>250</v>
+        <v>102</v>
       </c>
       <c r="P422" t="s">
         <v>937</v>
@@ -26141,7 +26141,7 @@
         <v>34</v>
       </c>
       <c r="E423" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="F423" t="s">
         <v>218</v>
@@ -26150,16 +26150,16 @@
         <v>41</v>
       </c>
       <c r="H423" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="I423" t="s">
         <v>938</v>
       </c>
       <c r="J423" t="s">
-        <v>90</v>
+        <v>126</v>
       </c>
       <c r="K423" t="s">
-        <v>229</v>
+        <v>119</v>
       </c>
       <c r="L423" t="s">
         <v>931</v>
@@ -26171,7 +26171,7 @@
         <v>47</v>
       </c>
       <c r="O423" t="s">
-        <v>91</v>
+        <v>436</v>
       </c>
       <c r="P423" t="s">
         <v>938</v>
@@ -26197,7 +26197,7 @@
         <v>34</v>
       </c>
       <c r="E424" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="F424" t="s">
         <v>218</v>
@@ -26206,16 +26206,16 @@
         <v>41</v>
       </c>
       <c r="H424" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="I424" t="s">
         <v>939</v>
       </c>
       <c r="J424" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="K424" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="L424" t="s">
         <v>931</v>
@@ -26227,7 +26227,7 @@
         <v>47</v>
       </c>
       <c r="O424" t="s">
-        <v>102</v>
+        <v>466</v>
       </c>
       <c r="P424" t="s">
         <v>939</v>
@@ -26253,7 +26253,7 @@
         <v>34</v>
       </c>
       <c r="E425" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="F425" t="s">
         <v>218</v>
@@ -26262,16 +26262,16 @@
         <v>41</v>
       </c>
       <c r="H425" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="I425" t="s">
         <v>940</v>
       </c>
       <c r="J425" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="K425" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="L425" t="s">
         <v>931</v>
@@ -26283,7 +26283,7 @@
         <v>47</v>
       </c>
       <c r="O425" t="s">
-        <v>247</v>
+        <v>114</v>
       </c>
       <c r="P425" t="s">
         <v>940</v>
@@ -26309,7 +26309,7 @@
         <v>34</v>
       </c>
       <c r="E426" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="F426" t="s">
         <v>218</v>
@@ -26318,16 +26318,16 @@
         <v>41</v>
       </c>
       <c r="H426" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="I426" t="s">
         <v>941</v>
       </c>
       <c r="J426" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="K426" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="L426" t="s">
         <v>931</v>
@@ -26339,7 +26339,7 @@
         <v>47</v>
       </c>
       <c r="O426" t="s">
-        <v>156</v>
+        <v>308</v>
       </c>
       <c r="P426" t="s">
         <v>941</v>
@@ -26365,7 +26365,7 @@
         <v>34</v>
       </c>
       <c r="E427" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="F427" t="s">
         <v>218</v>
@@ -26374,13 +26374,13 @@
         <v>41</v>
       </c>
       <c r="H427" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="I427" t="s">
         <v>942</v>
       </c>
       <c r="J427" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="K427" t="s">
         <v>119</v>
@@ -26395,7 +26395,7 @@
         <v>47</v>
       </c>
       <c r="O427" t="s">
-        <v>436</v>
+        <v>156</v>
       </c>
       <c r="P427" t="s">
         <v>942</v>
@@ -26421,7 +26421,7 @@
         <v>34</v>
       </c>
       <c r="E428" t="s">
-        <v>217</v>
+        <v>248</v>
       </c>
       <c r="F428" t="s">
         <v>218</v>
@@ -26430,13 +26430,13 @@
         <v>41</v>
       </c>
       <c r="H428" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="I428" t="s">
         <v>943</v>
       </c>
       <c r="J428" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="K428" t="s">
         <v>119</v>
@@ -26451,7 +26451,7 @@
         <v>47</v>
       </c>
       <c r="O428" t="s">
-        <v>466</v>
+        <v>250</v>
       </c>
       <c r="P428" t="s">
         <v>943</v>

--- a/xlsx/dre/DRE_02_2026.xlsx
+++ b/xlsx/dre/DRE_02_2026.xlsx
@@ -2028,15 +2028,15 @@
     <t>4.03.03.02.05.02 Assistência técnica medição</t>
   </si>
   <si>
+    <t>L E A Medicoes Tecnicas LTDA</t>
+  </si>
+  <si>
+    <t>R$  180,00</t>
+  </si>
+  <si>
     <t>PFP</t>
   </si>
   <si>
-    <t>L E A Medicoes Tecnicas LTDA</t>
-  </si>
-  <si>
-    <t>R$  180,00</t>
-  </si>
-  <si>
     <t>4.03.03.09 Marketing - mídias / ações comerciais / outros (CV)</t>
   </si>
   <si>
@@ -2058,6 +2058,27 @@
     <t>Google 2026</t>
   </si>
   <si>
+    <t>WEBGIGA SOLUCOES DIGITAIS LTDA</t>
+  </si>
+  <si>
+    <t>R$  4.588,50</t>
+  </si>
+  <si>
+    <t>Webgiga 2026</t>
+  </si>
+  <si>
+    <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
+  </si>
+  <si>
+    <t>R$  808,50</t>
+  </si>
+  <si>
+    <t>08/01/26</t>
+  </si>
+  <si>
+    <t>MHM - Honorários 2026</t>
+  </si>
+  <si>
     <t>498/1</t>
   </si>
   <si>
@@ -2070,27 +2091,6 @@
     <t>30/01/26</t>
   </si>
   <si>
-    <t>WEBGIGA SOLUCOES DIGITAIS LTDA</t>
-  </si>
-  <si>
-    <t>R$  4.588,50</t>
-  </si>
-  <si>
-    <t>Webgiga 2026</t>
-  </si>
-  <si>
-    <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
-  </si>
-  <si>
-    <t>R$  808,50</t>
-  </si>
-  <si>
-    <t>08/01/26</t>
-  </si>
-  <si>
-    <t>MHM - Honorários 2026</t>
-  </si>
-  <si>
     <t>4.04 DESPESAS ADMINISTRATIVAS</t>
   </si>
   <si>
@@ -2295,12 +2295,12 @@
     <t>VT fev 26/1</t>
   </si>
   <si>
+    <t>R$  313,70</t>
+  </si>
+  <si>
     <t>R$  433,98</t>
   </si>
   <si>
-    <t>R$  313,70</t>
-  </si>
-  <si>
     <t>4.04.02 GASTOS GERAIS ADMINISTRATIVOS</t>
   </si>
   <si>
@@ -2439,25 +2439,17 @@
     <t>R$  45,00</t>
   </si>
   <si>
-    <t>532/1</t>
-  </si>
-  <si>
-    <t>DIA BRASIL SUPERMERCADO</t>
-  </si>
-  <si>
-    <t>R$  59,96</t>
-  </si>
-  <si>
-    <t>cafés</t>
-  </si>
-  <si>
-    <t>502/1</t>
-  </si>
-  <si>
-    <t>R$  100,00</t>
-  </si>
-  <si>
-    <t>Cópia de chaves</t>
+    <t>531/1</t>
+  </si>
+  <si>
+    <t>Shopee</t>
+  </si>
+  <si>
+    <t>R$  65,93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freeco refil
+</t>
   </si>
   <si>
     <t>533/1</t>
@@ -2470,6 +2462,19 @@
   </si>
   <si>
     <t>material limpeza</t>
+  </si>
+  <si>
+    <t>530/1</t>
+  </si>
+  <si>
+    <t>Marinete</t>
+  </si>
+  <si>
+    <t>R$  17,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copo descartável para crianças
+</t>
   </si>
   <si>
     <t>529/1</t>
@@ -2486,6 +2491,27 @@
 </t>
   </si>
   <si>
+    <t>502/1</t>
+  </si>
+  <si>
+    <t>R$  100,00</t>
+  </si>
+  <si>
+    <t>Cópia de chaves</t>
+  </si>
+  <si>
+    <t>532/1</t>
+  </si>
+  <si>
+    <t>DIA BRASIL SUPERMERCADO</t>
+  </si>
+  <si>
+    <t>R$  59,96</t>
+  </si>
+  <si>
+    <t>cafés</t>
+  </si>
+  <si>
     <t>505/1</t>
   </si>
   <si>
@@ -2498,32 +2524,6 @@
     <t>Conserto vidro adega</t>
   </si>
   <si>
-    <t>531/1</t>
-  </si>
-  <si>
-    <t>Shopee</t>
-  </si>
-  <si>
-    <t>R$  65,93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freeco refil
-</t>
-  </si>
-  <si>
-    <t>530/1</t>
-  </si>
-  <si>
-    <t>Marinete</t>
-  </si>
-  <si>
-    <t>R$  17,00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Copo descartável para crianças
-</t>
-  </si>
-  <si>
     <t>4.04.02.07 Informática</t>
   </si>
   <si>
@@ -2587,6 +2587,15 @@
     <t>4.04.02.08.03 Mensalidades e assinaturas - outros gastos</t>
   </si>
   <si>
+    <t>534/1</t>
+  </si>
+  <si>
+    <t>Pipefy</t>
+  </si>
+  <si>
+    <t>R$  197,63</t>
+  </si>
+  <si>
     <t>D4 sign</t>
   </si>
   <si>
@@ -2596,15 +2605,6 @@
     <t>D4 sign 2026</t>
   </si>
   <si>
-    <t>534/1</t>
-  </si>
-  <si>
-    <t>Pipefy</t>
-  </si>
-  <si>
-    <t>R$  197,63</t>
-  </si>
-  <si>
     <t>10/2</t>
   </si>
   <si>
@@ -2617,19 +2617,19 @@
     <t>Promob 2026-1</t>
   </si>
   <si>
+    <t>3/1</t>
+  </si>
+  <si>
+    <t>R$  1.248,76</t>
+  </si>
+  <si>
+    <t>Promob 2026/2</t>
+  </si>
+  <si>
     <t>R$  599,00</t>
   </si>
   <si>
     <t>Promob 2026</t>
-  </si>
-  <si>
-    <t>3/1</t>
-  </si>
-  <si>
-    <t>R$  1.248,76</t>
-  </si>
-  <si>
-    <t>Promob 2026/2</t>
   </si>
   <si>
     <t>4.04.02.11 Manutenção de predio e equipamentos</t>
@@ -2726,6 +2726,15 @@
     <t>R$ 400,33</t>
   </si>
   <si>
+    <t>Jackson Fernando de Araujo</t>
+  </si>
+  <si>
+    <t>R$  150,00</t>
+  </si>
+  <si>
+    <t>Segurança 2026</t>
+  </si>
+  <si>
     <t>VERISURE</t>
   </si>
   <si>
@@ -2733,15 +2742,6 @@
   </si>
   <si>
     <t>Verisure - Alarme 2026</t>
-  </si>
-  <si>
-    <t>Jackson Fernando de Araujo</t>
-  </si>
-  <si>
-    <t>R$  150,00</t>
-  </si>
-  <si>
-    <t>Segurança 2026</t>
   </si>
   <si>
     <t>4.04.02.14.08 Site e newsletter da loja</t>
@@ -20093,25 +20093,25 @@
         <v>33</v>
       </c>
       <c r="E315" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="F315" t="s">
+        <v>40</v>
+      </c>
+      <c r="G315" t="s">
+        <v>41</v>
+      </c>
+      <c r="H315" t="s">
         <v>666</v>
       </c>
-      <c r="G315" t="s">
-        <v>41</v>
-      </c>
-      <c r="H315" t="s">
+      <c r="I315" t="s">
         <v>667</v>
       </c>
-      <c r="I315" t="s">
-        <v>668</v>
-      </c>
       <c r="J315" t="s">
-        <v>191</v>
+        <v>90</v>
       </c>
       <c r="K315" t="s">
-        <v>191</v>
+        <v>90</v>
       </c>
       <c r="L315" t="s">
         <v>34</v>
@@ -20123,13 +20123,13 @@
         <v>47</v>
       </c>
       <c r="O315" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="P315" t="s">
-        <v>34</v>
+        <v>667</v>
       </c>
       <c r="Q315" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R315" t="s">
         <v>34</v>
@@ -20149,7 +20149,7 @@
         <v>34</v>
       </c>
       <c r="E316" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="F316" t="s">
         <v>40</v>
@@ -20158,16 +20158,16 @@
         <v>41</v>
       </c>
       <c r="H316" t="s">
+        <v>666</v>
+      </c>
+      <c r="I316" t="s">
         <v>667</v>
       </c>
-      <c r="I316" t="s">
-        <v>668</v>
-      </c>
       <c r="J316" t="s">
-        <v>147</v>
+        <v>119</v>
       </c>
       <c r="K316" t="s">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="L316" t="s">
         <v>34</v>
@@ -20179,10 +20179,10 @@
         <v>47</v>
       </c>
       <c r="O316" t="s">
-        <v>114</v>
+        <v>247</v>
       </c>
       <c r="P316" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="Q316" t="s">
         <v>47</v>
@@ -20205,7 +20205,7 @@
         <v>34</v>
       </c>
       <c r="E317" t="s">
-        <v>275</v>
+        <v>248</v>
       </c>
       <c r="F317" t="s">
         <v>40</v>
@@ -20214,16 +20214,16 @@
         <v>41</v>
       </c>
       <c r="H317" t="s">
+        <v>666</v>
+      </c>
+      <c r="I317" t="s">
         <v>667</v>
       </c>
-      <c r="I317" t="s">
-        <v>668</v>
-      </c>
       <c r="J317" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="K317" t="s">
-        <v>58</v>
+        <v>119</v>
       </c>
       <c r="L317" t="s">
         <v>34</v>
@@ -20235,10 +20235,10 @@
         <v>47</v>
       </c>
       <c r="O317" t="s">
-        <v>105</v>
+        <v>250</v>
       </c>
       <c r="P317" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="Q317" t="s">
         <v>47</v>
@@ -20261,22 +20261,22 @@
         <v>34</v>
       </c>
       <c r="E318" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F318" t="s">
+        <v>40</v>
+      </c>
+      <c r="G318" t="s">
+        <v>41</v>
+      </c>
+      <c r="H318" t="s">
         <v>666</v>
       </c>
-      <c r="G318" t="s">
-        <v>41</v>
-      </c>
-      <c r="H318" t="s">
+      <c r="I318" t="s">
         <v>667</v>
       </c>
-      <c r="I318" t="s">
-        <v>668</v>
-      </c>
       <c r="J318" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K318" t="s">
         <v>119</v>
@@ -20291,13 +20291,13 @@
         <v>47</v>
       </c>
       <c r="O318" t="s">
-        <v>34</v>
+        <v>130</v>
       </c>
       <c r="P318" t="s">
-        <v>34</v>
+        <v>667</v>
       </c>
       <c r="Q318" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R318" t="s">
         <v>34</v>
@@ -20317,7 +20317,7 @@
         <v>34</v>
       </c>
       <c r="E319" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="F319" t="s">
         <v>40</v>
@@ -20326,16 +20326,16 @@
         <v>41</v>
       </c>
       <c r="H319" t="s">
+        <v>666</v>
+      </c>
+      <c r="I319" t="s">
         <v>667</v>
       </c>
-      <c r="I319" t="s">
-        <v>668</v>
-      </c>
       <c r="J319" t="s">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="K319" t="s">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="L319" t="s">
         <v>34</v>
@@ -20347,10 +20347,10 @@
         <v>47</v>
       </c>
       <c r="O319" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="P319" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="Q319" t="s">
         <v>47</v>
@@ -20373,25 +20373,25 @@
         <v>34</v>
       </c>
       <c r="E320" t="s">
-        <v>157</v>
+        <v>227</v>
       </c>
       <c r="F320" t="s">
-        <v>40</v>
+        <v>668</v>
       </c>
       <c r="G320" t="s">
         <v>41</v>
       </c>
       <c r="H320" t="s">
+        <v>666</v>
+      </c>
+      <c r="I320" t="s">
         <v>667</v>
       </c>
-      <c r="I320" t="s">
-        <v>668</v>
-      </c>
       <c r="J320" t="s">
-        <v>134</v>
+        <v>90</v>
       </c>
       <c r="K320" t="s">
-        <v>134</v>
+        <v>229</v>
       </c>
       <c r="L320" t="s">
         <v>34</v>
@@ -20403,13 +20403,13 @@
         <v>47</v>
       </c>
       <c r="O320" t="s">
-        <v>463</v>
+        <v>34</v>
       </c>
       <c r="P320" t="s">
-        <v>668</v>
+        <v>34</v>
       </c>
       <c r="Q320" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R320" t="s">
         <v>34</v>
@@ -20429,25 +20429,25 @@
         <v>34</v>
       </c>
       <c r="E321" t="s">
-        <v>221</v>
+        <v>256</v>
       </c>
       <c r="F321" t="s">
+        <v>668</v>
+      </c>
+      <c r="G321" t="s">
+        <v>41</v>
+      </c>
+      <c r="H321" t="s">
         <v>666</v>
       </c>
-      <c r="G321" t="s">
-        <v>41</v>
-      </c>
-      <c r="H321" t="s">
+      <c r="I321" t="s">
         <v>667</v>
       </c>
-      <c r="I321" t="s">
-        <v>668</v>
-      </c>
       <c r="J321" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K321" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L321" t="s">
         <v>34</v>
@@ -20485,25 +20485,25 @@
         <v>34</v>
       </c>
       <c r="E322" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="F322" t="s">
-        <v>40</v>
+        <v>668</v>
       </c>
       <c r="G322" t="s">
         <v>41</v>
       </c>
       <c r="H322" t="s">
+        <v>666</v>
+      </c>
+      <c r="I322" t="s">
         <v>667</v>
       </c>
-      <c r="I322" t="s">
-        <v>668</v>
-      </c>
       <c r="J322" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="K322" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="L322" t="s">
         <v>34</v>
@@ -20515,13 +20515,13 @@
         <v>47</v>
       </c>
       <c r="O322" t="s">
-        <v>255</v>
+        <v>34</v>
       </c>
       <c r="P322" t="s">
-        <v>668</v>
+        <v>34</v>
       </c>
       <c r="Q322" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R322" t="s">
         <v>34</v>
@@ -20541,7 +20541,7 @@
         <v>34</v>
       </c>
       <c r="E323" t="s">
-        <v>244</v>
+        <v>157</v>
       </c>
       <c r="F323" t="s">
         <v>40</v>
@@ -20550,16 +20550,16 @@
         <v>41</v>
       </c>
       <c r="H323" t="s">
+        <v>666</v>
+      </c>
+      <c r="I323" t="s">
         <v>667</v>
       </c>
-      <c r="I323" t="s">
-        <v>668</v>
-      </c>
       <c r="J323" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="K323" t="s">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="L323" t="s">
         <v>34</v>
@@ -20571,10 +20571,10 @@
         <v>47</v>
       </c>
       <c r="O323" t="s">
-        <v>247</v>
+        <v>463</v>
       </c>
       <c r="P323" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="Q323" t="s">
         <v>47</v>
@@ -20597,7 +20597,7 @@
         <v>34</v>
       </c>
       <c r="E324" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="F324" t="s">
         <v>40</v>
@@ -20606,16 +20606,16 @@
         <v>41</v>
       </c>
       <c r="H324" t="s">
+        <v>666</v>
+      </c>
+      <c r="I324" t="s">
         <v>667</v>
       </c>
-      <c r="I324" t="s">
-        <v>668</v>
-      </c>
       <c r="J324" t="s">
-        <v>90</v>
+        <v>147</v>
       </c>
       <c r="K324" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="L324" t="s">
         <v>34</v>
@@ -20627,10 +20627,10 @@
         <v>47</v>
       </c>
       <c r="O324" t="s">
-        <v>308</v>
+        <v>114</v>
       </c>
       <c r="P324" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="Q324" t="s">
         <v>47</v>
@@ -20653,7 +20653,7 @@
         <v>34</v>
       </c>
       <c r="E325" t="s">
-        <v>225</v>
+        <v>275</v>
       </c>
       <c r="F325" t="s">
         <v>40</v>
@@ -20662,16 +20662,16 @@
         <v>41</v>
       </c>
       <c r="H325" t="s">
+        <v>666</v>
+      </c>
+      <c r="I325" t="s">
         <v>667</v>
       </c>
-      <c r="I325" t="s">
-        <v>668</v>
-      </c>
       <c r="J325" t="s">
-        <v>178</v>
+        <v>96</v>
       </c>
       <c r="K325" t="s">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="L325" t="s">
         <v>34</v>
@@ -20683,10 +20683,10 @@
         <v>47</v>
       </c>
       <c r="O325" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="P325" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="Q325" t="s">
         <v>47</v>
@@ -20709,25 +20709,25 @@
         <v>34</v>
       </c>
       <c r="E326" t="s">
-        <v>256</v>
+        <v>221</v>
       </c>
       <c r="F326" t="s">
+        <v>668</v>
+      </c>
+      <c r="G326" t="s">
+        <v>41</v>
+      </c>
+      <c r="H326" t="s">
         <v>666</v>
       </c>
-      <c r="G326" t="s">
-        <v>41</v>
-      </c>
-      <c r="H326" t="s">
+      <c r="I326" t="s">
         <v>667</v>
       </c>
-      <c r="I326" t="s">
-        <v>668</v>
-      </c>
       <c r="J326" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K326" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L326" t="s">
         <v>34</v>
@@ -20765,25 +20765,25 @@
         <v>34</v>
       </c>
       <c r="E327" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="F327" t="s">
-        <v>40</v>
+        <v>668</v>
       </c>
       <c r="G327" t="s">
         <v>41</v>
       </c>
       <c r="H327" t="s">
+        <v>666</v>
+      </c>
+      <c r="I327" t="s">
         <v>667</v>
       </c>
-      <c r="I327" t="s">
-        <v>668</v>
-      </c>
       <c r="J327" t="s">
-        <v>118</v>
+        <v>191</v>
       </c>
       <c r="K327" t="s">
-        <v>119</v>
+        <v>191</v>
       </c>
       <c r="L327" t="s">
         <v>34</v>
@@ -20795,13 +20795,13 @@
         <v>47</v>
       </c>
       <c r="O327" t="s">
-        <v>130</v>
+        <v>34</v>
       </c>
       <c r="P327" t="s">
-        <v>668</v>
+        <v>34</v>
       </c>
       <c r="Q327" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R327" t="s">
         <v>34</v>
@@ -20821,25 +20821,25 @@
         <v>34</v>
       </c>
       <c r="E328" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F328" t="s">
+        <v>40</v>
+      </c>
+      <c r="G328" t="s">
+        <v>41</v>
+      </c>
+      <c r="H328" t="s">
         <v>666</v>
       </c>
-      <c r="G328" t="s">
-        <v>41</v>
-      </c>
-      <c r="H328" t="s">
+      <c r="I328" t="s">
         <v>667</v>
       </c>
-      <c r="I328" t="s">
-        <v>668</v>
-      </c>
       <c r="J328" t="s">
-        <v>90</v>
+        <v>178</v>
       </c>
       <c r="K328" t="s">
-        <v>229</v>
+        <v>101</v>
       </c>
       <c r="L328" t="s">
         <v>34</v>
@@ -20851,13 +20851,13 @@
         <v>47</v>
       </c>
       <c r="O328" t="s">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="P328" t="s">
-        <v>34</v>
+        <v>667</v>
       </c>
       <c r="Q328" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R328" t="s">
         <v>34</v>
@@ -20989,28 +20989,28 @@
         <v>34</v>
       </c>
       <c r="E331" t="s">
+        <v>175</v>
+      </c>
+      <c r="F331" t="s">
+        <v>40</v>
+      </c>
+      <c r="G331" t="s">
+        <v>41</v>
+      </c>
+      <c r="H331" t="s">
         <v>676</v>
       </c>
-      <c r="F331" t="s">
-        <v>211</v>
-      </c>
-      <c r="G331" t="s">
-        <v>41</v>
-      </c>
-      <c r="H331" t="s">
+      <c r="I331" t="s">
         <v>677</v>
       </c>
-      <c r="I331" t="s">
+      <c r="J331" t="s">
+        <v>178</v>
+      </c>
+      <c r="K331" t="s">
+        <v>178</v>
+      </c>
+      <c r="L331" t="s">
         <v>678</v>
-      </c>
-      <c r="J331" t="s">
-        <v>679</v>
-      </c>
-      <c r="K331" t="s">
-        <v>229</v>
-      </c>
-      <c r="L331" t="s">
-        <v>34</v>
       </c>
       <c r="M331" t="s">
         <v>671</v>
@@ -21022,7 +21022,7 @@
         <v>48</v>
       </c>
       <c r="P331" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="Q331" t="s">
         <v>47</v>
@@ -21045,7 +21045,7 @@
         <v>34</v>
       </c>
       <c r="E332" t="s">
-        <v>175</v>
+        <v>672</v>
       </c>
       <c r="F332" t="s">
         <v>40</v>
@@ -21054,16 +21054,16 @@
         <v>41</v>
       </c>
       <c r="H332" t="s">
+        <v>679</v>
+      </c>
+      <c r="I332" t="s">
         <v>680</v>
       </c>
-      <c r="I332" t="s">
+      <c r="J332" t="s">
         <v>681</v>
       </c>
-      <c r="J332" t="s">
-        <v>178</v>
-      </c>
       <c r="K332" t="s">
-        <v>178</v>
+        <v>229</v>
       </c>
       <c r="L332" t="s">
         <v>682</v>
@@ -21078,7 +21078,7 @@
         <v>48</v>
       </c>
       <c r="P332" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="Q332" t="s">
         <v>47</v>
@@ -21101,28 +21101,28 @@
         <v>34</v>
       </c>
       <c r="E333" t="s">
-        <v>672</v>
+        <v>683</v>
       </c>
       <c r="F333" t="s">
-        <v>40</v>
+        <v>211</v>
       </c>
       <c r="G333" t="s">
         <v>41</v>
       </c>
       <c r="H333" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="I333" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="J333" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="K333" t="s">
         <v>229</v>
       </c>
       <c r="L333" t="s">
-        <v>686</v>
+        <v>34</v>
       </c>
       <c r="M333" t="s">
         <v>671</v>
@@ -21134,7 +21134,7 @@
         <v>48</v>
       </c>
       <c r="P333" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="Q333" t="s">
         <v>47</v>
@@ -21340,7 +21340,7 @@
         <v>694</v>
       </c>
       <c r="J337" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="K337" t="s">
         <v>45</v>
@@ -21508,7 +21508,7 @@
         <v>703</v>
       </c>
       <c r="J340" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="K340" t="s">
         <v>45</v>
@@ -21564,7 +21564,7 @@
         <v>706</v>
       </c>
       <c r="J341" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="K341" t="s">
         <v>45</v>
@@ -21676,7 +21676,7 @@
         <v>694</v>
       </c>
       <c r="J343" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="K343" t="s">
         <v>45</v>
@@ -21732,7 +21732,7 @@
         <v>712</v>
       </c>
       <c r="J344" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="K344" t="s">
         <v>45</v>
@@ -21788,7 +21788,7 @@
         <v>715</v>
       </c>
       <c r="J345" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="K345" t="s">
         <v>45</v>
@@ -21900,7 +21900,7 @@
         <v>715</v>
       </c>
       <c r="J347" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="K347" t="s">
         <v>45</v>
@@ -22672,7 +22672,7 @@
         <v>187</v>
       </c>
       <c r="F361" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="G361" t="s">
         <v>41</v>
@@ -22846,16 +22846,16 @@
         <v>41</v>
       </c>
       <c r="H364" t="s">
-        <v>469</v>
+        <v>425</v>
       </c>
       <c r="I364" t="s">
         <v>755</v>
       </c>
       <c r="J364" t="s">
-        <v>101</v>
+        <v>178</v>
       </c>
       <c r="K364" t="s">
-        <v>101</v>
+        <v>178</v>
       </c>
       <c r="L364" t="s">
         <v>34</v>
@@ -22902,16 +22902,16 @@
         <v>41</v>
       </c>
       <c r="H365" t="s">
-        <v>425</v>
+        <v>469</v>
       </c>
       <c r="I365" t="s">
         <v>756</v>
       </c>
       <c r="J365" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="K365" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="L365" t="s">
         <v>34</v>
@@ -23076,7 +23076,7 @@
         <v>765</v>
       </c>
       <c r="J368" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="K368" t="s">
         <v>229</v>
@@ -23356,7 +23356,7 @@
         <v>783</v>
       </c>
       <c r="J373" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="K373" t="s">
         <v>45</v>
@@ -23524,7 +23524,7 @@
         <v>795</v>
       </c>
       <c r="J376" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="K376" t="s">
         <v>796</v>
@@ -23695,7 +23695,7 @@
         <v>320</v>
       </c>
       <c r="K379" t="s">
-        <v>75</v>
+        <v>122</v>
       </c>
       <c r="L379" t="s">
         <v>806</v>
@@ -23742,19 +23742,19 @@
         <v>41</v>
       </c>
       <c r="H380" t="s">
-        <v>425</v>
+        <v>808</v>
       </c>
       <c r="I380" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="J380" t="s">
-        <v>58</v>
+        <v>320</v>
       </c>
       <c r="K380" t="s">
-        <v>202</v>
+        <v>96</v>
       </c>
       <c r="L380" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="M380" t="s">
         <v>800</v>
@@ -23766,7 +23766,7 @@
         <v>48</v>
       </c>
       <c r="P380" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="Q380" t="s">
         <v>47</v>
@@ -23789,7 +23789,7 @@
         <v>34</v>
       </c>
       <c r="E381" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="F381" t="s">
         <v>211</v>
@@ -23798,10 +23798,10 @@
         <v>41</v>
       </c>
       <c r="H381" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="I381" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="J381" t="s">
         <v>320</v>
@@ -23810,7 +23810,7 @@
         <v>96</v>
       </c>
       <c r="L381" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="M381" t="s">
         <v>800</v>
@@ -23822,7 +23822,7 @@
         <v>48</v>
       </c>
       <c r="P381" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="Q381" t="s">
         <v>47</v>
@@ -23845,7 +23845,7 @@
         <v>34</v>
       </c>
       <c r="E382" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="F382" t="s">
         <v>211</v>
@@ -23854,10 +23854,10 @@
         <v>41</v>
       </c>
       <c r="H382" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="I382" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="J382" t="s">
         <v>320</v>
@@ -23866,7 +23866,7 @@
         <v>96</v>
       </c>
       <c r="L382" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="M382" t="s">
         <v>800</v>
@@ -23878,7 +23878,7 @@
         <v>48</v>
       </c>
       <c r="P382" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="Q382" t="s">
         <v>47</v>
@@ -23901,7 +23901,7 @@
         <v>34</v>
       </c>
       <c r="E383" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="F383" t="s">
         <v>211</v>
@@ -23910,7 +23910,7 @@
         <v>41</v>
       </c>
       <c r="H383" t="s">
-        <v>819</v>
+        <v>425</v>
       </c>
       <c r="I383" t="s">
         <v>820</v>
@@ -23975,7 +23975,7 @@
         <v>320</v>
       </c>
       <c r="K384" t="s">
-        <v>122</v>
+        <v>75</v>
       </c>
       <c r="L384" t="s">
         <v>825</v>
@@ -24028,10 +24028,10 @@
         <v>828</v>
       </c>
       <c r="J385" t="s">
-        <v>320</v>
+        <v>58</v>
       </c>
       <c r="K385" t="s">
-        <v>96</v>
+        <v>202</v>
       </c>
       <c r="L385" t="s">
         <v>829</v>
@@ -24140,7 +24140,7 @@
         <v>835</v>
       </c>
       <c r="J387" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="K387" t="s">
         <v>45</v>
@@ -24349,28 +24349,28 @@
         <v>33</v>
       </c>
       <c r="E391" t="s">
-        <v>672</v>
+        <v>851</v>
       </c>
       <c r="F391" t="s">
-        <v>40</v>
+        <v>211</v>
       </c>
       <c r="G391" t="s">
         <v>41</v>
       </c>
       <c r="H391" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="I391" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="J391" t="s">
-        <v>293</v>
+        <v>320</v>
       </c>
       <c r="K391" t="s">
-        <v>45</v>
+        <v>122</v>
       </c>
       <c r="L391" t="s">
-        <v>853</v>
+        <v>34</v>
       </c>
       <c r="M391" t="s">
         <v>850</v>
@@ -24382,7 +24382,7 @@
         <v>48</v>
       </c>
       <c r="P391" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="Q391" t="s">
         <v>47</v>
@@ -24405,28 +24405,28 @@
         <v>34</v>
       </c>
       <c r="E392" t="s">
+        <v>672</v>
+      </c>
+      <c r="F392" t="s">
+        <v>40</v>
+      </c>
+      <c r="G392" t="s">
+        <v>41</v>
+      </c>
+      <c r="H392" t="s">
         <v>854</v>
       </c>
-      <c r="F392" t="s">
-        <v>211</v>
-      </c>
-      <c r="G392" t="s">
-        <v>41</v>
-      </c>
-      <c r="H392" t="s">
+      <c r="I392" t="s">
         <v>855</v>
       </c>
-      <c r="I392" t="s">
+      <c r="J392" t="s">
+        <v>293</v>
+      </c>
+      <c r="K392" t="s">
+        <v>45</v>
+      </c>
+      <c r="L392" t="s">
         <v>856</v>
-      </c>
-      <c r="J392" t="s">
-        <v>320</v>
-      </c>
-      <c r="K392" t="s">
-        <v>122</v>
-      </c>
-      <c r="L392" t="s">
-        <v>34</v>
       </c>
       <c r="M392" t="s">
         <v>850</v>
@@ -24438,7 +24438,7 @@
         <v>48</v>
       </c>
       <c r="P392" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="Q392" t="s">
         <v>47</v>
@@ -24517,7 +24517,7 @@
         <v>34</v>
       </c>
       <c r="E394" t="s">
-        <v>672</v>
+        <v>861</v>
       </c>
       <c r="F394" t="s">
         <v>40</v>
@@ -24529,16 +24529,16 @@
         <v>846</v>
       </c>
       <c r="I394" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="J394" t="s">
-        <v>293</v>
+        <v>101</v>
       </c>
       <c r="K394" t="s">
-        <v>859</v>
+        <v>45</v>
       </c>
       <c r="L394" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="M394" t="s">
         <v>850</v>
@@ -24550,7 +24550,7 @@
         <v>48</v>
       </c>
       <c r="P394" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="Q394" t="s">
         <v>47</v>
@@ -24573,7 +24573,7 @@
         <v>34</v>
       </c>
       <c r="E395" t="s">
-        <v>863</v>
+        <v>672</v>
       </c>
       <c r="F395" t="s">
         <v>40</v>
@@ -24588,10 +24588,10 @@
         <v>864</v>
       </c>
       <c r="J395" t="s">
-        <v>101</v>
+        <v>293</v>
       </c>
       <c r="K395" t="s">
-        <v>45</v>
+        <v>859</v>
       </c>
       <c r="L395" t="s">
         <v>865</v>
@@ -24812,7 +24812,7 @@
         <v>878</v>
       </c>
       <c r="J399" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="K399" t="s">
         <v>45</v>
@@ -24865,7 +24865,7 @@
         <v>877</v>
       </c>
       <c r="I400" t="s">
-        <v>808</v>
+        <v>820</v>
       </c>
       <c r="J400" t="s">
         <v>58</v>
@@ -24886,7 +24886,7 @@
         <v>48</v>
       </c>
       <c r="P400" t="s">
-        <v>808</v>
+        <v>820</v>
       </c>
       <c r="Q400" t="s">
         <v>47</v>
@@ -25077,7 +25077,7 @@
         <v>33</v>
       </c>
       <c r="E404" t="s">
-        <v>763</v>
+        <v>672</v>
       </c>
       <c r="F404" t="s">
         <v>40</v>
@@ -25092,10 +25092,10 @@
         <v>898</v>
       </c>
       <c r="J404" t="s">
-        <v>178</v>
+        <v>681</v>
       </c>
       <c r="K404" t="s">
-        <v>178</v>
+        <v>45</v>
       </c>
       <c r="L404" t="s">
         <v>899</v>
@@ -25133,7 +25133,7 @@
         <v>34</v>
       </c>
       <c r="E405" t="s">
-        <v>672</v>
+        <v>763</v>
       </c>
       <c r="F405" t="s">
         <v>40</v>
@@ -25148,10 +25148,10 @@
         <v>901</v>
       </c>
       <c r="J405" t="s">
-        <v>685</v>
+        <v>178</v>
       </c>
       <c r="K405" t="s">
-        <v>45</v>
+        <v>178</v>
       </c>
       <c r="L405" t="s">
         <v>902</v>

--- a/xlsx/dre/DRE_02_2026.xlsx
+++ b/xlsx/dre/DRE_02_2026.xlsx
@@ -888,36 +888,25 @@
     <t>R$ 5.432,14</t>
   </si>
   <si>
-    <t>9/2</t>
-  </si>
-  <si>
-    <t>R$  91,87</t>
-  </si>
-  <si>
-    <t>09/01/26</t>
-  </si>
-  <si>
-    <t>Grapa</t>
-  </si>
-  <si>
-    <t>2/1</t>
-  </si>
-  <si>
-    <t>R$  106,63</t>
-  </si>
-  <si>
-    <t>Mercado livre - mat aspirador</t>
-  </si>
-  <si>
-    <t>54802/2</t>
-  </si>
-  <si>
-    <t>R$  279,56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155,4	Mercado Livre	 Rodizios cliente Krisdany
-124,16	Mercado Livre	dobradiças invisiveis Krisdany
-</t>
+    <t>East Glass- R t de Andrade Comercio E Servicos</t>
+  </si>
+  <si>
+    <t>R$  1.886,73</t>
+  </si>
+  <si>
+    <t>575/1</t>
+  </si>
+  <si>
+    <t>FERRAGENS FLORESTA EIRELI EPP</t>
+  </si>
+  <si>
+    <t>R$  256,50</t>
+  </si>
+  <si>
+    <t>18/03/26</t>
+  </si>
+  <si>
+    <t>estoque</t>
   </si>
   <si>
     <t>641/1</t>
@@ -933,37 +922,25 @@
 </t>
   </si>
   <si>
-    <t>63401/4</t>
+    <t>581/1</t>
+  </si>
+  <si>
+    <t>R$  137,93</t>
+  </si>
+  <si>
+    <t>05/03/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor	Fornecedor	Descrição
+35,9	Mercado Livre	5 Pé Pézinho Móveis 18cm Até 23cm (assistencia Carina)
+102,03	Mercado Livre	plafon show room moema
+</t>
+  </si>
+  <si>
+    <t>608/1</t>
   </si>
   <si>
     <t>R$  100,75</t>
-  </si>
-  <si>
-    <t>mão francesa 4/4</t>
-  </si>
-  <si>
-    <t>63401DANIELAIMM</t>
-  </si>
-  <si>
-    <t>63401/3</t>
-  </si>
-  <si>
-    <t>mao francesa 3 /4</t>
-  </si>
-  <si>
-    <t>63401/2</t>
-  </si>
-  <si>
-    <t>mão francesa 2/4</t>
-  </si>
-  <si>
-    <t>East Glass- R t de Andrade Comercio E Servicos</t>
-  </si>
-  <si>
-    <t>R$  1.886,73</t>
-  </si>
-  <si>
-    <t>608/1</t>
   </si>
   <si>
     <t>06/04/26</t>
@@ -973,13 +950,25 @@
 </t>
   </si>
   <si>
+    <t>63401DANIELAIMM</t>
+  </si>
+  <si>
+    <t>559/1</t>
+  </si>
+  <si>
+    <t>R$  630,00</t>
+  </si>
+  <si>
+    <t>63401/4</t>
+  </si>
+  <si>
+    <t>mão francesa 4/4</t>
+  </si>
+  <si>
     <t>580/1</t>
   </si>
   <si>
     <t>R$  165,83</t>
-  </si>
-  <si>
-    <t>05/03/26</t>
   </si>
   <si>
     <t>17/02/26</t>
@@ -995,6 +984,38 @@
     <t>29901FL8</t>
   </si>
   <si>
+    <t>560/1</t>
+  </si>
+  <si>
+    <t>R$  330,47</t>
+  </si>
+  <si>
+    <t>63401/3</t>
+  </si>
+  <si>
+    <t>mao francesa 3 /4</t>
+  </si>
+  <si>
+    <t>2/1</t>
+  </si>
+  <si>
+    <t>R$  106,63</t>
+  </si>
+  <si>
+    <t>Mercado livre - mat aspirador</t>
+  </si>
+  <si>
+    <t>54802/2</t>
+  </si>
+  <si>
+    <t>R$  279,56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155,4	Mercado Livre	 Rodizios cliente Krisdany
+124,16	Mercado Livre	dobradiças invisiveis Krisdany
+</t>
+  </si>
+  <si>
     <t>582/1</t>
   </si>
   <si>
@@ -1004,60 +1025,39 @@
     <t>36902LeticiaOC</t>
   </si>
   <si>
+    <t>9/2</t>
+  </si>
+  <si>
+    <t>R$  91,87</t>
+  </si>
+  <si>
+    <t>09/01/26</t>
+  </si>
+  <si>
+    <t>Grapa</t>
+  </si>
+  <si>
+    <t>63401/2</t>
+  </si>
+  <si>
+    <t>mão francesa 2/4</t>
+  </si>
+  <si>
     <t>584/1</t>
   </si>
   <si>
-    <t>FERRAGENS FLORESTA EIRELI EPP</t>
-  </si>
-  <si>
     <t>R$  381,46</t>
   </si>
   <si>
     <t>24/03/26</t>
   </si>
   <si>
-    <t>estoque</t>
-  </si>
-  <si>
     <t>571/1</t>
   </si>
   <si>
     <t>R$  443,00</t>
   </si>
   <si>
-    <t>581/1</t>
-  </si>
-  <si>
-    <t>R$  137,93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor	Fornecedor	Descrição
-35,9	Mercado Livre	5 Pé Pézinho Móveis 18cm Até 23cm (assistencia Carina)
-102,03	Mercado Livre	plafon show room moema
-</t>
-  </si>
-  <si>
-    <t>559/1</t>
-  </si>
-  <si>
-    <t>R$  630,00</t>
-  </si>
-  <si>
-    <t>560/1</t>
-  </si>
-  <si>
-    <t>R$  330,47</t>
-  </si>
-  <si>
-    <t>575/1</t>
-  </si>
-  <si>
-    <t>R$  256,50</t>
-  </si>
-  <si>
-    <t>18/03/26</t>
-  </si>
-  <si>
     <t>4.02.02 CUSTO DE TRANSPORTE</t>
   </si>
   <si>
@@ -1550,46 +1550,46 @@
     <t>R$ 10.123,95</t>
   </si>
   <si>
+    <t>R$  1.108,54</t>
+  </si>
+  <si>
+    <t>R$  1.196,02</t>
+  </si>
+  <si>
+    <t>RAYSSA BARBOSA SILVA</t>
+  </si>
+  <si>
+    <t>R$  727,31</t>
+  </si>
+  <si>
+    <t>07/04/26</t>
+  </si>
+  <si>
+    <t>FERNANDA DOCHVAT SILVA</t>
+  </si>
+  <si>
+    <t>01/06/26</t>
+  </si>
+  <si>
+    <t>01/04/26</t>
+  </si>
+  <si>
+    <t>R$  438,09</t>
+  </si>
+  <si>
+    <t>R$  3,60</t>
+  </si>
+  <si>
+    <t>63801/2</t>
+  </si>
+  <si>
     <t>R$  537,59</t>
   </si>
   <si>
-    <t>R$  438,09</t>
-  </si>
-  <si>
-    <t>63801/2</t>
-  </si>
-  <si>
-    <t>R$  3,60</t>
+    <t>R$  292,95</t>
   </si>
   <si>
     <t>R$  1.941,34</t>
-  </si>
-  <si>
-    <t>RAYSSA BARBOSA SILVA</t>
-  </si>
-  <si>
-    <t>01/06/26</t>
-  </si>
-  <si>
-    <t>FERNANDA DOCHVAT SILVA</t>
-  </si>
-  <si>
-    <t>R$  1.196,02</t>
-  </si>
-  <si>
-    <t>01/04/26</t>
-  </si>
-  <si>
-    <t>R$  727,31</t>
-  </si>
-  <si>
-    <t>07/04/26</t>
-  </si>
-  <si>
-    <t>R$  1.108,54</t>
-  </si>
-  <si>
-    <t>R$  292,95</t>
   </si>
   <si>
     <t>4.03.01.02.07 Comissões montagem - custo efetivo</t>
@@ -2028,15 +2028,15 @@
     <t>4.03.03.02.05.02 Assistência técnica medição</t>
   </si>
   <si>
+    <t>PFP</t>
+  </si>
+  <si>
     <t>L E A Medicoes Tecnicas LTDA</t>
   </si>
   <si>
     <t>R$  180,00</t>
   </si>
   <si>
-    <t>PFP</t>
-  </si>
-  <si>
     <t>4.03.03.09 Marketing - mídias / ações comerciais / outros (CV)</t>
   </si>
   <si>
@@ -2058,6 +2058,18 @@
     <t>Google 2026</t>
   </si>
   <si>
+    <t>498/1</t>
+  </si>
+  <si>
+    <t>Facebook</t>
+  </si>
+  <si>
+    <t>R$  3.750,00</t>
+  </si>
+  <si>
+    <t>30/01/26</t>
+  </si>
+  <si>
     <t>WEBGIGA SOLUCOES DIGITAIS LTDA</t>
   </si>
   <si>
@@ -2079,18 +2091,6 @@
     <t>MHM - Honorários 2026</t>
   </si>
   <si>
-    <t>498/1</t>
-  </si>
-  <si>
-    <t>Facebook</t>
-  </si>
-  <si>
-    <t>R$  3.750,00</t>
-  </si>
-  <si>
-    <t>30/01/26</t>
-  </si>
-  <si>
     <t>4.04 DESPESAS ADMINISTRATIVAS</t>
   </si>
   <si>
@@ -2136,6 +2136,54 @@
     <t>4.04.01.02.01.01 Salário fixo</t>
   </si>
   <si>
+    <t>Bianca Rodrigues - Salário fixo 2026</t>
+  </si>
+  <si>
+    <t>587/1</t>
+  </si>
+  <si>
+    <t>R$  2.075,32</t>
+  </si>
+  <si>
+    <t>Rateio salários Mayara, Rayssa e Efraim</t>
+  </si>
+  <si>
+    <t>Fernanda Dochvat - Fixo 2026</t>
+  </si>
+  <si>
+    <t>Danielle Martins da Silva</t>
+  </si>
+  <si>
+    <t>R$  2.090,00</t>
+  </si>
+  <si>
+    <t>Danielle - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>GUTEMBERG DIAS GOMES</t>
+  </si>
+  <si>
+    <t>R$  6.000,00</t>
+  </si>
+  <si>
+    <t>Gutemberg Dias - Pagamento</t>
+  </si>
+  <si>
+    <t>Leandro Henrique Simoes Campos</t>
+  </si>
+  <si>
+    <t>R$  2.000,00</t>
+  </si>
+  <si>
+    <t>Leandro Henrique Simoes Campos Fixo 2026</t>
+  </si>
+  <si>
+    <t>CARINA PEREIRA</t>
+  </si>
+  <si>
+    <t>Carina - Pagamento 2026</t>
+  </si>
+  <si>
     <t>Denny Lucas do Carmo Pereira</t>
   </si>
   <si>
@@ -2145,16 +2193,16 @@
     <t>Denny Lucas - Pagamento 2026</t>
   </si>
   <si>
-    <t>GUTEMBERG DIAS GOMES</t>
-  </si>
-  <si>
-    <t>R$  6.000,00</t>
-  </si>
-  <si>
-    <t>Gutemberg Dias - Pagamento</t>
-  </si>
-  <si>
-    <t>Fernanda Dochvat - Fixo 2026</t>
+    <t>Rubens - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>579/1</t>
+  </si>
+  <si>
+    <t>Eric Kevin de Souza Serpa</t>
+  </si>
+  <si>
+    <t>Salário Fixo -Eric Serpa 2026</t>
   </si>
   <si>
     <t>Teresinha Elvira Maximino de Menezes</t>
@@ -2163,6 +2211,12 @@
     <t>Tucha - Fixo 2026</t>
   </si>
   <si>
+    <t>578/1</t>
+  </si>
+  <si>
+    <t>R$  2.219,85</t>
+  </si>
+  <si>
     <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
   </si>
   <si>
@@ -2172,60 +2226,6 @@
     <t>Sabrina Braunbeck - Pagamento 2026</t>
   </si>
   <si>
-    <t>Danielle Martins da Silva</t>
-  </si>
-  <si>
-    <t>R$  2.090,00</t>
-  </si>
-  <si>
-    <t>Danielle - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>Leandro Henrique Simoes Campos</t>
-  </si>
-  <si>
-    <t>R$  2.000,00</t>
-  </si>
-  <si>
-    <t>Leandro Henrique Simoes Campos Fixo 2026</t>
-  </si>
-  <si>
-    <t>CARINA PEREIRA</t>
-  </si>
-  <si>
-    <t>Carina - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>Eric Kevin de Souza Serpa</t>
-  </si>
-  <si>
-    <t>Salário Fixo -Eric Serpa 2026</t>
-  </si>
-  <si>
-    <t>Bianca Rodrigues - Salário fixo 2026</t>
-  </si>
-  <si>
-    <t>587/1</t>
-  </si>
-  <si>
-    <t>R$  2.075,32</t>
-  </si>
-  <si>
-    <t>Rateio salários Mayara, Rayssa e Efraim</t>
-  </si>
-  <si>
-    <t>Rubens - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>578/1</t>
-  </si>
-  <si>
-    <t>R$  2.219,85</t>
-  </si>
-  <si>
-    <t>579/1</t>
-  </si>
-  <si>
     <t>4.04.01.02.05 IRRF sobre salários</t>
   </si>
   <si>
@@ -2295,12 +2295,12 @@
     <t>VT fev 26/1</t>
   </si>
   <si>
+    <t>R$  433,98</t>
+  </si>
+  <si>
     <t>R$  313,70</t>
   </si>
   <si>
-    <t>R$  433,98</t>
-  </si>
-  <si>
     <t>4.04.02 GASTOS GERAIS ADMINISTRATIVOS</t>
   </si>
   <si>
@@ -2439,17 +2439,25 @@
     <t>R$  45,00</t>
   </si>
   <si>
-    <t>531/1</t>
-  </si>
-  <si>
-    <t>Shopee</t>
-  </si>
-  <si>
-    <t>R$  65,93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freeco refil
-</t>
+    <t>532/1</t>
+  </si>
+  <si>
+    <t>DIA BRASIL SUPERMERCADO</t>
+  </si>
+  <si>
+    <t>R$  59,96</t>
+  </si>
+  <si>
+    <t>cafés</t>
+  </si>
+  <si>
+    <t>502/1</t>
+  </si>
+  <si>
+    <t>R$  100,00</t>
+  </si>
+  <si>
+    <t>Cópia de chaves</t>
   </si>
   <si>
     <t>533/1</t>
@@ -2462,19 +2470,6 @@
   </si>
   <si>
     <t>material limpeza</t>
-  </si>
-  <si>
-    <t>530/1</t>
-  </si>
-  <si>
-    <t>Marinete</t>
-  </si>
-  <si>
-    <t>R$  17,00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Copo descartável para crianças
-</t>
   </si>
   <si>
     <t>529/1</t>
@@ -2491,27 +2486,6 @@
 </t>
   </si>
   <si>
-    <t>502/1</t>
-  </si>
-  <si>
-    <t>R$  100,00</t>
-  </si>
-  <si>
-    <t>Cópia de chaves</t>
-  </si>
-  <si>
-    <t>532/1</t>
-  </si>
-  <si>
-    <t>DIA BRASIL SUPERMERCADO</t>
-  </si>
-  <si>
-    <t>R$  59,96</t>
-  </si>
-  <si>
-    <t>cafés</t>
-  </si>
-  <si>
     <t>505/1</t>
   </si>
   <si>
@@ -2524,6 +2498,32 @@
     <t>Conserto vidro adega</t>
   </si>
   <si>
+    <t>531/1</t>
+  </si>
+  <si>
+    <t>Shopee</t>
+  </si>
+  <si>
+    <t>R$  65,93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freeco refil
+</t>
+  </si>
+  <si>
+    <t>530/1</t>
+  </si>
+  <si>
+    <t>Marinete</t>
+  </si>
+  <si>
+    <t>R$  17,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copo descartável para crianças
+</t>
+  </si>
+  <si>
     <t>4.04.02.07 Informática</t>
   </si>
   <si>
@@ -2587,6 +2587,15 @@
     <t>4.04.02.08.03 Mensalidades e assinaturas - outros gastos</t>
   </si>
   <si>
+    <t>D4 sign</t>
+  </si>
+  <si>
+    <t>R$  49,95</t>
+  </si>
+  <si>
+    <t>D4 sign 2026</t>
+  </si>
+  <si>
     <t>534/1</t>
   </si>
   <si>
@@ -2596,15 +2605,6 @@
     <t>R$  197,63</t>
   </si>
   <si>
-    <t>D4 sign</t>
-  </si>
-  <si>
-    <t>R$  49,95</t>
-  </si>
-  <si>
-    <t>D4 sign 2026</t>
-  </si>
-  <si>
     <t>10/2</t>
   </si>
   <si>
@@ -2617,6 +2617,12 @@
     <t>Promob 2026-1</t>
   </si>
   <si>
+    <t>R$  599,00</t>
+  </si>
+  <si>
+    <t>Promob 2026</t>
+  </si>
+  <si>
     <t>3/1</t>
   </si>
   <si>
@@ -2624,12 +2630,6 @@
   </si>
   <si>
     <t>Promob 2026/2</t>
-  </si>
-  <si>
-    <t>R$  599,00</t>
-  </si>
-  <si>
-    <t>Promob 2026</t>
   </si>
   <si>
     <t>4.04.02.11 Manutenção de predio e equipamentos</t>
@@ -2726,6 +2726,15 @@
     <t>R$ 400,33</t>
   </si>
   <si>
+    <t>VERISURE</t>
+  </si>
+  <si>
+    <t>R$  250,33</t>
+  </si>
+  <si>
+    <t>Verisure - Alarme 2026</t>
+  </si>
+  <si>
     <t>Jackson Fernando de Araujo</t>
   </si>
   <si>
@@ -2735,15 +2744,6 @@
     <t>Segurança 2026</t>
   </si>
   <si>
-    <t>VERISURE</t>
-  </si>
-  <si>
-    <t>R$  250,33</t>
-  </si>
-  <si>
-    <t>Verisure - Alarme 2026</t>
-  </si>
-  <si>
     <t>4.04.02.14.08 Site e newsletter da loja</t>
   </si>
   <si>
@@ -2822,49 +2822,49 @@
     <t>4.07.01.01.01 Operações financeiras - desconto de cheques (financeiras)</t>
   </si>
   <si>
+    <t>Italíneacredi</t>
+  </si>
+  <si>
+    <t>R$  2.297,09</t>
+  </si>
+  <si>
+    <t>Título referente a Valor da Taxa Financeira</t>
+  </si>
+  <si>
     <t>PAGSEGURO</t>
   </si>
   <si>
+    <t>R$  1.856,00</t>
+  </si>
+  <si>
+    <t>R$  3.337,10</t>
+  </si>
+  <si>
+    <t>R$  5.371,28</t>
+  </si>
+  <si>
+    <t>R$  618,68</t>
+  </si>
+  <si>
+    <t>R$  1.084,60</t>
+  </si>
+  <si>
+    <t>R$  4.023,17</t>
+  </si>
+  <si>
+    <t>R$  389,78</t>
+  </si>
+  <si>
     <t>R$  2.389,60</t>
   </si>
   <si>
-    <t>Título referente a Valor da Taxa Financeira</t>
-  </si>
-  <si>
-    <t>R$  1.856,00</t>
-  </si>
-  <si>
-    <t>Italíneacredi</t>
-  </si>
-  <si>
-    <t>R$  2.297,09</t>
-  </si>
-  <si>
-    <t>R$  4.023,17</t>
-  </si>
-  <si>
-    <t>R$  5.371,28</t>
-  </si>
-  <si>
-    <t>R$  389,78</t>
+    <t>R$  8.136,54</t>
   </si>
   <si>
     <t>R$  20.470,96</t>
   </si>
   <si>
     <t>R$  19.259,44</t>
-  </si>
-  <si>
-    <t>R$  3.337,10</t>
-  </si>
-  <si>
-    <t>R$  618,68</t>
-  </si>
-  <si>
-    <t>R$  8.136,54</t>
-  </si>
-  <si>
-    <t>R$  1.084,60</t>
   </si>
   <si>
     <t>6.01 ATIVO</t>
@@ -7829,28 +7829,28 @@
         <v>33</v>
       </c>
       <c r="E96" t="s">
+        <v>275</v>
+      </c>
+      <c r="F96" t="s">
+        <v>211</v>
+      </c>
+      <c r="G96" t="s">
+        <v>41</v>
+      </c>
+      <c r="H96" t="s">
         <v>291</v>
-      </c>
-      <c r="F96" t="s">
-        <v>40</v>
-      </c>
-      <c r="G96" t="s">
-        <v>41</v>
-      </c>
-      <c r="H96" t="s">
-        <v>56</v>
       </c>
       <c r="I96" t="s">
         <v>292</v>
       </c>
       <c r="J96" t="s">
-        <v>293</v>
+        <v>119</v>
       </c>
       <c r="K96" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="L96" t="s">
-        <v>294</v>
+        <v>34</v>
       </c>
       <c r="M96" t="s">
         <v>289</v>
@@ -7859,7 +7859,7 @@
         <v>47</v>
       </c>
       <c r="O96" t="s">
-        <v>48</v>
+        <v>105</v>
       </c>
       <c r="P96" t="s">
         <v>292</v>
@@ -7885,25 +7885,25 @@
         <v>34</v>
       </c>
       <c r="E97" t="s">
+        <v>293</v>
+      </c>
+      <c r="F97" t="s">
+        <v>211</v>
+      </c>
+      <c r="G97" t="s">
+        <v>41</v>
+      </c>
+      <c r="H97" t="s">
+        <v>294</v>
+      </c>
+      <c r="I97" t="s">
         <v>295</v>
       </c>
-      <c r="F97" t="s">
-        <v>40</v>
-      </c>
-      <c r="G97" t="s">
-        <v>41</v>
-      </c>
-      <c r="H97" t="s">
-        <v>56</v>
-      </c>
-      <c r="I97" t="s">
+      <c r="J97" t="s">
         <v>296</v>
       </c>
-      <c r="J97" t="s">
-        <v>101</v>
-      </c>
       <c r="K97" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="L97" t="s">
         <v>297</v>
@@ -7918,7 +7918,7 @@
         <v>48</v>
       </c>
       <c r="P97" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Q97" t="s">
         <v>47</v>
@@ -7956,13 +7956,13 @@
         <v>299</v>
       </c>
       <c r="J98" t="s">
-        <v>119</v>
+        <v>300</v>
       </c>
       <c r="K98" t="s">
-        <v>58</v>
+        <v>147</v>
       </c>
       <c r="L98" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M98" t="s">
         <v>289</v>
@@ -7971,7 +7971,7 @@
         <v>47</v>
       </c>
       <c r="O98" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="P98" t="s">
         <v>299</v>
@@ -7997,7 +7997,7 @@
         <v>34</v>
       </c>
       <c r="E99" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F99" t="s">
         <v>211</v>
@@ -8009,16 +8009,16 @@
         <v>56</v>
       </c>
       <c r="I99" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="J99" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K99" t="s">
-        <v>147</v>
+        <v>178</v>
       </c>
       <c r="L99" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M99" t="s">
         <v>289</v>
@@ -8027,10 +8027,10 @@
         <v>47</v>
       </c>
       <c r="O99" t="s">
-        <v>114</v>
+        <v>48</v>
       </c>
       <c r="P99" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q99" t="s">
         <v>47</v>
@@ -8053,7 +8053,7 @@
         <v>34</v>
       </c>
       <c r="E100" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F100" t="s">
         <v>211</v>
@@ -8065,16 +8065,16 @@
         <v>56</v>
       </c>
       <c r="I100" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J100" t="s">
-        <v>178</v>
+        <v>308</v>
       </c>
       <c r="K100" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="L100" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="M100" t="s">
         <v>289</v>
@@ -8083,10 +8083,10 @@
         <v>47</v>
       </c>
       <c r="O100" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="P100" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q100" t="s">
         <v>47</v>
@@ -8109,7 +8109,7 @@
         <v>34</v>
       </c>
       <c r="E101" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F101" t="s">
         <v>211</v>
@@ -8118,19 +8118,19 @@
         <v>41</v>
       </c>
       <c r="H101" t="s">
-        <v>56</v>
+        <v>294</v>
       </c>
       <c r="I101" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="J101" t="s">
-        <v>96</v>
+        <v>304</v>
       </c>
       <c r="K101" t="s">
-        <v>90</v>
+        <v>134</v>
       </c>
       <c r="L101" t="s">
-        <v>310</v>
+        <v>297</v>
       </c>
       <c r="M101" t="s">
         <v>289</v>
@@ -8139,10 +8139,10 @@
         <v>47</v>
       </c>
       <c r="O101" t="s">
-        <v>308</v>
+        <v>48</v>
       </c>
       <c r="P101" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="Q101" t="s">
         <v>47</v>
@@ -8165,7 +8165,7 @@
         <v>34</v>
       </c>
       <c r="E102" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F102" t="s">
         <v>211</v>
@@ -8177,16 +8177,16 @@
         <v>56</v>
       </c>
       <c r="I102" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J102" t="s">
-        <v>119</v>
+        <v>178</v>
       </c>
       <c r="K102" t="s">
         <v>90</v>
       </c>
       <c r="L102" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M102" t="s">
         <v>289</v>
@@ -8195,10 +8195,10 @@
         <v>47</v>
       </c>
       <c r="O102" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="P102" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q102" t="s">
         <v>47</v>
@@ -8221,7 +8221,7 @@
         <v>34</v>
       </c>
       <c r="E103" t="s">
-        <v>275</v>
+        <v>315</v>
       </c>
       <c r="F103" t="s">
         <v>211</v>
@@ -8230,19 +8230,19 @@
         <v>41</v>
       </c>
       <c r="H103" t="s">
-        <v>313</v>
+        <v>56</v>
       </c>
       <c r="I103" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="J103" t="s">
-        <v>119</v>
+        <v>304</v>
       </c>
       <c r="K103" t="s">
-        <v>58</v>
+        <v>317</v>
       </c>
       <c r="L103" t="s">
-        <v>34</v>
+        <v>318</v>
       </c>
       <c r="M103" t="s">
         <v>289</v>
@@ -8251,10 +8251,10 @@
         <v>47</v>
       </c>
       <c r="O103" t="s">
-        <v>105</v>
+        <v>319</v>
       </c>
       <c r="P103" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q103" t="s">
         <v>47</v>
@@ -8277,7 +8277,7 @@
         <v>34</v>
       </c>
       <c r="E104" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="F104" t="s">
         <v>211</v>
@@ -8286,19 +8286,19 @@
         <v>41</v>
       </c>
       <c r="H104" t="s">
-        <v>56</v>
+        <v>294</v>
       </c>
       <c r="I104" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="J104" t="s">
-        <v>316</v>
+        <v>138</v>
       </c>
       <c r="K104" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L104" t="s">
-        <v>317</v>
+        <v>297</v>
       </c>
       <c r="M104" t="s">
         <v>289</v>
@@ -8307,10 +8307,10 @@
         <v>47</v>
       </c>
       <c r="O104" t="s">
-        <v>308</v>
+        <v>48</v>
       </c>
       <c r="P104" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="Q104" t="s">
         <v>47</v>
@@ -8333,7 +8333,7 @@
         <v>34</v>
       </c>
       <c r="E105" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="F105" t="s">
         <v>211</v>
@@ -8345,16 +8345,16 @@
         <v>56</v>
       </c>
       <c r="I105" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="J105" t="s">
-        <v>320</v>
+        <v>96</v>
       </c>
       <c r="K105" t="s">
-        <v>321</v>
+        <v>90</v>
       </c>
       <c r="L105" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M105" t="s">
         <v>289</v>
@@ -8363,10 +8363,10 @@
         <v>47</v>
       </c>
       <c r="O105" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="P105" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="Q105" t="s">
         <v>47</v>
@@ -8392,7 +8392,7 @@
         <v>324</v>
       </c>
       <c r="F106" t="s">
-        <v>211</v>
+        <v>40</v>
       </c>
       <c r="G106" t="s">
         <v>41</v>
@@ -8404,13 +8404,13 @@
         <v>325</v>
       </c>
       <c r="J106" t="s">
-        <v>320</v>
+        <v>101</v>
       </c>
       <c r="K106" t="s">
-        <v>191</v>
+        <v>45</v>
       </c>
       <c r="L106" t="s">
-        <v>34</v>
+        <v>326</v>
       </c>
       <c r="M106" t="s">
         <v>289</v>
@@ -8419,7 +8419,7 @@
         <v>47</v>
       </c>
       <c r="O106" t="s">
-        <v>326</v>
+        <v>48</v>
       </c>
       <c r="P106" t="s">
         <v>325</v>
@@ -8454,19 +8454,19 @@
         <v>41</v>
       </c>
       <c r="H107" t="s">
+        <v>56</v>
+      </c>
+      <c r="I107" t="s">
         <v>328</v>
       </c>
-      <c r="I107" t="s">
+      <c r="J107" t="s">
+        <v>119</v>
+      </c>
+      <c r="K107" t="s">
+        <v>58</v>
+      </c>
+      <c r="L107" t="s">
         <v>329</v>
-      </c>
-      <c r="J107" t="s">
-        <v>330</v>
-      </c>
-      <c r="K107" t="s">
-        <v>90</v>
-      </c>
-      <c r="L107" t="s">
-        <v>331</v>
       </c>
       <c r="M107" t="s">
         <v>289</v>
@@ -8475,10 +8475,10 @@
         <v>47</v>
       </c>
       <c r="O107" t="s">
-        <v>48</v>
+        <v>105</v>
       </c>
       <c r="P107" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="Q107" t="s">
         <v>47</v>
@@ -8501,7 +8501,7 @@
         <v>34</v>
       </c>
       <c r="E108" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F108" t="s">
         <v>211</v>
@@ -8510,19 +8510,19 @@
         <v>41</v>
       </c>
       <c r="H108" t="s">
-        <v>328</v>
+        <v>56</v>
       </c>
       <c r="I108" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="J108" t="s">
-        <v>163</v>
+        <v>304</v>
       </c>
       <c r="K108" t="s">
-        <v>96</v>
+        <v>191</v>
       </c>
       <c r="L108" t="s">
-        <v>331</v>
+        <v>34</v>
       </c>
       <c r="M108" t="s">
         <v>289</v>
@@ -8531,10 +8531,10 @@
         <v>47</v>
       </c>
       <c r="O108" t="s">
-        <v>48</v>
+        <v>332</v>
       </c>
       <c r="P108" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="Q108" t="s">
         <v>47</v>
@@ -8557,10 +8557,10 @@
         <v>34</v>
       </c>
       <c r="E109" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F109" t="s">
-        <v>211</v>
+        <v>40</v>
       </c>
       <c r="G109" t="s">
         <v>41</v>
@@ -8569,13 +8569,13 @@
         <v>56</v>
       </c>
       <c r="I109" t="s">
+        <v>334</v>
+      </c>
+      <c r="J109" t="s">
         <v>335</v>
       </c>
-      <c r="J109" t="s">
-        <v>320</v>
-      </c>
       <c r="K109" t="s">
-        <v>178</v>
+        <v>45</v>
       </c>
       <c r="L109" t="s">
         <v>336</v>
@@ -8590,7 +8590,7 @@
         <v>48</v>
       </c>
       <c r="P109" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="Q109" t="s">
         <v>47</v>
@@ -8622,19 +8622,19 @@
         <v>41</v>
       </c>
       <c r="H110" t="s">
-        <v>328</v>
+        <v>56</v>
       </c>
       <c r="I110" t="s">
+        <v>307</v>
+      </c>
+      <c r="J110" t="s">
+        <v>119</v>
+      </c>
+      <c r="K110" t="s">
+        <v>90</v>
+      </c>
+      <c r="L110" t="s">
         <v>338</v>
-      </c>
-      <c r="J110" t="s">
-        <v>320</v>
-      </c>
-      <c r="K110" t="s">
-        <v>134</v>
-      </c>
-      <c r="L110" t="s">
-        <v>331</v>
       </c>
       <c r="M110" t="s">
         <v>289</v>
@@ -8643,10 +8643,10 @@
         <v>47</v>
       </c>
       <c r="O110" t="s">
-        <v>48</v>
+        <v>310</v>
       </c>
       <c r="P110" t="s">
-        <v>338</v>
+        <v>307</v>
       </c>
       <c r="Q110" t="s">
         <v>47</v>
@@ -8678,19 +8678,19 @@
         <v>41</v>
       </c>
       <c r="H111" t="s">
-        <v>328</v>
+        <v>294</v>
       </c>
       <c r="I111" t="s">
         <v>340</v>
       </c>
       <c r="J111" t="s">
-        <v>138</v>
+        <v>341</v>
       </c>
       <c r="K111" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="L111" t="s">
-        <v>331</v>
+        <v>297</v>
       </c>
       <c r="M111" t="s">
         <v>289</v>
@@ -8725,7 +8725,7 @@
         <v>34</v>
       </c>
       <c r="E112" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F112" t="s">
         <v>211</v>
@@ -8734,19 +8734,19 @@
         <v>41</v>
       </c>
       <c r="H112" t="s">
-        <v>328</v>
+        <v>294</v>
       </c>
       <c r="I112" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J112" t="s">
-        <v>343</v>
+        <v>163</v>
       </c>
       <c r="K112" t="s">
         <v>96</v>
       </c>
       <c r="L112" t="s">
-        <v>331</v>
+        <v>297</v>
       </c>
       <c r="M112" t="s">
         <v>289</v>
@@ -8758,7 +8758,7 @@
         <v>48</v>
       </c>
       <c r="P112" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q112" t="s">
         <v>47</v>
@@ -9453,7 +9453,7 @@
         <v>34</v>
       </c>
       <c r="E125" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="F125" t="s">
         <v>218</v>
@@ -9483,7 +9483,7 @@
         <v>47</v>
       </c>
       <c r="O125" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="P125" t="s">
         <v>366</v>
@@ -9957,7 +9957,7 @@
         <v>34</v>
       </c>
       <c r="E134" t="s">
-        <v>298</v>
+        <v>327</v>
       </c>
       <c r="F134" t="s">
         <v>218</v>
@@ -10013,7 +10013,7 @@
         <v>34</v>
       </c>
       <c r="E135" t="s">
-        <v>311</v>
+        <v>337</v>
       </c>
       <c r="F135" t="s">
         <v>218</v>
@@ -10043,7 +10043,7 @@
         <v>47</v>
       </c>
       <c r="O135" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="P135" t="s">
         <v>379</v>
@@ -11708,7 +11708,7 @@
         <v>426</v>
       </c>
       <c r="J165" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K165" t="s">
         <v>58</v>
@@ -11764,7 +11764,7 @@
         <v>427</v>
       </c>
       <c r="J166" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K166" t="s">
         <v>119</v>
@@ -11820,7 +11820,7 @@
         <v>428</v>
       </c>
       <c r="J167" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K167" t="s">
         <v>119</v>
@@ -11876,7 +11876,7 @@
         <v>429</v>
       </c>
       <c r="J168" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K168" t="s">
         <v>80</v>
@@ -11932,7 +11932,7 @@
         <v>430</v>
       </c>
       <c r="J169" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K169" t="s">
         <v>70</v>
@@ -11988,7 +11988,7 @@
         <v>431</v>
       </c>
       <c r="J170" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K170" t="s">
         <v>119</v>
@@ -12044,7 +12044,7 @@
         <v>433</v>
       </c>
       <c r="J171" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K171" t="s">
         <v>119</v>
@@ -12100,7 +12100,7 @@
         <v>434</v>
       </c>
       <c r="J172" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K172" t="s">
         <v>229</v>
@@ -12156,7 +12156,7 @@
         <v>435</v>
       </c>
       <c r="J173" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K173" t="s">
         <v>119</v>
@@ -12212,7 +12212,7 @@
         <v>437</v>
       </c>
       <c r="J174" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K174" t="s">
         <v>80</v>
@@ -12268,7 +12268,7 @@
         <v>438</v>
       </c>
       <c r="J175" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K175" t="s">
         <v>90</v>
@@ -12283,7 +12283,7 @@
         <v>47</v>
       </c>
       <c r="O175" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="P175" t="s">
         <v>438</v>
@@ -12324,7 +12324,7 @@
         <v>439</v>
       </c>
       <c r="J176" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K176" t="s">
         <v>113</v>
@@ -12380,7 +12380,7 @@
         <v>440</v>
       </c>
       <c r="J177" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K177" t="s">
         <v>101</v>
@@ -12436,7 +12436,7 @@
         <v>441</v>
       </c>
       <c r="J178" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K178" t="s">
         <v>119</v>
@@ -12548,7 +12548,7 @@
         <v>446</v>
       </c>
       <c r="J180" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K180" t="s">
         <v>80</v>
@@ -12604,7 +12604,7 @@
         <v>448</v>
       </c>
       <c r="J181" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K181" t="s">
         <v>119</v>
@@ -12660,7 +12660,7 @@
         <v>430</v>
       </c>
       <c r="J182" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K182" t="s">
         <v>70</v>
@@ -12716,7 +12716,7 @@
         <v>451</v>
       </c>
       <c r="J183" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K183" t="s">
         <v>70</v>
@@ -12772,7 +12772,7 @@
         <v>427</v>
       </c>
       <c r="J184" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K184" t="s">
         <v>119</v>
@@ -12828,7 +12828,7 @@
         <v>452</v>
       </c>
       <c r="J185" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K185" t="s">
         <v>119</v>
@@ -12884,7 +12884,7 @@
         <v>439</v>
       </c>
       <c r="J186" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K186" t="s">
         <v>113</v>
@@ -12940,7 +12940,7 @@
         <v>453</v>
       </c>
       <c r="J187" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K187" t="s">
         <v>113</v>
@@ -12996,7 +12996,7 @@
         <v>438</v>
       </c>
       <c r="J188" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K188" t="s">
         <v>90</v>
@@ -13011,7 +13011,7 @@
         <v>47</v>
       </c>
       <c r="O188" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="P188" t="s">
         <v>438</v>
@@ -13052,7 +13052,7 @@
         <v>454</v>
       </c>
       <c r="J189" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K189" t="s">
         <v>90</v>
@@ -13067,7 +13067,7 @@
         <v>47</v>
       </c>
       <c r="O189" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="P189" t="s">
         <v>454</v>
@@ -13108,7 +13108,7 @@
         <v>434</v>
       </c>
       <c r="J190" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K190" t="s">
         <v>229</v>
@@ -13164,7 +13164,7 @@
         <v>455</v>
       </c>
       <c r="J191" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K191" t="s">
         <v>229</v>
@@ -13332,7 +13332,7 @@
         <v>462</v>
       </c>
       <c r="J194" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K194" t="s">
         <v>134</v>
@@ -13388,7 +13388,7 @@
         <v>464</v>
       </c>
       <c r="J195" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K195" t="s">
         <v>134</v>
@@ -13444,7 +13444,7 @@
         <v>465</v>
       </c>
       <c r="J196" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K196" t="s">
         <v>101</v>
@@ -13500,7 +13500,7 @@
         <v>431</v>
       </c>
       <c r="J197" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K197" t="s">
         <v>119</v>
@@ -13556,7 +13556,7 @@
         <v>467</v>
       </c>
       <c r="J198" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K198" t="s">
         <v>119</v>
@@ -13612,7 +13612,7 @@
         <v>441</v>
       </c>
       <c r="J199" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K199" t="s">
         <v>119</v>
@@ -13668,7 +13668,7 @@
         <v>468</v>
       </c>
       <c r="J200" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K200" t="s">
         <v>119</v>
@@ -13724,7 +13724,7 @@
         <v>470</v>
       </c>
       <c r="J201" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K201" t="s">
         <v>119</v>
@@ -13780,7 +13780,7 @@
         <v>433</v>
       </c>
       <c r="J202" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K202" t="s">
         <v>119</v>
@@ -13836,7 +13836,7 @@
         <v>471</v>
       </c>
       <c r="J203" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K203" t="s">
         <v>119</v>
@@ -14004,7 +14004,7 @@
         <v>426</v>
       </c>
       <c r="J206" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K206" t="s">
         <v>58</v>
@@ -14060,7 +14060,7 @@
         <v>477</v>
       </c>
       <c r="J207" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K207" t="s">
         <v>58</v>
@@ -14116,7 +14116,7 @@
         <v>440</v>
       </c>
       <c r="J208" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K208" t="s">
         <v>101</v>
@@ -14172,7 +14172,7 @@
         <v>478</v>
       </c>
       <c r="J209" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K209" t="s">
         <v>101</v>
@@ -14228,7 +14228,7 @@
         <v>479</v>
       </c>
       <c r="J210" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K210" t="s">
         <v>119</v>
@@ -14284,7 +14284,7 @@
         <v>428</v>
       </c>
       <c r="J211" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K211" t="s">
         <v>119</v>
@@ -14340,7 +14340,7 @@
         <v>480</v>
       </c>
       <c r="J212" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K212" t="s">
         <v>119</v>
@@ -14396,7 +14396,7 @@
         <v>437</v>
       </c>
       <c r="J213" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K213" t="s">
         <v>80</v>
@@ -14452,7 +14452,7 @@
         <v>481</v>
       </c>
       <c r="J214" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K214" t="s">
         <v>80</v>
@@ -14508,7 +14508,7 @@
         <v>435</v>
       </c>
       <c r="J215" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K215" t="s">
         <v>119</v>
@@ -14564,7 +14564,7 @@
         <v>482</v>
       </c>
       <c r="J216" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K216" t="s">
         <v>119</v>
@@ -14620,7 +14620,7 @@
         <v>483</v>
       </c>
       <c r="J217" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K217" t="s">
         <v>58</v>
@@ -14676,7 +14676,7 @@
         <v>484</v>
       </c>
       <c r="J218" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K218" t="s">
         <v>70</v>
@@ -14732,7 +14732,7 @@
         <v>485</v>
       </c>
       <c r="J219" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K219" t="s">
         <v>119</v>
@@ -14788,7 +14788,7 @@
         <v>486</v>
       </c>
       <c r="J220" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K220" t="s">
         <v>119</v>
@@ -14844,7 +14844,7 @@
         <v>429</v>
       </c>
       <c r="J221" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K221" t="s">
         <v>80</v>
@@ -14900,7 +14900,7 @@
         <v>487</v>
       </c>
       <c r="J222" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K222" t="s">
         <v>80</v>
@@ -14956,7 +14956,7 @@
         <v>488</v>
       </c>
       <c r="J223" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K223" t="s">
         <v>119</v>
@@ -15012,7 +15012,7 @@
         <v>489</v>
       </c>
       <c r="J224" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K224" t="s">
         <v>80</v>
@@ -15068,7 +15068,7 @@
         <v>490</v>
       </c>
       <c r="J225" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K225" t="s">
         <v>229</v>
@@ -15124,7 +15124,7 @@
         <v>491</v>
       </c>
       <c r="J226" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K226" t="s">
         <v>90</v>
@@ -15139,7 +15139,7 @@
         <v>47</v>
       </c>
       <c r="O226" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="P226" t="s">
         <v>491</v>
@@ -15180,7 +15180,7 @@
         <v>492</v>
       </c>
       <c r="J227" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K227" t="s">
         <v>119</v>
@@ -15236,7 +15236,7 @@
         <v>493</v>
       </c>
       <c r="J228" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K228" t="s">
         <v>113</v>
@@ -15460,7 +15460,7 @@
         <v>505</v>
       </c>
       <c r="J232" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K232" t="s">
         <v>119</v>
@@ -15516,7 +15516,7 @@
         <v>471</v>
       </c>
       <c r="J233" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K233" t="s">
         <v>119</v>
@@ -15557,25 +15557,25 @@
         <v>33</v>
       </c>
       <c r="E234" t="s">
-        <v>354</v>
+        <v>275</v>
       </c>
       <c r="F234" t="s">
-        <v>499</v>
+        <v>218</v>
       </c>
       <c r="G234" t="s">
         <v>41</v>
       </c>
       <c r="H234" t="s">
-        <v>215</v>
+        <v>457</v>
       </c>
       <c r="I234" t="s">
         <v>508</v>
       </c>
       <c r="J234" t="s">
-        <v>90</v>
+        <v>304</v>
       </c>
       <c r="K234" t="s">
-        <v>229</v>
+        <v>58</v>
       </c>
       <c r="L234" t="s">
         <v>34</v>
@@ -15587,13 +15587,13 @@
         <v>47</v>
       </c>
       <c r="O234" t="s">
-        <v>34</v>
+        <v>105</v>
       </c>
       <c r="P234" t="s">
-        <v>34</v>
+        <v>508</v>
       </c>
       <c r="Q234" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R234" t="s">
         <v>34</v>
@@ -15613,22 +15613,22 @@
         <v>34</v>
       </c>
       <c r="E235" t="s">
-        <v>360</v>
+        <v>234</v>
       </c>
       <c r="F235" t="s">
-        <v>499</v>
+        <v>218</v>
       </c>
       <c r="G235" t="s">
         <v>41</v>
       </c>
       <c r="H235" t="s">
-        <v>215</v>
+        <v>457</v>
       </c>
       <c r="I235" t="s">
         <v>509</v>
       </c>
       <c r="J235" t="s">
-        <v>119</v>
+        <v>300</v>
       </c>
       <c r="K235" t="s">
         <v>119</v>
@@ -15643,13 +15643,13 @@
         <v>47</v>
       </c>
       <c r="O235" t="s">
-        <v>34</v>
+        <v>130</v>
       </c>
       <c r="P235" t="s">
-        <v>34</v>
+        <v>509</v>
       </c>
       <c r="Q235" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R235" t="s">
         <v>34</v>
@@ -15669,25 +15669,25 @@
         <v>34</v>
       </c>
       <c r="E236" t="s">
+        <v>244</v>
+      </c>
+      <c r="F236" t="s">
+        <v>218</v>
+      </c>
+      <c r="G236" t="s">
+        <v>41</v>
+      </c>
+      <c r="H236" t="s">
         <v>510</v>
       </c>
-      <c r="F236" t="s">
-        <v>499</v>
-      </c>
-      <c r="G236" t="s">
-        <v>41</v>
-      </c>
-      <c r="H236" t="s">
-        <v>215</v>
-      </c>
       <c r="I236" t="s">
-        <v>464</v>
+        <v>511</v>
       </c>
       <c r="J236" t="s">
-        <v>134</v>
+        <v>512</v>
       </c>
       <c r="K236" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="L236" t="s">
         <v>34</v>
@@ -15699,13 +15699,13 @@
         <v>47</v>
       </c>
       <c r="O236" t="s">
-        <v>34</v>
+        <v>247</v>
       </c>
       <c r="P236" t="s">
-        <v>34</v>
+        <v>511</v>
       </c>
       <c r="Q236" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R236" t="s">
         <v>34</v>
@@ -15725,25 +15725,25 @@
         <v>34</v>
       </c>
       <c r="E237" t="s">
-        <v>357</v>
+        <v>248</v>
       </c>
       <c r="F237" t="s">
-        <v>499</v>
+        <v>218</v>
       </c>
       <c r="G237" t="s">
         <v>41</v>
       </c>
       <c r="H237" t="s">
-        <v>215</v>
+        <v>513</v>
       </c>
       <c r="I237" t="s">
-        <v>511</v>
+        <v>428</v>
       </c>
       <c r="J237" t="s">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="K237" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="L237" t="s">
         <v>34</v>
@@ -15755,13 +15755,13 @@
         <v>47</v>
       </c>
       <c r="O237" t="s">
-        <v>34</v>
+        <v>250</v>
       </c>
       <c r="P237" t="s">
-        <v>34</v>
+        <v>428</v>
       </c>
       <c r="Q237" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R237" t="s">
         <v>34</v>
@@ -15781,25 +15781,25 @@
         <v>34</v>
       </c>
       <c r="E238" t="s">
-        <v>363</v>
+        <v>253</v>
       </c>
       <c r="F238" t="s">
-        <v>499</v>
+        <v>218</v>
       </c>
       <c r="G238" t="s">
         <v>41</v>
       </c>
       <c r="H238" t="s">
-        <v>215</v>
+        <v>510</v>
       </c>
       <c r="I238" t="s">
-        <v>512</v>
+        <v>429</v>
       </c>
       <c r="J238" t="s">
-        <v>126</v>
+        <v>514</v>
       </c>
       <c r="K238" t="s">
-        <v>126</v>
+        <v>80</v>
       </c>
       <c r="L238" t="s">
         <v>34</v>
@@ -15811,13 +15811,13 @@
         <v>47</v>
       </c>
       <c r="O238" t="s">
-        <v>34</v>
+        <v>255</v>
       </c>
       <c r="P238" t="s">
-        <v>34</v>
+        <v>429</v>
       </c>
       <c r="Q238" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R238" t="s">
         <v>34</v>
@@ -15837,25 +15837,25 @@
         <v>34</v>
       </c>
       <c r="E239" t="s">
-        <v>348</v>
+        <v>223</v>
       </c>
       <c r="F239" t="s">
-        <v>499</v>
+        <v>218</v>
       </c>
       <c r="G239" t="s">
         <v>41</v>
       </c>
       <c r="H239" t="s">
-        <v>215</v>
+        <v>513</v>
       </c>
       <c r="I239" t="s">
-        <v>512</v>
+        <v>439</v>
       </c>
       <c r="J239" t="s">
-        <v>126</v>
+        <v>515</v>
       </c>
       <c r="K239" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="L239" t="s">
         <v>34</v>
@@ -15867,13 +15867,13 @@
         <v>47</v>
       </c>
       <c r="O239" t="s">
-        <v>34</v>
+        <v>114</v>
       </c>
       <c r="P239" t="s">
-        <v>34</v>
+        <v>439</v>
       </c>
       <c r="Q239" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R239" t="s">
         <v>34</v>
@@ -15949,25 +15949,25 @@
         <v>34</v>
       </c>
       <c r="E241" t="s">
-        <v>253</v>
+        <v>360</v>
       </c>
       <c r="F241" t="s">
-        <v>218</v>
+        <v>499</v>
       </c>
       <c r="G241" t="s">
         <v>41</v>
       </c>
       <c r="H241" t="s">
-        <v>513</v>
+        <v>215</v>
       </c>
       <c r="I241" t="s">
-        <v>429</v>
+        <v>516</v>
       </c>
       <c r="J241" t="s">
-        <v>514</v>
+        <v>119</v>
       </c>
       <c r="K241" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="L241" t="s">
         <v>34</v>
@@ -15979,13 +15979,13 @@
         <v>47</v>
       </c>
       <c r="O241" t="s">
-        <v>255</v>
+        <v>34</v>
       </c>
       <c r="P241" t="s">
-        <v>429</v>
+        <v>34</v>
       </c>
       <c r="Q241" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R241" t="s">
         <v>34</v>
@@ -16005,25 +16005,25 @@
         <v>34</v>
       </c>
       <c r="E242" t="s">
-        <v>248</v>
+        <v>357</v>
       </c>
       <c r="F242" t="s">
-        <v>218</v>
+        <v>499</v>
       </c>
       <c r="G242" t="s">
         <v>41</v>
       </c>
       <c r="H242" t="s">
-        <v>515</v>
+        <v>215</v>
       </c>
       <c r="I242" t="s">
-        <v>428</v>
+        <v>517</v>
       </c>
       <c r="J242" t="s">
-        <v>303</v>
+        <v>80</v>
       </c>
       <c r="K242" t="s">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="L242" t="s">
         <v>34</v>
@@ -16035,13 +16035,13 @@
         <v>47</v>
       </c>
       <c r="O242" t="s">
-        <v>250</v>
+        <v>34</v>
       </c>
       <c r="P242" t="s">
-        <v>428</v>
+        <v>34</v>
       </c>
       <c r="Q242" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R242" t="s">
         <v>34</v>
@@ -16061,7 +16061,7 @@
         <v>34</v>
       </c>
       <c r="E243" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="F243" t="s">
         <v>218</v>
@@ -16070,16 +16070,16 @@
         <v>41</v>
       </c>
       <c r="H243" t="s">
-        <v>457</v>
+        <v>513</v>
       </c>
       <c r="I243" t="s">
-        <v>516</v>
+        <v>430</v>
       </c>
       <c r="J243" t="s">
-        <v>303</v>
+        <v>515</v>
       </c>
       <c r="K243" t="s">
-        <v>119</v>
+        <v>70</v>
       </c>
       <c r="L243" t="s">
         <v>34</v>
@@ -16091,10 +16091,10 @@
         <v>47</v>
       </c>
       <c r="O243" t="s">
-        <v>130</v>
+        <v>71</v>
       </c>
       <c r="P243" t="s">
-        <v>516</v>
+        <v>430</v>
       </c>
       <c r="Q243" t="s">
         <v>47</v>
@@ -16117,7 +16117,7 @@
         <v>34</v>
       </c>
       <c r="E244" t="s">
-        <v>223</v>
+        <v>472</v>
       </c>
       <c r="F244" t="s">
         <v>218</v>
@@ -16126,13 +16126,13 @@
         <v>41</v>
       </c>
       <c r="H244" t="s">
-        <v>515</v>
+        <v>457</v>
       </c>
       <c r="I244" t="s">
-        <v>439</v>
+        <v>473</v>
       </c>
       <c r="J244" t="s">
-        <v>517</v>
+        <v>461</v>
       </c>
       <c r="K244" t="s">
         <v>113</v>
@@ -16147,10 +16147,10 @@
         <v>47</v>
       </c>
       <c r="O244" t="s">
-        <v>114</v>
+        <v>475</v>
       </c>
       <c r="P244" t="s">
-        <v>439</v>
+        <v>473</v>
       </c>
       <c r="Q244" t="s">
         <v>47</v>
@@ -16173,25 +16173,25 @@
         <v>34</v>
       </c>
       <c r="E245" t="s">
-        <v>251</v>
+        <v>518</v>
       </c>
       <c r="F245" t="s">
-        <v>218</v>
+        <v>499</v>
       </c>
       <c r="G245" t="s">
         <v>41</v>
       </c>
       <c r="H245" t="s">
-        <v>515</v>
+        <v>215</v>
       </c>
       <c r="I245" t="s">
-        <v>430</v>
+        <v>464</v>
       </c>
       <c r="J245" t="s">
-        <v>517</v>
+        <v>134</v>
       </c>
       <c r="K245" t="s">
-        <v>70</v>
+        <v>134</v>
       </c>
       <c r="L245" t="s">
         <v>34</v>
@@ -16203,13 +16203,13 @@
         <v>47</v>
       </c>
       <c r="O245" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="P245" t="s">
-        <v>430</v>
+        <v>34</v>
       </c>
       <c r="Q245" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R245" t="s">
         <v>34</v>
@@ -16229,7 +16229,7 @@
         <v>34</v>
       </c>
       <c r="E246" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="F246" t="s">
         <v>218</v>
@@ -16241,13 +16241,13 @@
         <v>513</v>
       </c>
       <c r="I246" t="s">
-        <v>518</v>
+        <v>438</v>
       </c>
       <c r="J246" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="K246" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L246" t="s">
         <v>34</v>
@@ -16259,10 +16259,10 @@
         <v>47</v>
       </c>
       <c r="O246" t="s">
-        <v>247</v>
+        <v>310</v>
       </c>
       <c r="P246" t="s">
-        <v>518</v>
+        <v>438</v>
       </c>
       <c r="Q246" t="s">
         <v>47</v>
@@ -16285,25 +16285,25 @@
         <v>34</v>
       </c>
       <c r="E247" t="s">
-        <v>275</v>
+        <v>354</v>
       </c>
       <c r="F247" t="s">
-        <v>218</v>
+        <v>499</v>
       </c>
       <c r="G247" t="s">
         <v>41</v>
       </c>
       <c r="H247" t="s">
-        <v>457</v>
+        <v>215</v>
       </c>
       <c r="I247" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="J247" t="s">
-        <v>320</v>
+        <v>90</v>
       </c>
       <c r="K247" t="s">
-        <v>58</v>
+        <v>229</v>
       </c>
       <c r="L247" t="s">
         <v>34</v>
@@ -16315,13 +16315,13 @@
         <v>47</v>
       </c>
       <c r="O247" t="s">
-        <v>105</v>
+        <v>34</v>
       </c>
       <c r="P247" t="s">
-        <v>520</v>
+        <v>34</v>
       </c>
       <c r="Q247" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R247" t="s">
         <v>34</v>
@@ -16341,7 +16341,7 @@
         <v>34</v>
       </c>
       <c r="E248" t="s">
-        <v>472</v>
+        <v>225</v>
       </c>
       <c r="F248" t="s">
         <v>218</v>
@@ -16353,13 +16353,13 @@
         <v>457</v>
       </c>
       <c r="I248" t="s">
-        <v>473</v>
+        <v>520</v>
       </c>
       <c r="J248" t="s">
-        <v>461</v>
+        <v>304</v>
       </c>
       <c r="K248" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="L248" t="s">
         <v>34</v>
@@ -16371,10 +16371,10 @@
         <v>47</v>
       </c>
       <c r="O248" t="s">
-        <v>475</v>
+        <v>102</v>
       </c>
       <c r="P248" t="s">
-        <v>473</v>
+        <v>520</v>
       </c>
       <c r="Q248" t="s">
         <v>47</v>
@@ -16397,25 +16397,25 @@
         <v>34</v>
       </c>
       <c r="E249" t="s">
-        <v>225</v>
+        <v>348</v>
       </c>
       <c r="F249" t="s">
-        <v>218</v>
+        <v>499</v>
       </c>
       <c r="G249" t="s">
         <v>41</v>
       </c>
       <c r="H249" t="s">
-        <v>457</v>
+        <v>215</v>
       </c>
       <c r="I249" t="s">
         <v>521</v>
       </c>
       <c r="J249" t="s">
-        <v>320</v>
+        <v>126</v>
       </c>
       <c r="K249" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="L249" t="s">
         <v>34</v>
@@ -16427,13 +16427,13 @@
         <v>47</v>
       </c>
       <c r="O249" t="s">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="P249" t="s">
-        <v>521</v>
+        <v>34</v>
       </c>
       <c r="Q249" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R249" t="s">
         <v>34</v>
@@ -16453,25 +16453,25 @@
         <v>34</v>
       </c>
       <c r="E250" t="s">
-        <v>232</v>
+        <v>363</v>
       </c>
       <c r="F250" t="s">
-        <v>218</v>
+        <v>499</v>
       </c>
       <c r="G250" t="s">
         <v>41</v>
       </c>
       <c r="H250" t="s">
-        <v>515</v>
+        <v>215</v>
       </c>
       <c r="I250" t="s">
-        <v>438</v>
+        <v>521</v>
       </c>
       <c r="J250" t="s">
-        <v>517</v>
+        <v>126</v>
       </c>
       <c r="K250" t="s">
-        <v>90</v>
+        <v>126</v>
       </c>
       <c r="L250" t="s">
         <v>34</v>
@@ -16483,13 +16483,13 @@
         <v>47</v>
       </c>
       <c r="O250" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="P250" t="s">
-        <v>438</v>
+        <v>34</v>
       </c>
       <c r="Q250" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R250" t="s">
         <v>34</v>
@@ -17414,7 +17414,7 @@
         <v>41</v>
       </c>
       <c r="H267" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="I267" t="s">
         <v>554</v>
@@ -17924,7 +17924,7 @@
         <v>574</v>
       </c>
       <c r="J276" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K276" t="s">
         <v>96</v>
@@ -18036,7 +18036,7 @@
         <v>580</v>
       </c>
       <c r="J278" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K278" t="s">
         <v>96</v>
@@ -18092,7 +18092,7 @@
         <v>583</v>
       </c>
       <c r="J279" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K279" t="s">
         <v>96</v>
@@ -18148,7 +18148,7 @@
         <v>586</v>
       </c>
       <c r="J280" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K280" t="s">
         <v>75</v>
@@ -18260,7 +18260,7 @@
         <v>592</v>
       </c>
       <c r="J282" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K282" t="s">
         <v>96</v>
@@ -18316,7 +18316,7 @@
         <v>595</v>
       </c>
       <c r="J283" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K283" t="s">
         <v>96</v>
@@ -18372,7 +18372,7 @@
         <v>598</v>
       </c>
       <c r="J284" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K284" t="s">
         <v>96</v>
@@ -18428,7 +18428,7 @@
         <v>601</v>
       </c>
       <c r="J285" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K285" t="s">
         <v>96</v>
@@ -18484,7 +18484,7 @@
         <v>604</v>
       </c>
       <c r="J286" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K286" t="s">
         <v>96</v>
@@ -18540,7 +18540,7 @@
         <v>607</v>
       </c>
       <c r="J287" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K287" t="s">
         <v>85</v>
@@ -18596,7 +18596,7 @@
         <v>609</v>
       </c>
       <c r="J288" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K288" t="s">
         <v>96</v>
@@ -18652,7 +18652,7 @@
         <v>612</v>
       </c>
       <c r="J289" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K289" t="s">
         <v>96</v>
@@ -18708,7 +18708,7 @@
         <v>615</v>
       </c>
       <c r="J290" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K290" t="s">
         <v>96</v>
@@ -18764,7 +18764,7 @@
         <v>617</v>
       </c>
       <c r="J291" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K291" t="s">
         <v>96</v>
@@ -18820,7 +18820,7 @@
         <v>619</v>
       </c>
       <c r="J292" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K292" t="s">
         <v>96</v>
@@ -18835,7 +18835,7 @@
         <v>47</v>
       </c>
       <c r="O292" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="P292" t="s">
         <v>619</v>
@@ -18876,7 +18876,7 @@
         <v>621</v>
       </c>
       <c r="J293" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K293" t="s">
         <v>96</v>
@@ -18932,7 +18932,7 @@
         <v>624</v>
       </c>
       <c r="J294" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K294" t="s">
         <v>96</v>
@@ -18988,7 +18988,7 @@
         <v>627</v>
       </c>
       <c r="J295" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K295" t="s">
         <v>96</v>
@@ -19044,7 +19044,7 @@
         <v>630</v>
       </c>
       <c r="J296" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K296" t="s">
         <v>96</v>
@@ -19059,7 +19059,7 @@
         <v>47</v>
       </c>
       <c r="O296" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="P296" t="s">
         <v>630</v>
@@ -19100,7 +19100,7 @@
         <v>632</v>
       </c>
       <c r="J297" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K297" t="s">
         <v>96</v>
@@ -19156,7 +19156,7 @@
         <v>609</v>
       </c>
       <c r="J298" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K298" t="s">
         <v>96</v>
@@ -19940,7 +19940,7 @@
         <v>660</v>
       </c>
       <c r="J312" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K312" t="s">
         <v>96</v>
@@ -20093,25 +20093,25 @@
         <v>33</v>
       </c>
       <c r="E315" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="F315" t="s">
-        <v>40</v>
+        <v>666</v>
       </c>
       <c r="G315" t="s">
         <v>41</v>
       </c>
       <c r="H315" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="I315" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="J315" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="K315" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="L315" t="s">
         <v>34</v>
@@ -20123,13 +20123,13 @@
         <v>47</v>
       </c>
       <c r="O315" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="P315" t="s">
-        <v>667</v>
+        <v>34</v>
       </c>
       <c r="Q315" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R315" t="s">
         <v>34</v>
@@ -20149,7 +20149,7 @@
         <v>34</v>
       </c>
       <c r="E316" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="F316" t="s">
         <v>40</v>
@@ -20158,16 +20158,16 @@
         <v>41</v>
       </c>
       <c r="H316" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="I316" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="J316" t="s">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="K316" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="L316" t="s">
         <v>34</v>
@@ -20179,10 +20179,10 @@
         <v>47</v>
       </c>
       <c r="O316" t="s">
-        <v>247</v>
+        <v>114</v>
       </c>
       <c r="P316" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="Q316" t="s">
         <v>47</v>
@@ -20205,7 +20205,7 @@
         <v>34</v>
       </c>
       <c r="E317" t="s">
-        <v>248</v>
+        <v>275</v>
       </c>
       <c r="F317" t="s">
         <v>40</v>
@@ -20214,16 +20214,16 @@
         <v>41</v>
       </c>
       <c r="H317" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="I317" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="J317" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="K317" t="s">
-        <v>119</v>
+        <v>58</v>
       </c>
       <c r="L317" t="s">
         <v>34</v>
@@ -20235,10 +20235,10 @@
         <v>47</v>
       </c>
       <c r="O317" t="s">
-        <v>250</v>
+        <v>105</v>
       </c>
       <c r="P317" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="Q317" t="s">
         <v>47</v>
@@ -20261,22 +20261,22 @@
         <v>34</v>
       </c>
       <c r="E318" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F318" t="s">
-        <v>40</v>
+        <v>666</v>
       </c>
       <c r="G318" t="s">
         <v>41</v>
       </c>
       <c r="H318" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="I318" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="J318" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K318" t="s">
         <v>119</v>
@@ -20291,13 +20291,13 @@
         <v>47</v>
       </c>
       <c r="O318" t="s">
-        <v>130</v>
+        <v>34</v>
       </c>
       <c r="P318" t="s">
-        <v>667</v>
+        <v>34</v>
       </c>
       <c r="Q318" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R318" t="s">
         <v>34</v>
@@ -20317,7 +20317,7 @@
         <v>34</v>
       </c>
       <c r="E319" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="F319" t="s">
         <v>40</v>
@@ -20326,16 +20326,16 @@
         <v>41</v>
       </c>
       <c r="H319" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="I319" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="J319" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="K319" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="L319" t="s">
         <v>34</v>
@@ -20347,10 +20347,10 @@
         <v>47</v>
       </c>
       <c r="O319" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="P319" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="Q319" t="s">
         <v>47</v>
@@ -20373,25 +20373,25 @@
         <v>34</v>
       </c>
       <c r="E320" t="s">
-        <v>227</v>
+        <v>157</v>
       </c>
       <c r="F320" t="s">
+        <v>40</v>
+      </c>
+      <c r="G320" t="s">
+        <v>41</v>
+      </c>
+      <c r="H320" t="s">
+        <v>667</v>
+      </c>
+      <c r="I320" t="s">
         <v>668</v>
       </c>
-      <c r="G320" t="s">
-        <v>41</v>
-      </c>
-      <c r="H320" t="s">
-        <v>666</v>
-      </c>
-      <c r="I320" t="s">
-        <v>667</v>
-      </c>
       <c r="J320" t="s">
-        <v>90</v>
+        <v>134</v>
       </c>
       <c r="K320" t="s">
-        <v>229</v>
+        <v>134</v>
       </c>
       <c r="L320" t="s">
         <v>34</v>
@@ -20403,13 +20403,13 @@
         <v>47</v>
       </c>
       <c r="O320" t="s">
-        <v>34</v>
+        <v>463</v>
       </c>
       <c r="P320" t="s">
-        <v>34</v>
+        <v>668</v>
       </c>
       <c r="Q320" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R320" t="s">
         <v>34</v>
@@ -20429,25 +20429,25 @@
         <v>34</v>
       </c>
       <c r="E321" t="s">
-        <v>256</v>
+        <v>221</v>
       </c>
       <c r="F321" t="s">
+        <v>666</v>
+      </c>
+      <c r="G321" t="s">
+        <v>41</v>
+      </c>
+      <c r="H321" t="s">
+        <v>667</v>
+      </c>
+      <c r="I321" t="s">
         <v>668</v>
       </c>
-      <c r="G321" t="s">
-        <v>41</v>
-      </c>
-      <c r="H321" t="s">
-        <v>666</v>
-      </c>
-      <c r="I321" t="s">
-        <v>667</v>
-      </c>
       <c r="J321" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K321" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L321" t="s">
         <v>34</v>
@@ -20485,25 +20485,25 @@
         <v>34</v>
       </c>
       <c r="E322" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="F322" t="s">
+        <v>40</v>
+      </c>
+      <c r="G322" t="s">
+        <v>41</v>
+      </c>
+      <c r="H322" t="s">
+        <v>667</v>
+      </c>
+      <c r="I322" t="s">
         <v>668</v>
       </c>
-      <c r="G322" t="s">
-        <v>41</v>
-      </c>
-      <c r="H322" t="s">
-        <v>666</v>
-      </c>
-      <c r="I322" t="s">
-        <v>667</v>
-      </c>
       <c r="J322" t="s">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="K322" t="s">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="L322" t="s">
         <v>34</v>
@@ -20515,13 +20515,13 @@
         <v>47</v>
       </c>
       <c r="O322" t="s">
-        <v>34</v>
+        <v>255</v>
       </c>
       <c r="P322" t="s">
-        <v>34</v>
+        <v>668</v>
       </c>
       <c r="Q322" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R322" t="s">
         <v>34</v>
@@ -20541,7 +20541,7 @@
         <v>34</v>
       </c>
       <c r="E323" t="s">
-        <v>157</v>
+        <v>244</v>
       </c>
       <c r="F323" t="s">
         <v>40</v>
@@ -20550,16 +20550,16 @@
         <v>41</v>
       </c>
       <c r="H323" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="I323" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="J323" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="K323" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="L323" t="s">
         <v>34</v>
@@ -20571,10 +20571,10 @@
         <v>47</v>
       </c>
       <c r="O323" t="s">
-        <v>463</v>
+        <v>247</v>
       </c>
       <c r="P323" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="Q323" t="s">
         <v>47</v>
@@ -20597,7 +20597,7 @@
         <v>34</v>
       </c>
       <c r="E324" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="F324" t="s">
         <v>40</v>
@@ -20606,16 +20606,16 @@
         <v>41</v>
       </c>
       <c r="H324" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="I324" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="J324" t="s">
-        <v>147</v>
+        <v>90</v>
       </c>
       <c r="K324" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="L324" t="s">
         <v>34</v>
@@ -20627,10 +20627,10 @@
         <v>47</v>
       </c>
       <c r="O324" t="s">
-        <v>114</v>
+        <v>310</v>
       </c>
       <c r="P324" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="Q324" t="s">
         <v>47</v>
@@ -20653,7 +20653,7 @@
         <v>34</v>
       </c>
       <c r="E325" t="s">
-        <v>275</v>
+        <v>225</v>
       </c>
       <c r="F325" t="s">
         <v>40</v>
@@ -20662,16 +20662,16 @@
         <v>41</v>
       </c>
       <c r="H325" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="I325" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="J325" t="s">
-        <v>96</v>
+        <v>178</v>
       </c>
       <c r="K325" t="s">
-        <v>58</v>
+        <v>101</v>
       </c>
       <c r="L325" t="s">
         <v>34</v>
@@ -20683,10 +20683,10 @@
         <v>47</v>
       </c>
       <c r="O325" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="P325" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="Q325" t="s">
         <v>47</v>
@@ -20709,25 +20709,25 @@
         <v>34</v>
       </c>
       <c r="E326" t="s">
-        <v>221</v>
+        <v>256</v>
       </c>
       <c r="F326" t="s">
+        <v>666</v>
+      </c>
+      <c r="G326" t="s">
+        <v>41</v>
+      </c>
+      <c r="H326" t="s">
+        <v>667</v>
+      </c>
+      <c r="I326" t="s">
         <v>668</v>
       </c>
-      <c r="G326" t="s">
-        <v>41</v>
-      </c>
-      <c r="H326" t="s">
-        <v>666</v>
-      </c>
-      <c r="I326" t="s">
-        <v>667</v>
-      </c>
       <c r="J326" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K326" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L326" t="s">
         <v>34</v>
@@ -20765,25 +20765,25 @@
         <v>34</v>
       </c>
       <c r="E327" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="F327" t="s">
+        <v>40</v>
+      </c>
+      <c r="G327" t="s">
+        <v>41</v>
+      </c>
+      <c r="H327" t="s">
+        <v>667</v>
+      </c>
+      <c r="I327" t="s">
         <v>668</v>
       </c>
-      <c r="G327" t="s">
-        <v>41</v>
-      </c>
-      <c r="H327" t="s">
-        <v>666</v>
-      </c>
-      <c r="I327" t="s">
-        <v>667</v>
-      </c>
       <c r="J327" t="s">
-        <v>191</v>
+        <v>118</v>
       </c>
       <c r="K327" t="s">
-        <v>191</v>
+        <v>119</v>
       </c>
       <c r="L327" t="s">
         <v>34</v>
@@ -20795,13 +20795,13 @@
         <v>47</v>
       </c>
       <c r="O327" t="s">
-        <v>34</v>
+        <v>130</v>
       </c>
       <c r="P327" t="s">
-        <v>34</v>
+        <v>668</v>
       </c>
       <c r="Q327" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R327" t="s">
         <v>34</v>
@@ -20821,25 +20821,25 @@
         <v>34</v>
       </c>
       <c r="E328" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F328" t="s">
-        <v>40</v>
+        <v>666</v>
       </c>
       <c r="G328" t="s">
         <v>41</v>
       </c>
       <c r="H328" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="I328" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="J328" t="s">
-        <v>178</v>
+        <v>90</v>
       </c>
       <c r="K328" t="s">
-        <v>101</v>
+        <v>229</v>
       </c>
       <c r="L328" t="s">
         <v>34</v>
@@ -20851,13 +20851,13 @@
         <v>47</v>
       </c>
       <c r="O328" t="s">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="P328" t="s">
-        <v>667</v>
+        <v>34</v>
       </c>
       <c r="Q328" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R328" t="s">
         <v>34</v>
@@ -20948,7 +20948,7 @@
         <v>674</v>
       </c>
       <c r="J330" t="s">
-        <v>293</v>
+        <v>335</v>
       </c>
       <c r="K330" t="s">
         <v>45</v>
@@ -20989,28 +20989,28 @@
         <v>34</v>
       </c>
       <c r="E331" t="s">
-        <v>175</v>
+        <v>676</v>
       </c>
       <c r="F331" t="s">
-        <v>40</v>
+        <v>211</v>
       </c>
       <c r="G331" t="s">
         <v>41</v>
       </c>
       <c r="H331" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="I331" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="J331" t="s">
-        <v>178</v>
+        <v>679</v>
       </c>
       <c r="K331" t="s">
-        <v>178</v>
+        <v>229</v>
       </c>
       <c r="L331" t="s">
-        <v>678</v>
+        <v>34</v>
       </c>
       <c r="M331" t="s">
         <v>671</v>
@@ -21022,7 +21022,7 @@
         <v>48</v>
       </c>
       <c r="P331" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="Q331" t="s">
         <v>47</v>
@@ -21045,7 +21045,7 @@
         <v>34</v>
       </c>
       <c r="E332" t="s">
-        <v>672</v>
+        <v>175</v>
       </c>
       <c r="F332" t="s">
         <v>40</v>
@@ -21054,16 +21054,16 @@
         <v>41</v>
       </c>
       <c r="H332" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="I332" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="J332" t="s">
-        <v>681</v>
+        <v>178</v>
       </c>
       <c r="K332" t="s">
-        <v>229</v>
+        <v>178</v>
       </c>
       <c r="L332" t="s">
         <v>682</v>
@@ -21078,7 +21078,7 @@
         <v>48</v>
       </c>
       <c r="P332" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="Q332" t="s">
         <v>47</v>
@@ -21101,28 +21101,28 @@
         <v>34</v>
       </c>
       <c r="E333" t="s">
+        <v>672</v>
+      </c>
+      <c r="F333" t="s">
+        <v>40</v>
+      </c>
+      <c r="G333" t="s">
+        <v>41</v>
+      </c>
+      <c r="H333" t="s">
         <v>683</v>
       </c>
-      <c r="F333" t="s">
-        <v>211</v>
-      </c>
-      <c r="G333" t="s">
-        <v>41</v>
-      </c>
-      <c r="H333" t="s">
+      <c r="I333" t="s">
         <v>684</v>
       </c>
-      <c r="I333" t="s">
+      <c r="J333" t="s">
         <v>685</v>
-      </c>
-      <c r="J333" t="s">
-        <v>686</v>
       </c>
       <c r="K333" t="s">
         <v>229</v>
       </c>
       <c r="L333" t="s">
-        <v>34</v>
+        <v>686</v>
       </c>
       <c r="M333" t="s">
         <v>671</v>
@@ -21134,7 +21134,7 @@
         <v>48</v>
       </c>
       <c r="P333" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="Q333" t="s">
         <v>47</v>
@@ -21340,7 +21340,7 @@
         <v>694</v>
       </c>
       <c r="J337" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K337" t="s">
         <v>45</v>
@@ -21493,7 +21493,7 @@
         <v>33</v>
       </c>
       <c r="E340" t="s">
-        <v>672</v>
+        <v>175</v>
       </c>
       <c r="F340" t="s">
         <v>40</v>
@@ -21502,19 +21502,19 @@
         <v>41</v>
       </c>
       <c r="H340" t="s">
-        <v>702</v>
+        <v>447</v>
       </c>
       <c r="I340" t="s">
-        <v>703</v>
+        <v>155</v>
       </c>
       <c r="J340" t="s">
-        <v>681</v>
+        <v>122</v>
       </c>
       <c r="K340" t="s">
         <v>45</v>
       </c>
       <c r="L340" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="M340" t="s">
         <v>701</v>
@@ -21526,7 +21526,7 @@
         <v>48</v>
       </c>
       <c r="P340" t="s">
-        <v>703</v>
+        <v>155</v>
       </c>
       <c r="Q340" t="s">
         <v>47</v>
@@ -21549,28 +21549,28 @@
         <v>34</v>
       </c>
       <c r="E341" t="s">
-        <v>672</v>
+        <v>703</v>
       </c>
       <c r="F341" t="s">
-        <v>40</v>
+        <v>211</v>
       </c>
       <c r="G341" t="s">
         <v>41</v>
       </c>
       <c r="H341" t="s">
+        <v>215</v>
+      </c>
+      <c r="I341" t="s">
+        <v>704</v>
+      </c>
+      <c r="J341" t="s">
+        <v>474</v>
+      </c>
+      <c r="K341" t="s">
+        <v>80</v>
+      </c>
+      <c r="L341" t="s">
         <v>705</v>
-      </c>
-      <c r="I341" t="s">
-        <v>706</v>
-      </c>
-      <c r="J341" t="s">
-        <v>681</v>
-      </c>
-      <c r="K341" t="s">
-        <v>45</v>
-      </c>
-      <c r="L341" t="s">
-        <v>707</v>
       </c>
       <c r="M341" t="s">
         <v>701</v>
@@ -21582,7 +21582,7 @@
         <v>48</v>
       </c>
       <c r="P341" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="Q341" t="s">
         <v>47</v>
@@ -21614,7 +21614,7 @@
         <v>41</v>
       </c>
       <c r="H342" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="I342" t="s">
         <v>694</v>
@@ -21626,7 +21626,7 @@
         <v>45</v>
       </c>
       <c r="L342" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="M342" t="s">
         <v>701</v>
@@ -21670,19 +21670,19 @@
         <v>41</v>
       </c>
       <c r="H343" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="I343" t="s">
-        <v>694</v>
+        <v>708</v>
       </c>
       <c r="J343" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K343" t="s">
         <v>45</v>
       </c>
       <c r="L343" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="M343" t="s">
         <v>701</v>
@@ -21694,7 +21694,7 @@
         <v>48</v>
       </c>
       <c r="P343" t="s">
-        <v>694</v>
+        <v>708</v>
       </c>
       <c r="Q343" t="s">
         <v>47</v>
@@ -21726,19 +21726,19 @@
         <v>41</v>
       </c>
       <c r="H344" t="s">
+        <v>710</v>
+      </c>
+      <c r="I344" t="s">
         <v>711</v>
       </c>
-      <c r="I344" t="s">
-        <v>712</v>
-      </c>
       <c r="J344" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K344" t="s">
         <v>45</v>
       </c>
       <c r="L344" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="M344" t="s">
         <v>701</v>
@@ -21750,7 +21750,7 @@
         <v>48</v>
       </c>
       <c r="P344" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="Q344" t="s">
         <v>47</v>
@@ -21782,19 +21782,19 @@
         <v>41</v>
       </c>
       <c r="H345" t="s">
+        <v>713</v>
+      </c>
+      <c r="I345" t="s">
         <v>714</v>
       </c>
-      <c r="I345" t="s">
-        <v>715</v>
-      </c>
       <c r="J345" t="s">
-        <v>681</v>
+        <v>335</v>
       </c>
       <c r="K345" t="s">
         <v>45</v>
       </c>
       <c r="L345" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="M345" t="s">
         <v>701</v>
@@ -21806,7 +21806,7 @@
         <v>48</v>
       </c>
       <c r="P345" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Q345" t="s">
         <v>47</v>
@@ -21838,19 +21838,19 @@
         <v>41</v>
       </c>
       <c r="H346" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="I346" t="s">
-        <v>718</v>
+        <v>708</v>
       </c>
       <c r="J346" t="s">
-        <v>293</v>
+        <v>685</v>
       </c>
       <c r="K346" t="s">
         <v>45</v>
       </c>
       <c r="L346" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="M346" t="s">
         <v>701</v>
@@ -21862,7 +21862,7 @@
         <v>48</v>
       </c>
       <c r="P346" t="s">
-        <v>718</v>
+        <v>708</v>
       </c>
       <c r="Q346" t="s">
         <v>47</v>
@@ -21894,19 +21894,19 @@
         <v>41</v>
       </c>
       <c r="H347" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="I347" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="J347" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K347" t="s">
         <v>45</v>
       </c>
       <c r="L347" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="M347" t="s">
         <v>701</v>
@@ -21918,7 +21918,7 @@
         <v>48</v>
       </c>
       <c r="P347" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="Q347" t="s">
         <v>47</v>
@@ -21941,7 +21941,7 @@
         <v>34</v>
       </c>
       <c r="E348" t="s">
-        <v>175</v>
+        <v>672</v>
       </c>
       <c r="F348" t="s">
         <v>40</v>
@@ -21950,19 +21950,19 @@
         <v>41</v>
       </c>
       <c r="H348" t="s">
-        <v>722</v>
+        <v>457</v>
       </c>
       <c r="I348" t="s">
-        <v>155</v>
+        <v>694</v>
       </c>
       <c r="J348" t="s">
-        <v>122</v>
+        <v>335</v>
       </c>
       <c r="K348" t="s">
-        <v>122</v>
+        <v>45</v>
       </c>
       <c r="L348" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="M348" t="s">
         <v>701</v>
@@ -21974,7 +21974,7 @@
         <v>48</v>
       </c>
       <c r="P348" t="s">
-        <v>155</v>
+        <v>694</v>
       </c>
       <c r="Q348" t="s">
         <v>47</v>
@@ -21997,28 +21997,28 @@
         <v>34</v>
       </c>
       <c r="E349" t="s">
-        <v>175</v>
+        <v>722</v>
       </c>
       <c r="F349" t="s">
-        <v>40</v>
+        <v>211</v>
       </c>
       <c r="G349" t="s">
         <v>41</v>
       </c>
       <c r="H349" t="s">
-        <v>447</v>
+        <v>556</v>
       </c>
       <c r="I349" t="s">
-        <v>155</v>
+        <v>694</v>
       </c>
       <c r="J349" t="s">
+        <v>474</v>
+      </c>
+      <c r="K349" t="s">
         <v>122</v>
       </c>
-      <c r="K349" t="s">
-        <v>45</v>
-      </c>
       <c r="L349" t="s">
-        <v>724</v>
+        <v>34</v>
       </c>
       <c r="M349" t="s">
         <v>701</v>
@@ -22030,7 +22030,7 @@
         <v>48</v>
       </c>
       <c r="P349" t="s">
-        <v>155</v>
+        <v>694</v>
       </c>
       <c r="Q349" t="s">
         <v>47</v>
@@ -22053,28 +22053,28 @@
         <v>34</v>
       </c>
       <c r="E350" t="s">
-        <v>725</v>
+        <v>175</v>
       </c>
       <c r="F350" t="s">
-        <v>211</v>
+        <v>40</v>
       </c>
       <c r="G350" t="s">
         <v>41</v>
       </c>
       <c r="H350" t="s">
-        <v>215</v>
+        <v>723</v>
       </c>
       <c r="I350" t="s">
-        <v>726</v>
+        <v>155</v>
       </c>
       <c r="J350" t="s">
-        <v>474</v>
+        <v>122</v>
       </c>
       <c r="K350" t="s">
-        <v>80</v>
+        <v>122</v>
       </c>
       <c r="L350" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="M350" t="s">
         <v>701</v>
@@ -22086,7 +22086,7 @@
         <v>48</v>
       </c>
       <c r="P350" t="s">
-        <v>726</v>
+        <v>155</v>
       </c>
       <c r="Q350" t="s">
         <v>47</v>
@@ -22118,19 +22118,19 @@
         <v>41</v>
       </c>
       <c r="H351" t="s">
-        <v>457</v>
+        <v>725</v>
       </c>
       <c r="I351" t="s">
         <v>694</v>
       </c>
       <c r="J351" t="s">
-        <v>293</v>
+        <v>685</v>
       </c>
       <c r="K351" t="s">
         <v>45</v>
       </c>
       <c r="L351" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="M351" t="s">
         <v>701</v>
@@ -22165,7 +22165,7 @@
         <v>34</v>
       </c>
       <c r="E352" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="F352" t="s">
         <v>211</v>
@@ -22177,7 +22177,7 @@
         <v>425</v>
       </c>
       <c r="I352" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="J352" t="s">
         <v>474</v>
@@ -22198,7 +22198,7 @@
         <v>48</v>
       </c>
       <c r="P352" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="Q352" t="s">
         <v>47</v>
@@ -22221,28 +22221,28 @@
         <v>34</v>
       </c>
       <c r="E353" t="s">
+        <v>672</v>
+      </c>
+      <c r="F353" t="s">
+        <v>40</v>
+      </c>
+      <c r="G353" t="s">
+        <v>41</v>
+      </c>
+      <c r="H353" t="s">
+        <v>729</v>
+      </c>
+      <c r="I353" t="s">
+        <v>730</v>
+      </c>
+      <c r="J353" t="s">
+        <v>685</v>
+      </c>
+      <c r="K353" t="s">
+        <v>45</v>
+      </c>
+      <c r="L353" t="s">
         <v>731</v>
-      </c>
-      <c r="F353" t="s">
-        <v>211</v>
-      </c>
-      <c r="G353" t="s">
-        <v>41</v>
-      </c>
-      <c r="H353" t="s">
-        <v>556</v>
-      </c>
-      <c r="I353" t="s">
-        <v>694</v>
-      </c>
-      <c r="J353" t="s">
-        <v>474</v>
-      </c>
-      <c r="K353" t="s">
-        <v>122</v>
-      </c>
-      <c r="L353" t="s">
-        <v>34</v>
       </c>
       <c r="M353" t="s">
         <v>701</v>
@@ -22254,7 +22254,7 @@
         <v>48</v>
       </c>
       <c r="P353" t="s">
-        <v>694</v>
+        <v>730</v>
       </c>
       <c r="Q353" t="s">
         <v>47</v>
@@ -22672,7 +22672,7 @@
         <v>187</v>
       </c>
       <c r="F361" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="G361" t="s">
         <v>41</v>
@@ -22846,16 +22846,16 @@
         <v>41</v>
       </c>
       <c r="H364" t="s">
-        <v>425</v>
+        <v>469</v>
       </c>
       <c r="I364" t="s">
         <v>755</v>
       </c>
       <c r="J364" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="K364" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="L364" t="s">
         <v>34</v>
@@ -22902,16 +22902,16 @@
         <v>41</v>
       </c>
       <c r="H365" t="s">
-        <v>469</v>
+        <v>425</v>
       </c>
       <c r="I365" t="s">
         <v>756</v>
       </c>
       <c r="J365" t="s">
-        <v>101</v>
+        <v>178</v>
       </c>
       <c r="K365" t="s">
-        <v>101</v>
+        <v>178</v>
       </c>
       <c r="L365" t="s">
         <v>34</v>
@@ -23076,7 +23076,7 @@
         <v>765</v>
       </c>
       <c r="J368" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K368" t="s">
         <v>229</v>
@@ -23356,7 +23356,7 @@
         <v>783</v>
       </c>
       <c r="J373" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K373" t="s">
         <v>45</v>
@@ -23524,7 +23524,7 @@
         <v>795</v>
       </c>
       <c r="J376" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K376" t="s">
         <v>796</v>
@@ -23692,10 +23692,10 @@
         <v>805</v>
       </c>
       <c r="J379" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K379" t="s">
-        <v>122</v>
+        <v>75</v>
       </c>
       <c r="L379" t="s">
         <v>806</v>
@@ -23742,19 +23742,19 @@
         <v>41</v>
       </c>
       <c r="H380" t="s">
+        <v>425</v>
+      </c>
+      <c r="I380" t="s">
         <v>808</v>
       </c>
-      <c r="I380" t="s">
+      <c r="J380" t="s">
+        <v>58</v>
+      </c>
+      <c r="K380" t="s">
+        <v>202</v>
+      </c>
+      <c r="L380" t="s">
         <v>809</v>
-      </c>
-      <c r="J380" t="s">
-        <v>320</v>
-      </c>
-      <c r="K380" t="s">
-        <v>96</v>
-      </c>
-      <c r="L380" t="s">
-        <v>810</v>
       </c>
       <c r="M380" t="s">
         <v>800</v>
@@ -23766,7 +23766,7 @@
         <v>48</v>
       </c>
       <c r="P380" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="Q380" t="s">
         <v>47</v>
@@ -23789,7 +23789,7 @@
         <v>34</v>
       </c>
       <c r="E381" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="F381" t="s">
         <v>211</v>
@@ -23798,19 +23798,19 @@
         <v>41</v>
       </c>
       <c r="H381" t="s">
+        <v>811</v>
+      </c>
+      <c r="I381" t="s">
         <v>812</v>
       </c>
-      <c r="I381" t="s">
-        <v>813</v>
-      </c>
       <c r="J381" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K381" t="s">
         <v>96</v>
       </c>
       <c r="L381" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="M381" t="s">
         <v>800</v>
@@ -23822,7 +23822,7 @@
         <v>48</v>
       </c>
       <c r="P381" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="Q381" t="s">
         <v>47</v>
@@ -23845,7 +23845,7 @@
         <v>34</v>
       </c>
       <c r="E382" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="F382" t="s">
         <v>211</v>
@@ -23854,19 +23854,19 @@
         <v>41</v>
       </c>
       <c r="H382" t="s">
+        <v>815</v>
+      </c>
+      <c r="I382" t="s">
         <v>816</v>
       </c>
-      <c r="I382" t="s">
-        <v>817</v>
-      </c>
       <c r="J382" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K382" t="s">
         <v>96</v>
       </c>
       <c r="L382" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="M382" t="s">
         <v>800</v>
@@ -23878,7 +23878,7 @@
         <v>48</v>
       </c>
       <c r="P382" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="Q382" t="s">
         <v>47</v>
@@ -23901,7 +23901,7 @@
         <v>34</v>
       </c>
       <c r="E383" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="F383" t="s">
         <v>211</v>
@@ -23910,7 +23910,7 @@
         <v>41</v>
       </c>
       <c r="H383" t="s">
-        <v>425</v>
+        <v>819</v>
       </c>
       <c r="I383" t="s">
         <v>820</v>
@@ -23972,10 +23972,10 @@
         <v>824</v>
       </c>
       <c r="J384" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K384" t="s">
-        <v>75</v>
+        <v>122</v>
       </c>
       <c r="L384" t="s">
         <v>825</v>
@@ -24028,10 +24028,10 @@
         <v>828</v>
       </c>
       <c r="J385" t="s">
-        <v>58</v>
+        <v>304</v>
       </c>
       <c r="K385" t="s">
-        <v>202</v>
+        <v>96</v>
       </c>
       <c r="L385" t="s">
         <v>829</v>
@@ -24140,7 +24140,7 @@
         <v>835</v>
       </c>
       <c r="J387" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K387" t="s">
         <v>45</v>
@@ -24349,28 +24349,28 @@
         <v>33</v>
       </c>
       <c r="E391" t="s">
+        <v>672</v>
+      </c>
+      <c r="F391" t="s">
+        <v>40</v>
+      </c>
+      <c r="G391" t="s">
+        <v>41</v>
+      </c>
+      <c r="H391" t="s">
         <v>851</v>
       </c>
-      <c r="F391" t="s">
-        <v>211</v>
-      </c>
-      <c r="G391" t="s">
-        <v>41</v>
-      </c>
-      <c r="H391" t="s">
+      <c r="I391" t="s">
         <v>852</v>
       </c>
-      <c r="I391" t="s">
+      <c r="J391" t="s">
+        <v>335</v>
+      </c>
+      <c r="K391" t="s">
+        <v>45</v>
+      </c>
+      <c r="L391" t="s">
         <v>853</v>
-      </c>
-      <c r="J391" t="s">
-        <v>320</v>
-      </c>
-      <c r="K391" t="s">
-        <v>122</v>
-      </c>
-      <c r="L391" t="s">
-        <v>34</v>
       </c>
       <c r="M391" t="s">
         <v>850</v>
@@ -24382,7 +24382,7 @@
         <v>48</v>
       </c>
       <c r="P391" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="Q391" t="s">
         <v>47</v>
@@ -24405,28 +24405,28 @@
         <v>34</v>
       </c>
       <c r="E392" t="s">
-        <v>672</v>
+        <v>854</v>
       </c>
       <c r="F392" t="s">
-        <v>40</v>
+        <v>211</v>
       </c>
       <c r="G392" t="s">
         <v>41</v>
       </c>
       <c r="H392" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="I392" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="J392" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="K392" t="s">
-        <v>45</v>
+        <v>122</v>
       </c>
       <c r="L392" t="s">
-        <v>856</v>
+        <v>34</v>
       </c>
       <c r="M392" t="s">
         <v>850</v>
@@ -24438,7 +24438,7 @@
         <v>48</v>
       </c>
       <c r="P392" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="Q392" t="s">
         <v>47</v>
@@ -24476,7 +24476,7 @@
         <v>858</v>
       </c>
       <c r="J393" t="s">
-        <v>293</v>
+        <v>335</v>
       </c>
       <c r="K393" t="s">
         <v>859</v>
@@ -24517,7 +24517,7 @@
         <v>34</v>
       </c>
       <c r="E394" t="s">
-        <v>861</v>
+        <v>672</v>
       </c>
       <c r="F394" t="s">
         <v>40</v>
@@ -24529,16 +24529,16 @@
         <v>846</v>
       </c>
       <c r="I394" t="s">
+        <v>861</v>
+      </c>
+      <c r="J394" t="s">
+        <v>335</v>
+      </c>
+      <c r="K394" t="s">
+        <v>859</v>
+      </c>
+      <c r="L394" t="s">
         <v>862</v>
-      </c>
-      <c r="J394" t="s">
-        <v>101</v>
-      </c>
-      <c r="K394" t="s">
-        <v>45</v>
-      </c>
-      <c r="L394" t="s">
-        <v>863</v>
       </c>
       <c r="M394" t="s">
         <v>850</v>
@@ -24550,7 +24550,7 @@
         <v>48</v>
       </c>
       <c r="P394" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="Q394" t="s">
         <v>47</v>
@@ -24573,7 +24573,7 @@
         <v>34</v>
       </c>
       <c r="E395" t="s">
-        <v>672</v>
+        <v>863</v>
       </c>
       <c r="F395" t="s">
         <v>40</v>
@@ -24588,10 +24588,10 @@
         <v>864</v>
       </c>
       <c r="J395" t="s">
-        <v>293</v>
+        <v>101</v>
       </c>
       <c r="K395" t="s">
-        <v>859</v>
+        <v>45</v>
       </c>
       <c r="L395" t="s">
         <v>865</v>
@@ -24812,7 +24812,7 @@
         <v>878</v>
       </c>
       <c r="J399" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K399" t="s">
         <v>45</v>
@@ -24865,7 +24865,7 @@
         <v>877</v>
       </c>
       <c r="I400" t="s">
-        <v>820</v>
+        <v>808</v>
       </c>
       <c r="J400" t="s">
         <v>58</v>
@@ -24886,7 +24886,7 @@
         <v>48</v>
       </c>
       <c r="P400" t="s">
-        <v>820</v>
+        <v>808</v>
       </c>
       <c r="Q400" t="s">
         <v>47</v>
@@ -25077,7 +25077,7 @@
         <v>33</v>
       </c>
       <c r="E404" t="s">
-        <v>672</v>
+        <v>763</v>
       </c>
       <c r="F404" t="s">
         <v>40</v>
@@ -25092,10 +25092,10 @@
         <v>898</v>
       </c>
       <c r="J404" t="s">
-        <v>681</v>
+        <v>178</v>
       </c>
       <c r="K404" t="s">
-        <v>45</v>
+        <v>178</v>
       </c>
       <c r="L404" t="s">
         <v>899</v>
@@ -25133,7 +25133,7 @@
         <v>34</v>
       </c>
       <c r="E405" t="s">
-        <v>763</v>
+        <v>672</v>
       </c>
       <c r="F405" t="s">
         <v>40</v>
@@ -25148,10 +25148,10 @@
         <v>901</v>
       </c>
       <c r="J405" t="s">
-        <v>178</v>
+        <v>685</v>
       </c>
       <c r="K405" t="s">
-        <v>178</v>
+        <v>45</v>
       </c>
       <c r="L405" t="s">
         <v>902</v>
@@ -25596,7 +25596,7 @@
         <v>923</v>
       </c>
       <c r="J413" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K413" t="s">
         <v>96</v>
@@ -25805,7 +25805,7 @@
         <v>33</v>
       </c>
       <c r="E417" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="F417" t="s">
         <v>218</v>
@@ -25820,10 +25820,10 @@
         <v>930</v>
       </c>
       <c r="J417" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="K417" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="L417" t="s">
         <v>931</v>
@@ -25835,7 +25835,7 @@
         <v>47</v>
       </c>
       <c r="O417" t="s">
-        <v>247</v>
+        <v>130</v>
       </c>
       <c r="P417" t="s">
         <v>930</v>
@@ -25870,10 +25870,10 @@
         <v>41</v>
       </c>
       <c r="H418" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="I418" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="J418" t="s">
         <v>80</v>
@@ -25894,7 +25894,7 @@
         <v>255</v>
       </c>
       <c r="P418" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="Q418" t="s">
         <v>47</v>
@@ -25917,7 +25917,7 @@
         <v>34</v>
       </c>
       <c r="E419" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="F419" t="s">
         <v>218</v>
@@ -25926,16 +25926,16 @@
         <v>41</v>
       </c>
       <c r="H419" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="I419" t="s">
         <v>934</v>
       </c>
       <c r="J419" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="K419" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="L419" t="s">
         <v>931</v>
@@ -25947,7 +25947,7 @@
         <v>47</v>
       </c>
       <c r="O419" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="P419" t="s">
         <v>934</v>
@@ -25973,7 +25973,7 @@
         <v>34</v>
       </c>
       <c r="E420" t="s">
-        <v>227</v>
+        <v>275</v>
       </c>
       <c r="F420" t="s">
         <v>218</v>
@@ -25982,16 +25982,16 @@
         <v>41</v>
       </c>
       <c r="H420" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="I420" t="s">
         <v>935</v>
       </c>
       <c r="J420" t="s">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="K420" t="s">
-        <v>229</v>
+        <v>58</v>
       </c>
       <c r="L420" t="s">
         <v>931</v>
@@ -26003,7 +26003,7 @@
         <v>47</v>
       </c>
       <c r="O420" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="P420" t="s">
         <v>935</v>
@@ -26029,7 +26029,7 @@
         <v>34</v>
       </c>
       <c r="E421" t="s">
-        <v>275</v>
+        <v>232</v>
       </c>
       <c r="F421" t="s">
         <v>218</v>
@@ -26038,16 +26038,16 @@
         <v>41</v>
       </c>
       <c r="H421" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="I421" t="s">
         <v>936</v>
       </c>
       <c r="J421" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="K421" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="L421" t="s">
         <v>931</v>
@@ -26059,7 +26059,7 @@
         <v>47</v>
       </c>
       <c r="O421" t="s">
-        <v>105</v>
+        <v>310</v>
       </c>
       <c r="P421" t="s">
         <v>936</v>
@@ -26085,7 +26085,7 @@
         <v>34</v>
       </c>
       <c r="E422" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="F422" t="s">
         <v>218</v>
@@ -26094,16 +26094,16 @@
         <v>41</v>
       </c>
       <c r="H422" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="I422" t="s">
         <v>937</v>
       </c>
       <c r="J422" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="K422" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="L422" t="s">
         <v>931</v>
@@ -26115,7 +26115,7 @@
         <v>47</v>
       </c>
       <c r="O422" t="s">
-        <v>102</v>
+        <v>250</v>
       </c>
       <c r="P422" t="s">
         <v>937</v>
@@ -26141,7 +26141,7 @@
         <v>34</v>
       </c>
       <c r="E423" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="F423" t="s">
         <v>218</v>
@@ -26150,16 +26150,16 @@
         <v>41</v>
       </c>
       <c r="H423" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="I423" t="s">
         <v>938</v>
       </c>
       <c r="J423" t="s">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="K423" t="s">
-        <v>119</v>
+        <v>229</v>
       </c>
       <c r="L423" t="s">
         <v>931</v>
@@ -26171,7 +26171,7 @@
         <v>47</v>
       </c>
       <c r="O423" t="s">
-        <v>436</v>
+        <v>91</v>
       </c>
       <c r="P423" t="s">
         <v>938</v>
@@ -26197,7 +26197,7 @@
         <v>34</v>
       </c>
       <c r="E424" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="F424" t="s">
         <v>218</v>
@@ -26206,16 +26206,16 @@
         <v>41</v>
       </c>
       <c r="H424" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="I424" t="s">
         <v>939</v>
       </c>
       <c r="J424" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="K424" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="L424" t="s">
         <v>931</v>
@@ -26227,7 +26227,7 @@
         <v>47</v>
       </c>
       <c r="O424" t="s">
-        <v>466</v>
+        <v>102</v>
       </c>
       <c r="P424" t="s">
         <v>939</v>
@@ -26253,7 +26253,7 @@
         <v>34</v>
       </c>
       <c r="E425" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="F425" t="s">
         <v>218</v>
@@ -26262,16 +26262,16 @@
         <v>41</v>
       </c>
       <c r="H425" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="I425" t="s">
         <v>940</v>
       </c>
       <c r="J425" t="s">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="K425" t="s">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="L425" t="s">
         <v>931</v>
@@ -26283,7 +26283,7 @@
         <v>47</v>
       </c>
       <c r="O425" t="s">
-        <v>114</v>
+        <v>247</v>
       </c>
       <c r="P425" t="s">
         <v>940</v>
@@ -26309,7 +26309,7 @@
         <v>34</v>
       </c>
       <c r="E426" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="F426" t="s">
         <v>218</v>
@@ -26318,16 +26318,16 @@
         <v>41</v>
       </c>
       <c r="H426" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="I426" t="s">
         <v>941</v>
       </c>
       <c r="J426" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="K426" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="L426" t="s">
         <v>931</v>
@@ -26339,7 +26339,7 @@
         <v>47</v>
       </c>
       <c r="O426" t="s">
-        <v>308</v>
+        <v>156</v>
       </c>
       <c r="P426" t="s">
         <v>941</v>
@@ -26365,7 +26365,7 @@
         <v>34</v>
       </c>
       <c r="E427" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="F427" t="s">
         <v>218</v>
@@ -26374,13 +26374,13 @@
         <v>41</v>
       </c>
       <c r="H427" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="I427" t="s">
         <v>942</v>
       </c>
       <c r="J427" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="K427" t="s">
         <v>119</v>
@@ -26395,7 +26395,7 @@
         <v>47</v>
       </c>
       <c r="O427" t="s">
-        <v>156</v>
+        <v>436</v>
       </c>
       <c r="P427" t="s">
         <v>942</v>
@@ -26421,7 +26421,7 @@
         <v>34</v>
       </c>
       <c r="E428" t="s">
-        <v>248</v>
+        <v>217</v>
       </c>
       <c r="F428" t="s">
         <v>218</v>
@@ -26430,13 +26430,13 @@
         <v>41</v>
       </c>
       <c r="H428" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="I428" t="s">
         <v>943</v>
       </c>
       <c r="J428" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="K428" t="s">
         <v>119</v>
@@ -26451,7 +26451,7 @@
         <v>47</v>
       </c>
       <c r="O428" t="s">
-        <v>250</v>
+        <v>466</v>
       </c>
       <c r="P428" t="s">
         <v>943</v>

--- a/xlsx/dre/DRE_02_2026.xlsx
+++ b/xlsx/dre/DRE_02_2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8950" uniqueCount="1053">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8950" uniqueCount="1054">
   <si>
     <t>Movimentações Financeiras</t>
   </si>
@@ -1583,6 +1583,9 @@
     <t>63801/2</t>
   </si>
   <si>
+    <t>Jose Carlos de Carvalho</t>
+  </si>
+  <si>
     <t>R$  537,59</t>
   </si>
   <si>
@@ -2028,15 +2031,15 @@
     <t>4.03.03.02.05.02 Assistência técnica medição</t>
   </si>
   <si>
+    <t>PFP</t>
+  </si>
+  <si>
     <t>L E A Medicoes Tecnicas LTDA</t>
   </si>
   <si>
     <t>R$  180,00</t>
   </si>
   <si>
-    <t>PFP</t>
-  </si>
-  <si>
     <t>4.03.03.09 Marketing - mídias / ações comerciais / outros (CV)</t>
   </si>
   <si>
@@ -2058,6 +2061,18 @@
     <t>Google 2026</t>
   </si>
   <si>
+    <t>498/1</t>
+  </si>
+  <si>
+    <t>Facebook</t>
+  </si>
+  <si>
+    <t>R$  3.750,00</t>
+  </si>
+  <si>
+    <t>30/01/26</t>
+  </si>
+  <si>
     <t>WEBGIGA SOLUCOES DIGITAIS LTDA</t>
   </si>
   <si>
@@ -2079,18 +2094,6 @@
     <t>MHM - Honorários 2026</t>
   </si>
   <si>
-    <t>498/1</t>
-  </si>
-  <si>
-    <t>Facebook</t>
-  </si>
-  <si>
-    <t>R$  3.750,00</t>
-  </si>
-  <si>
-    <t>30/01/26</t>
-  </si>
-  <si>
     <t>4.04 DESPESAS ADMINISTRATIVAS</t>
   </si>
   <si>
@@ -2316,12 +2319,12 @@
     <t>VT fev 26/1</t>
   </si>
   <si>
+    <t>R$  433,98</t>
+  </si>
+  <si>
     <t>R$  313,70</t>
   </si>
   <si>
-    <t>R$  433,98</t>
-  </si>
-  <si>
     <t>4.04.02 GASTOS GERAIS ADMINISTRATIVOS</t>
   </si>
   <si>
@@ -2460,17 +2463,25 @@
     <t>R$  45,00</t>
   </si>
   <si>
-    <t>531/1</t>
-  </si>
-  <si>
-    <t>Shopee</t>
-  </si>
-  <si>
-    <t>R$  65,93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freeco refil
-</t>
+    <t>532/1</t>
+  </si>
+  <si>
+    <t>DIA BRASIL SUPERMERCADO</t>
+  </si>
+  <si>
+    <t>R$  59,96</t>
+  </si>
+  <si>
+    <t>cafés</t>
+  </si>
+  <si>
+    <t>502/1</t>
+  </si>
+  <si>
+    <t>R$  100,00</t>
+  </si>
+  <si>
+    <t>Cópia de chaves</t>
   </si>
   <si>
     <t>533/1</t>
@@ -2483,19 +2494,6 @@
   </si>
   <si>
     <t>material limpeza</t>
-  </si>
-  <si>
-    <t>530/1</t>
-  </si>
-  <si>
-    <t>Marinete</t>
-  </si>
-  <si>
-    <t>R$  17,00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Copo descartável para crianças
-</t>
   </si>
   <si>
     <t>529/1</t>
@@ -2512,27 +2510,6 @@
 </t>
   </si>
   <si>
-    <t>502/1</t>
-  </si>
-  <si>
-    <t>R$  100,00</t>
-  </si>
-  <si>
-    <t>Cópia de chaves</t>
-  </si>
-  <si>
-    <t>532/1</t>
-  </si>
-  <si>
-    <t>DIA BRASIL SUPERMERCADO</t>
-  </si>
-  <si>
-    <t>R$  59,96</t>
-  </si>
-  <si>
-    <t>cafés</t>
-  </si>
-  <si>
     <t>505/1</t>
   </si>
   <si>
@@ -2545,6 +2522,32 @@
     <t>Conserto vidro adega</t>
   </si>
   <si>
+    <t>531/1</t>
+  </si>
+  <si>
+    <t>Shopee</t>
+  </si>
+  <si>
+    <t>R$  65,93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freeco refil
+</t>
+  </si>
+  <si>
+    <t>530/1</t>
+  </si>
+  <si>
+    <t>Marinete</t>
+  </si>
+  <si>
+    <t>R$  17,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copo descartável para crianças
+</t>
+  </si>
+  <si>
     <t>4.04.02.07 Informática</t>
   </si>
   <si>
@@ -2608,6 +2611,15 @@
     <t>4.04.02.08.03 Mensalidades e assinaturas - outros gastos</t>
   </si>
   <si>
+    <t>D4 sign</t>
+  </si>
+  <si>
+    <t>R$  49,95</t>
+  </si>
+  <si>
+    <t>D4 sign 2026</t>
+  </si>
+  <si>
     <t>534/1</t>
   </si>
   <si>
@@ -2617,15 +2629,6 @@
     <t>R$  197,63</t>
   </si>
   <si>
-    <t>D4 sign</t>
-  </si>
-  <si>
-    <t>R$  49,95</t>
-  </si>
-  <si>
-    <t>D4 sign 2026</t>
-  </si>
-  <si>
     <t>10/2</t>
   </si>
   <si>
@@ -2638,6 +2641,12 @@
     <t>Promob 2026-1</t>
   </si>
   <si>
+    <t>R$  599,00</t>
+  </si>
+  <si>
+    <t>Promob 2026</t>
+  </si>
+  <si>
     <t>3/1</t>
   </si>
   <si>
@@ -2645,12 +2654,6 @@
   </si>
   <si>
     <t>Promob 2026/2</t>
-  </si>
-  <si>
-    <t>R$  599,00</t>
-  </si>
-  <si>
-    <t>Promob 2026</t>
   </si>
   <si>
     <t>4.04.02.11 Manutenção de predio e equipamentos</t>
@@ -2747,6 +2750,15 @@
     <t>R$ 400,33</t>
   </si>
   <si>
+    <t>VERISURE</t>
+  </si>
+  <si>
+    <t>R$  250,33</t>
+  </si>
+  <si>
+    <t>Verisure - Alarme 2026</t>
+  </si>
+  <si>
     <t>Jackson Fernando de Araujo</t>
   </si>
   <si>
@@ -2754,15 +2766,6 @@
   </si>
   <si>
     <t>Segurança 2026</t>
-  </si>
-  <si>
-    <t>VERISURE</t>
-  </si>
-  <si>
-    <t>R$  250,33</t>
-  </si>
-  <si>
-    <t>Verisure - Alarme 2026</t>
   </si>
   <si>
     <t>4.04.02.14.08 Site e newsletter da loja</t>
@@ -16315,10 +16318,10 @@
         <v>41</v>
       </c>
       <c r="H247" t="s">
-        <v>215</v>
+        <v>519</v>
       </c>
       <c r="I247" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="J247" t="s">
         <v>90</v>
@@ -16374,7 +16377,7 @@
         <v>457</v>
       </c>
       <c r="I248" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="J248" t="s">
         <v>304</v>
@@ -16395,7 +16398,7 @@
         <v>102</v>
       </c>
       <c r="P248" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="Q248" t="s">
         <v>47</v>
@@ -16430,7 +16433,7 @@
         <v>215</v>
       </c>
       <c r="I249" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="J249" t="s">
         <v>126</v>
@@ -16486,7 +16489,7 @@
         <v>215</v>
       </c>
       <c r="I250" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="J250" t="s">
         <v>126</v>
@@ -16518,13 +16521,13 @@
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B251" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C251" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D251" t="s">
         <v>33</v>
@@ -16542,7 +16545,7 @@
         <v>267</v>
       </c>
       <c r="I251" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="J251" t="s">
         <v>101</v>
@@ -16554,7 +16557,7 @@
         <v>34</v>
       </c>
       <c r="M251" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N251" t="s">
         <v>47</v>
@@ -16563,7 +16566,7 @@
         <v>102</v>
       </c>
       <c r="P251" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="Q251" t="s">
         <v>47</v>
@@ -16574,13 +16577,13 @@
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B252" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C252" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D252" t="s">
         <v>33</v>
@@ -16598,7 +16601,7 @@
         <v>215</v>
       </c>
       <c r="I252" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="J252" t="s">
         <v>126</v>
@@ -16610,7 +16613,7 @@
         <v>34</v>
       </c>
       <c r="M252" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N252" t="s">
         <v>47</v>
@@ -16630,7 +16633,7 @@
     </row>
     <row r="253">
       <c r="A253" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B253" t="s">
         <v>34</v>
@@ -16654,7 +16657,7 @@
         <v>215</v>
       </c>
       <c r="I253" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="J253" t="s">
         <v>126</v>
@@ -16666,7 +16669,7 @@
         <v>34</v>
       </c>
       <c r="M253" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N253" t="s">
         <v>47</v>
@@ -16686,7 +16689,7 @@
     </row>
     <row r="254">
       <c r="A254" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B254" t="s">
         <v>34</v>
@@ -16710,7 +16713,7 @@
         <v>215</v>
       </c>
       <c r="I254" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="J254" t="s">
         <v>80</v>
@@ -16722,7 +16725,7 @@
         <v>34</v>
       </c>
       <c r="M254" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N254" t="s">
         <v>47</v>
@@ -16742,7 +16745,7 @@
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B255" t="s">
         <v>34</v>
@@ -16766,7 +16769,7 @@
         <v>215</v>
       </c>
       <c r="I255" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="J255" t="s">
         <v>90</v>
@@ -16778,7 +16781,7 @@
         <v>34</v>
       </c>
       <c r="M255" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N255" t="s">
         <v>47</v>
@@ -16798,7 +16801,7 @@
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B256" t="s">
         <v>34</v>
@@ -16822,7 +16825,7 @@
         <v>215</v>
       </c>
       <c r="I256" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="J256" t="s">
         <v>90</v>
@@ -16834,7 +16837,7 @@
         <v>34</v>
       </c>
       <c r="M256" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N256" t="s">
         <v>47</v>
@@ -16854,7 +16857,7 @@
     </row>
     <row r="257">
       <c r="A257" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B257" t="s">
         <v>34</v>
@@ -16878,7 +16881,7 @@
         <v>215</v>
       </c>
       <c r="I257" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="J257" t="s">
         <v>119</v>
@@ -16890,7 +16893,7 @@
         <v>34</v>
       </c>
       <c r="M257" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N257" t="s">
         <v>47</v>
@@ -16910,7 +16913,7 @@
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B258" t="s">
         <v>34</v>
@@ -16931,10 +16934,10 @@
         <v>41</v>
       </c>
       <c r="H258" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="I258" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="J258" t="s">
         <v>119</v>
@@ -16946,7 +16949,7 @@
         <v>34</v>
       </c>
       <c r="M258" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N258" t="s">
         <v>47</v>
@@ -16955,7 +16958,7 @@
         <v>130</v>
       </c>
       <c r="P258" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="Q258" t="s">
         <v>47</v>
@@ -16966,7 +16969,7 @@
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B259" t="s">
         <v>34</v>
@@ -16978,7 +16981,7 @@
         <v>34</v>
       </c>
       <c r="E259" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F259" t="s">
         <v>211</v>
@@ -16987,13 +16990,13 @@
         <v>41</v>
       </c>
       <c r="H259" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="I259" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="J259" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="K259" t="s">
         <v>80</v>
@@ -17002,7 +17005,7 @@
         <v>34</v>
       </c>
       <c r="M259" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N259" t="s">
         <v>47</v>
@@ -17011,7 +17014,7 @@
         <v>255</v>
       </c>
       <c r="P259" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="Q259" t="s">
         <v>47</v>
@@ -17022,7 +17025,7 @@
     </row>
     <row r="260">
       <c r="A260" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B260" t="s">
         <v>34</v>
@@ -17034,7 +17037,7 @@
         <v>34</v>
       </c>
       <c r="E260" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F260" t="s">
         <v>211</v>
@@ -17043,10 +17046,10 @@
         <v>41</v>
       </c>
       <c r="H260" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="I260" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="J260" t="s">
         <v>514</v>
@@ -17058,7 +17061,7 @@
         <v>34</v>
       </c>
       <c r="M260" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N260" t="s">
         <v>47</v>
@@ -17067,7 +17070,7 @@
         <v>250</v>
       </c>
       <c r="P260" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="Q260" t="s">
         <v>47</v>
@@ -17078,7 +17081,7 @@
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B261" t="s">
         <v>34</v>
@@ -17099,13 +17102,13 @@
         <v>41</v>
       </c>
       <c r="H261" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="I261" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="J261" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="K261" t="s">
         <v>119</v>
@@ -17114,7 +17117,7 @@
         <v>34</v>
       </c>
       <c r="M261" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N261" t="s">
         <v>47</v>
@@ -17123,7 +17126,7 @@
         <v>250</v>
       </c>
       <c r="P261" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="Q261" t="s">
         <v>47</v>
@@ -17134,7 +17137,7 @@
     </row>
     <row r="262">
       <c r="A262" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B262" t="s">
         <v>34</v>
@@ -17158,7 +17161,7 @@
         <v>215</v>
       </c>
       <c r="I262" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="J262" t="s">
         <v>134</v>
@@ -17170,7 +17173,7 @@
         <v>34</v>
       </c>
       <c r="M262" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N262" t="s">
         <v>47</v>
@@ -17190,7 +17193,7 @@
     </row>
     <row r="263">
       <c r="A263" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B263" t="s">
         <v>34</v>
@@ -17211,13 +17214,13 @@
         <v>41</v>
       </c>
       <c r="H263" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="I263" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="J263" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="K263" t="s">
         <v>58</v>
@@ -17226,7 +17229,7 @@
         <v>34</v>
       </c>
       <c r="M263" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N263" t="s">
         <v>47</v>
@@ -17235,7 +17238,7 @@
         <v>105</v>
       </c>
       <c r="P263" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="Q263" t="s">
         <v>47</v>
@@ -17246,7 +17249,7 @@
     </row>
     <row r="264">
       <c r="A264" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B264" t="s">
         <v>34</v>
@@ -17267,10 +17270,10 @@
         <v>41</v>
       </c>
       <c r="H264" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="I264" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="J264" t="s">
         <v>113</v>
@@ -17282,7 +17285,7 @@
         <v>34</v>
       </c>
       <c r="M264" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N264" t="s">
         <v>47</v>
@@ -17291,7 +17294,7 @@
         <v>114</v>
       </c>
       <c r="P264" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="Q264" t="s">
         <v>47</v>
@@ -17302,7 +17305,7 @@
     </row>
     <row r="265">
       <c r="A265" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B265" t="s">
         <v>34</v>
@@ -17326,7 +17329,7 @@
         <v>267</v>
       </c>
       <c r="I265" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="J265" t="s">
         <v>70</v>
@@ -17335,10 +17338,10 @@
         <v>70</v>
       </c>
       <c r="L265" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M265" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N265" t="s">
         <v>47</v>
@@ -17347,7 +17350,7 @@
         <v>71</v>
       </c>
       <c r="P265" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="Q265" t="s">
         <v>47</v>
@@ -17358,7 +17361,7 @@
     </row>
     <row r="266">
       <c r="A266" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B266" t="s">
         <v>34</v>
@@ -17379,10 +17382,10 @@
         <v>41</v>
       </c>
       <c r="H266" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="I266" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="J266" t="s">
         <v>80</v>
@@ -17394,7 +17397,7 @@
         <v>34</v>
       </c>
       <c r="M266" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N266" t="s">
         <v>47</v>
@@ -17403,7 +17406,7 @@
         <v>247</v>
       </c>
       <c r="P266" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="Q266" t="s">
         <v>47</v>
@@ -17414,19 +17417,19 @@
     </row>
     <row r="267">
       <c r="A267" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B267" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C267" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D267" t="s">
         <v>33</v>
       </c>
       <c r="E267" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F267" t="s">
         <v>211</v>
@@ -17438,7 +17441,7 @@
         <v>510</v>
       </c>
       <c r="I267" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="J267" t="s">
         <v>122</v>
@@ -17450,7 +17453,7 @@
         <v>34</v>
       </c>
       <c r="M267" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N267" t="s">
         <v>47</v>
@@ -17459,7 +17462,7 @@
         <v>48</v>
       </c>
       <c r="P267" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="Q267" t="s">
         <v>47</v>
@@ -17470,7 +17473,7 @@
     </row>
     <row r="268">
       <c r="A268" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B268" t="s">
         <v>34</v>
@@ -17482,7 +17485,7 @@
         <v>34</v>
       </c>
       <c r="E268" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F268" t="s">
         <v>211</v>
@@ -17491,10 +17494,10 @@
         <v>41</v>
       </c>
       <c r="H268" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="I268" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="J268" t="s">
         <v>70</v>
@@ -17506,7 +17509,7 @@
         <v>34</v>
       </c>
       <c r="M268" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N268" t="s">
         <v>47</v>
@@ -17515,7 +17518,7 @@
         <v>48</v>
       </c>
       <c r="P268" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="Q268" t="s">
         <v>47</v>
@@ -17526,7 +17529,7 @@
     </row>
     <row r="269">
       <c r="A269" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B269" t="s">
         <v>34</v>
@@ -17538,7 +17541,7 @@
         <v>34</v>
       </c>
       <c r="E269" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="F269" t="s">
         <v>211</v>
@@ -17550,7 +17553,7 @@
         <v>469</v>
       </c>
       <c r="I269" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="J269" t="s">
         <v>101</v>
@@ -17562,7 +17565,7 @@
         <v>34</v>
       </c>
       <c r="M269" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N269" t="s">
         <v>47</v>
@@ -17571,7 +17574,7 @@
         <v>48</v>
       </c>
       <c r="P269" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="Q269" t="s">
         <v>47</v>
@@ -17582,7 +17585,7 @@
     </row>
     <row r="270">
       <c r="A270" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B270" t="s">
         <v>34</v>
@@ -17594,7 +17597,7 @@
         <v>34</v>
       </c>
       <c r="E270" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F270" t="s">
         <v>211</v>
@@ -17606,7 +17609,7 @@
         <v>425</v>
       </c>
       <c r="I270" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="J270" t="s">
         <v>178</v>
@@ -17618,7 +17621,7 @@
         <v>34</v>
       </c>
       <c r="M270" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N270" t="s">
         <v>47</v>
@@ -17627,7 +17630,7 @@
         <v>48</v>
       </c>
       <c r="P270" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="Q270" t="s">
         <v>47</v>
@@ -17638,13 +17641,13 @@
     </row>
     <row r="271">
       <c r="A271" t="s" s="1">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B271" t="s" s="1">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C271" t="s" s="1">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D271" t="s" s="1">
         <v>33</v>
@@ -17694,13 +17697,13 @@
     </row>
     <row r="272">
       <c r="A272" t="s" s="1">
+        <v>564</v>
+      </c>
+      <c r="B272" t="s" s="1">
         <v>563</v>
       </c>
-      <c r="B272" t="s" s="1">
-        <v>562</v>
-      </c>
       <c r="C272" t="s" s="1">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D272" t="s" s="1">
         <v>33</v>
@@ -17750,13 +17753,13 @@
     </row>
     <row r="273">
       <c r="A273" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B273" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C273" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D273" t="s">
         <v>33</v>
@@ -17771,10 +17774,10 @@
         <v>41</v>
       </c>
       <c r="H273" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="I273" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="J273" t="s">
         <v>96</v>
@@ -17783,10 +17786,10 @@
         <v>229</v>
       </c>
       <c r="L273" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M273" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N273" t="s">
         <v>47</v>
@@ -17795,7 +17798,7 @@
         <v>91</v>
       </c>
       <c r="P273" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="Q273" t="s">
         <v>47</v>
@@ -17806,13 +17809,13 @@
     </row>
     <row r="274">
       <c r="A274" t="s" s="1">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B274" t="s" s="1">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C274" t="s" s="1">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D274" t="s" s="1">
         <v>33</v>
@@ -17862,13 +17865,13 @@
     </row>
     <row r="275">
       <c r="A275" t="s" s="1">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B275" t="s" s="1">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C275" t="s" s="1">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D275" t="s" s="1">
         <v>33</v>
@@ -17918,19 +17921,19 @@
     </row>
     <row r="276">
       <c r="A276" t="s">
+        <v>572</v>
+      </c>
+      <c r="B276" t="s">
         <v>571</v>
       </c>
-      <c r="B276" t="s">
-        <v>570</v>
-      </c>
       <c r="C276" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D276" t="s">
         <v>33</v>
       </c>
       <c r="E276" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="F276" t="s">
         <v>211</v>
@@ -17939,10 +17942,10 @@
         <v>41</v>
       </c>
       <c r="H276" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I276" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="J276" t="s">
         <v>304</v>
@@ -17954,16 +17957,16 @@
         <v>34</v>
       </c>
       <c r="M276" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N276" t="s">
         <v>47</v>
       </c>
       <c r="O276" t="s">
+        <v>576</v>
+      </c>
+      <c r="P276" t="s">
         <v>575</v>
-      </c>
-      <c r="P276" t="s">
-        <v>574</v>
       </c>
       <c r="Q276" t="s">
         <v>47</v>
@@ -17974,7 +17977,7 @@
     </row>
     <row r="277">
       <c r="A277" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B277" t="s">
         <v>34</v>
@@ -17986,7 +17989,7 @@
         <v>34</v>
       </c>
       <c r="E277" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="F277" t="s">
         <v>211</v>
@@ -17995,13 +17998,13 @@
         <v>41</v>
       </c>
       <c r="H277" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I277" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="J277" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="K277" t="s">
         <v>80</v>
@@ -18010,7 +18013,7 @@
         <v>34</v>
       </c>
       <c r="M277" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N277" t="s">
         <v>47</v>
@@ -18019,7 +18022,7 @@
         <v>247</v>
       </c>
       <c r="P277" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="Q277" t="s">
         <v>47</v>
@@ -18030,7 +18033,7 @@
     </row>
     <row r="278">
       <c r="A278" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B278" t="s">
         <v>34</v>
@@ -18042,7 +18045,7 @@
         <v>34</v>
       </c>
       <c r="E278" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F278" t="s">
         <v>211</v>
@@ -18051,10 +18054,10 @@
         <v>41</v>
       </c>
       <c r="H278" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I278" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="J278" t="s">
         <v>304</v>
@@ -18066,16 +18069,16 @@
         <v>34</v>
       </c>
       <c r="M278" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N278" t="s">
         <v>47</v>
       </c>
       <c r="O278" t="s">
+        <v>582</v>
+      </c>
+      <c r="P278" t="s">
         <v>581</v>
-      </c>
-      <c r="P278" t="s">
-        <v>580</v>
       </c>
       <c r="Q278" t="s">
         <v>47</v>
@@ -18086,7 +18089,7 @@
     </row>
     <row r="279">
       <c r="A279" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B279" t="s">
         <v>34</v>
@@ -18098,7 +18101,7 @@
         <v>34</v>
       </c>
       <c r="E279" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F279" t="s">
         <v>211</v>
@@ -18107,10 +18110,10 @@
         <v>41</v>
       </c>
       <c r="H279" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I279" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="J279" t="s">
         <v>304</v>
@@ -18122,16 +18125,16 @@
         <v>34</v>
       </c>
       <c r="M279" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N279" t="s">
         <v>47</v>
       </c>
       <c r="O279" t="s">
+        <v>585</v>
+      </c>
+      <c r="P279" t="s">
         <v>584</v>
-      </c>
-      <c r="P279" t="s">
-        <v>583</v>
       </c>
       <c r="Q279" t="s">
         <v>47</v>
@@ -18142,7 +18145,7 @@
     </row>
     <row r="280">
       <c r="A280" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B280" t="s">
         <v>34</v>
@@ -18154,7 +18157,7 @@
         <v>34</v>
       </c>
       <c r="E280" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="F280" t="s">
         <v>211</v>
@@ -18163,10 +18166,10 @@
         <v>41</v>
       </c>
       <c r="H280" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I280" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="J280" t="s">
         <v>304</v>
@@ -18178,16 +18181,16 @@
         <v>34</v>
       </c>
       <c r="M280" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N280" t="s">
         <v>47</v>
       </c>
       <c r="O280" t="s">
+        <v>588</v>
+      </c>
+      <c r="P280" t="s">
         <v>587</v>
-      </c>
-      <c r="P280" t="s">
-        <v>586</v>
       </c>
       <c r="Q280" t="s">
         <v>47</v>
@@ -18198,7 +18201,7 @@
     </row>
     <row r="281">
       <c r="A281" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B281" t="s">
         <v>34</v>
@@ -18210,7 +18213,7 @@
         <v>34</v>
       </c>
       <c r="E281" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F281" t="s">
         <v>211</v>
@@ -18219,10 +18222,10 @@
         <v>41</v>
       </c>
       <c r="H281" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I281" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="J281" t="s">
         <v>70</v>
@@ -18234,16 +18237,16 @@
         <v>34</v>
       </c>
       <c r="M281" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N281" t="s">
         <v>47</v>
       </c>
       <c r="O281" t="s">
+        <v>591</v>
+      </c>
+      <c r="P281" t="s">
         <v>590</v>
-      </c>
-      <c r="P281" t="s">
-        <v>589</v>
       </c>
       <c r="Q281" t="s">
         <v>47</v>
@@ -18254,7 +18257,7 @@
     </row>
     <row r="282">
       <c r="A282" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B282" t="s">
         <v>34</v>
@@ -18266,7 +18269,7 @@
         <v>34</v>
       </c>
       <c r="E282" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="F282" t="s">
         <v>211</v>
@@ -18275,10 +18278,10 @@
         <v>41</v>
       </c>
       <c r="H282" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I282" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="J282" t="s">
         <v>304</v>
@@ -18290,16 +18293,16 @@
         <v>34</v>
       </c>
       <c r="M282" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N282" t="s">
         <v>47</v>
       </c>
       <c r="O282" t="s">
+        <v>594</v>
+      </c>
+      <c r="P282" t="s">
         <v>593</v>
-      </c>
-      <c r="P282" t="s">
-        <v>592</v>
       </c>
       <c r="Q282" t="s">
         <v>47</v>
@@ -18310,7 +18313,7 @@
     </row>
     <row r="283">
       <c r="A283" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B283" t="s">
         <v>34</v>
@@ -18322,7 +18325,7 @@
         <v>34</v>
       </c>
       <c r="E283" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="F283" t="s">
         <v>211</v>
@@ -18331,10 +18334,10 @@
         <v>41</v>
       </c>
       <c r="H283" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I283" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="J283" t="s">
         <v>304</v>
@@ -18346,16 +18349,16 @@
         <v>34</v>
       </c>
       <c r="M283" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N283" t="s">
         <v>47</v>
       </c>
       <c r="O283" t="s">
+        <v>597</v>
+      </c>
+      <c r="P283" t="s">
         <v>596</v>
-      </c>
-      <c r="P283" t="s">
-        <v>595</v>
       </c>
       <c r="Q283" t="s">
         <v>47</v>
@@ -18366,7 +18369,7 @@
     </row>
     <row r="284">
       <c r="A284" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B284" t="s">
         <v>34</v>
@@ -18378,7 +18381,7 @@
         <v>34</v>
       </c>
       <c r="E284" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="F284" t="s">
         <v>211</v>
@@ -18387,10 +18390,10 @@
         <v>41</v>
       </c>
       <c r="H284" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I284" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="J284" t="s">
         <v>304</v>
@@ -18402,16 +18405,16 @@
         <v>34</v>
       </c>
       <c r="M284" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N284" t="s">
         <v>47</v>
       </c>
       <c r="O284" t="s">
+        <v>600</v>
+      </c>
+      <c r="P284" t="s">
         <v>599</v>
-      </c>
-      <c r="P284" t="s">
-        <v>598</v>
       </c>
       <c r="Q284" t="s">
         <v>47</v>
@@ -18422,7 +18425,7 @@
     </row>
     <row r="285">
       <c r="A285" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B285" t="s">
         <v>34</v>
@@ -18434,7 +18437,7 @@
         <v>34</v>
       </c>
       <c r="E285" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F285" t="s">
         <v>211</v>
@@ -18443,10 +18446,10 @@
         <v>41</v>
       </c>
       <c r="H285" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I285" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="J285" t="s">
         <v>304</v>
@@ -18458,16 +18461,16 @@
         <v>34</v>
       </c>
       <c r="M285" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N285" t="s">
         <v>47</v>
       </c>
       <c r="O285" t="s">
+        <v>603</v>
+      </c>
+      <c r="P285" t="s">
         <v>602</v>
-      </c>
-      <c r="P285" t="s">
-        <v>601</v>
       </c>
       <c r="Q285" t="s">
         <v>47</v>
@@ -18478,7 +18481,7 @@
     </row>
     <row r="286">
       <c r="A286" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B286" t="s">
         <v>34</v>
@@ -18490,7 +18493,7 @@
         <v>34</v>
       </c>
       <c r="E286" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F286" t="s">
         <v>211</v>
@@ -18499,10 +18502,10 @@
         <v>41</v>
       </c>
       <c r="H286" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I286" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="J286" t="s">
         <v>304</v>
@@ -18514,16 +18517,16 @@
         <v>34</v>
       </c>
       <c r="M286" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N286" t="s">
         <v>47</v>
       </c>
       <c r="O286" t="s">
+        <v>606</v>
+      </c>
+      <c r="P286" t="s">
         <v>605</v>
-      </c>
-      <c r="P286" t="s">
-        <v>604</v>
       </c>
       <c r="Q286" t="s">
         <v>47</v>
@@ -18534,7 +18537,7 @@
     </row>
     <row r="287">
       <c r="A287" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B287" t="s">
         <v>34</v>
@@ -18546,7 +18549,7 @@
         <v>34</v>
       </c>
       <c r="E287" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F287" t="s">
         <v>211</v>
@@ -18555,10 +18558,10 @@
         <v>41</v>
       </c>
       <c r="H287" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I287" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="J287" t="s">
         <v>304</v>
@@ -18570,7 +18573,7 @@
         <v>34</v>
       </c>
       <c r="M287" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N287" t="s">
         <v>47</v>
@@ -18579,7 +18582,7 @@
         <v>86</v>
       </c>
       <c r="P287" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="Q287" t="s">
         <v>47</v>
@@ -18590,7 +18593,7 @@
     </row>
     <row r="288">
       <c r="A288" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B288" t="s">
         <v>34</v>
@@ -18602,7 +18605,7 @@
         <v>34</v>
       </c>
       <c r="E288" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F288" t="s">
         <v>211</v>
@@ -18611,10 +18614,10 @@
         <v>41</v>
       </c>
       <c r="H288" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I288" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="J288" t="s">
         <v>304</v>
@@ -18626,16 +18629,16 @@
         <v>34</v>
       </c>
       <c r="M288" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N288" t="s">
         <v>47</v>
       </c>
       <c r="O288" t="s">
+        <v>611</v>
+      </c>
+      <c r="P288" t="s">
         <v>610</v>
-      </c>
-      <c r="P288" t="s">
-        <v>609</v>
       </c>
       <c r="Q288" t="s">
         <v>47</v>
@@ -18646,7 +18649,7 @@
     </row>
     <row r="289">
       <c r="A289" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B289" t="s">
         <v>34</v>
@@ -18658,7 +18661,7 @@
         <v>34</v>
       </c>
       <c r="E289" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F289" t="s">
         <v>211</v>
@@ -18667,10 +18670,10 @@
         <v>41</v>
       </c>
       <c r="H289" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I289" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="J289" t="s">
         <v>304</v>
@@ -18682,16 +18685,16 @@
         <v>34</v>
       </c>
       <c r="M289" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N289" t="s">
         <v>47</v>
       </c>
       <c r="O289" t="s">
+        <v>614</v>
+      </c>
+      <c r="P289" t="s">
         <v>613</v>
-      </c>
-      <c r="P289" t="s">
-        <v>612</v>
       </c>
       <c r="Q289" t="s">
         <v>47</v>
@@ -18702,7 +18705,7 @@
     </row>
     <row r="290">
       <c r="A290" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B290" t="s">
         <v>34</v>
@@ -18714,7 +18717,7 @@
         <v>34</v>
       </c>
       <c r="E290" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="F290" t="s">
         <v>211</v>
@@ -18723,10 +18726,10 @@
         <v>41</v>
       </c>
       <c r="H290" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I290" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="J290" t="s">
         <v>304</v>
@@ -18738,7 +18741,7 @@
         <v>34</v>
       </c>
       <c r="M290" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N290" t="s">
         <v>47</v>
@@ -18747,7 +18750,7 @@
         <v>48</v>
       </c>
       <c r="P290" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="Q290" t="s">
         <v>47</v>
@@ -18758,7 +18761,7 @@
     </row>
     <row r="291">
       <c r="A291" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B291" t="s">
         <v>34</v>
@@ -18770,7 +18773,7 @@
         <v>34</v>
       </c>
       <c r="E291" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="F291" t="s">
         <v>211</v>
@@ -18779,10 +18782,10 @@
         <v>41</v>
       </c>
       <c r="H291" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I291" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="J291" t="s">
         <v>304</v>
@@ -18794,7 +18797,7 @@
         <v>34</v>
       </c>
       <c r="M291" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N291" t="s">
         <v>47</v>
@@ -18803,7 +18806,7 @@
         <v>48</v>
       </c>
       <c r="P291" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="Q291" t="s">
         <v>47</v>
@@ -18814,7 +18817,7 @@
     </row>
     <row r="292">
       <c r="A292" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B292" t="s">
         <v>34</v>
@@ -18826,7 +18829,7 @@
         <v>34</v>
       </c>
       <c r="E292" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="F292" t="s">
         <v>211</v>
@@ -18835,10 +18838,10 @@
         <v>41</v>
       </c>
       <c r="H292" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I292" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="J292" t="s">
         <v>304</v>
@@ -18850,7 +18853,7 @@
         <v>34</v>
       </c>
       <c r="M292" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N292" t="s">
         <v>47</v>
@@ -18859,7 +18862,7 @@
         <v>319</v>
       </c>
       <c r="P292" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="Q292" t="s">
         <v>47</v>
@@ -18870,7 +18873,7 @@
     </row>
     <row r="293">
       <c r="A293" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B293" t="s">
         <v>34</v>
@@ -18882,7 +18885,7 @@
         <v>34</v>
       </c>
       <c r="E293" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F293" t="s">
         <v>211</v>
@@ -18891,10 +18894,10 @@
         <v>41</v>
       </c>
       <c r="H293" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I293" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="J293" t="s">
         <v>304</v>
@@ -18906,16 +18909,16 @@
         <v>34</v>
       </c>
       <c r="M293" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N293" t="s">
         <v>47</v>
       </c>
       <c r="O293" t="s">
+        <v>623</v>
+      </c>
+      <c r="P293" t="s">
         <v>622</v>
-      </c>
-      <c r="P293" t="s">
-        <v>621</v>
       </c>
       <c r="Q293" t="s">
         <v>47</v>
@@ -18926,7 +18929,7 @@
     </row>
     <row r="294">
       <c r="A294" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B294" t="s">
         <v>34</v>
@@ -18938,7 +18941,7 @@
         <v>34</v>
       </c>
       <c r="E294" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F294" t="s">
         <v>211</v>
@@ -18947,10 +18950,10 @@
         <v>41</v>
       </c>
       <c r="H294" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I294" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="J294" t="s">
         <v>304</v>
@@ -18962,16 +18965,16 @@
         <v>34</v>
       </c>
       <c r="M294" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N294" t="s">
         <v>47</v>
       </c>
       <c r="O294" t="s">
+        <v>626</v>
+      </c>
+      <c r="P294" t="s">
         <v>625</v>
-      </c>
-      <c r="P294" t="s">
-        <v>624</v>
       </c>
       <c r="Q294" t="s">
         <v>47</v>
@@ -18982,7 +18985,7 @@
     </row>
     <row r="295">
       <c r="A295" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B295" t="s">
         <v>34</v>
@@ -18994,7 +18997,7 @@
         <v>34</v>
       </c>
       <c r="E295" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="F295" t="s">
         <v>211</v>
@@ -19003,10 +19006,10 @@
         <v>41</v>
       </c>
       <c r="H295" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I295" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="J295" t="s">
         <v>304</v>
@@ -19015,10 +19018,10 @@
         <v>96</v>
       </c>
       <c r="L295" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M295" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N295" t="s">
         <v>47</v>
@@ -19027,7 +19030,7 @@
         <v>48</v>
       </c>
       <c r="P295" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="Q295" t="s">
         <v>47</v>
@@ -19038,7 +19041,7 @@
     </row>
     <row r="296">
       <c r="A296" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B296" t="s">
         <v>34</v>
@@ -19050,7 +19053,7 @@
         <v>34</v>
       </c>
       <c r="E296" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="F296" t="s">
         <v>211</v>
@@ -19059,10 +19062,10 @@
         <v>41</v>
       </c>
       <c r="H296" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I296" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="J296" t="s">
         <v>304</v>
@@ -19074,7 +19077,7 @@
         <v>34</v>
       </c>
       <c r="M296" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N296" t="s">
         <v>47</v>
@@ -19083,7 +19086,7 @@
         <v>332</v>
       </c>
       <c r="P296" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="Q296" t="s">
         <v>47</v>
@@ -19094,7 +19097,7 @@
     </row>
     <row r="297">
       <c r="A297" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B297" t="s">
         <v>34</v>
@@ -19106,7 +19109,7 @@
         <v>34</v>
       </c>
       <c r="E297" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="F297" t="s">
         <v>211</v>
@@ -19115,10 +19118,10 @@
         <v>41</v>
       </c>
       <c r="H297" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I297" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="J297" t="s">
         <v>304</v>
@@ -19130,16 +19133,16 @@
         <v>34</v>
       </c>
       <c r="M297" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N297" t="s">
         <v>47</v>
       </c>
       <c r="O297" t="s">
+        <v>634</v>
+      </c>
+      <c r="P297" t="s">
         <v>633</v>
-      </c>
-      <c r="P297" t="s">
-        <v>632</v>
       </c>
       <c r="Q297" t="s">
         <v>47</v>
@@ -19150,7 +19153,7 @@
     </row>
     <row r="298">
       <c r="A298" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B298" t="s">
         <v>34</v>
@@ -19162,7 +19165,7 @@
         <v>34</v>
       </c>
       <c r="E298" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="F298" t="s">
         <v>211</v>
@@ -19171,10 +19174,10 @@
         <v>41</v>
       </c>
       <c r="H298" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I298" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="J298" t="s">
         <v>304</v>
@@ -19186,16 +19189,16 @@
         <v>34</v>
       </c>
       <c r="M298" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N298" t="s">
         <v>47</v>
       </c>
       <c r="O298" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="P298" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="Q298" t="s">
         <v>47</v>
@@ -19206,7 +19209,7 @@
     </row>
     <row r="299">
       <c r="A299" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B299" t="s">
         <v>34</v>
@@ -19218,7 +19221,7 @@
         <v>34</v>
       </c>
       <c r="E299" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F299" t="s">
         <v>211</v>
@@ -19227,13 +19230,13 @@
         <v>41</v>
       </c>
       <c r="H299" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I299" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="J299" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="K299" t="s">
         <v>113</v>
@@ -19242,16 +19245,16 @@
         <v>34</v>
       </c>
       <c r="M299" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N299" t="s">
         <v>47</v>
       </c>
       <c r="O299" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="P299" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="Q299" t="s">
         <v>47</v>
@@ -19262,7 +19265,7 @@
     </row>
     <row r="300">
       <c r="A300" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B300" t="s">
         <v>34</v>
@@ -19283,13 +19286,13 @@
         <v>41</v>
       </c>
       <c r="H300" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I300" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="J300" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="K300" t="s">
         <v>85</v>
@@ -19298,7 +19301,7 @@
         <v>34</v>
       </c>
       <c r="M300" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N300" t="s">
         <v>47</v>
@@ -19307,7 +19310,7 @@
         <v>86</v>
       </c>
       <c r="P300" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="Q300" t="s">
         <v>47</v>
@@ -19318,7 +19321,7 @@
     </row>
     <row r="301">
       <c r="A301" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B301" t="s">
         <v>34</v>
@@ -19339,13 +19342,13 @@
         <v>41</v>
       </c>
       <c r="H301" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I301" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="J301" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="K301" t="s">
         <v>113</v>
@@ -19354,7 +19357,7 @@
         <v>34</v>
       </c>
       <c r="M301" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N301" t="s">
         <v>47</v>
@@ -19363,7 +19366,7 @@
         <v>114</v>
       </c>
       <c r="P301" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="Q301" t="s">
         <v>47</v>
@@ -19374,7 +19377,7 @@
     </row>
     <row r="302">
       <c r="A302" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B302" t="s">
         <v>34</v>
@@ -19395,13 +19398,13 @@
         <v>41</v>
       </c>
       <c r="H302" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I302" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="J302" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="K302" t="s">
         <v>58</v>
@@ -19410,7 +19413,7 @@
         <v>34</v>
       </c>
       <c r="M302" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N302" t="s">
         <v>47</v>
@@ -19419,7 +19422,7 @@
         <v>105</v>
       </c>
       <c r="P302" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="Q302" t="s">
         <v>47</v>
@@ -19430,7 +19433,7 @@
     </row>
     <row r="303">
       <c r="A303" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B303" t="s">
         <v>34</v>
@@ -19451,13 +19454,13 @@
         <v>41</v>
       </c>
       <c r="H303" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I303" t="s">
+        <v>645</v>
+      </c>
+      <c r="J303" t="s">
         <v>644</v>
-      </c>
-      <c r="J303" t="s">
-        <v>643</v>
       </c>
       <c r="K303" t="s">
         <v>80</v>
@@ -19466,7 +19469,7 @@
         <v>34</v>
       </c>
       <c r="M303" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N303" t="s">
         <v>47</v>
@@ -19475,7 +19478,7 @@
         <v>247</v>
       </c>
       <c r="P303" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="Q303" t="s">
         <v>47</v>
@@ -19486,7 +19489,7 @@
     </row>
     <row r="304">
       <c r="A304" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B304" t="s">
         <v>34</v>
@@ -19507,13 +19510,13 @@
         <v>41</v>
       </c>
       <c r="H304" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I304" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="J304" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="K304" t="s">
         <v>70</v>
@@ -19522,7 +19525,7 @@
         <v>34</v>
       </c>
       <c r="M304" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N304" t="s">
         <v>47</v>
@@ -19531,7 +19534,7 @@
         <v>71</v>
       </c>
       <c r="P304" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="Q304" t="s">
         <v>47</v>
@@ -19542,7 +19545,7 @@
     </row>
     <row r="305">
       <c r="A305" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B305" t="s">
         <v>34</v>
@@ -19563,13 +19566,13 @@
         <v>41</v>
       </c>
       <c r="H305" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I305" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="J305" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="K305" t="s">
         <v>101</v>
@@ -19578,7 +19581,7 @@
         <v>34</v>
       </c>
       <c r="M305" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N305" t="s">
         <v>47</v>
@@ -19587,7 +19590,7 @@
         <v>102</v>
       </c>
       <c r="P305" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="Q305" t="s">
         <v>47</v>
@@ -19598,7 +19601,7 @@
     </row>
     <row r="306">
       <c r="A306" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B306" t="s">
         <v>34</v>
@@ -19610,7 +19613,7 @@
         <v>34</v>
       </c>
       <c r="E306" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F306" t="s">
         <v>211</v>
@@ -19619,13 +19622,13 @@
         <v>41</v>
       </c>
       <c r="H306" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I306" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="J306" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="K306" t="s">
         <v>113</v>
@@ -19634,7 +19637,7 @@
         <v>34</v>
       </c>
       <c r="M306" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N306" t="s">
         <v>47</v>
@@ -19643,7 +19646,7 @@
         <v>114</v>
       </c>
       <c r="P306" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="Q306" t="s">
         <v>47</v>
@@ -19654,7 +19657,7 @@
     </row>
     <row r="307">
       <c r="A307" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B307" t="s">
         <v>34</v>
@@ -19666,7 +19669,7 @@
         <v>34</v>
       </c>
       <c r="E307" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="F307" t="s">
         <v>211</v>
@@ -19675,13 +19678,13 @@
         <v>41</v>
       </c>
       <c r="H307" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I307" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="J307" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="K307" t="s">
         <v>134</v>
@@ -19690,7 +19693,7 @@
         <v>34</v>
       </c>
       <c r="M307" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N307" t="s">
         <v>47</v>
@@ -19699,7 +19702,7 @@
         <v>160</v>
       </c>
       <c r="P307" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="Q307" t="s">
         <v>47</v>
@@ -19710,7 +19713,7 @@
     </row>
     <row r="308">
       <c r="A308" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B308" t="s">
         <v>34</v>
@@ -19722,7 +19725,7 @@
         <v>34</v>
       </c>
       <c r="E308" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="F308" t="s">
         <v>211</v>
@@ -19731,13 +19734,13 @@
         <v>41</v>
       </c>
       <c r="H308" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I308" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="J308" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="K308" t="s">
         <v>58</v>
@@ -19746,7 +19749,7 @@
         <v>34</v>
       </c>
       <c r="M308" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N308" t="s">
         <v>47</v>
@@ -19755,7 +19758,7 @@
         <v>105</v>
       </c>
       <c r="P308" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="Q308" t="s">
         <v>47</v>
@@ -19766,7 +19769,7 @@
     </row>
     <row r="309">
       <c r="A309" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B309" t="s">
         <v>34</v>
@@ -19778,7 +19781,7 @@
         <v>34</v>
       </c>
       <c r="E309" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="F309" t="s">
         <v>211</v>
@@ -19787,13 +19790,13 @@
         <v>41</v>
       </c>
       <c r="H309" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I309" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="J309" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="K309" t="s">
         <v>101</v>
@@ -19802,7 +19805,7 @@
         <v>34</v>
       </c>
       <c r="M309" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N309" t="s">
         <v>47</v>
@@ -19811,7 +19814,7 @@
         <v>102</v>
       </c>
       <c r="P309" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="Q309" t="s">
         <v>47</v>
@@ -19822,7 +19825,7 @@
     </row>
     <row r="310">
       <c r="A310" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B310" t="s">
         <v>34</v>
@@ -19834,7 +19837,7 @@
         <v>34</v>
       </c>
       <c r="E310" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="F310" t="s">
         <v>211</v>
@@ -19843,13 +19846,13 @@
         <v>41</v>
       </c>
       <c r="H310" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I310" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="J310" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="K310" t="s">
         <v>58</v>
@@ -19858,7 +19861,7 @@
         <v>34</v>
       </c>
       <c r="M310" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N310" t="s">
         <v>47</v>
@@ -19867,7 +19870,7 @@
         <v>105</v>
       </c>
       <c r="P310" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="Q310" t="s">
         <v>47</v>
@@ -19878,7 +19881,7 @@
     </row>
     <row r="311">
       <c r="A311" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B311" t="s">
         <v>34</v>
@@ -19890,7 +19893,7 @@
         <v>34</v>
       </c>
       <c r="E311" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F311" t="s">
         <v>211</v>
@@ -19899,13 +19902,13 @@
         <v>41</v>
       </c>
       <c r="H311" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I311" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="J311" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="K311" t="s">
         <v>80</v>
@@ -19914,7 +19917,7 @@
         <v>34</v>
       </c>
       <c r="M311" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N311" t="s">
         <v>47</v>
@@ -19923,7 +19926,7 @@
         <v>255</v>
       </c>
       <c r="P311" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="Q311" t="s">
         <v>47</v>
@@ -19934,7 +19937,7 @@
     </row>
     <row r="312">
       <c r="A312" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B312" t="s">
         <v>34</v>
@@ -19946,7 +19949,7 @@
         <v>34</v>
       </c>
       <c r="E312" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="F312" t="s">
         <v>211</v>
@@ -19955,10 +19958,10 @@
         <v>41</v>
       </c>
       <c r="H312" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I312" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="J312" t="s">
         <v>304</v>
@@ -19970,16 +19973,16 @@
         <v>34</v>
       </c>
       <c r="M312" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N312" t="s">
         <v>47</v>
       </c>
       <c r="O312" t="s">
+        <v>662</v>
+      </c>
+      <c r="P312" t="s">
         <v>661</v>
-      </c>
-      <c r="P312" t="s">
-        <v>660</v>
       </c>
       <c r="Q312" t="s">
         <v>47</v>
@@ -19990,13 +19993,13 @@
     </row>
     <row r="313">
       <c r="A313" t="s" s="1">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B313" t="s" s="1">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C313" t="s" s="1">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D313" t="s" s="1">
         <v>33</v>
@@ -20046,13 +20049,13 @@
     </row>
     <row r="314">
       <c r="A314" t="s" s="1">
+        <v>665</v>
+      </c>
+      <c r="B314" t="s" s="1">
         <v>664</v>
       </c>
-      <c r="B314" t="s" s="1">
-        <v>663</v>
-      </c>
       <c r="C314" t="s" s="1">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D314" t="s" s="1">
         <v>33</v>
@@ -20102,55 +20105,55 @@
     </row>
     <row r="315">
       <c r="A315" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B315" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C315" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D315" t="s">
         <v>33</v>
       </c>
       <c r="E315" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="F315" t="s">
-        <v>40</v>
+        <v>667</v>
       </c>
       <c r="G315" t="s">
         <v>41</v>
       </c>
       <c r="H315" t="s">
+        <v>668</v>
+      </c>
+      <c r="I315" t="s">
+        <v>669</v>
+      </c>
+      <c r="J315" t="s">
+        <v>191</v>
+      </c>
+      <c r="K315" t="s">
+        <v>191</v>
+      </c>
+      <c r="L315" t="s">
+        <v>34</v>
+      </c>
+      <c r="M315" t="s">
         <v>666</v>
       </c>
-      <c r="I315" t="s">
-        <v>667</v>
-      </c>
-      <c r="J315" t="s">
-        <v>90</v>
-      </c>
-      <c r="K315" t="s">
-        <v>90</v>
-      </c>
-      <c r="L315" t="s">
-        <v>34</v>
-      </c>
-      <c r="M315" t="s">
-        <v>665</v>
-      </c>
       <c r="N315" t="s">
         <v>47</v>
       </c>
       <c r="O315" t="s">
-        <v>310</v>
+        <v>34</v>
       </c>
       <c r="P315" t="s">
-        <v>667</v>
+        <v>34</v>
       </c>
       <c r="Q315" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R315" t="s">
         <v>34</v>
@@ -20158,7 +20161,7 @@
     </row>
     <row r="316">
       <c r="A316" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B316" t="s">
         <v>34</v>
@@ -20170,7 +20173,7 @@
         <v>34</v>
       </c>
       <c r="E316" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="F316" t="s">
         <v>40</v>
@@ -20179,31 +20182,31 @@
         <v>41</v>
       </c>
       <c r="H316" t="s">
+        <v>668</v>
+      </c>
+      <c r="I316" t="s">
+        <v>669</v>
+      </c>
+      <c r="J316" t="s">
+        <v>147</v>
+      </c>
+      <c r="K316" t="s">
+        <v>113</v>
+      </c>
+      <c r="L316" t="s">
+        <v>34</v>
+      </c>
+      <c r="M316" t="s">
         <v>666</v>
       </c>
-      <c r="I316" t="s">
-        <v>667</v>
-      </c>
-      <c r="J316" t="s">
-        <v>119</v>
-      </c>
-      <c r="K316" t="s">
-        <v>80</v>
-      </c>
-      <c r="L316" t="s">
-        <v>34</v>
-      </c>
-      <c r="M316" t="s">
-        <v>665</v>
-      </c>
       <c r="N316" t="s">
         <v>47</v>
       </c>
       <c r="O316" t="s">
-        <v>247</v>
+        <v>114</v>
       </c>
       <c r="P316" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="Q316" t="s">
         <v>47</v>
@@ -20214,7 +20217,7 @@
     </row>
     <row r="317">
       <c r="A317" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B317" t="s">
         <v>34</v>
@@ -20226,7 +20229,7 @@
         <v>34</v>
       </c>
       <c r="E317" t="s">
-        <v>248</v>
+        <v>275</v>
       </c>
       <c r="F317" t="s">
         <v>40</v>
@@ -20235,31 +20238,31 @@
         <v>41</v>
       </c>
       <c r="H317" t="s">
+        <v>668</v>
+      </c>
+      <c r="I317" t="s">
+        <v>669</v>
+      </c>
+      <c r="J317" t="s">
+        <v>96</v>
+      </c>
+      <c r="K317" t="s">
+        <v>58</v>
+      </c>
+      <c r="L317" t="s">
+        <v>34</v>
+      </c>
+      <c r="M317" t="s">
         <v>666</v>
       </c>
-      <c r="I317" t="s">
-        <v>667</v>
-      </c>
-      <c r="J317" t="s">
-        <v>119</v>
-      </c>
-      <c r="K317" t="s">
-        <v>119</v>
-      </c>
-      <c r="L317" t="s">
-        <v>34</v>
-      </c>
-      <c r="M317" t="s">
-        <v>665</v>
-      </c>
       <c r="N317" t="s">
         <v>47</v>
       </c>
       <c r="O317" t="s">
-        <v>250</v>
+        <v>105</v>
       </c>
       <c r="P317" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="Q317" t="s">
         <v>47</v>
@@ -20270,7 +20273,7 @@
     </row>
     <row r="318">
       <c r="A318" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B318" t="s">
         <v>34</v>
@@ -20282,22 +20285,22 @@
         <v>34</v>
       </c>
       <c r="E318" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F318" t="s">
-        <v>40</v>
+        <v>667</v>
       </c>
       <c r="G318" t="s">
         <v>41</v>
       </c>
       <c r="H318" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="I318" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="J318" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K318" t="s">
         <v>119</v>
@@ -20306,19 +20309,19 @@
         <v>34</v>
       </c>
       <c r="M318" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N318" t="s">
         <v>47</v>
       </c>
       <c r="O318" t="s">
-        <v>130</v>
+        <v>34</v>
       </c>
       <c r="P318" t="s">
-        <v>667</v>
+        <v>34</v>
       </c>
       <c r="Q318" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R318" t="s">
         <v>34</v>
@@ -20326,7 +20329,7 @@
     </row>
     <row r="319">
       <c r="A319" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B319" t="s">
         <v>34</v>
@@ -20338,7 +20341,7 @@
         <v>34</v>
       </c>
       <c r="E319" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="F319" t="s">
         <v>40</v>
@@ -20347,31 +20350,31 @@
         <v>41</v>
       </c>
       <c r="H319" t="s">
+        <v>668</v>
+      </c>
+      <c r="I319" t="s">
+        <v>669</v>
+      </c>
+      <c r="J319" t="s">
+        <v>119</v>
+      </c>
+      <c r="K319" t="s">
+        <v>119</v>
+      </c>
+      <c r="L319" t="s">
+        <v>34</v>
+      </c>
+      <c r="M319" t="s">
         <v>666</v>
       </c>
-      <c r="I319" t="s">
-        <v>667</v>
-      </c>
-      <c r="J319" t="s">
-        <v>80</v>
-      </c>
-      <c r="K319" t="s">
-        <v>80</v>
-      </c>
-      <c r="L319" t="s">
-        <v>34</v>
-      </c>
-      <c r="M319" t="s">
-        <v>665</v>
-      </c>
       <c r="N319" t="s">
         <v>47</v>
       </c>
       <c r="O319" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="P319" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="Q319" t="s">
         <v>47</v>
@@ -20382,7 +20385,7 @@
     </row>
     <row r="320">
       <c r="A320" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B320" t="s">
         <v>34</v>
@@ -20394,43 +20397,43 @@
         <v>34</v>
       </c>
       <c r="E320" t="s">
-        <v>227</v>
+        <v>157</v>
       </c>
       <c r="F320" t="s">
+        <v>40</v>
+      </c>
+      <c r="G320" t="s">
+        <v>41</v>
+      </c>
+      <c r="H320" t="s">
         <v>668</v>
       </c>
-      <c r="G320" t="s">
-        <v>41</v>
-      </c>
-      <c r="H320" t="s">
+      <c r="I320" t="s">
+        <v>669</v>
+      </c>
+      <c r="J320" t="s">
+        <v>134</v>
+      </c>
+      <c r="K320" t="s">
+        <v>134</v>
+      </c>
+      <c r="L320" t="s">
+        <v>34</v>
+      </c>
+      <c r="M320" t="s">
         <v>666</v>
       </c>
-      <c r="I320" t="s">
-        <v>667</v>
-      </c>
-      <c r="J320" t="s">
-        <v>90</v>
-      </c>
-      <c r="K320" t="s">
-        <v>229</v>
-      </c>
-      <c r="L320" t="s">
-        <v>34</v>
-      </c>
-      <c r="M320" t="s">
-        <v>665</v>
-      </c>
       <c r="N320" t="s">
         <v>47</v>
       </c>
       <c r="O320" t="s">
-        <v>34</v>
+        <v>463</v>
       </c>
       <c r="P320" t="s">
-        <v>34</v>
+        <v>669</v>
       </c>
       <c r="Q320" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R320" t="s">
         <v>34</v>
@@ -20438,7 +20441,7 @@
     </row>
     <row r="321">
       <c r="A321" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B321" t="s">
         <v>34</v>
@@ -20450,31 +20453,31 @@
         <v>34</v>
       </c>
       <c r="E321" t="s">
-        <v>256</v>
+        <v>221</v>
       </c>
       <c r="F321" t="s">
+        <v>667</v>
+      </c>
+      <c r="G321" t="s">
+        <v>41</v>
+      </c>
+      <c r="H321" t="s">
         <v>668</v>
       </c>
-      <c r="G321" t="s">
-        <v>41</v>
-      </c>
-      <c r="H321" t="s">
+      <c r="I321" t="s">
+        <v>669</v>
+      </c>
+      <c r="J321" t="s">
+        <v>90</v>
+      </c>
+      <c r="K321" t="s">
+        <v>90</v>
+      </c>
+      <c r="L321" t="s">
+        <v>34</v>
+      </c>
+      <c r="M321" t="s">
         <v>666</v>
-      </c>
-      <c r="I321" t="s">
-        <v>667</v>
-      </c>
-      <c r="J321" t="s">
-        <v>80</v>
-      </c>
-      <c r="K321" t="s">
-        <v>80</v>
-      </c>
-      <c r="L321" t="s">
-        <v>34</v>
-      </c>
-      <c r="M321" t="s">
-        <v>665</v>
       </c>
       <c r="N321" t="s">
         <v>47</v>
@@ -20494,7 +20497,7 @@
     </row>
     <row r="322">
       <c r="A322" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B322" t="s">
         <v>34</v>
@@ -20506,43 +20509,43 @@
         <v>34</v>
       </c>
       <c r="E322" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="F322" t="s">
+        <v>40</v>
+      </c>
+      <c r="G322" t="s">
+        <v>41</v>
+      </c>
+      <c r="H322" t="s">
         <v>668</v>
       </c>
-      <c r="G322" t="s">
-        <v>41</v>
-      </c>
-      <c r="H322" t="s">
+      <c r="I322" t="s">
+        <v>669</v>
+      </c>
+      <c r="J322" t="s">
+        <v>80</v>
+      </c>
+      <c r="K322" t="s">
+        <v>80</v>
+      </c>
+      <c r="L322" t="s">
+        <v>34</v>
+      </c>
+      <c r="M322" t="s">
         <v>666</v>
       </c>
-      <c r="I322" t="s">
-        <v>667</v>
-      </c>
-      <c r="J322" t="s">
-        <v>119</v>
-      </c>
-      <c r="K322" t="s">
-        <v>119</v>
-      </c>
-      <c r="L322" t="s">
-        <v>34</v>
-      </c>
-      <c r="M322" t="s">
-        <v>665</v>
-      </c>
       <c r="N322" t="s">
         <v>47</v>
       </c>
       <c r="O322" t="s">
-        <v>34</v>
+        <v>255</v>
       </c>
       <c r="P322" t="s">
-        <v>34</v>
+        <v>669</v>
       </c>
       <c r="Q322" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R322" t="s">
         <v>34</v>
@@ -20550,7 +20553,7 @@
     </row>
     <row r="323">
       <c r="A323" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B323" t="s">
         <v>34</v>
@@ -20562,7 +20565,7 @@
         <v>34</v>
       </c>
       <c r="E323" t="s">
-        <v>157</v>
+        <v>244</v>
       </c>
       <c r="F323" t="s">
         <v>40</v>
@@ -20571,31 +20574,31 @@
         <v>41</v>
       </c>
       <c r="H323" t="s">
+        <v>668</v>
+      </c>
+      <c r="I323" t="s">
+        <v>669</v>
+      </c>
+      <c r="J323" t="s">
+        <v>119</v>
+      </c>
+      <c r="K323" t="s">
+        <v>80</v>
+      </c>
+      <c r="L323" t="s">
+        <v>34</v>
+      </c>
+      <c r="M323" t="s">
         <v>666</v>
       </c>
-      <c r="I323" t="s">
-        <v>667</v>
-      </c>
-      <c r="J323" t="s">
-        <v>134</v>
-      </c>
-      <c r="K323" t="s">
-        <v>134</v>
-      </c>
-      <c r="L323" t="s">
-        <v>34</v>
-      </c>
-      <c r="M323" t="s">
-        <v>665</v>
-      </c>
       <c r="N323" t="s">
         <v>47</v>
       </c>
       <c r="O323" t="s">
-        <v>463</v>
+        <v>247</v>
       </c>
       <c r="P323" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="Q323" t="s">
         <v>47</v>
@@ -20606,7 +20609,7 @@
     </row>
     <row r="324">
       <c r="A324" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B324" t="s">
         <v>34</v>
@@ -20618,7 +20621,7 @@
         <v>34</v>
       </c>
       <c r="E324" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="F324" t="s">
         <v>40</v>
@@ -20627,31 +20630,31 @@
         <v>41</v>
       </c>
       <c r="H324" t="s">
+        <v>668</v>
+      </c>
+      <c r="I324" t="s">
+        <v>669</v>
+      </c>
+      <c r="J324" t="s">
+        <v>90</v>
+      </c>
+      <c r="K324" t="s">
+        <v>90</v>
+      </c>
+      <c r="L324" t="s">
+        <v>34</v>
+      </c>
+      <c r="M324" t="s">
         <v>666</v>
       </c>
-      <c r="I324" t="s">
-        <v>667</v>
-      </c>
-      <c r="J324" t="s">
-        <v>147</v>
-      </c>
-      <c r="K324" t="s">
-        <v>113</v>
-      </c>
-      <c r="L324" t="s">
-        <v>34</v>
-      </c>
-      <c r="M324" t="s">
-        <v>665</v>
-      </c>
       <c r="N324" t="s">
         <v>47</v>
       </c>
       <c r="O324" t="s">
-        <v>114</v>
+        <v>310</v>
       </c>
       <c r="P324" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="Q324" t="s">
         <v>47</v>
@@ -20662,7 +20665,7 @@
     </row>
     <row r="325">
       <c r="A325" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B325" t="s">
         <v>34</v>
@@ -20674,7 +20677,7 @@
         <v>34</v>
       </c>
       <c r="E325" t="s">
-        <v>275</v>
+        <v>225</v>
       </c>
       <c r="F325" t="s">
         <v>40</v>
@@ -20683,31 +20686,31 @@
         <v>41</v>
       </c>
       <c r="H325" t="s">
+        <v>668</v>
+      </c>
+      <c r="I325" t="s">
+        <v>669</v>
+      </c>
+      <c r="J325" t="s">
+        <v>178</v>
+      </c>
+      <c r="K325" t="s">
+        <v>101</v>
+      </c>
+      <c r="L325" t="s">
+        <v>34</v>
+      </c>
+      <c r="M325" t="s">
         <v>666</v>
       </c>
-      <c r="I325" t="s">
-        <v>667</v>
-      </c>
-      <c r="J325" t="s">
-        <v>96</v>
-      </c>
-      <c r="K325" t="s">
-        <v>58</v>
-      </c>
-      <c r="L325" t="s">
-        <v>34</v>
-      </c>
-      <c r="M325" t="s">
-        <v>665</v>
-      </c>
       <c r="N325" t="s">
         <v>47</v>
       </c>
       <c r="O325" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="P325" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="Q325" t="s">
         <v>47</v>
@@ -20718,7 +20721,7 @@
     </row>
     <row r="326">
       <c r="A326" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B326" t="s">
         <v>34</v>
@@ -20730,31 +20733,31 @@
         <v>34</v>
       </c>
       <c r="E326" t="s">
-        <v>221</v>
+        <v>256</v>
       </c>
       <c r="F326" t="s">
+        <v>667</v>
+      </c>
+      <c r="G326" t="s">
+        <v>41</v>
+      </c>
+      <c r="H326" t="s">
         <v>668</v>
       </c>
-      <c r="G326" t="s">
-        <v>41</v>
-      </c>
-      <c r="H326" t="s">
+      <c r="I326" t="s">
+        <v>669</v>
+      </c>
+      <c r="J326" t="s">
+        <v>80</v>
+      </c>
+      <c r="K326" t="s">
+        <v>80</v>
+      </c>
+      <c r="L326" t="s">
+        <v>34</v>
+      </c>
+      <c r="M326" t="s">
         <v>666</v>
-      </c>
-      <c r="I326" t="s">
-        <v>667</v>
-      </c>
-      <c r="J326" t="s">
-        <v>90</v>
-      </c>
-      <c r="K326" t="s">
-        <v>90</v>
-      </c>
-      <c r="L326" t="s">
-        <v>34</v>
-      </c>
-      <c r="M326" t="s">
-        <v>665</v>
       </c>
       <c r="N326" t="s">
         <v>47</v>
@@ -20774,7 +20777,7 @@
     </row>
     <row r="327">
       <c r="A327" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B327" t="s">
         <v>34</v>
@@ -20786,43 +20789,43 @@
         <v>34</v>
       </c>
       <c r="E327" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="F327" t="s">
+        <v>40</v>
+      </c>
+      <c r="G327" t="s">
+        <v>41</v>
+      </c>
+      <c r="H327" t="s">
         <v>668</v>
       </c>
-      <c r="G327" t="s">
-        <v>41</v>
-      </c>
-      <c r="H327" t="s">
+      <c r="I327" t="s">
+        <v>669</v>
+      </c>
+      <c r="J327" t="s">
+        <v>118</v>
+      </c>
+      <c r="K327" t="s">
+        <v>119</v>
+      </c>
+      <c r="L327" t="s">
+        <v>34</v>
+      </c>
+      <c r="M327" t="s">
         <v>666</v>
       </c>
-      <c r="I327" t="s">
-        <v>667</v>
-      </c>
-      <c r="J327" t="s">
-        <v>191</v>
-      </c>
-      <c r="K327" t="s">
-        <v>191</v>
-      </c>
-      <c r="L327" t="s">
-        <v>34</v>
-      </c>
-      <c r="M327" t="s">
-        <v>665</v>
-      </c>
       <c r="N327" t="s">
         <v>47</v>
       </c>
       <c r="O327" t="s">
-        <v>34</v>
+        <v>130</v>
       </c>
       <c r="P327" t="s">
-        <v>34</v>
+        <v>669</v>
       </c>
       <c r="Q327" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R327" t="s">
         <v>34</v>
@@ -20830,7 +20833,7 @@
     </row>
     <row r="328">
       <c r="A328" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B328" t="s">
         <v>34</v>
@@ -20842,43 +20845,43 @@
         <v>34</v>
       </c>
       <c r="E328" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F328" t="s">
-        <v>40</v>
+        <v>667</v>
       </c>
       <c r="G328" t="s">
         <v>41</v>
       </c>
       <c r="H328" t="s">
+        <v>668</v>
+      </c>
+      <c r="I328" t="s">
+        <v>669</v>
+      </c>
+      <c r="J328" t="s">
+        <v>90</v>
+      </c>
+      <c r="K328" t="s">
+        <v>229</v>
+      </c>
+      <c r="L328" t="s">
+        <v>34</v>
+      </c>
+      <c r="M328" t="s">
         <v>666</v>
       </c>
-      <c r="I328" t="s">
-        <v>667</v>
-      </c>
-      <c r="J328" t="s">
-        <v>178</v>
-      </c>
-      <c r="K328" t="s">
-        <v>101</v>
-      </c>
-      <c r="L328" t="s">
-        <v>34</v>
-      </c>
-      <c r="M328" t="s">
-        <v>665</v>
-      </c>
       <c r="N328" t="s">
         <v>47</v>
       </c>
       <c r="O328" t="s">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="P328" t="s">
-        <v>667</v>
+        <v>34</v>
       </c>
       <c r="Q328" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R328" t="s">
         <v>34</v>
@@ -20886,13 +20889,13 @@
     </row>
     <row r="329">
       <c r="A329" t="s" s="1">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B329" t="s" s="1">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C329" t="s" s="1">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D329" t="s" s="1">
         <v>33</v>
@@ -20942,19 +20945,19 @@
     </row>
     <row r="330">
       <c r="A330" t="s">
+        <v>672</v>
+      </c>
+      <c r="B330" t="s">
         <v>671</v>
       </c>
-      <c r="B330" t="s">
-        <v>670</v>
-      </c>
       <c r="C330" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D330" t="s">
         <v>33</v>
       </c>
       <c r="E330" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F330" t="s">
         <v>40</v>
@@ -20963,10 +20966,10 @@
         <v>41</v>
       </c>
       <c r="H330" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="I330" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="J330" t="s">
         <v>335</v>
@@ -20975,10 +20978,10 @@
         <v>45</v>
       </c>
       <c r="L330" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="M330" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="N330" t="s">
         <v>47</v>
@@ -20987,7 +20990,7 @@
         <v>48</v>
       </c>
       <c r="P330" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="Q330" t="s">
         <v>47</v>
@@ -20998,7 +21001,7 @@
     </row>
     <row r="331">
       <c r="A331" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B331" t="s">
         <v>34</v>
@@ -21010,31 +21013,31 @@
         <v>34</v>
       </c>
       <c r="E331" t="s">
-        <v>175</v>
+        <v>677</v>
       </c>
       <c r="F331" t="s">
-        <v>40</v>
+        <v>211</v>
       </c>
       <c r="G331" t="s">
         <v>41</v>
       </c>
       <c r="H331" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="I331" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="J331" t="s">
-        <v>178</v>
+        <v>680</v>
       </c>
       <c r="K331" t="s">
-        <v>178</v>
+        <v>229</v>
       </c>
       <c r="L331" t="s">
-        <v>678</v>
+        <v>34</v>
       </c>
       <c r="M331" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="N331" t="s">
         <v>47</v>
@@ -21043,7 +21046,7 @@
         <v>48</v>
       </c>
       <c r="P331" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="Q331" t="s">
         <v>47</v>
@@ -21054,7 +21057,7 @@
     </row>
     <row r="332">
       <c r="A332" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B332" t="s">
         <v>34</v>
@@ -21066,7 +21069,7 @@
         <v>34</v>
       </c>
       <c r="E332" t="s">
-        <v>672</v>
+        <v>175</v>
       </c>
       <c r="F332" t="s">
         <v>40</v>
@@ -21075,22 +21078,22 @@
         <v>41</v>
       </c>
       <c r="H332" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="I332" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="J332" t="s">
-        <v>681</v>
+        <v>178</v>
       </c>
       <c r="K332" t="s">
-        <v>229</v>
+        <v>178</v>
       </c>
       <c r="L332" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="M332" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="N332" t="s">
         <v>47</v>
@@ -21099,7 +21102,7 @@
         <v>48</v>
       </c>
       <c r="P332" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="Q332" t="s">
         <v>47</v>
@@ -21110,7 +21113,7 @@
     </row>
     <row r="333">
       <c r="A333" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B333" t="s">
         <v>34</v>
@@ -21122,10 +21125,10 @@
         <v>34</v>
       </c>
       <c r="E333" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="F333" t="s">
-        <v>211</v>
+        <v>40</v>
       </c>
       <c r="G333" t="s">
         <v>41</v>
@@ -21143,10 +21146,10 @@
         <v>229</v>
       </c>
       <c r="L333" t="s">
-        <v>34</v>
+        <v>687</v>
       </c>
       <c r="M333" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="N333" t="s">
         <v>47</v>
@@ -21166,13 +21169,13 @@
     </row>
     <row r="334">
       <c r="A334" t="s" s="1">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B334" t="s" s="1">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C334" t="s" s="1">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D334" t="s" s="1">
         <v>33</v>
@@ -21222,13 +21225,13 @@
     </row>
     <row r="335">
       <c r="A335" t="s" s="1">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B335" t="s" s="1">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C335" t="s" s="1">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D335" t="s" s="1">
         <v>33</v>
@@ -21278,13 +21281,13 @@
     </row>
     <row r="336">
       <c r="A336" t="s" s="1">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B336" t="s" s="1">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C336" t="s" s="1">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D336" t="s" s="1">
         <v>33</v>
@@ -21334,19 +21337,19 @@
     </row>
     <row r="337">
       <c r="A337" t="s">
+        <v>694</v>
+      </c>
+      <c r="B337" t="s">
         <v>693</v>
       </c>
-      <c r="B337" t="s">
-        <v>692</v>
-      </c>
       <c r="C337" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D337" t="s">
         <v>33</v>
       </c>
       <c r="E337" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F337" t="s">
         <v>40</v>
@@ -21358,19 +21361,19 @@
         <v>449</v>
       </c>
       <c r="I337" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="J337" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="K337" t="s">
         <v>45</v>
       </c>
       <c r="L337" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="M337" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="N337" t="s">
         <v>47</v>
@@ -21379,7 +21382,7 @@
         <v>48</v>
       </c>
       <c r="P337" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="Q337" t="s">
         <v>47</v>
@@ -21390,13 +21393,13 @@
     </row>
     <row r="338">
       <c r="A338" t="s" s="1">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B338" t="s" s="1">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C338" t="s" s="1">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="D338" t="s" s="1">
         <v>33</v>
@@ -21446,13 +21449,13 @@
     </row>
     <row r="339">
       <c r="A339" t="s" s="1">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B339" t="s" s="1">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C339" t="s" s="1">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="D339" t="s" s="1">
         <v>33</v>
@@ -21502,19 +21505,19 @@
     </row>
     <row r="340">
       <c r="A340" t="s">
+        <v>702</v>
+      </c>
+      <c r="B340" t="s">
         <v>701</v>
       </c>
-      <c r="B340" t="s">
-        <v>700</v>
-      </c>
       <c r="C340" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="D340" t="s">
         <v>33</v>
       </c>
       <c r="E340" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="F340" t="s">
         <v>211</v>
@@ -21526,7 +21529,7 @@
         <v>510</v>
       </c>
       <c r="I340" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="J340" t="s">
         <v>474</v>
@@ -21538,7 +21541,7 @@
         <v>34</v>
       </c>
       <c r="M340" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="N340" t="s">
         <v>47</v>
@@ -21547,7 +21550,7 @@
         <v>48</v>
       </c>
       <c r="P340" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="Q340" t="s">
         <v>47</v>
@@ -21558,7 +21561,7 @@
     </row>
     <row r="341">
       <c r="A341" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B341" t="s">
         <v>34</v>
@@ -21570,7 +21573,7 @@
         <v>34</v>
       </c>
       <c r="E341" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="F341" t="s">
         <v>211</v>
@@ -21579,10 +21582,10 @@
         <v>41</v>
       </c>
       <c r="H341" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="I341" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="J341" t="s">
         <v>461</v>
@@ -21594,7 +21597,7 @@
         <v>34</v>
       </c>
       <c r="M341" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="N341" t="s">
         <v>47</v>
@@ -21603,7 +21606,7 @@
         <v>48</v>
       </c>
       <c r="P341" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="Q341" t="s">
         <v>47</v>
@@ -21614,7 +21617,7 @@
     </row>
     <row r="342">
       <c r="A342" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B342" t="s">
         <v>34</v>
@@ -21626,7 +21629,7 @@
         <v>34</v>
       </c>
       <c r="E342" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="F342" t="s">
         <v>211</v>
@@ -21635,10 +21638,10 @@
         <v>41</v>
       </c>
       <c r="H342" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I342" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J342" t="s">
         <v>474</v>
@@ -21650,7 +21653,7 @@
         <v>34</v>
       </c>
       <c r="M342" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="N342" t="s">
         <v>47</v>
@@ -21659,7 +21662,7 @@
         <v>48</v>
       </c>
       <c r="P342" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="Q342" t="s">
         <v>47</v>
@@ -21670,7 +21673,7 @@
     </row>
     <row r="343">
       <c r="A343" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B343" t="s">
         <v>34</v>
@@ -21682,7 +21685,7 @@
         <v>34</v>
       </c>
       <c r="E343" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F343" t="s">
         <v>40</v>
@@ -21691,10 +21694,10 @@
         <v>41</v>
       </c>
       <c r="H343" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="I343" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="J343" t="s">
         <v>335</v>
@@ -21703,10 +21706,10 @@
         <v>45</v>
       </c>
       <c r="L343" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="M343" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="N343" t="s">
         <v>47</v>
@@ -21715,7 +21718,7 @@
         <v>48</v>
       </c>
       <c r="P343" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="Q343" t="s">
         <v>47</v>
@@ -21726,7 +21729,7 @@
     </row>
     <row r="344">
       <c r="A344" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B344" t="s">
         <v>34</v>
@@ -21738,7 +21741,7 @@
         <v>34</v>
       </c>
       <c r="E344" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F344" t="s">
         <v>40</v>
@@ -21750,7 +21753,7 @@
         <v>457</v>
       </c>
       <c r="I344" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="J344" t="s">
         <v>335</v>
@@ -21759,10 +21762,10 @@
         <v>45</v>
       </c>
       <c r="L344" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="M344" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="N344" t="s">
         <v>47</v>
@@ -21771,7 +21774,7 @@
         <v>48</v>
       </c>
       <c r="P344" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="Q344" t="s">
         <v>47</v>
@@ -21782,7 +21785,7 @@
     </row>
     <row r="345">
       <c r="A345" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B345" t="s">
         <v>34</v>
@@ -21806,7 +21809,7 @@
         <v>513</v>
       </c>
       <c r="I345" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="J345" t="s">
         <v>70</v>
@@ -21815,10 +21818,10 @@
         <v>45</v>
       </c>
       <c r="L345" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="M345" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="N345" t="s">
         <v>47</v>
@@ -21827,7 +21830,7 @@
         <v>48</v>
       </c>
       <c r="P345" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="Q345" t="s">
         <v>47</v>
@@ -21838,7 +21841,7 @@
     </row>
     <row r="346">
       <c r="A346" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B346" t="s">
         <v>34</v>
@@ -21850,7 +21853,7 @@
         <v>34</v>
       </c>
       <c r="E346" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F346" t="s">
         <v>211</v>
@@ -21859,10 +21862,10 @@
         <v>41</v>
       </c>
       <c r="H346" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="I346" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="J346" t="s">
         <v>474</v>
@@ -21874,7 +21877,7 @@
         <v>34</v>
       </c>
       <c r="M346" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="N346" t="s">
         <v>47</v>
@@ -21883,7 +21886,7 @@
         <v>48</v>
       </c>
       <c r="P346" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="Q346" t="s">
         <v>47</v>
@@ -21894,7 +21897,7 @@
     </row>
     <row r="347">
       <c r="A347" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B347" t="s">
         <v>34</v>
@@ -21906,7 +21909,7 @@
         <v>34</v>
       </c>
       <c r="E347" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F347" t="s">
         <v>40</v>
@@ -21915,22 +21918,22 @@
         <v>41</v>
       </c>
       <c r="H347" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="I347" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="J347" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="K347" t="s">
         <v>45</v>
       </c>
       <c r="L347" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="M347" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="N347" t="s">
         <v>47</v>
@@ -21939,7 +21942,7 @@
         <v>48</v>
       </c>
       <c r="P347" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="Q347" t="s">
         <v>47</v>
@@ -21950,7 +21953,7 @@
     </row>
     <row r="348">
       <c r="A348" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B348" t="s">
         <v>34</v>
@@ -21962,7 +21965,7 @@
         <v>34</v>
       </c>
       <c r="E348" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="F348" t="s">
         <v>211</v>
@@ -21974,7 +21977,7 @@
         <v>215</v>
       </c>
       <c r="I348" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="J348" t="s">
         <v>474</v>
@@ -21983,10 +21986,10 @@
         <v>80</v>
       </c>
       <c r="L348" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="M348" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="N348" t="s">
         <v>47</v>
@@ -21995,7 +21998,7 @@
         <v>48</v>
       </c>
       <c r="P348" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="Q348" t="s">
         <v>47</v>
@@ -22006,7 +22009,7 @@
     </row>
     <row r="349">
       <c r="A349" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B349" t="s">
         <v>34</v>
@@ -22039,10 +22042,10 @@
         <v>45</v>
       </c>
       <c r="L349" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="M349" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="N349" t="s">
         <v>47</v>
@@ -22062,7 +22065,7 @@
     </row>
     <row r="350">
       <c r="A350" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B350" t="s">
         <v>34</v>
@@ -22074,7 +22077,7 @@
         <v>34</v>
       </c>
       <c r="E350" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F350" t="s">
         <v>40</v>
@@ -22083,22 +22086,22 @@
         <v>41</v>
       </c>
       <c r="H350" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="I350" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="J350" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="K350" t="s">
         <v>45</v>
       </c>
       <c r="L350" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="M350" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="N350" t="s">
         <v>47</v>
@@ -22107,7 +22110,7 @@
         <v>48</v>
       </c>
       <c r="P350" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="Q350" t="s">
         <v>47</v>
@@ -22118,7 +22121,7 @@
     </row>
     <row r="351">
       <c r="A351" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B351" t="s">
         <v>34</v>
@@ -22139,7 +22142,7 @@
         <v>41</v>
       </c>
       <c r="H351" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="I351" t="s">
         <v>155</v>
@@ -22151,10 +22154,10 @@
         <v>122</v>
       </c>
       <c r="L351" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="M351" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="N351" t="s">
         <v>47</v>
@@ -22174,7 +22177,7 @@
     </row>
     <row r="352">
       <c r="A352" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B352" t="s">
         <v>34</v>
@@ -22186,7 +22189,7 @@
         <v>34</v>
       </c>
       <c r="E352" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F352" t="s">
         <v>40</v>
@@ -22195,22 +22198,22 @@
         <v>41</v>
       </c>
       <c r="H352" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="I352" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="J352" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="K352" t="s">
         <v>45</v>
       </c>
       <c r="L352" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="M352" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="N352" t="s">
         <v>47</v>
@@ -22219,7 +22222,7 @@
         <v>48</v>
       </c>
       <c r="P352" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="Q352" t="s">
         <v>47</v>
@@ -22230,7 +22233,7 @@
     </row>
     <row r="353">
       <c r="A353" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B353" t="s">
         <v>34</v>
@@ -22242,7 +22245,7 @@
         <v>34</v>
       </c>
       <c r="E353" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F353" t="s">
         <v>40</v>
@@ -22251,22 +22254,22 @@
         <v>41</v>
       </c>
       <c r="H353" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="I353" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="J353" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="K353" t="s">
         <v>45</v>
       </c>
       <c r="L353" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="M353" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="N353" t="s">
         <v>47</v>
@@ -22275,7 +22278,7 @@
         <v>48</v>
       </c>
       <c r="P353" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="Q353" t="s">
         <v>47</v>
@@ -22286,7 +22289,7 @@
     </row>
     <row r="354">
       <c r="A354" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B354" t="s">
         <v>34</v>
@@ -22298,7 +22301,7 @@
         <v>34</v>
       </c>
       <c r="E354" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F354" t="s">
         <v>40</v>
@@ -22307,22 +22310,22 @@
         <v>41</v>
       </c>
       <c r="H354" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="I354" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="J354" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="K354" t="s">
         <v>45</v>
       </c>
       <c r="L354" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="M354" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="N354" t="s">
         <v>47</v>
@@ -22331,7 +22334,7 @@
         <v>48</v>
       </c>
       <c r="P354" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="Q354" t="s">
         <v>47</v>
@@ -22342,7 +22345,7 @@
     </row>
     <row r="355">
       <c r="A355" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B355" t="s">
         <v>34</v>
@@ -22354,7 +22357,7 @@
         <v>34</v>
       </c>
       <c r="E355" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F355" t="s">
         <v>40</v>
@@ -22363,22 +22366,22 @@
         <v>41</v>
       </c>
       <c r="H355" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="I355" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="J355" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="K355" t="s">
         <v>45</v>
       </c>
       <c r="L355" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="M355" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="N355" t="s">
         <v>47</v>
@@ -22387,7 +22390,7 @@
         <v>48</v>
       </c>
       <c r="P355" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="Q355" t="s">
         <v>47</v>
@@ -22398,7 +22401,7 @@
     </row>
     <row r="356">
       <c r="A356" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B356" t="s">
         <v>34</v>
@@ -22410,7 +22413,7 @@
         <v>34</v>
       </c>
       <c r="E356" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="F356" t="s">
         <v>211</v>
@@ -22422,7 +22425,7 @@
         <v>425</v>
       </c>
       <c r="I356" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="J356" t="s">
         <v>474</v>
@@ -22434,7 +22437,7 @@
         <v>34</v>
       </c>
       <c r="M356" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="N356" t="s">
         <v>47</v>
@@ -22443,7 +22446,7 @@
         <v>48</v>
       </c>
       <c r="P356" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="Q356" t="s">
         <v>47</v>
@@ -22454,13 +22457,13 @@
     </row>
     <row r="357">
       <c r="A357" t="s" s="1">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B357" t="s" s="1">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C357" t="s" s="1">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D357" t="s" s="1">
         <v>33</v>
@@ -22510,13 +22513,13 @@
     </row>
     <row r="358">
       <c r="A358" t="s">
+        <v>742</v>
+      </c>
+      <c r="B358" t="s">
         <v>741</v>
       </c>
-      <c r="B358" t="s">
-        <v>740</v>
-      </c>
       <c r="C358" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D358" t="s">
         <v>33</v>
@@ -22543,10 +22546,10 @@
         <v>191</v>
       </c>
       <c r="L358" t="s">
+        <v>743</v>
+      </c>
+      <c r="M358" t="s">
         <v>742</v>
-      </c>
-      <c r="M358" t="s">
-        <v>741</v>
       </c>
       <c r="N358" t="s">
         <v>47</v>
@@ -22566,13 +22569,13 @@
     </row>
     <row r="359">
       <c r="A359" t="s" s="1">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B359" t="s" s="1">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C359" t="s" s="1">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="D359" t="s" s="1">
         <v>33</v>
@@ -22622,13 +22625,13 @@
     </row>
     <row r="360">
       <c r="A360" t="s">
+        <v>746</v>
+      </c>
+      <c r="B360" t="s">
         <v>745</v>
       </c>
-      <c r="B360" t="s">
-        <v>744</v>
-      </c>
       <c r="C360" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="D360" t="s">
         <v>33</v>
@@ -22655,10 +22658,10 @@
         <v>191</v>
       </c>
       <c r="L360" t="s">
+        <v>747</v>
+      </c>
+      <c r="M360" t="s">
         <v>746</v>
-      </c>
-      <c r="M360" t="s">
-        <v>745</v>
       </c>
       <c r="N360" t="s">
         <v>47</v>
@@ -22678,13 +22681,13 @@
     </row>
     <row r="361">
       <c r="A361" t="s" s="1">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B361" t="s" s="1">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C361" t="s" s="1">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="D361" t="s" s="1">
         <v>33</v>
@@ -22734,13 +22737,13 @@
     </row>
     <row r="362">
       <c r="A362" t="s">
+        <v>750</v>
+      </c>
+      <c r="B362" t="s">
         <v>749</v>
       </c>
-      <c r="B362" t="s">
-        <v>748</v>
-      </c>
       <c r="C362" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="D362" t="s">
         <v>33</v>
@@ -22755,10 +22758,10 @@
         <v>41</v>
       </c>
       <c r="H362" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="I362" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="J362" t="s">
         <v>190</v>
@@ -22767,10 +22770,10 @@
         <v>191</v>
       </c>
       <c r="L362" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="M362" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="N362" t="s">
         <v>47</v>
@@ -22779,7 +22782,7 @@
         <v>48</v>
       </c>
       <c r="P362" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="Q362" t="s">
         <v>47</v>
@@ -22790,13 +22793,13 @@
     </row>
     <row r="363">
       <c r="A363" t="s" s="1">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B363" t="s" s="1">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C363" t="s" s="1">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="D363" t="s" s="1">
         <v>33</v>
@@ -22846,13 +22849,13 @@
     </row>
     <row r="364">
       <c r="A364" t="s">
+        <v>756</v>
+      </c>
+      <c r="B364" t="s">
         <v>755</v>
       </c>
-      <c r="B364" t="s">
-        <v>754</v>
-      </c>
       <c r="C364" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="D364" t="s">
         <v>33</v>
@@ -22861,7 +22864,7 @@
         <v>187</v>
       </c>
       <c r="F364" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G364" t="s">
         <v>41</v>
@@ -22870,7 +22873,7 @@
         <v>215</v>
       </c>
       <c r="I364" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="J364" t="s">
         <v>190</v>
@@ -22882,7 +22885,7 @@
         <v>34</v>
       </c>
       <c r="M364" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="N364" t="s">
         <v>47</v>
@@ -22902,13 +22905,13 @@
     </row>
     <row r="365">
       <c r="A365" t="s" s="1">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B365" t="s" s="1">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C365" t="s" s="1">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D365" t="s" s="1">
         <v>33</v>
@@ -22958,13 +22961,13 @@
     </row>
     <row r="366">
       <c r="A366" t="s" s="1">
+        <v>760</v>
+      </c>
+      <c r="B366" t="s" s="1">
         <v>759</v>
       </c>
-      <c r="B366" t="s" s="1">
-        <v>758</v>
-      </c>
       <c r="C366" t="s" s="1">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D366" t="s" s="1">
         <v>33</v>
@@ -23014,19 +23017,19 @@
     </row>
     <row r="367">
       <c r="A367" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B367" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C367" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D367" t="s">
         <v>33</v>
       </c>
       <c r="E367" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="F367" t="s">
         <v>211</v>
@@ -23035,22 +23038,22 @@
         <v>41</v>
       </c>
       <c r="H367" t="s">
-        <v>425</v>
+        <v>469</v>
       </c>
       <c r="I367" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="J367" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="K367" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="L367" t="s">
         <v>34</v>
       </c>
       <c r="M367" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="N367" t="s">
         <v>47</v>
@@ -23059,7 +23062,7 @@
         <v>48</v>
       </c>
       <c r="P367" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="Q367" t="s">
         <v>47</v>
@@ -23070,7 +23073,7 @@
     </row>
     <row r="368">
       <c r="A368" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B368" t="s">
         <v>34</v>
@@ -23082,7 +23085,7 @@
         <v>34</v>
       </c>
       <c r="E368" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="F368" t="s">
         <v>211</v>
@@ -23091,22 +23094,22 @@
         <v>41</v>
       </c>
       <c r="H368" t="s">
-        <v>469</v>
+        <v>425</v>
       </c>
       <c r="I368" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="J368" t="s">
-        <v>101</v>
+        <v>178</v>
       </c>
       <c r="K368" t="s">
-        <v>101</v>
+        <v>178</v>
       </c>
       <c r="L368" t="s">
         <v>34</v>
       </c>
       <c r="M368" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="N368" t="s">
         <v>47</v>
@@ -23115,7 +23118,7 @@
         <v>48</v>
       </c>
       <c r="P368" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="Q368" t="s">
         <v>47</v>
@@ -23126,13 +23129,13 @@
     </row>
     <row r="369">
       <c r="A369" t="s" s="1">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B369" t="s" s="1">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C369" t="s" s="1">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="D369" t="s" s="1">
         <v>33</v>
@@ -23182,13 +23185,13 @@
     </row>
     <row r="370">
       <c r="A370" t="s" s="1">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B370" t="s" s="1">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C370" t="s" s="1">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D370" t="s" s="1">
         <v>33</v>
@@ -23238,19 +23241,19 @@
     </row>
     <row r="371">
       <c r="A371" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B371" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C371" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="D371" t="s">
         <v>33</v>
       </c>
       <c r="E371" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="F371" t="s">
         <v>40</v>
@@ -23259,22 +23262,22 @@
         <v>41</v>
       </c>
       <c r="H371" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="I371" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="J371" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="K371" t="s">
         <v>229</v>
       </c>
       <c r="L371" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="M371" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="N371" t="s">
         <v>47</v>
@@ -23283,7 +23286,7 @@
         <v>48</v>
       </c>
       <c r="P371" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="Q371" t="s">
         <v>47</v>
@@ -23294,19 +23297,19 @@
     </row>
     <row r="372">
       <c r="A372" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B372" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C372" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="D372" t="s">
         <v>33</v>
       </c>
       <c r="E372" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="F372" t="s">
         <v>211</v>
@@ -23318,7 +23321,7 @@
         <v>172</v>
       </c>
       <c r="I372" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="J372" t="s">
         <v>169</v>
@@ -23330,7 +23333,7 @@
         <v>34</v>
       </c>
       <c r="M372" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="N372" t="s">
         <v>47</v>
@@ -23339,7 +23342,7 @@
         <v>48</v>
       </c>
       <c r="P372" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="Q372" t="s">
         <v>47</v>
@@ -23350,13 +23353,13 @@
     </row>
     <row r="373">
       <c r="A373" t="s" s="1">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B373" t="s" s="1">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C373" t="s" s="1">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="D373" t="s" s="1">
         <v>33</v>
@@ -23406,19 +23409,19 @@
     </row>
     <row r="374">
       <c r="A374" t="s">
+        <v>781</v>
+      </c>
+      <c r="B374" t="s">
         <v>780</v>
       </c>
-      <c r="B374" t="s">
-        <v>779</v>
-      </c>
       <c r="C374" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="D374" t="s">
         <v>33</v>
       </c>
       <c r="E374" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F374" t="s">
         <v>40</v>
@@ -23427,22 +23430,22 @@
         <v>41</v>
       </c>
       <c r="H374" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="I374" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="J374" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="K374" t="s">
         <v>70</v>
       </c>
       <c r="L374" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="M374" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="N374" t="s">
         <v>47</v>
@@ -23451,7 +23454,7 @@
         <v>48</v>
       </c>
       <c r="P374" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="Q374" t="s">
         <v>47</v>
@@ -23462,13 +23465,13 @@
     </row>
     <row r="375">
       <c r="A375" t="s" s="1">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B375" t="s" s="1">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C375" t="s" s="1">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="D375" t="s" s="1">
         <v>33</v>
@@ -23518,19 +23521,19 @@
     </row>
     <row r="376">
       <c r="A376" t="s">
+        <v>789</v>
+      </c>
+      <c r="B376" t="s">
         <v>788</v>
       </c>
-      <c r="B376" t="s">
-        <v>787</v>
-      </c>
       <c r="C376" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="D376" t="s">
         <v>33</v>
       </c>
       <c r="E376" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F376" t="s">
         <v>40</v>
@@ -23539,22 +23542,22 @@
         <v>41</v>
       </c>
       <c r="H376" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="I376" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="J376" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="K376" t="s">
         <v>45</v>
       </c>
       <c r="L376" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="M376" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="N376" t="s">
         <v>47</v>
@@ -23563,7 +23566,7 @@
         <v>48</v>
       </c>
       <c r="P376" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="Q376" t="s">
         <v>47</v>
@@ -23574,13 +23577,13 @@
     </row>
     <row r="377">
       <c r="A377" t="s" s="1">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B377" t="s" s="1">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C377" t="s" s="1">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D377" t="s" s="1">
         <v>33</v>
@@ -23630,19 +23633,19 @@
     </row>
     <row r="378">
       <c r="A378" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B378" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C378" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="D378" t="s">
         <v>33</v>
       </c>
       <c r="E378" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F378" t="s">
         <v>40</v>
@@ -23651,22 +23654,22 @@
         <v>41</v>
       </c>
       <c r="H378" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="I378" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="J378" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="K378" t="s">
         <v>134</v>
       </c>
       <c r="L378" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="M378" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="N378" t="s">
         <v>47</v>
@@ -23675,7 +23678,7 @@
         <v>48</v>
       </c>
       <c r="P378" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="Q378" t="s">
         <v>47</v>
@@ -23686,19 +23689,19 @@
     </row>
     <row r="379">
       <c r="A379" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B379" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C379" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="D379" t="s">
         <v>33</v>
       </c>
       <c r="E379" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F379" t="s">
         <v>40</v>
@@ -23707,22 +23710,22 @@
         <v>41</v>
       </c>
       <c r="H379" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="I379" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="J379" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="K379" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="L379" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="M379" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="N379" t="s">
         <v>47</v>
@@ -23731,7 +23734,7 @@
         <v>48</v>
       </c>
       <c r="P379" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="Q379" t="s">
         <v>47</v>
@@ -23742,13 +23745,13 @@
     </row>
     <row r="380">
       <c r="A380" t="s" s="1">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B380" t="s" s="1">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C380" t="s" s="1">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D380" t="s" s="1">
         <v>33</v>
@@ -23798,19 +23801,19 @@
     </row>
     <row r="381">
       <c r="A381" t="s">
+        <v>808</v>
+      </c>
+      <c r="B381" t="s">
         <v>807</v>
       </c>
-      <c r="B381" t="s">
-        <v>806</v>
-      </c>
       <c r="C381" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D381" t="s">
         <v>33</v>
       </c>
       <c r="E381" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="F381" t="s">
         <v>211</v>
@@ -23822,7 +23825,7 @@
         <v>425</v>
       </c>
       <c r="I381" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="J381" t="s">
         <v>90</v>
@@ -23834,7 +23837,7 @@
         <v>34</v>
       </c>
       <c r="M381" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="N381" t="s">
         <v>47</v>
@@ -23843,7 +23846,7 @@
         <v>48</v>
       </c>
       <c r="P381" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="Q381" t="s">
         <v>47</v>
@@ -23854,7 +23857,7 @@
     </row>
     <row r="382">
       <c r="A382" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B382" t="s">
         <v>34</v>
@@ -23866,7 +23869,7 @@
         <v>34</v>
       </c>
       <c r="E382" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="F382" t="s">
         <v>211</v>
@@ -23875,22 +23878,22 @@
         <v>41</v>
       </c>
       <c r="H382" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="I382" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="J382" t="s">
         <v>304</v>
       </c>
       <c r="K382" t="s">
-        <v>122</v>
+        <v>75</v>
       </c>
       <c r="L382" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="M382" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="N382" t="s">
         <v>47</v>
@@ -23899,7 +23902,7 @@
         <v>48</v>
       </c>
       <c r="P382" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="Q382" t="s">
         <v>47</v>
@@ -23910,7 +23913,7 @@
     </row>
     <row r="383">
       <c r="A383" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B383" t="s">
         <v>34</v>
@@ -23922,7 +23925,7 @@
         <v>34</v>
       </c>
       <c r="E383" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="F383" t="s">
         <v>211</v>
@@ -23931,22 +23934,22 @@
         <v>41</v>
       </c>
       <c r="H383" t="s">
-        <v>815</v>
+        <v>425</v>
       </c>
       <c r="I383" t="s">
         <v>816</v>
       </c>
       <c r="J383" t="s">
-        <v>304</v>
+        <v>58</v>
       </c>
       <c r="K383" t="s">
-        <v>96</v>
+        <v>202</v>
       </c>
       <c r="L383" t="s">
         <v>817</v>
       </c>
       <c r="M383" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="N383" t="s">
         <v>47</v>
@@ -23966,7 +23969,7 @@
     </row>
     <row r="384">
       <c r="A384" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B384" t="s">
         <v>34</v>
@@ -24002,7 +24005,7 @@
         <v>821</v>
       </c>
       <c r="M384" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="N384" t="s">
         <v>47</v>
@@ -24022,7 +24025,7 @@
     </row>
     <row r="385">
       <c r="A385" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B385" t="s">
         <v>34</v>
@@ -24058,7 +24061,7 @@
         <v>825</v>
       </c>
       <c r="M385" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="N385" t="s">
         <v>47</v>
@@ -24078,7 +24081,7 @@
     </row>
     <row r="386">
       <c r="A386" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B386" t="s">
         <v>34</v>
@@ -24099,10 +24102,10 @@
         <v>41</v>
       </c>
       <c r="H386" t="s">
-        <v>425</v>
+        <v>827</v>
       </c>
       <c r="I386" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="J386" t="s">
         <v>58</v>
@@ -24111,10 +24114,10 @@
         <v>202</v>
       </c>
       <c r="L386" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="M386" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="N386" t="s">
         <v>47</v>
@@ -24123,7 +24126,7 @@
         <v>48</v>
       </c>
       <c r="P386" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="Q386" t="s">
         <v>47</v>
@@ -24134,7 +24137,7 @@
     </row>
     <row r="387">
       <c r="A387" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B387" t="s">
         <v>34</v>
@@ -24146,7 +24149,7 @@
         <v>34</v>
       </c>
       <c r="E387" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="F387" t="s">
         <v>211</v>
@@ -24155,22 +24158,22 @@
         <v>41</v>
       </c>
       <c r="H387" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="I387" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="J387" t="s">
         <v>304</v>
       </c>
       <c r="K387" t="s">
-        <v>75</v>
+        <v>122</v>
       </c>
       <c r="L387" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="M387" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="N387" t="s">
         <v>47</v>
@@ -24179,7 +24182,7 @@
         <v>48</v>
       </c>
       <c r="P387" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="Q387" t="s">
         <v>47</v>
@@ -24190,7 +24193,7 @@
     </row>
     <row r="388">
       <c r="A388" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B388" t="s">
         <v>34</v>
@@ -24202,7 +24205,7 @@
         <v>34</v>
       </c>
       <c r="E388" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="F388" t="s">
         <v>211</v>
@@ -24211,22 +24214,22 @@
         <v>41</v>
       </c>
       <c r="H388" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="I388" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="J388" t="s">
-        <v>58</v>
+        <v>304</v>
       </c>
       <c r="K388" t="s">
-        <v>202</v>
+        <v>96</v>
       </c>
       <c r="L388" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="M388" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="N388" t="s">
         <v>47</v>
@@ -24235,7 +24238,7 @@
         <v>48</v>
       </c>
       <c r="P388" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="Q388" t="s">
         <v>47</v>
@@ -24246,13 +24249,13 @@
     </row>
     <row r="389">
       <c r="A389" t="s" s="1">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B389" t="s" s="1">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="C389" t="s" s="1">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D389" t="s" s="1">
         <v>33</v>
@@ -24302,19 +24305,19 @@
     </row>
     <row r="390">
       <c r="A390" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B390" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C390" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="D390" t="s">
         <v>33</v>
       </c>
       <c r="E390" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F390" t="s">
         <v>40</v>
@@ -24323,22 +24326,22 @@
         <v>41</v>
       </c>
       <c r="H390" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="I390" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="J390" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="K390" t="s">
         <v>45</v>
       </c>
       <c r="L390" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="M390" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="N390" t="s">
         <v>47</v>
@@ -24347,7 +24350,7 @@
         <v>48</v>
       </c>
       <c r="P390" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="Q390" t="s">
         <v>47</v>
@@ -24358,19 +24361,19 @@
     </row>
     <row r="391">
       <c r="A391" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B391" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C391" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D391" t="s">
         <v>33</v>
       </c>
       <c r="E391" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F391" t="s">
         <v>40</v>
@@ -24379,22 +24382,22 @@
         <v>41</v>
       </c>
       <c r="H391" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="I391" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="J391" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="K391" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L391" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="M391" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="N391" t="s">
         <v>47</v>
@@ -24403,7 +24406,7 @@
         <v>48</v>
       </c>
       <c r="P391" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="Q391" t="s">
         <v>47</v>
@@ -24414,19 +24417,19 @@
     </row>
     <row r="392">
       <c r="A392" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B392" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C392" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="D392" t="s">
         <v>33</v>
       </c>
       <c r="E392" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="F392" t="s">
         <v>40</v>
@@ -24435,10 +24438,10 @@
         <v>41</v>
       </c>
       <c r="H392" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="I392" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="J392" t="s">
         <v>44</v>
@@ -24447,10 +24450,10 @@
         <v>45</v>
       </c>
       <c r="L392" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="M392" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="N392" t="s">
         <v>47</v>
@@ -24459,7 +24462,7 @@
         <v>48</v>
       </c>
       <c r="P392" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="Q392" t="s">
         <v>47</v>
@@ -24470,13 +24473,13 @@
     </row>
     <row r="393">
       <c r="A393" t="s" s="1">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B393" t="s" s="1">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="C393" t="s" s="1">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="D393" t="s" s="1">
         <v>33</v>
@@ -24526,22 +24529,22 @@
     </row>
     <row r="394">
       <c r="A394" t="s">
+        <v>858</v>
+      </c>
+      <c r="B394" t="s">
         <v>857</v>
       </c>
-      <c r="B394" t="s">
-        <v>856</v>
-      </c>
       <c r="C394" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="D394" t="s">
         <v>33</v>
       </c>
       <c r="E394" t="s">
-        <v>858</v>
+        <v>673</v>
       </c>
       <c r="F394" t="s">
-        <v>211</v>
+        <v>40</v>
       </c>
       <c r="G394" t="s">
         <v>41</v>
@@ -24553,16 +24556,16 @@
         <v>860</v>
       </c>
       <c r="J394" t="s">
-        <v>304</v>
+        <v>335</v>
       </c>
       <c r="K394" t="s">
-        <v>122</v>
+        <v>45</v>
       </c>
       <c r="L394" t="s">
-        <v>34</v>
+        <v>861</v>
       </c>
       <c r="M394" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="N394" t="s">
         <v>47</v>
@@ -24582,7 +24585,7 @@
     </row>
     <row r="395">
       <c r="A395" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B395" t="s">
         <v>34</v>
@@ -24594,31 +24597,31 @@
         <v>34</v>
       </c>
       <c r="E395" t="s">
-        <v>672</v>
+        <v>862</v>
       </c>
       <c r="F395" t="s">
-        <v>40</v>
+        <v>211</v>
       </c>
       <c r="G395" t="s">
         <v>41</v>
       </c>
       <c r="H395" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="I395" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="J395" t="s">
-        <v>335</v>
+        <v>304</v>
       </c>
       <c r="K395" t="s">
-        <v>45</v>
+        <v>122</v>
       </c>
       <c r="L395" t="s">
-        <v>863</v>
+        <v>34</v>
       </c>
       <c r="M395" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="N395" t="s">
         <v>47</v>
@@ -24627,7 +24630,7 @@
         <v>48</v>
       </c>
       <c r="P395" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="Q395" t="s">
         <v>47</v>
@@ -24638,7 +24641,7 @@
     </row>
     <row r="396">
       <c r="A396" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B396" t="s">
         <v>34</v>
@@ -24650,7 +24653,7 @@
         <v>34</v>
       </c>
       <c r="E396" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="F396" t="s">
         <v>40</v>
@@ -24659,22 +24662,22 @@
         <v>41</v>
       </c>
       <c r="H396" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="I396" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="J396" t="s">
         <v>335</v>
       </c>
       <c r="K396" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="L396" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="M396" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="N396" t="s">
         <v>47</v>
@@ -24683,7 +24686,7 @@
         <v>48</v>
       </c>
       <c r="P396" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="Q396" t="s">
         <v>47</v>
@@ -24694,7 +24697,7 @@
     </row>
     <row r="397">
       <c r="A397" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B397" t="s">
         <v>34</v>
@@ -24706,7 +24709,7 @@
         <v>34</v>
       </c>
       <c r="E397" t="s">
-        <v>868</v>
+        <v>673</v>
       </c>
       <c r="F397" t="s">
         <v>40</v>
@@ -24715,22 +24718,22 @@
         <v>41</v>
       </c>
       <c r="H397" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="I397" t="s">
         <v>869</v>
       </c>
       <c r="J397" t="s">
-        <v>101</v>
+        <v>335</v>
       </c>
       <c r="K397" t="s">
-        <v>45</v>
+        <v>867</v>
       </c>
       <c r="L397" t="s">
         <v>870</v>
       </c>
       <c r="M397" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="N397" t="s">
         <v>47</v>
@@ -24750,7 +24753,7 @@
     </row>
     <row r="398">
       <c r="A398" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B398" t="s">
         <v>34</v>
@@ -24762,7 +24765,7 @@
         <v>34</v>
       </c>
       <c r="E398" t="s">
-        <v>672</v>
+        <v>871</v>
       </c>
       <c r="F398" t="s">
         <v>40</v>
@@ -24771,22 +24774,22 @@
         <v>41</v>
       </c>
       <c r="H398" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="I398" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="J398" t="s">
-        <v>335</v>
+        <v>101</v>
       </c>
       <c r="K398" t="s">
-        <v>866</v>
+        <v>45</v>
       </c>
       <c r="L398" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="M398" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="N398" t="s">
         <v>47</v>
@@ -24795,7 +24798,7 @@
         <v>48</v>
       </c>
       <c r="P398" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="Q398" t="s">
         <v>47</v>
@@ -24806,13 +24809,13 @@
     </row>
     <row r="399">
       <c r="A399" t="s" s="1">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B399" t="s" s="1">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C399" t="s" s="1">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="D399" t="s" s="1">
         <v>33</v>
@@ -24862,19 +24865,19 @@
     </row>
     <row r="400">
       <c r="A400" t="s">
+        <v>876</v>
+      </c>
+      <c r="B400" t="s">
         <v>875</v>
       </c>
-      <c r="B400" t="s">
-        <v>874</v>
-      </c>
       <c r="C400" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="D400" t="s">
         <v>33</v>
       </c>
       <c r="E400" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="F400" t="s">
         <v>211</v>
@@ -24883,22 +24886,22 @@
         <v>41</v>
       </c>
       <c r="H400" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="I400" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="J400" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="K400" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L400" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="M400" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="N400" t="s">
         <v>47</v>
@@ -24907,7 +24910,7 @@
         <v>48</v>
       </c>
       <c r="P400" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="Q400" t="s">
         <v>47</v>
@@ -24918,13 +24921,13 @@
     </row>
     <row r="401">
       <c r="A401" t="s" s="1">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B401" t="s" s="1">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C401" t="s" s="1">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="D401" t="s" s="1">
         <v>33</v>
@@ -24974,19 +24977,19 @@
     </row>
     <row r="402">
       <c r="A402" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B402" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C402" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="D402" t="s">
         <v>33</v>
       </c>
       <c r="E402" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F402" t="s">
         <v>40</v>
@@ -24995,22 +24998,22 @@
         <v>41</v>
       </c>
       <c r="H402" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="I402" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="J402" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="K402" t="s">
         <v>45</v>
       </c>
       <c r="L402" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="M402" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="N402" t="s">
         <v>47</v>
@@ -25019,7 +25022,7 @@
         <v>48</v>
       </c>
       <c r="P402" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="Q402" t="s">
         <v>47</v>
@@ -25030,7 +25033,7 @@
     </row>
     <row r="403">
       <c r="A403" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B403" t="s">
         <v>34</v>
@@ -25042,7 +25045,7 @@
         <v>34</v>
       </c>
       <c r="E403" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="F403" t="s">
         <v>211</v>
@@ -25051,10 +25054,10 @@
         <v>41</v>
       </c>
       <c r="H403" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="I403" t="s">
-        <v>827</v>
+        <v>816</v>
       </c>
       <c r="J403" t="s">
         <v>58</v>
@@ -25063,10 +25066,10 @@
         <v>202</v>
       </c>
       <c r="L403" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="M403" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="N403" t="s">
         <v>47</v>
@@ -25075,7 +25078,7 @@
         <v>48</v>
       </c>
       <c r="P403" t="s">
-        <v>827</v>
+        <v>816</v>
       </c>
       <c r="Q403" t="s">
         <v>47</v>
@@ -25086,19 +25089,19 @@
     </row>
     <row r="404">
       <c r="A404" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B404" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C404" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="D404" t="s">
         <v>33</v>
       </c>
       <c r="E404" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="F404" t="s">
         <v>211</v>
@@ -25107,10 +25110,10 @@
         <v>41</v>
       </c>
       <c r="H404" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="I404" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="J404" t="s">
         <v>85</v>
@@ -25119,10 +25122,10 @@
         <v>202</v>
       </c>
       <c r="L404" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="M404" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="N404" t="s">
         <v>47</v>
@@ -25131,7 +25134,7 @@
         <v>48</v>
       </c>
       <c r="P404" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="Q404" t="s">
         <v>47</v>
@@ -25142,13 +25145,13 @@
     </row>
     <row r="405">
       <c r="A405" t="s" s="1">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B405" t="s" s="1">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="C405" t="s" s="1">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="D405" t="s" s="1">
         <v>33</v>
@@ -25198,13 +25201,13 @@
     </row>
     <row r="406">
       <c r="A406" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B406" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C406" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="D406" t="s">
         <v>33</v>
@@ -25219,10 +25222,10 @@
         <v>41</v>
       </c>
       <c r="H406" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="I406" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="J406" t="s">
         <v>190</v>
@@ -25231,10 +25234,10 @@
         <v>202</v>
       </c>
       <c r="L406" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="M406" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="N406" t="s">
         <v>47</v>
@@ -25243,7 +25246,7 @@
         <v>48</v>
       </c>
       <c r="P406" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="Q406" t="s">
         <v>47</v>
@@ -25254,19 +25257,19 @@
     </row>
     <row r="407">
       <c r="A407" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B407" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="C407" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="D407" t="s">
         <v>33</v>
       </c>
       <c r="E407" t="s">
-        <v>672</v>
+        <v>771</v>
       </c>
       <c r="F407" t="s">
         <v>40</v>
@@ -25275,22 +25278,22 @@
         <v>41</v>
       </c>
       <c r="H407" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="I407" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="J407" t="s">
-        <v>681</v>
+        <v>178</v>
       </c>
       <c r="K407" t="s">
-        <v>45</v>
+        <v>178</v>
       </c>
       <c r="L407" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="M407" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="N407" t="s">
         <v>47</v>
@@ -25299,7 +25302,7 @@
         <v>48</v>
       </c>
       <c r="P407" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="Q407" t="s">
         <v>47</v>
@@ -25310,7 +25313,7 @@
     </row>
     <row r="408">
       <c r="A408" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B408" t="s">
         <v>34</v>
@@ -25322,7 +25325,7 @@
         <v>34</v>
       </c>
       <c r="E408" t="s">
-        <v>770</v>
+        <v>673</v>
       </c>
       <c r="F408" t="s">
         <v>40</v>
@@ -25331,22 +25334,22 @@
         <v>41</v>
       </c>
       <c r="H408" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="I408" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="J408" t="s">
-        <v>178</v>
+        <v>686</v>
       </c>
       <c r="K408" t="s">
-        <v>178</v>
+        <v>45</v>
       </c>
       <c r="L408" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="M408" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="N408" t="s">
         <v>47</v>
@@ -25355,7 +25358,7 @@
         <v>48</v>
       </c>
       <c r="P408" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="Q408" t="s">
         <v>47</v>
@@ -25366,13 +25369,13 @@
     </row>
     <row r="409">
       <c r="A409" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B409" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="C409" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="D409" t="s">
         <v>33</v>
@@ -25387,10 +25390,10 @@
         <v>41</v>
       </c>
       <c r="H409" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="I409" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="J409" t="s">
         <v>101</v>
@@ -25399,10 +25402,10 @@
         <v>45</v>
       </c>
       <c r="L409" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="M409" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="N409" t="s">
         <v>47</v>
@@ -25411,7 +25414,7 @@
         <v>48</v>
       </c>
       <c r="P409" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="Q409" t="s">
         <v>47</v>
@@ -25422,13 +25425,13 @@
     </row>
     <row r="410">
       <c r="A410" t="s" s="1">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B410" t="s" s="1">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C410" t="s" s="1">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D410" t="s" s="1">
         <v>33</v>
@@ -25478,13 +25481,13 @@
     </row>
     <row r="411">
       <c r="A411" t="s" s="1">
+        <v>918</v>
+      </c>
+      <c r="B411" t="s" s="1">
         <v>917</v>
       </c>
-      <c r="B411" t="s" s="1">
-        <v>916</v>
-      </c>
       <c r="C411" t="s" s="1">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D411" t="s" s="1">
         <v>33</v>
@@ -25534,19 +25537,19 @@
     </row>
     <row r="412">
       <c r="A412" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B412" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C412" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D412" t="s">
         <v>33</v>
       </c>
       <c r="E412" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="F412" t="s">
         <v>40</v>
@@ -25555,22 +25558,22 @@
         <v>41</v>
       </c>
       <c r="H412" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="I412" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="J412" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="K412" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L412" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="M412" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="N412" t="s">
         <v>47</v>
@@ -25579,7 +25582,7 @@
         <v>48</v>
       </c>
       <c r="P412" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="Q412" t="s">
         <v>47</v>
@@ -25590,13 +25593,13 @@
     </row>
     <row r="413">
       <c r="A413" t="s" s="1">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B413" t="s" s="1">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="C413" t="s" s="1">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D413" t="s" s="1">
         <v>33</v>
@@ -25646,13 +25649,13 @@
     </row>
     <row r="414">
       <c r="A414" t="s" s="1">
+        <v>926</v>
+      </c>
+      <c r="B414" t="s" s="1">
         <v>925</v>
       </c>
-      <c r="B414" t="s" s="1">
-        <v>924</v>
-      </c>
       <c r="C414" t="s" s="1">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D414" t="s" s="1">
         <v>33</v>
@@ -25702,13 +25705,13 @@
     </row>
     <row r="415">
       <c r="A415" t="s" s="1">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B415" t="s" s="1">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="C415" t="s" s="1">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D415" t="s" s="1">
         <v>33</v>
@@ -25758,19 +25761,19 @@
     </row>
     <row r="416">
       <c r="A416" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B416" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="C416" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D416" t="s">
         <v>33</v>
       </c>
       <c r="E416" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="F416" t="s">
         <v>211</v>
@@ -25779,10 +25782,10 @@
         <v>41</v>
       </c>
       <c r="H416" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="I416" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="J416" t="s">
         <v>304</v>
@@ -25794,7 +25797,7 @@
         <v>34</v>
       </c>
       <c r="M416" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="N416" t="s">
         <v>47</v>
@@ -25803,7 +25806,7 @@
         <v>48</v>
       </c>
       <c r="P416" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="Q416" t="s">
         <v>47</v>
@@ -25814,13 +25817,13 @@
     </row>
     <row r="417">
       <c r="A417" t="s" s="1">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B417" t="s" s="1">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C417" t="s" s="1">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="D417" t="s" s="1">
         <v>33</v>
@@ -25870,13 +25873,13 @@
     </row>
     <row r="418">
       <c r="A418" t="s" s="1">
+        <v>934</v>
+      </c>
+      <c r="B418" t="s" s="1">
         <v>933</v>
       </c>
-      <c r="B418" t="s" s="1">
-        <v>932</v>
-      </c>
       <c r="C418" t="s" s="1">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="D418" t="s" s="1">
         <v>33</v>
@@ -25926,13 +25929,13 @@
     </row>
     <row r="419">
       <c r="A419" t="s" s="1">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B419" t="s" s="1">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C419" t="s" s="1">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="D419" t="s" s="1">
         <v>33</v>
@@ -25982,13 +25985,13 @@
     </row>
     <row r="420">
       <c r="A420" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B420" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C420" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="D420" t="s">
         <v>33</v>
@@ -26003,10 +26006,10 @@
         <v>41</v>
       </c>
       <c r="H420" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="I420" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="J420" t="s">
         <v>119</v>
@@ -26015,10 +26018,10 @@
         <v>119</v>
       </c>
       <c r="L420" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="M420" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="N420" t="s">
         <v>47</v>
@@ -26027,7 +26030,7 @@
         <v>130</v>
       </c>
       <c r="P420" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="Q420" t="s">
         <v>47</v>
@@ -26038,7 +26041,7 @@
     </row>
     <row r="421">
       <c r="A421" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B421" t="s">
         <v>34</v>
@@ -26059,10 +26062,10 @@
         <v>41</v>
       </c>
       <c r="H421" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="I421" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="J421" t="s">
         <v>80</v>
@@ -26071,10 +26074,10 @@
         <v>80</v>
       </c>
       <c r="L421" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="M421" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="N421" t="s">
         <v>47</v>
@@ -26083,7 +26086,7 @@
         <v>255</v>
       </c>
       <c r="P421" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="Q421" t="s">
         <v>47</v>
@@ -26094,7 +26097,7 @@
     </row>
     <row r="422">
       <c r="A422" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B422" t="s">
         <v>34</v>
@@ -26115,10 +26118,10 @@
         <v>41</v>
       </c>
       <c r="H422" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="I422" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="J422" t="s">
         <v>113</v>
@@ -26127,10 +26130,10 @@
         <v>113</v>
       </c>
       <c r="L422" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="M422" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="N422" t="s">
         <v>47</v>
@@ -26139,7 +26142,7 @@
         <v>114</v>
       </c>
       <c r="P422" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="Q422" t="s">
         <v>47</v>
@@ -26150,7 +26153,7 @@
     </row>
     <row r="423">
       <c r="A423" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B423" t="s">
         <v>34</v>
@@ -26171,10 +26174,10 @@
         <v>41</v>
       </c>
       <c r="H423" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="I423" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="J423" t="s">
         <v>58</v>
@@ -26183,10 +26186,10 @@
         <v>58</v>
       </c>
       <c r="L423" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="M423" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="N423" t="s">
         <v>47</v>
@@ -26195,7 +26198,7 @@
         <v>105</v>
       </c>
       <c r="P423" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="Q423" t="s">
         <v>47</v>
@@ -26206,7 +26209,7 @@
     </row>
     <row r="424">
       <c r="A424" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B424" t="s">
         <v>34</v>
@@ -26227,10 +26230,10 @@
         <v>41</v>
       </c>
       <c r="H424" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="I424" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="J424" t="s">
         <v>90</v>
@@ -26239,10 +26242,10 @@
         <v>90</v>
       </c>
       <c r="L424" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="M424" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="N424" t="s">
         <v>47</v>
@@ -26251,7 +26254,7 @@
         <v>310</v>
       </c>
       <c r="P424" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="Q424" t="s">
         <v>47</v>
@@ -26262,7 +26265,7 @@
     </row>
     <row r="425">
       <c r="A425" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B425" t="s">
         <v>34</v>
@@ -26283,10 +26286,10 @@
         <v>41</v>
       </c>
       <c r="H425" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="I425" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="J425" t="s">
         <v>119</v>
@@ -26295,10 +26298,10 @@
         <v>119</v>
       </c>
       <c r="L425" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="M425" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="N425" t="s">
         <v>47</v>
@@ -26307,7 +26310,7 @@
         <v>250</v>
       </c>
       <c r="P425" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="Q425" t="s">
         <v>47</v>
@@ -26318,7 +26321,7 @@
     </row>
     <row r="426">
       <c r="A426" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B426" t="s">
         <v>34</v>
@@ -26339,10 +26342,10 @@
         <v>41</v>
       </c>
       <c r="H426" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="I426" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="J426" t="s">
         <v>90</v>
@@ -26351,10 +26354,10 @@
         <v>229</v>
       </c>
       <c r="L426" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="M426" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="N426" t="s">
         <v>47</v>
@@ -26363,7 +26366,7 @@
         <v>91</v>
       </c>
       <c r="P426" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="Q426" t="s">
         <v>47</v>
@@ -26374,7 +26377,7 @@
     </row>
     <row r="427">
       <c r="A427" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B427" t="s">
         <v>34</v>
@@ -26395,10 +26398,10 @@
         <v>41</v>
       </c>
       <c r="H427" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="I427" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="J427" t="s">
         <v>101</v>
@@ -26407,10 +26410,10 @@
         <v>101</v>
       </c>
       <c r="L427" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="M427" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="N427" t="s">
         <v>47</v>
@@ -26419,7 +26422,7 @@
         <v>102</v>
       </c>
       <c r="P427" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="Q427" t="s">
         <v>47</v>
@@ -26430,7 +26433,7 @@
     </row>
     <row r="428">
       <c r="A428" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B428" t="s">
         <v>34</v>
@@ -26451,10 +26454,10 @@
         <v>41</v>
       </c>
       <c r="H428" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="I428" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="J428" t="s">
         <v>80</v>
@@ -26463,10 +26466,10 @@
         <v>80</v>
       </c>
       <c r="L428" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="M428" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="N428" t="s">
         <v>47</v>
@@ -26475,7 +26478,7 @@
         <v>247</v>
       </c>
       <c r="P428" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="Q428" t="s">
         <v>47</v>
@@ -26486,7 +26489,7 @@
     </row>
     <row r="429">
       <c r="A429" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B429" t="s">
         <v>34</v>
@@ -26507,10 +26510,10 @@
         <v>41</v>
       </c>
       <c r="H429" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="I429" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="J429" t="s">
         <v>119</v>
@@ -26519,10 +26522,10 @@
         <v>119</v>
       </c>
       <c r="L429" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="M429" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="N429" t="s">
         <v>47</v>
@@ -26531,7 +26534,7 @@
         <v>156</v>
       </c>
       <c r="P429" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="Q429" t="s">
         <v>47</v>
@@ -26542,7 +26545,7 @@
     </row>
     <row r="430">
       <c r="A430" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B430" t="s">
         <v>34</v>
@@ -26563,10 +26566,10 @@
         <v>41</v>
       </c>
       <c r="H430" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="I430" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="J430" t="s">
         <v>126</v>
@@ -26575,10 +26578,10 @@
         <v>119</v>
       </c>
       <c r="L430" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="M430" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="N430" t="s">
         <v>47</v>
@@ -26587,7 +26590,7 @@
         <v>436</v>
       </c>
       <c r="P430" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="Q430" t="s">
         <v>47</v>
@@ -26598,7 +26601,7 @@
     </row>
     <row r="431">
       <c r="A431" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B431" t="s">
         <v>34</v>
@@ -26619,10 +26622,10 @@
         <v>41</v>
       </c>
       <c r="H431" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="I431" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="J431" t="s">
         <v>126</v>
@@ -26631,10 +26634,10 @@
         <v>119</v>
       </c>
       <c r="L431" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="M431" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="N431" t="s">
         <v>47</v>
@@ -26643,7 +26646,7 @@
         <v>466</v>
       </c>
       <c r="P431" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="Q431" t="s">
         <v>47</v>
@@ -26654,7 +26657,7 @@
     </row>
     <row r="432">
       <c r="A432" t="s" s="1">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B432" t="s" s="1">
         <v>32</v>
@@ -26710,7 +26713,7 @@
     </row>
     <row r="433">
       <c r="A433" t="s" s="1">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B433" t="s" s="1">
         <v>32</v>
@@ -26766,7 +26769,7 @@
     </row>
     <row r="434">
       <c r="A434" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B434" t="s">
         <v>32</v>
@@ -26822,7 +26825,7 @@
     </row>
     <row r="435">
       <c r="A435" t="s" s="1">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B435" t="s" s="1">
         <v>61</v>
@@ -26878,7 +26881,7 @@
     </row>
     <row r="436">
       <c r="A436" t="s" s="1">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B436" t="s" s="1">
         <v>61</v>
@@ -26934,7 +26937,7 @@
     </row>
     <row r="437">
       <c r="A437" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B437" t="s">
         <v>61</v>
@@ -26990,7 +26993,7 @@
     </row>
     <row r="438">
       <c r="A438" t="s" s="1">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B438" t="s" s="1">
         <v>183</v>
@@ -27046,7 +27049,7 @@
     </row>
     <row r="439">
       <c r="A439" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B439" t="s">
         <v>183</v>
@@ -27102,13 +27105,13 @@
     </row>
     <row r="440">
       <c r="A440" t="s" s="1">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B440" t="s" s="1">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C440" t="s" s="1">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="D440" t="s" s="1">
         <v>33</v>
@@ -27158,7 +27161,7 @@
     </row>
     <row r="441">
       <c r="A441" t="s" s="1">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B441" t="s" s="1">
         <v>205</v>
@@ -27214,7 +27217,7 @@
     </row>
     <row r="442">
       <c r="A442" t="s" s="1">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B442" t="s" s="1">
         <v>207</v>
@@ -27270,7 +27273,7 @@
     </row>
     <row r="443">
       <c r="A443" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B443" t="s">
         <v>207</v>
@@ -27326,7 +27329,7 @@
     </row>
     <row r="444">
       <c r="A444" t="s" s="1">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B444" t="s" s="1">
         <v>345</v>
@@ -27382,7 +27385,7 @@
     </row>
     <row r="445">
       <c r="A445" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B445" t="s">
         <v>345</v>
@@ -27438,13 +27441,13 @@
     </row>
     <row r="446">
       <c r="A446" t="s" s="1">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B446" t="s" s="1">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="C446" t="s" s="1">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="D446" t="s" s="1">
         <v>33</v>
@@ -27494,13 +27497,13 @@
     </row>
     <row r="447">
       <c r="A447" t="s" s="1">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B447" t="s" s="1">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="C447" t="s" s="1">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="D447" t="s" s="1">
         <v>33</v>
@@ -27550,7 +27553,7 @@
     </row>
     <row r="448">
       <c r="A448" t="s" s="1">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B448" t="s" s="1">
         <v>418</v>
@@ -27606,7 +27609,7 @@
     </row>
     <row r="449">
       <c r="A449" t="s" s="1">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B449" t="s" s="1">
         <v>420</v>
@@ -27662,7 +27665,7 @@
     </row>
     <row r="450">
       <c r="A450" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B450" t="s">
         <v>420</v>
@@ -27718,13 +27721,13 @@
     </row>
     <row r="451">
       <c r="A451" t="s" s="1">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B451" t="s" s="1">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C451" t="s" s="1">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D451" t="s" s="1">
         <v>33</v>
@@ -27774,13 +27777,13 @@
     </row>
     <row r="452">
       <c r="A452" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B452" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C452" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D452" t="s">
         <v>33</v>
@@ -27830,13 +27833,13 @@
     </row>
     <row r="453">
       <c r="A453" t="s" s="1">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B453" t="s" s="1">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C453" t="s" s="1">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D453" t="s" s="1">
         <v>33</v>
@@ -27886,13 +27889,13 @@
     </row>
     <row r="454">
       <c r="A454" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B454" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C454" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D454" t="s">
         <v>33</v>
@@ -27942,13 +27945,13 @@
     </row>
     <row r="455">
       <c r="A455" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B455" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C455" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D455" t="s">
         <v>33</v>
@@ -27998,13 +28001,13 @@
     </row>
     <row r="456">
       <c r="A456" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B456" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C456" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D456" t="s">
         <v>33</v>
@@ -28054,13 +28057,13 @@
     </row>
     <row r="457">
       <c r="A457" t="s" s="1">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B457" t="s" s="1">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C457" t="s" s="1">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D457" t="s" s="1">
         <v>33</v>
@@ -28110,13 +28113,13 @@
     </row>
     <row r="458">
       <c r="A458" t="s" s="1">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B458" t="s" s="1">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C458" t="s" s="1">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D458" t="s" s="1">
         <v>33</v>
@@ -28166,13 +28169,13 @@
     </row>
     <row r="459">
       <c r="A459" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B459" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C459" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D459" t="s">
         <v>33</v>
@@ -28222,13 +28225,13 @@
     </row>
     <row r="460">
       <c r="A460" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B460" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C460" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="D460" t="s">
         <v>33</v>
@@ -28278,13 +28281,13 @@
     </row>
     <row r="461">
       <c r="A461" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B461" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C461" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="D461" t="s">
         <v>33</v>
@@ -28334,13 +28337,13 @@
     </row>
     <row r="462">
       <c r="A462" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B462" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C462" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="D462" t="s">
         <v>33</v>
@@ -28390,13 +28393,13 @@
     </row>
     <row r="463">
       <c r="A463" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B463" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C463" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D463" t="s">
         <v>33</v>
@@ -28446,13 +28449,13 @@
     </row>
     <row r="464">
       <c r="A464" t="s" s="1">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B464" t="s" s="1">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C464" t="s" s="1">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="D464" t="s" s="1">
         <v>33</v>
@@ -28502,13 +28505,13 @@
     </row>
     <row r="465">
       <c r="A465" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="B465" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C465" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D465" t="s">
         <v>33</v>
@@ -28558,13 +28561,13 @@
     </row>
     <row r="466">
       <c r="A466" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B466" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C466" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="D466" t="s">
         <v>33</v>
@@ -28614,13 +28617,13 @@
     </row>
     <row r="467">
       <c r="A467" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B467" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C467" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="D467" t="s">
         <v>33</v>
@@ -28670,13 +28673,13 @@
     </row>
     <row r="468">
       <c r="A468" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B468" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C468" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D468" t="s">
         <v>33</v>
@@ -28726,13 +28729,13 @@
     </row>
     <row r="469">
       <c r="A469" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B469" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C469" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D469" t="s">
         <v>33</v>
@@ -28782,13 +28785,13 @@
     </row>
     <row r="470">
       <c r="A470" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B470" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="C470" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D470" t="s">
         <v>33</v>
@@ -28838,13 +28841,13 @@
     </row>
     <row r="471">
       <c r="A471" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B471" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="C471" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="D471" t="s">
         <v>33</v>
@@ -28894,13 +28897,13 @@
     </row>
     <row r="472">
       <c r="A472" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B472" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C472" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="D472" t="s">
         <v>33</v>
@@ -28950,13 +28953,13 @@
     </row>
     <row r="473">
       <c r="A473" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B473" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C473" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="D473" t="s">
         <v>33</v>
@@ -29006,13 +29009,13 @@
     </row>
     <row r="474">
       <c r="A474" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B474" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="C474" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="D474" t="s">
         <v>33</v>
@@ -29062,13 +29065,13 @@
     </row>
     <row r="475">
       <c r="A475" t="s" s="1">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B475" t="s" s="1">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C475" t="s" s="1">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D475" t="s" s="1">
         <v>33</v>
@@ -29118,13 +29121,13 @@
     </row>
     <row r="476">
       <c r="A476" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B476" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C476" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D476" t="s">
         <v>33</v>
@@ -29174,13 +29177,13 @@
     </row>
     <row r="477">
       <c r="A477" t="s" s="1">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B477" t="s" s="1">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C477" t="s" s="1">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="D477" t="s" s="1">
         <v>33</v>
@@ -29230,13 +29233,13 @@
     </row>
     <row r="478">
       <c r="A478" t="s" s="1">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B478" t="s" s="1">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="C478" t="s" s="1">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="D478" t="s" s="1">
         <v>33</v>
@@ -29286,13 +29289,13 @@
     </row>
     <row r="479">
       <c r="A479" t="s" s="1">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B479" t="s" s="1">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="C479" t="s" s="1">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D479" t="s" s="1">
         <v>33</v>
@@ -29342,13 +29345,13 @@
     </row>
     <row r="480">
       <c r="A480" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B480" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="C480" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D480" t="s">
         <v>33</v>
@@ -29398,13 +29401,13 @@
     </row>
     <row r="481">
       <c r="A481" t="s" s="1">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B481" t="s" s="1">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C481" t="s" s="1">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="D481" t="s" s="1">
         <v>33</v>
@@ -29454,13 +29457,13 @@
     </row>
     <row r="482">
       <c r="A482" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B482" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C482" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="D482" t="s">
         <v>33</v>
@@ -29510,13 +29513,13 @@
     </row>
     <row r="483">
       <c r="A483" t="s" s="1">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B483" t="s" s="1">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="C483" t="s" s="1">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="D483" t="s" s="1">
         <v>33</v>
@@ -29566,13 +29569,13 @@
     </row>
     <row r="484">
       <c r="A484" t="s" s="1">
+        <v>1010</v>
+      </c>
+      <c r="B484" t="s" s="1">
         <v>1009</v>
       </c>
-      <c r="B484" t="s" s="1">
-        <v>1008</v>
-      </c>
       <c r="C484" t="s" s="1">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="D484" t="s" s="1">
         <v>33</v>
@@ -29622,13 +29625,13 @@
     </row>
     <row r="485">
       <c r="A485" t="s" s="1">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B485" t="s" s="1">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C485" t="s" s="1">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="D485" t="s" s="1">
         <v>33</v>
@@ -29678,7 +29681,7 @@
     </row>
     <row r="486">
       <c r="A486" t="s" s="1">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B486" t="s" s="1">
         <v>61</v>
@@ -29734,13 +29737,13 @@
     </row>
     <row r="487">
       <c r="A487" t="s" s="1">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B487" t="s" s="1">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="C487" t="s" s="1">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="D487" t="s" s="1">
         <v>33</v>
@@ -29790,7 +29793,7 @@
     </row>
     <row r="488">
       <c r="A488" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B488" t="s">
         <v>183</v>
@@ -29846,7 +29849,7 @@
     </row>
     <row r="489">
       <c r="A489" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B489" t="s">
         <v>205</v>
@@ -29902,7 +29905,7 @@
     </row>
     <row r="490">
       <c r="A490" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B490" t="s">
         <v>418</v>
@@ -29958,13 +29961,13 @@
     </row>
     <row r="491">
       <c r="A491" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B491" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C491" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="D491" t="s">
         <v>33</v>
@@ -30014,13 +30017,13 @@
     </row>
     <row r="492">
       <c r="A492" t="s" s="1">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B492" t="s" s="1">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="C492" t="s" s="1">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="D492" t="s" s="1">
         <v>33</v>
@@ -30070,13 +30073,13 @@
     </row>
     <row r="493">
       <c r="A493" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B493" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C493" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D493" t="s">
         <v>33</v>
@@ -30126,13 +30129,13 @@
     </row>
     <row r="494">
       <c r="A494" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="B494" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="C494" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D494" t="s">
         <v>33</v>
@@ -30182,7 +30185,7 @@
     </row>
     <row r="495">
       <c r="A495" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B495" t="s">
         <v>61</v>
@@ -30238,13 +30241,13 @@
     </row>
     <row r="496">
       <c r="A496" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="B496" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="C496" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="D496" t="s">
         <v>33</v>
@@ -30294,13 +30297,13 @@
     </row>
     <row r="497">
       <c r="A497" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B497" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="C497" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="D497" t="s">
         <v>33</v>
@@ -30350,7 +30353,7 @@
     </row>
     <row r="498">
       <c r="A498" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="B498" t="s">
         <v>207</v>
@@ -30406,7 +30409,7 @@
     </row>
     <row r="499">
       <c r="A499" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B499" t="s">
         <v>420</v>
@@ -30462,13 +30465,13 @@
     </row>
     <row r="500">
       <c r="A500" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="B500" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C500" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D500" t="s">
         <v>33</v>
@@ -30518,13 +30521,13 @@
     </row>
     <row r="501">
       <c r="A501" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B501" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C501" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D501" t="s">
         <v>33</v>
@@ -30574,7 +30577,7 @@
     </row>
     <row r="502">
       <c r="A502" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B502" t="s">
         <v>183</v>
@@ -30630,13 +30633,13 @@
     </row>
     <row r="503">
       <c r="A503" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="B503" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="C503" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="D503" t="s">
         <v>33</v>
@@ -30686,13 +30689,13 @@
     </row>
     <row r="504">
       <c r="A504" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B504" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C504" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="D504" t="s">
         <v>33</v>
@@ -30742,13 +30745,13 @@
     </row>
     <row r="505">
       <c r="A505" t="s" s="1">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="B505" t="s" s="1">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="C505" t="s" s="1">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="D505" t="s" s="1">
         <v>33</v>
@@ -30798,16 +30801,16 @@
     </row>
     <row r="506">
       <c r="A506" t="s" s="1">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B506" t="s" s="1">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="C506" t="s" s="1">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D506" t="s" s="1">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="E506" t="s" s="1">
         <v>34</v>
@@ -30854,16 +30857,16 @@
     </row>
     <row r="507">
       <c r="A507" t="s" s="1">
+        <v>1040</v>
+      </c>
+      <c r="B507" t="s" s="1">
+        <v>1041</v>
+      </c>
+      <c r="C507" t="s" s="1">
+        <v>1041</v>
+      </c>
+      <c r="D507" t="s" s="1">
         <v>1039</v>
-      </c>
-      <c r="B507" t="s" s="1">
-        <v>1040</v>
-      </c>
-      <c r="C507" t="s" s="1">
-        <v>1040</v>
-      </c>
-      <c r="D507" t="s" s="1">
-        <v>1038</v>
       </c>
       <c r="E507" t="s" s="1">
         <v>34</v>
@@ -30910,16 +30913,16 @@
     </row>
     <row r="508">
       <c r="A508" t="s" s="1">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B508" t="s" s="1">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C508" t="s" s="1">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="D508" t="s" s="1">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="E508" t="s" s="1">
         <v>34</v>
@@ -30966,13 +30969,13 @@
     </row>
     <row r="509">
       <c r="A509" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B509" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="C509" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="D509" t="s">
         <v>33</v>
@@ -31022,31 +31025,31 @@
     </row>
     <row r="510">
       <c r="A510" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B510" t="s">
         <v>1045</v>
       </c>
-      <c r="B510" t="s">
-        <v>1044</v>
-      </c>
       <c r="C510" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="D510" t="s">
         <v>33</v>
       </c>
       <c r="E510" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="F510" t="s">
         <v>93</v>
       </c>
       <c r="G510" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="H510" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="I510" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="J510" t="s">
         <v>90</v>
@@ -31055,10 +31058,10 @@
         <v>90</v>
       </c>
       <c r="L510" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="M510" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="N510" t="s">
         <v>47</v>
@@ -31067,7 +31070,7 @@
         <v>48</v>
       </c>
       <c r="P510" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="Q510" t="s">
         <v>47</v>
@@ -31078,7 +31081,7 @@
     </row>
     <row r="511">
       <c r="A511" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B511" t="s">
         <v>34</v>
@@ -31090,7 +31093,7 @@
         <v>34</v>
       </c>
       <c r="E511" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="F511" t="s">
         <v>211</v>
@@ -31099,10 +31102,10 @@
         <v>41</v>
       </c>
       <c r="H511" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="I511" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="J511" t="s">
         <v>70</v>
@@ -31114,7 +31117,7 @@
         <v>34</v>
       </c>
       <c r="M511" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="N511" t="s">
         <v>47</v>
@@ -31123,7 +31126,7 @@
         <v>48</v>
       </c>
       <c r="P511" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="Q511" t="s">
         <v>47</v>

--- a/xlsx/dre/DRE_02_2026.xlsx
+++ b/xlsx/dre/DRE_02_2026.xlsx
@@ -684,61 +684,61 @@
     <t>R$  37.036,08</t>
   </si>
   <si>
+    <t>61401/1</t>
+  </si>
+  <si>
+    <t>R$  5.288,30</t>
+  </si>
+  <si>
+    <t>62301/1</t>
+  </si>
+  <si>
+    <t>R$  11.202,63</t>
+  </si>
+  <si>
+    <t>01/02/26</t>
+  </si>
+  <si>
+    <t>60501/1</t>
+  </si>
+  <si>
+    <t>R$  4.155,65</t>
+  </si>
+  <si>
+    <t>63401/1</t>
+  </si>
+  <si>
+    <t>R$  2.664,41</t>
+  </si>
+  <si>
+    <t>63501/1</t>
+  </si>
+  <si>
+    <t>R$  24.333,46</t>
+  </si>
+  <si>
+    <t>62801/1</t>
+  </si>
+  <si>
+    <t>R$  8.611,10</t>
+  </si>
+  <si>
+    <t>63501/2</t>
+  </si>
+  <si>
+    <t>R$  2.361,24</t>
+  </si>
+  <si>
+    <t>15/06/26</t>
+  </si>
+  <si>
+    <t>Título gerado pela diferença de valor da revisão.</t>
+  </si>
+  <si>
     <t>61901/1</t>
   </si>
   <si>
     <t>R$  12.309,90</t>
-  </si>
-  <si>
-    <t>61401/1</t>
-  </si>
-  <si>
-    <t>R$  5.288,30</t>
-  </si>
-  <si>
-    <t>62301/1</t>
-  </si>
-  <si>
-    <t>R$  11.202,63</t>
-  </si>
-  <si>
-    <t>01/02/26</t>
-  </si>
-  <si>
-    <t>60501/1</t>
-  </si>
-  <si>
-    <t>R$  4.155,65</t>
-  </si>
-  <si>
-    <t>63401/1</t>
-  </si>
-  <si>
-    <t>R$  2.664,41</t>
-  </si>
-  <si>
-    <t>63501/1</t>
-  </si>
-  <si>
-    <t>R$  24.333,46</t>
-  </si>
-  <si>
-    <t>62801/1</t>
-  </si>
-  <si>
-    <t>R$  8.611,10</t>
-  </si>
-  <si>
-    <t>63501/2</t>
-  </si>
-  <si>
-    <t>R$  2.361,24</t>
-  </si>
-  <si>
-    <t>15/06/26</t>
-  </si>
-  <si>
-    <t>Título gerado pela diferença de valor da revisão.</t>
   </si>
   <si>
     <t>64401/2</t>
@@ -1550,46 +1550,46 @@
     <t>R$ 10.123,95</t>
   </si>
   <si>
+    <t>RAYSSA BARBOSA SILVA</t>
+  </si>
+  <si>
+    <t>R$  727,31</t>
+  </si>
+  <si>
+    <t>07/04/26</t>
+  </si>
+  <si>
+    <t>FERNANDA DOCHVAT SILVA</t>
+  </si>
+  <si>
+    <t>01/04/26</t>
+  </si>
+  <si>
+    <t>R$  1.196,02</t>
+  </si>
+  <si>
+    <t>01/06/26</t>
+  </si>
+  <si>
     <t>R$  1.108,54</t>
   </si>
   <si>
-    <t>R$  1.196,02</t>
-  </si>
-  <si>
-    <t>RAYSSA BARBOSA SILVA</t>
-  </si>
-  <si>
-    <t>R$  727,31</t>
-  </si>
-  <si>
-    <t>07/04/26</t>
-  </si>
-  <si>
-    <t>FERNANDA DOCHVAT SILVA</t>
-  </si>
-  <si>
-    <t>01/06/26</t>
-  </si>
-  <si>
-    <t>01/04/26</t>
+    <t>63801/2</t>
   </si>
   <si>
     <t>R$  438,09</t>
   </si>
   <si>
+    <t>R$  292,95</t>
+  </si>
+  <si>
+    <t>Jose Carlos de Carvalho</t>
+  </si>
+  <si>
+    <t>R$  537,59</t>
+  </si>
+  <si>
     <t>R$  3,60</t>
-  </si>
-  <si>
-    <t>63801/2</t>
-  </si>
-  <si>
-    <t>Jose Carlos de Carvalho</t>
-  </si>
-  <si>
-    <t>R$  537,59</t>
-  </si>
-  <si>
-    <t>R$  292,95</t>
   </si>
   <si>
     <t>R$  1.941,34</t>
@@ -1746,52 +1746,109 @@
     <t>4.03.03.01.01 Frete logístico - entrega a clientes</t>
   </si>
   <si>
+    <t>552/1</t>
+  </si>
+  <si>
+    <t>Uber</t>
+  </si>
+  <si>
+    <t>R$  21,95</t>
+  </si>
+  <si>
+    <t>34301ThiagoBFG</t>
+  </si>
+  <si>
+    <t>555/1</t>
+  </si>
+  <si>
+    <t>R$  32,02</t>
+  </si>
+  <si>
+    <t>MarthaLBM009501</t>
+  </si>
+  <si>
+    <t>556/1</t>
+  </si>
+  <si>
+    <t>R$  34,34</t>
+  </si>
+  <si>
+    <t>536/1</t>
+  </si>
+  <si>
+    <t>R$  31,04</t>
+  </si>
+  <si>
+    <t>25001CarlaRCK</t>
+  </si>
+  <si>
+    <t>544/1</t>
+  </si>
+  <si>
+    <t>R$  10,83</t>
+  </si>
+  <si>
+    <t>551/1</t>
+  </si>
+  <si>
+    <t>R$  68,90</t>
+  </si>
+  <si>
+    <t>SungHK003001</t>
+  </si>
+  <si>
+    <t>547/1</t>
+  </si>
+  <si>
+    <t>R$  10,96</t>
+  </si>
+  <si>
+    <t>AnaCAL0016003</t>
+  </si>
+  <si>
+    <t>535/1</t>
+  </si>
+  <si>
+    <t>R$  14,63</t>
+  </si>
+  <si>
+    <t>45001ANACLARABLA</t>
+  </si>
+  <si>
+    <t>554/1</t>
+  </si>
+  <si>
+    <t>R$  36,22</t>
+  </si>
+  <si>
+    <t>41801PhilipeKHO</t>
+  </si>
+  <si>
+    <t>538/1</t>
+  </si>
+  <si>
+    <t>R$  10,94</t>
+  </si>
+  <si>
+    <t>CleoniceH006101</t>
+  </si>
+  <si>
     <t>537/1</t>
   </si>
   <si>
-    <t>Uber</t>
-  </si>
-  <si>
     <t>R$  16,98</t>
   </si>
   <si>
     <t>33201BRUNALESS</t>
   </si>
   <si>
-    <t>62901U/0</t>
-  </si>
-  <si>
-    <t>R$  8,43</t>
-  </si>
-  <si>
-    <t>05/08/26</t>
-  </si>
-  <si>
-    <t>551/1</t>
-  </si>
-  <si>
-    <t>R$  68,90</t>
-  </si>
-  <si>
-    <t>SungHK003001</t>
-  </si>
-  <si>
-    <t>554/1</t>
-  </si>
-  <si>
-    <t>R$  36,22</t>
-  </si>
-  <si>
-    <t>41801PhilipeKHO</t>
-  </si>
-  <si>
-    <t>536/1</t>
-  </si>
-  <si>
-    <t>R$  31,04</t>
-  </si>
-  <si>
-    <t>25001CarlaRCK</t>
+    <t>541/1</t>
+  </si>
+  <si>
+    <t>R$  68,35</t>
+  </si>
+  <si>
+    <t>50503FABIOTN</t>
   </si>
   <si>
     <t>Uber/1</t>
@@ -1803,24 +1860,6 @@
     <t>45901ANAMARIDEO</t>
   </si>
   <si>
-    <t>535/1</t>
-  </si>
-  <si>
-    <t>R$  14,63</t>
-  </si>
-  <si>
-    <t>45001ANACLARABLA</t>
-  </si>
-  <si>
-    <t>541/1</t>
-  </si>
-  <si>
-    <t>R$  68,35</t>
-  </si>
-  <si>
-    <t>50503FABIOTN</t>
-  </si>
-  <si>
     <t>543/1</t>
   </si>
   <si>
@@ -1839,30 +1878,6 @@
     <t>47101MarciaOA</t>
   </si>
   <si>
-    <t>548/1</t>
-  </si>
-  <si>
-    <t>R$  44,94</t>
-  </si>
-  <si>
-    <t>49401ARIK</t>
-  </si>
-  <si>
-    <t>549/1</t>
-  </si>
-  <si>
-    <t>R$  15,94</t>
-  </si>
-  <si>
-    <t>539/1</t>
-  </si>
-  <si>
-    <t>R$  21,95</t>
-  </si>
-  <si>
-    <t>NazarethPR0016901</t>
-  </si>
-  <si>
     <t>553/1</t>
   </si>
   <si>
@@ -1870,42 +1885,6 @@
   </si>
   <si>
     <t>WilliamW004901</t>
-  </si>
-  <si>
-    <t>556/1</t>
-  </si>
-  <si>
-    <t>R$  34,34</t>
-  </si>
-  <si>
-    <t>557/1</t>
-  </si>
-  <si>
-    <t>R$  51,90</t>
-  </si>
-  <si>
-    <t>542/1</t>
-  </si>
-  <si>
-    <t>R$  66,01</t>
-  </si>
-  <si>
-    <t>555/1</t>
-  </si>
-  <si>
-    <t>R$  32,02</t>
-  </si>
-  <si>
-    <t>MarthaLBM009501</t>
-  </si>
-  <si>
-    <t>547/1</t>
-  </si>
-  <si>
-    <t>R$  10,96</t>
-  </si>
-  <si>
-    <t>AnaCAL0016003</t>
   </si>
   <si>
     <t>558/1</t>
@@ -1920,12 +1899,6 @@
 </t>
   </si>
   <si>
-    <t>544/1</t>
-  </si>
-  <si>
-    <t>R$  10,83</t>
-  </si>
-  <si>
     <t>540/1</t>
   </si>
   <si>
@@ -1935,10 +1908,37 @@
     <t>42701ERIKA</t>
   </si>
   <si>
-    <t>552/1</t>
-  </si>
-  <si>
-    <t>34301ThiagoBFG</t>
+    <t>557/1</t>
+  </si>
+  <si>
+    <t>R$  51,90</t>
+  </si>
+  <si>
+    <t>539/1</t>
+  </si>
+  <si>
+    <t>NazarethPR0016901</t>
+  </si>
+  <si>
+    <t>548/1</t>
+  </si>
+  <si>
+    <t>R$  44,94</t>
+  </si>
+  <si>
+    <t>49401ARIK</t>
+  </si>
+  <si>
+    <t>549/1</t>
+  </si>
+  <si>
+    <t>R$  15,94</t>
+  </si>
+  <si>
+    <t>542/1</t>
+  </si>
+  <si>
+    <t>R$  66,01</t>
   </si>
   <si>
     <t>61001/0</t>
@@ -1953,46 +1953,55 @@
     <t>61001FABIOLBM</t>
   </si>
   <si>
+    <t>R$  20,15</t>
+  </si>
+  <si>
     <t>R$  73,87</t>
   </si>
   <si>
-    <t>R$  20,15</t>
+    <t>R$  20,33</t>
+  </si>
+  <si>
+    <t>16/06/26</t>
+  </si>
+  <si>
+    <t>R$  33,58</t>
+  </si>
+  <si>
+    <t>05/06/26</t>
+  </si>
+  <si>
+    <t>61901UBER/0</t>
+  </si>
+  <si>
+    <t>R$  19,39</t>
+  </si>
+  <si>
+    <t>63801/0</t>
+  </si>
+  <si>
+    <t>R$  22,94</t>
   </si>
   <si>
     <t>R$  59,01</t>
   </si>
   <si>
-    <t>05/06/26</t>
-  </si>
-  <si>
-    <t>R$  33,58</t>
+    <t>54802UBER/0</t>
+  </si>
+  <si>
+    <t>R$  164,15</t>
   </si>
   <si>
     <t>R$  35,23</t>
   </si>
   <si>
-    <t>R$  20,33</t>
-  </si>
-  <si>
-    <t>16/06/26</t>
-  </si>
-  <si>
-    <t>61901UBER/0</t>
-  </si>
-  <si>
-    <t>R$  19,39</t>
-  </si>
-  <si>
-    <t>63801/0</t>
-  </si>
-  <si>
-    <t>R$  22,94</t>
-  </si>
-  <si>
-    <t>54802UBER/0</t>
-  </si>
-  <si>
-    <t>R$  164,15</t>
+    <t>54802U/0</t>
+  </si>
+  <si>
+    <t>R$  36,09</t>
+  </si>
+  <si>
+    <t>05/08/26</t>
   </si>
   <si>
     <t>61401U/0</t>
@@ -2001,24 +2010,15 @@
     <t>R$  10,33</t>
   </si>
   <si>
-    <t>54802U/0</t>
-  </si>
-  <si>
-    <t>R$  36,09</t>
+    <t>62901U/0</t>
+  </si>
+  <si>
+    <t>R$  8,43</t>
   </si>
   <si>
     <t>R$  20,57</t>
   </si>
   <si>
-    <t>538/1</t>
-  </si>
-  <si>
-    <t>R$  10,94</t>
-  </si>
-  <si>
-    <t>CleoniceH006101</t>
-  </si>
-  <si>
     <t>4.03.03.02 Agregados e outros gastos de montagens</t>
   </si>
   <si>
@@ -2139,115 +2139,115 @@
     <t>4.04.01.02.01.01 Salário fixo</t>
   </si>
   <si>
+    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
+  </si>
+  <si>
+    <t>R$  4.422,07</t>
+  </si>
+  <si>
+    <t>Sabrina Braunbeck - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>578/1</t>
+  </si>
+  <si>
+    <t>R$  2.219,85</t>
+  </si>
+  <si>
+    <t>790/1</t>
+  </si>
+  <si>
+    <t>Mayara Silva Martins</t>
+  </si>
+  <si>
+    <t>R$  247,33</t>
+  </si>
+  <si>
+    <t>587/1</t>
+  </si>
+  <si>
+    <t>R$  2.075,32</t>
+  </si>
+  <si>
+    <t>Rateio salários Mayara, Rayssa e Efraim</t>
+  </si>
+  <si>
+    <t>780/1</t>
+  </si>
+  <si>
+    <t>R$  1.060,00</t>
+  </si>
+  <si>
+    <t>Danielle Martins da Silva</t>
+  </si>
+  <si>
+    <t>R$  2.090,00</t>
+  </si>
+  <si>
+    <t>Danielle - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>GUTEMBERG DIAS GOMES</t>
+  </si>
+  <si>
+    <t>R$  6.000,00</t>
+  </si>
+  <si>
+    <t>Gutemberg Dias - Pagamento</t>
+  </si>
+  <si>
+    <t>579/1</t>
+  </si>
+  <si>
+    <t>Leandro Henrique Simoes Campos</t>
+  </si>
+  <si>
+    <t>R$  2.000,00</t>
+  </si>
+  <si>
+    <t>Leandro Henrique Simoes Campos Fixo 2026</t>
+  </si>
+  <si>
     <t>784/1</t>
   </si>
   <si>
     <t>R$  1.268,00</t>
   </si>
   <si>
-    <t>780/1</t>
-  </si>
-  <si>
-    <t>R$  1.060,00</t>
-  </si>
-  <si>
-    <t>790/1</t>
-  </si>
-  <si>
-    <t>Mayara Silva Martins</t>
-  </si>
-  <si>
-    <t>R$  247,33</t>
-  </si>
-  <si>
-    <t>Leandro Henrique Simoes Campos</t>
-  </si>
-  <si>
-    <t>R$  2.000,00</t>
-  </si>
-  <si>
-    <t>Leandro Henrique Simoes Campos Fixo 2026</t>
+    <t>CARINA PEREIRA</t>
+  </si>
+  <si>
+    <t>Carina - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>Denny Lucas do Carmo Pereira</t>
+  </si>
+  <si>
+    <t>R$  2.645,58</t>
+  </si>
+  <si>
+    <t>Denny Lucas - Pagamento 2026</t>
   </si>
   <si>
     <t>Rubens - Pagamento 2026</t>
   </si>
   <si>
+    <t>Eric Kevin de Souza Serpa</t>
+  </si>
+  <si>
+    <t>Salário Fixo -Eric Serpa 2026</t>
+  </si>
+  <si>
+    <t>Bianca Rodrigues - Salário fixo 2026</t>
+  </si>
+  <si>
+    <t>Teresinha Elvira Maximino de Menezes</t>
+  </si>
+  <si>
+    <t>Tucha - Fixo 2026</t>
+  </si>
+  <si>
     <t>Fernanda Dochvat - Fixo 2026</t>
-  </si>
-  <si>
-    <t>579/1</t>
-  </si>
-  <si>
-    <t>Teresinha Elvira Maximino de Menezes</t>
-  </si>
-  <si>
-    <t>Tucha - Fixo 2026</t>
-  </si>
-  <si>
-    <t>587/1</t>
-  </si>
-  <si>
-    <t>R$  2.075,32</t>
-  </si>
-  <si>
-    <t>Rateio salários Mayara, Rayssa e Efraim</t>
-  </si>
-  <si>
-    <t>Bianca Rodrigues - Salário fixo 2026</t>
-  </si>
-  <si>
-    <t>CARINA PEREIRA</t>
-  </si>
-  <si>
-    <t>R$  2.090,00</t>
-  </si>
-  <si>
-    <t>Carina - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>Eric Kevin de Souza Serpa</t>
-  </si>
-  <si>
-    <t>Salário Fixo -Eric Serpa 2026</t>
-  </si>
-  <si>
-    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
-  </si>
-  <si>
-    <t>R$  4.422,07</t>
-  </si>
-  <si>
-    <t>Sabrina Braunbeck - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>Danielle Martins da Silva</t>
-  </si>
-  <si>
-    <t>Danielle - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>GUTEMBERG DIAS GOMES</t>
-  </si>
-  <si>
-    <t>R$  6.000,00</t>
-  </si>
-  <si>
-    <t>Gutemberg Dias - Pagamento</t>
-  </si>
-  <si>
-    <t>Denny Lucas do Carmo Pereira</t>
-  </si>
-  <si>
-    <t>R$  2.645,58</t>
-  </si>
-  <si>
-    <t>Denny Lucas - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>578/1</t>
-  </si>
-  <si>
-    <t>R$  2.219,85</t>
   </si>
   <si>
     <t>4.04.01.02.05 IRRF sobre salários</t>
@@ -6244,10 +6244,10 @@
         <v>224</v>
       </c>
       <c r="J67" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="K67" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="L67" t="s">
         <v>34</v>
@@ -6259,7 +6259,7 @@
         <v>47</v>
       </c>
       <c r="O67" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="P67" t="s">
         <v>224</v>
@@ -6300,10 +6300,10 @@
         <v>226</v>
       </c>
       <c r="J68" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="K68" t="s">
-        <v>101</v>
+        <v>227</v>
       </c>
       <c r="L68" t="s">
         <v>34</v>
@@ -6315,13 +6315,13 @@
         <v>47</v>
       </c>
       <c r="O68" t="s">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="P68" t="s">
-        <v>226</v>
+        <v>34</v>
       </c>
       <c r="Q68" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R68" t="s">
         <v>34</v>
@@ -6341,7 +6341,7 @@
         <v>34</v>
       </c>
       <c r="E69" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F69" t="s">
         <v>218</v>
@@ -6353,13 +6353,13 @@
         <v>219</v>
       </c>
       <c r="I69" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J69" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="K69" t="s">
-        <v>229</v>
+        <v>101</v>
       </c>
       <c r="L69" t="s">
         <v>34</v>
@@ -6412,10 +6412,10 @@
         <v>231</v>
       </c>
       <c r="J70" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="K70" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="L70" t="s">
         <v>34</v>
@@ -6468,10 +6468,10 @@
         <v>233</v>
       </c>
       <c r="J71" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="K71" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="L71" t="s">
         <v>34</v>
@@ -6483,13 +6483,13 @@
         <v>47</v>
       </c>
       <c r="O71" t="s">
-        <v>34</v>
+        <v>130</v>
       </c>
       <c r="P71" t="s">
-        <v>34</v>
+        <v>233</v>
       </c>
       <c r="Q71" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R71" t="s">
         <v>34</v>
@@ -6539,13 +6539,13 @@
         <v>47</v>
       </c>
       <c r="O72" t="s">
-        <v>130</v>
+        <v>34</v>
       </c>
       <c r="P72" t="s">
-        <v>235</v>
+        <v>34</v>
       </c>
       <c r="Q72" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R72" t="s">
         <v>34</v>
@@ -6580,13 +6580,13 @@
         <v>237</v>
       </c>
       <c r="J73" t="s">
-        <v>119</v>
+        <v>238</v>
       </c>
       <c r="K73" t="s">
         <v>119</v>
       </c>
       <c r="L73" t="s">
-        <v>34</v>
+        <v>239</v>
       </c>
       <c r="M73" t="s">
         <v>209</v>
@@ -6595,13 +6595,13 @@
         <v>47</v>
       </c>
       <c r="O73" t="s">
-        <v>34</v>
+        <v>130</v>
       </c>
       <c r="P73" t="s">
-        <v>34</v>
+        <v>237</v>
       </c>
       <c r="Q73" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R73" t="s">
         <v>34</v>
@@ -6621,7 +6621,7 @@
         <v>34</v>
       </c>
       <c r="E74" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F74" t="s">
         <v>218</v>
@@ -6633,16 +6633,16 @@
         <v>219</v>
       </c>
       <c r="I74" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J74" t="s">
-        <v>240</v>
+        <v>113</v>
       </c>
       <c r="K74" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="L74" t="s">
-        <v>241</v>
+        <v>34</v>
       </c>
       <c r="M74" t="s">
         <v>209</v>
@@ -6651,10 +6651,10 @@
         <v>47</v>
       </c>
       <c r="O74" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="P74" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q74" t="s">
         <v>47</v>
@@ -7013,7 +7013,7 @@
         <v>34</v>
       </c>
       <c r="E81" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="F81" t="s">
         <v>211</v>
@@ -7069,7 +7069,7 @@
         <v>34</v>
       </c>
       <c r="E82" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F82" t="s">
         <v>211</v>
@@ -7762,7 +7762,7 @@
         <v>134</v>
       </c>
       <c r="L94" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="M94" t="s">
         <v>283</v>
@@ -7818,7 +7818,7 @@
         <v>45</v>
       </c>
       <c r="L95" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="M95" t="s">
         <v>283</v>
@@ -9047,7 +9047,7 @@
         <v>90</v>
       </c>
       <c r="K117" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L117" t="s">
         <v>351</v>
@@ -9103,7 +9103,7 @@
         <v>90</v>
       </c>
       <c r="K118" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L118" t="s">
         <v>351</v>
@@ -10485,7 +10485,7 @@
         <v>34</v>
       </c>
       <c r="E143" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F143" t="s">
         <v>218</v>
@@ -11773,7 +11773,7 @@
         <v>34</v>
       </c>
       <c r="E166" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F166" t="s">
         <v>218</v>
@@ -12053,7 +12053,7 @@
         <v>34</v>
       </c>
       <c r="E171" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F171" t="s">
         <v>218</v>
@@ -12109,7 +12109,7 @@
         <v>34</v>
       </c>
       <c r="E172" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F172" t="s">
         <v>218</v>
@@ -12127,7 +12127,7 @@
         <v>304</v>
       </c>
       <c r="K172" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L172" t="s">
         <v>34</v>
@@ -12277,7 +12277,7 @@
         <v>34</v>
       </c>
       <c r="E175" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F175" t="s">
         <v>218</v>
@@ -12333,7 +12333,7 @@
         <v>34</v>
       </c>
       <c r="E176" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="F176" t="s">
         <v>218</v>
@@ -12389,7 +12389,7 @@
         <v>34</v>
       </c>
       <c r="E177" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F177" t="s">
         <v>218</v>
@@ -12781,7 +12781,7 @@
         <v>34</v>
       </c>
       <c r="E184" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F184" t="s">
         <v>218</v>
@@ -12837,7 +12837,7 @@
         <v>34</v>
       </c>
       <c r="E185" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F185" t="s">
         <v>218</v>
@@ -12893,7 +12893,7 @@
         <v>34</v>
       </c>
       <c r="E186" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="F186" t="s">
         <v>218</v>
@@ -12949,7 +12949,7 @@
         <v>34</v>
       </c>
       <c r="E187" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="F187" t="s">
         <v>218</v>
@@ -13005,7 +13005,7 @@
         <v>34</v>
       </c>
       <c r="E188" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F188" t="s">
         <v>218</v>
@@ -13061,7 +13061,7 @@
         <v>34</v>
       </c>
       <c r="E189" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F189" t="s">
         <v>218</v>
@@ -13117,7 +13117,7 @@
         <v>34</v>
       </c>
       <c r="E190" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F190" t="s">
         <v>218</v>
@@ -13135,7 +13135,7 @@
         <v>304</v>
       </c>
       <c r="K190" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L190" t="s">
         <v>34</v>
@@ -13173,7 +13173,7 @@
         <v>34</v>
       </c>
       <c r="E191" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F191" t="s">
         <v>218</v>
@@ -13191,7 +13191,7 @@
         <v>304</v>
       </c>
       <c r="K191" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L191" t="s">
         <v>34</v>
@@ -13453,7 +13453,7 @@
         <v>34</v>
       </c>
       <c r="E196" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F196" t="s">
         <v>218</v>
@@ -13733,7 +13733,7 @@
         <v>34</v>
       </c>
       <c r="E201" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F201" t="s">
         <v>218</v>
@@ -13789,7 +13789,7 @@
         <v>34</v>
       </c>
       <c r="E202" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F202" t="s">
         <v>218</v>
@@ -13845,7 +13845,7 @@
         <v>34</v>
       </c>
       <c r="E203" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F203" t="s">
         <v>218</v>
@@ -14125,7 +14125,7 @@
         <v>34</v>
       </c>
       <c r="E208" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F208" t="s">
         <v>218</v>
@@ -14181,7 +14181,7 @@
         <v>34</v>
       </c>
       <c r="E209" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F209" t="s">
         <v>218</v>
@@ -15077,7 +15077,7 @@
         <v>34</v>
       </c>
       <c r="E225" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F225" t="s">
         <v>218</v>
@@ -15095,7 +15095,7 @@
         <v>304</v>
       </c>
       <c r="K225" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L225" t="s">
         <v>34</v>
@@ -15133,7 +15133,7 @@
         <v>34</v>
       </c>
       <c r="E226" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F226" t="s">
         <v>218</v>
@@ -15189,7 +15189,7 @@
         <v>34</v>
       </c>
       <c r="E227" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F227" t="s">
         <v>218</v>
@@ -15245,7 +15245,7 @@
         <v>34</v>
       </c>
       <c r="E228" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="F228" t="s">
         <v>218</v>
@@ -15469,7 +15469,7 @@
         <v>33</v>
       </c>
       <c r="E232" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F232" t="s">
         <v>218</v>
@@ -15525,7 +15525,7 @@
         <v>34</v>
       </c>
       <c r="E233" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F233" t="s">
         <v>218</v>
@@ -15581,7 +15581,7 @@
         <v>33</v>
       </c>
       <c r="E234" t="s">
-        <v>275</v>
+        <v>244</v>
       </c>
       <c r="F234" t="s">
         <v>218</v>
@@ -15590,16 +15590,16 @@
         <v>41</v>
       </c>
       <c r="H234" t="s">
-        <v>457</v>
+        <v>508</v>
       </c>
       <c r="I234" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="J234" t="s">
-        <v>304</v>
+        <v>510</v>
       </c>
       <c r="K234" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="L234" t="s">
         <v>34</v>
@@ -15611,10 +15611,10 @@
         <v>47</v>
       </c>
       <c r="O234" t="s">
-        <v>105</v>
+        <v>247</v>
       </c>
       <c r="P234" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="Q234" t="s">
         <v>47</v>
@@ -15637,7 +15637,7 @@
         <v>34</v>
       </c>
       <c r="E235" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="F235" t="s">
         <v>218</v>
@@ -15646,16 +15646,16 @@
         <v>41</v>
       </c>
       <c r="H235" t="s">
-        <v>457</v>
+        <v>511</v>
       </c>
       <c r="I235" t="s">
-        <v>509</v>
+        <v>430</v>
       </c>
       <c r="J235" t="s">
-        <v>300</v>
+        <v>512</v>
       </c>
       <c r="K235" t="s">
-        <v>119</v>
+        <v>70</v>
       </c>
       <c r="L235" t="s">
         <v>34</v>
@@ -15667,10 +15667,10 @@
         <v>47</v>
       </c>
       <c r="O235" t="s">
-        <v>130</v>
+        <v>71</v>
       </c>
       <c r="P235" t="s">
-        <v>509</v>
+        <v>430</v>
       </c>
       <c r="Q235" t="s">
         <v>47</v>
@@ -15693,7 +15693,7 @@
         <v>34</v>
       </c>
       <c r="E236" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="F236" t="s">
         <v>218</v>
@@ -15702,16 +15702,16 @@
         <v>41</v>
       </c>
       <c r="H236" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="I236" t="s">
-        <v>511</v>
+        <v>439</v>
       </c>
       <c r="J236" t="s">
         <v>512</v>
       </c>
       <c r="K236" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="L236" t="s">
         <v>34</v>
@@ -15723,10 +15723,10 @@
         <v>47</v>
       </c>
       <c r="O236" t="s">
-        <v>247</v>
+        <v>114</v>
       </c>
       <c r="P236" t="s">
-        <v>511</v>
+        <v>439</v>
       </c>
       <c r="Q236" t="s">
         <v>47</v>
@@ -15749,7 +15749,7 @@
         <v>34</v>
       </c>
       <c r="E237" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="F237" t="s">
         <v>218</v>
@@ -15758,10 +15758,10 @@
         <v>41</v>
       </c>
       <c r="H237" t="s">
+        <v>457</v>
+      </c>
+      <c r="I237" t="s">
         <v>513</v>
-      </c>
-      <c r="I237" t="s">
-        <v>428</v>
       </c>
       <c r="J237" t="s">
         <v>300</v>
@@ -15779,10 +15779,10 @@
         <v>47</v>
       </c>
       <c r="O237" t="s">
-        <v>250</v>
+        <v>130</v>
       </c>
       <c r="P237" t="s">
-        <v>428</v>
+        <v>513</v>
       </c>
       <c r="Q237" t="s">
         <v>47</v>
@@ -15805,7 +15805,7 @@
         <v>34</v>
       </c>
       <c r="E238" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="F238" t="s">
         <v>218</v>
@@ -15814,16 +15814,16 @@
         <v>41</v>
       </c>
       <c r="H238" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="I238" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="J238" t="s">
-        <v>514</v>
+        <v>300</v>
       </c>
       <c r="K238" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="L238" t="s">
         <v>34</v>
@@ -15835,10 +15835,10 @@
         <v>47</v>
       </c>
       <c r="O238" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="P238" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="Q238" t="s">
         <v>47</v>
@@ -15861,7 +15861,7 @@
         <v>34</v>
       </c>
       <c r="E239" t="s">
-        <v>223</v>
+        <v>253</v>
       </c>
       <c r="F239" t="s">
         <v>218</v>
@@ -15870,16 +15870,16 @@
         <v>41</v>
       </c>
       <c r="H239" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="I239" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="J239" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="K239" t="s">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="L239" t="s">
         <v>34</v>
@@ -15891,10 +15891,10 @@
         <v>47</v>
       </c>
       <c r="O239" t="s">
-        <v>114</v>
+        <v>255</v>
       </c>
       <c r="P239" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="Q239" t="s">
         <v>47</v>
@@ -15917,25 +15917,25 @@
         <v>34</v>
       </c>
       <c r="E240" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F240" t="s">
-        <v>499</v>
+        <v>218</v>
       </c>
       <c r="G240" t="s">
         <v>41</v>
       </c>
       <c r="H240" t="s">
-        <v>457</v>
+        <v>511</v>
       </c>
       <c r="I240" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="J240" t="s">
-        <v>80</v>
+        <v>512</v>
       </c>
       <c r="K240" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L240" t="s">
         <v>34</v>
@@ -15947,13 +15947,13 @@
         <v>47</v>
       </c>
       <c r="O240" t="s">
-        <v>34</v>
+        <v>310</v>
       </c>
       <c r="P240" t="s">
-        <v>34</v>
+        <v>438</v>
       </c>
       <c r="Q240" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R240" t="s">
         <v>34</v>
@@ -15973,25 +15973,25 @@
         <v>34</v>
       </c>
       <c r="E241" t="s">
-        <v>360</v>
+        <v>275</v>
       </c>
       <c r="F241" t="s">
-        <v>499</v>
+        <v>218</v>
       </c>
       <c r="G241" t="s">
         <v>41</v>
       </c>
       <c r="H241" t="s">
-        <v>215</v>
+        <v>457</v>
       </c>
       <c r="I241" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="J241" t="s">
-        <v>119</v>
+        <v>304</v>
       </c>
       <c r="K241" t="s">
-        <v>119</v>
+        <v>58</v>
       </c>
       <c r="L241" t="s">
         <v>34</v>
@@ -16003,13 +16003,13 @@
         <v>47</v>
       </c>
       <c r="O241" t="s">
-        <v>34</v>
+        <v>105</v>
       </c>
       <c r="P241" t="s">
-        <v>34</v>
+        <v>515</v>
       </c>
       <c r="Q241" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R241" t="s">
         <v>34</v>
@@ -16029,25 +16029,25 @@
         <v>34</v>
       </c>
       <c r="E242" t="s">
-        <v>357</v>
+        <v>472</v>
       </c>
       <c r="F242" t="s">
-        <v>499</v>
+        <v>218</v>
       </c>
       <c r="G242" t="s">
         <v>41</v>
       </c>
       <c r="H242" t="s">
-        <v>215</v>
+        <v>457</v>
       </c>
       <c r="I242" t="s">
-        <v>517</v>
+        <v>473</v>
       </c>
       <c r="J242" t="s">
-        <v>80</v>
+        <v>461</v>
       </c>
       <c r="K242" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="L242" t="s">
         <v>34</v>
@@ -16059,13 +16059,13 @@
         <v>47</v>
       </c>
       <c r="O242" t="s">
-        <v>34</v>
+        <v>475</v>
       </c>
       <c r="P242" t="s">
-        <v>34</v>
+        <v>473</v>
       </c>
       <c r="Q242" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R242" t="s">
         <v>34</v>
@@ -16085,25 +16085,25 @@
         <v>34</v>
       </c>
       <c r="E243" t="s">
-        <v>251</v>
+        <v>516</v>
       </c>
       <c r="F243" t="s">
-        <v>218</v>
+        <v>499</v>
       </c>
       <c r="G243" t="s">
         <v>41</v>
       </c>
       <c r="H243" t="s">
-        <v>513</v>
+        <v>215</v>
       </c>
       <c r="I243" t="s">
-        <v>430</v>
+        <v>464</v>
       </c>
       <c r="J243" t="s">
-        <v>515</v>
+        <v>134</v>
       </c>
       <c r="K243" t="s">
-        <v>70</v>
+        <v>134</v>
       </c>
       <c r="L243" t="s">
         <v>34</v>
@@ -16115,13 +16115,13 @@
         <v>47</v>
       </c>
       <c r="O243" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="P243" t="s">
-        <v>430</v>
+        <v>34</v>
       </c>
       <c r="Q243" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R243" t="s">
         <v>34</v>
@@ -16141,25 +16141,25 @@
         <v>34</v>
       </c>
       <c r="E244" t="s">
-        <v>472</v>
+        <v>360</v>
       </c>
       <c r="F244" t="s">
-        <v>218</v>
+        <v>499</v>
       </c>
       <c r="G244" t="s">
         <v>41</v>
       </c>
       <c r="H244" t="s">
-        <v>457</v>
+        <v>215</v>
       </c>
       <c r="I244" t="s">
-        <v>473</v>
+        <v>517</v>
       </c>
       <c r="J244" t="s">
-        <v>461</v>
+        <v>119</v>
       </c>
       <c r="K244" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="L244" t="s">
         <v>34</v>
@@ -16171,13 +16171,13 @@
         <v>47</v>
       </c>
       <c r="O244" t="s">
-        <v>475</v>
+        <v>34</v>
       </c>
       <c r="P244" t="s">
-        <v>473</v>
+        <v>34</v>
       </c>
       <c r="Q244" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R244" t="s">
         <v>34</v>
@@ -16197,25 +16197,25 @@
         <v>34</v>
       </c>
       <c r="E245" t="s">
+        <v>223</v>
+      </c>
+      <c r="F245" t="s">
+        <v>218</v>
+      </c>
+      <c r="G245" t="s">
+        <v>41</v>
+      </c>
+      <c r="H245" t="s">
+        <v>457</v>
+      </c>
+      <c r="I245" t="s">
         <v>518</v>
       </c>
-      <c r="F245" t="s">
-        <v>499</v>
-      </c>
-      <c r="G245" t="s">
-        <v>41</v>
-      </c>
-      <c r="H245" t="s">
-        <v>215</v>
-      </c>
-      <c r="I245" t="s">
-        <v>464</v>
-      </c>
       <c r="J245" t="s">
-        <v>134</v>
+        <v>304</v>
       </c>
       <c r="K245" t="s">
-        <v>134</v>
+        <v>101</v>
       </c>
       <c r="L245" t="s">
         <v>34</v>
@@ -16227,13 +16227,13 @@
         <v>47</v>
       </c>
       <c r="O245" t="s">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="P245" t="s">
-        <v>34</v>
+        <v>518</v>
       </c>
       <c r="Q245" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R245" t="s">
         <v>34</v>
@@ -16253,25 +16253,25 @@
         <v>34</v>
       </c>
       <c r="E246" t="s">
-        <v>232</v>
+        <v>354</v>
       </c>
       <c r="F246" t="s">
-        <v>218</v>
+        <v>499</v>
       </c>
       <c r="G246" t="s">
         <v>41</v>
       </c>
       <c r="H246" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="I246" t="s">
-        <v>438</v>
+        <v>520</v>
       </c>
       <c r="J246" t="s">
-        <v>515</v>
+        <v>90</v>
       </c>
       <c r="K246" t="s">
-        <v>90</v>
+        <v>227</v>
       </c>
       <c r="L246" t="s">
         <v>34</v>
@@ -16283,13 +16283,13 @@
         <v>47</v>
       </c>
       <c r="O246" t="s">
-        <v>310</v>
+        <v>34</v>
       </c>
       <c r="P246" t="s">
-        <v>438</v>
+        <v>34</v>
       </c>
       <c r="Q246" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R246" t="s">
         <v>34</v>
@@ -16309,7 +16309,7 @@
         <v>34</v>
       </c>
       <c r="E247" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F247" t="s">
         <v>499</v>
@@ -16318,16 +16318,16 @@
         <v>41</v>
       </c>
       <c r="H247" t="s">
-        <v>519</v>
+        <v>215</v>
       </c>
       <c r="I247" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="J247" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K247" t="s">
-        <v>229</v>
+        <v>80</v>
       </c>
       <c r="L247" t="s">
         <v>34</v>
@@ -16365,25 +16365,25 @@
         <v>34</v>
       </c>
       <c r="E248" t="s">
-        <v>225</v>
+        <v>363</v>
       </c>
       <c r="F248" t="s">
-        <v>218</v>
+        <v>499</v>
       </c>
       <c r="G248" t="s">
         <v>41</v>
       </c>
       <c r="H248" t="s">
-        <v>457</v>
+        <v>511</v>
       </c>
       <c r="I248" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="J248" t="s">
-        <v>304</v>
+        <v>126</v>
       </c>
       <c r="K248" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="L248" t="s">
         <v>34</v>
@@ -16395,13 +16395,13 @@
         <v>47</v>
       </c>
       <c r="O248" t="s">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="P248" t="s">
-        <v>521</v>
+        <v>34</v>
       </c>
       <c r="Q248" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R248" t="s">
         <v>34</v>
@@ -16421,7 +16421,7 @@
         <v>34</v>
       </c>
       <c r="E249" t="s">
-        <v>348</v>
+        <v>242</v>
       </c>
       <c r="F249" t="s">
         <v>499</v>
@@ -16430,16 +16430,16 @@
         <v>41</v>
       </c>
       <c r="H249" t="s">
-        <v>215</v>
+        <v>457</v>
       </c>
       <c r="I249" t="s">
-        <v>522</v>
+        <v>441</v>
       </c>
       <c r="J249" t="s">
-        <v>126</v>
+        <v>80</v>
       </c>
       <c r="K249" t="s">
-        <v>126</v>
+        <v>80</v>
       </c>
       <c r="L249" t="s">
         <v>34</v>
@@ -16477,7 +16477,7 @@
         <v>34</v>
       </c>
       <c r="E250" t="s">
-        <v>363</v>
+        <v>348</v>
       </c>
       <c r="F250" t="s">
         <v>499</v>
@@ -16533,7 +16533,7 @@
         <v>33</v>
       </c>
       <c r="E251" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F251" t="s">
         <v>211</v>
@@ -16757,7 +16757,7 @@
         <v>34</v>
       </c>
       <c r="E255" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F255" t="s">
         <v>499</v>
@@ -16813,7 +16813,7 @@
         <v>34</v>
       </c>
       <c r="E256" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F256" t="s">
         <v>499</v>
@@ -16831,7 +16831,7 @@
         <v>90</v>
       </c>
       <c r="K256" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L256" t="s">
         <v>34</v>
@@ -16869,7 +16869,7 @@
         <v>34</v>
       </c>
       <c r="E257" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F257" t="s">
         <v>499</v>
@@ -17261,7 +17261,7 @@
         <v>34</v>
       </c>
       <c r="E264" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="F264" t="s">
         <v>211</v>
@@ -17438,7 +17438,7 @@
         <v>41</v>
       </c>
       <c r="H267" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="I267" t="s">
         <v>555</v>
@@ -17765,7 +17765,7 @@
         <v>33</v>
       </c>
       <c r="E273" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F273" t="s">
         <v>211</v>
@@ -17783,7 +17783,7 @@
         <v>96</v>
       </c>
       <c r="K273" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L273" t="s">
         <v>567</v>
@@ -18004,10 +18004,10 @@
         <v>578</v>
       </c>
       <c r="J277" t="s">
-        <v>579</v>
+        <v>304</v>
       </c>
       <c r="K277" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="L277" t="s">
         <v>34</v>
@@ -18019,7 +18019,7 @@
         <v>47</v>
       </c>
       <c r="O277" t="s">
-        <v>247</v>
+        <v>579</v>
       </c>
       <c r="P277" t="s">
         <v>578</v>
@@ -18075,7 +18075,7 @@
         <v>47</v>
       </c>
       <c r="O278" t="s">
-        <v>582</v>
+        <v>48</v>
       </c>
       <c r="P278" t="s">
         <v>581</v>
@@ -18101,7 +18101,7 @@
         <v>34</v>
       </c>
       <c r="E279" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="F279" t="s">
         <v>211</v>
@@ -18113,13 +18113,13 @@
         <v>574</v>
       </c>
       <c r="I279" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="J279" t="s">
         <v>304</v>
       </c>
       <c r="K279" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="L279" t="s">
         <v>34</v>
@@ -18131,10 +18131,10 @@
         <v>47</v>
       </c>
       <c r="O279" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="P279" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="Q279" t="s">
         <v>47</v>
@@ -18157,7 +18157,7 @@
         <v>34</v>
       </c>
       <c r="E280" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="F280" t="s">
         <v>211</v>
@@ -18169,13 +18169,13 @@
         <v>574</v>
       </c>
       <c r="I280" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="J280" t="s">
         <v>304</v>
       </c>
       <c r="K280" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="L280" t="s">
         <v>34</v>
@@ -18187,10 +18187,10 @@
         <v>47</v>
       </c>
       <c r="O280" t="s">
-        <v>588</v>
+        <v>332</v>
       </c>
       <c r="P280" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="Q280" t="s">
         <v>47</v>
@@ -18213,7 +18213,7 @@
         <v>34</v>
       </c>
       <c r="E281" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="F281" t="s">
         <v>211</v>
@@ -18225,13 +18225,13 @@
         <v>574</v>
       </c>
       <c r="I281" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="J281" t="s">
-        <v>70</v>
+        <v>304</v>
       </c>
       <c r="K281" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="L281" t="s">
         <v>34</v>
@@ -18243,10 +18243,10 @@
         <v>47</v>
       </c>
       <c r="O281" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="P281" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="Q281" t="s">
         <v>47</v>
@@ -18269,7 +18269,7 @@
         <v>34</v>
       </c>
       <c r="E282" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="F282" t="s">
         <v>211</v>
@@ -18281,7 +18281,7 @@
         <v>574</v>
       </c>
       <c r="I282" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="J282" t="s">
         <v>304</v>
@@ -18299,10 +18299,10 @@
         <v>47</v>
       </c>
       <c r="O282" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="P282" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="Q282" t="s">
         <v>47</v>
@@ -18325,7 +18325,7 @@
         <v>34</v>
       </c>
       <c r="E283" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="F283" t="s">
         <v>211</v>
@@ -18337,7 +18337,7 @@
         <v>574</v>
       </c>
       <c r="I283" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="J283" t="s">
         <v>304</v>
@@ -18355,10 +18355,10 @@
         <v>47</v>
       </c>
       <c r="O283" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="P283" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="Q283" t="s">
         <v>47</v>
@@ -18381,7 +18381,7 @@
         <v>34</v>
       </c>
       <c r="E284" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="F284" t="s">
         <v>211</v>
@@ -18393,7 +18393,7 @@
         <v>574</v>
       </c>
       <c r="I284" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="J284" t="s">
         <v>304</v>
@@ -18411,10 +18411,10 @@
         <v>47</v>
       </c>
       <c r="O284" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="P284" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="Q284" t="s">
         <v>47</v>
@@ -18437,7 +18437,7 @@
         <v>34</v>
       </c>
       <c r="E285" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F285" t="s">
         <v>211</v>
@@ -18449,7 +18449,7 @@
         <v>574</v>
       </c>
       <c r="I285" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="J285" t="s">
         <v>304</v>
@@ -18467,10 +18467,10 @@
         <v>47</v>
       </c>
       <c r="O285" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="P285" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="Q285" t="s">
         <v>47</v>
@@ -18493,7 +18493,7 @@
         <v>34</v>
       </c>
       <c r="E286" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="F286" t="s">
         <v>211</v>
@@ -18505,7 +18505,7 @@
         <v>574</v>
       </c>
       <c r="I286" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="J286" t="s">
         <v>304</v>
@@ -18523,10 +18523,10 @@
         <v>47</v>
       </c>
       <c r="O286" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="P286" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="Q286" t="s">
         <v>47</v>
@@ -18549,7 +18549,7 @@
         <v>34</v>
       </c>
       <c r="E287" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="F287" t="s">
         <v>211</v>
@@ -18561,13 +18561,13 @@
         <v>574</v>
       </c>
       <c r="I287" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="J287" t="s">
         <v>304</v>
       </c>
       <c r="K287" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="L287" t="s">
         <v>34</v>
@@ -18579,10 +18579,10 @@
         <v>47</v>
       </c>
       <c r="O287" t="s">
-        <v>86</v>
+        <v>607</v>
       </c>
       <c r="P287" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="Q287" t="s">
         <v>47</v>
@@ -18605,7 +18605,7 @@
         <v>34</v>
       </c>
       <c r="E288" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F288" t="s">
         <v>211</v>
@@ -18617,13 +18617,13 @@
         <v>574</v>
       </c>
       <c r="I288" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="J288" t="s">
-        <v>304</v>
+        <v>70</v>
       </c>
       <c r="K288" t="s">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="L288" t="s">
         <v>34</v>
@@ -18635,10 +18635,10 @@
         <v>47</v>
       </c>
       <c r="O288" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P288" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q288" t="s">
         <v>47</v>
@@ -18661,7 +18661,7 @@
         <v>34</v>
       </c>
       <c r="E289" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="F289" t="s">
         <v>211</v>
@@ -18673,7 +18673,7 @@
         <v>574</v>
       </c>
       <c r="I289" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="J289" t="s">
         <v>304</v>
@@ -18691,10 +18691,10 @@
         <v>47</v>
       </c>
       <c r="O289" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="P289" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="Q289" t="s">
         <v>47</v>
@@ -18717,7 +18717,7 @@
         <v>34</v>
       </c>
       <c r="E290" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F290" t="s">
         <v>211</v>
@@ -18729,7 +18729,7 @@
         <v>574</v>
       </c>
       <c r="I290" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="J290" t="s">
         <v>304</v>
@@ -18747,10 +18747,10 @@
         <v>47</v>
       </c>
       <c r="O290" t="s">
-        <v>48</v>
+        <v>616</v>
       </c>
       <c r="P290" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="Q290" t="s">
         <v>47</v>
@@ -18803,7 +18803,7 @@
         <v>47</v>
       </c>
       <c r="O291" t="s">
-        <v>48</v>
+        <v>619</v>
       </c>
       <c r="P291" t="s">
         <v>618</v>
@@ -18829,7 +18829,7 @@
         <v>34</v>
       </c>
       <c r="E292" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F292" t="s">
         <v>211</v>
@@ -18841,7 +18841,7 @@
         <v>574</v>
       </c>
       <c r="I292" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="J292" t="s">
         <v>304</v>
@@ -18850,7 +18850,7 @@
         <v>96</v>
       </c>
       <c r="L292" t="s">
-        <v>34</v>
+        <v>622</v>
       </c>
       <c r="M292" t="s">
         <v>572</v>
@@ -18859,10 +18859,10 @@
         <v>47</v>
       </c>
       <c r="O292" t="s">
-        <v>319</v>
+        <v>48</v>
       </c>
       <c r="P292" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="Q292" t="s">
         <v>47</v>
@@ -18885,7 +18885,7 @@
         <v>34</v>
       </c>
       <c r="E293" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="F293" t="s">
         <v>211</v>
@@ -18897,7 +18897,7 @@
         <v>574</v>
       </c>
       <c r="I293" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="J293" t="s">
         <v>304</v>
@@ -18915,10 +18915,10 @@
         <v>47</v>
       </c>
       <c r="O293" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="P293" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="Q293" t="s">
         <v>47</v>
@@ -18941,7 +18941,7 @@
         <v>34</v>
       </c>
       <c r="E294" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="F294" t="s">
         <v>211</v>
@@ -18953,7 +18953,7 @@
         <v>574</v>
       </c>
       <c r="I294" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="J294" t="s">
         <v>304</v>
@@ -18971,10 +18971,10 @@
         <v>47</v>
       </c>
       <c r="O294" t="s">
-        <v>626</v>
+        <v>48</v>
       </c>
       <c r="P294" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="Q294" t="s">
         <v>47</v>
@@ -18997,7 +18997,7 @@
         <v>34</v>
       </c>
       <c r="E295" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F295" t="s">
         <v>211</v>
@@ -19009,7 +19009,7 @@
         <v>574</v>
       </c>
       <c r="I295" t="s">
-        <v>628</v>
+        <v>575</v>
       </c>
       <c r="J295" t="s">
         <v>304</v>
@@ -19018,7 +19018,7 @@
         <v>96</v>
       </c>
       <c r="L295" t="s">
-        <v>629</v>
+        <v>34</v>
       </c>
       <c r="M295" t="s">
         <v>572</v>
@@ -19027,10 +19027,10 @@
         <v>47</v>
       </c>
       <c r="O295" t="s">
-        <v>48</v>
+        <v>629</v>
       </c>
       <c r="P295" t="s">
-        <v>628</v>
+        <v>575</v>
       </c>
       <c r="Q295" t="s">
         <v>47</v>
@@ -19083,7 +19083,7 @@
         <v>47</v>
       </c>
       <c r="O296" t="s">
-        <v>332</v>
+        <v>632</v>
       </c>
       <c r="P296" t="s">
         <v>631</v>
@@ -19109,7 +19109,7 @@
         <v>34</v>
       </c>
       <c r="E297" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="F297" t="s">
         <v>211</v>
@@ -19121,13 +19121,13 @@
         <v>574</v>
       </c>
       <c r="I297" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="J297" t="s">
         <v>304</v>
       </c>
       <c r="K297" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="L297" t="s">
         <v>34</v>
@@ -19139,10 +19139,10 @@
         <v>47</v>
       </c>
       <c r="O297" t="s">
+        <v>86</v>
+      </c>
+      <c r="P297" t="s">
         <v>634</v>
-      </c>
-      <c r="P297" t="s">
-        <v>633</v>
       </c>
       <c r="Q297" t="s">
         <v>47</v>
@@ -19177,7 +19177,7 @@
         <v>574</v>
       </c>
       <c r="I298" t="s">
-        <v>610</v>
+        <v>636</v>
       </c>
       <c r="J298" t="s">
         <v>304</v>
@@ -19195,10 +19195,10 @@
         <v>47</v>
       </c>
       <c r="O298" t="s">
+        <v>319</v>
+      </c>
+      <c r="P298" t="s">
         <v>636</v>
-      </c>
-      <c r="P298" t="s">
-        <v>610</v>
       </c>
       <c r="Q298" t="s">
         <v>47</v>
@@ -19277,7 +19277,7 @@
         <v>34</v>
       </c>
       <c r="E300" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="F300" t="s">
         <v>211</v>
@@ -19295,7 +19295,7 @@
         <v>639</v>
       </c>
       <c r="K300" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="L300" t="s">
         <v>34</v>
@@ -19307,7 +19307,7 @@
         <v>47</v>
       </c>
       <c r="O300" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="P300" t="s">
         <v>641</v>
@@ -19333,7 +19333,7 @@
         <v>34</v>
       </c>
       <c r="E301" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="F301" t="s">
         <v>211</v>
@@ -19351,7 +19351,7 @@
         <v>639</v>
       </c>
       <c r="K301" t="s">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="L301" t="s">
         <v>34</v>
@@ -19363,7 +19363,7 @@
         <v>47</v>
       </c>
       <c r="O301" t="s">
-        <v>114</v>
+        <v>86</v>
       </c>
       <c r="P301" t="s">
         <v>642</v>
@@ -19389,7 +19389,7 @@
         <v>34</v>
       </c>
       <c r="E302" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="F302" t="s">
         <v>211</v>
@@ -19407,7 +19407,7 @@
         <v>644</v>
       </c>
       <c r="K302" t="s">
-        <v>58</v>
+        <v>101</v>
       </c>
       <c r="L302" t="s">
         <v>34</v>
@@ -19419,7 +19419,7 @@
         <v>47</v>
       </c>
       <c r="O302" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="P302" t="s">
         <v>643</v>
@@ -19460,7 +19460,7 @@
         <v>645</v>
       </c>
       <c r="J303" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="K303" t="s">
         <v>80</v>
@@ -19501,7 +19501,7 @@
         <v>34</v>
       </c>
       <c r="E304" t="s">
-        <v>66</v>
+        <v>647</v>
       </c>
       <c r="F304" t="s">
         <v>211</v>
@@ -19513,13 +19513,13 @@
         <v>574</v>
       </c>
       <c r="I304" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="J304" t="s">
         <v>644</v>
       </c>
       <c r="K304" t="s">
-        <v>70</v>
+        <v>113</v>
       </c>
       <c r="L304" t="s">
         <v>34</v>
@@ -19531,10 +19531,10 @@
         <v>47</v>
       </c>
       <c r="O304" t="s">
-        <v>71</v>
+        <v>114</v>
       </c>
       <c r="P304" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="Q304" t="s">
         <v>47</v>
@@ -19557,7 +19557,7 @@
         <v>34</v>
       </c>
       <c r="E305" t="s">
-        <v>98</v>
+        <v>649</v>
       </c>
       <c r="F305" t="s">
         <v>211</v>
@@ -19569,13 +19569,13 @@
         <v>574</v>
       </c>
       <c r="I305" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="J305" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="K305" t="s">
-        <v>101</v>
+        <v>134</v>
       </c>
       <c r="L305" t="s">
         <v>34</v>
@@ -19587,10 +19587,10 @@
         <v>47</v>
       </c>
       <c r="O305" t="s">
-        <v>102</v>
+        <v>160</v>
       </c>
       <c r="P305" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="Q305" t="s">
         <v>47</v>
@@ -19613,7 +19613,7 @@
         <v>34</v>
       </c>
       <c r="E306" t="s">
-        <v>649</v>
+        <v>103</v>
       </c>
       <c r="F306" t="s">
         <v>211</v>
@@ -19625,13 +19625,13 @@
         <v>574</v>
       </c>
       <c r="I306" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="J306" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="K306" t="s">
-        <v>113</v>
+        <v>58</v>
       </c>
       <c r="L306" t="s">
         <v>34</v>
@@ -19643,10 +19643,10 @@
         <v>47</v>
       </c>
       <c r="O306" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="P306" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="Q306" t="s">
         <v>47</v>
@@ -19669,7 +19669,7 @@
         <v>34</v>
       </c>
       <c r="E307" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F307" t="s">
         <v>211</v>
@@ -19681,13 +19681,13 @@
         <v>574</v>
       </c>
       <c r="I307" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="J307" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="K307" t="s">
-        <v>134</v>
+        <v>58</v>
       </c>
       <c r="L307" t="s">
         <v>34</v>
@@ -19699,10 +19699,10 @@
         <v>47</v>
       </c>
       <c r="O307" t="s">
-        <v>160</v>
+        <v>105</v>
       </c>
       <c r="P307" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="Q307" t="s">
         <v>47</v>
@@ -19725,7 +19725,7 @@
         <v>34</v>
       </c>
       <c r="E308" t="s">
-        <v>653</v>
+        <v>66</v>
       </c>
       <c r="F308" t="s">
         <v>211</v>
@@ -19740,10 +19740,10 @@
         <v>654</v>
       </c>
       <c r="J308" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="K308" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="L308" t="s">
         <v>34</v>
@@ -19755,7 +19755,7 @@
         <v>47</v>
       </c>
       <c r="O308" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="P308" t="s">
         <v>654</v>
@@ -19796,10 +19796,10 @@
         <v>656</v>
       </c>
       <c r="J309" t="s">
-        <v>579</v>
+        <v>657</v>
       </c>
       <c r="K309" t="s">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="L309" t="s">
         <v>34</v>
@@ -19811,7 +19811,7 @@
         <v>47</v>
       </c>
       <c r="O309" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="P309" t="s">
         <v>656</v>
@@ -19837,7 +19837,7 @@
         <v>34</v>
       </c>
       <c r="E310" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="F310" t="s">
         <v>211</v>
@@ -19849,13 +19849,13 @@
         <v>574</v>
       </c>
       <c r="I310" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="J310" t="s">
-        <v>579</v>
+        <v>657</v>
       </c>
       <c r="K310" t="s">
-        <v>58</v>
+        <v>101</v>
       </c>
       <c r="L310" t="s">
         <v>34</v>
@@ -19867,10 +19867,10 @@
         <v>47</v>
       </c>
       <c r="O310" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="P310" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="Q310" t="s">
         <v>47</v>
@@ -19893,7 +19893,7 @@
         <v>34</v>
       </c>
       <c r="E311" t="s">
-        <v>535</v>
+        <v>660</v>
       </c>
       <c r="F311" t="s">
         <v>211</v>
@@ -19905,10 +19905,10 @@
         <v>574</v>
       </c>
       <c r="I311" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="J311" t="s">
-        <v>579</v>
+        <v>657</v>
       </c>
       <c r="K311" t="s">
         <v>80</v>
@@ -19923,10 +19923,10 @@
         <v>47</v>
       </c>
       <c r="O311" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="P311" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="Q311" t="s">
         <v>47</v>
@@ -19949,7 +19949,7 @@
         <v>34</v>
       </c>
       <c r="E312" t="s">
-        <v>660</v>
+        <v>535</v>
       </c>
       <c r="F312" t="s">
         <v>211</v>
@@ -19961,13 +19961,13 @@
         <v>574</v>
       </c>
       <c r="I312" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="J312" t="s">
-        <v>304</v>
+        <v>657</v>
       </c>
       <c r="K312" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="L312" t="s">
         <v>34</v>
@@ -19979,10 +19979,10 @@
         <v>47</v>
       </c>
       <c r="O312" t="s">
+        <v>255</v>
+      </c>
+      <c r="P312" t="s">
         <v>662</v>
-      </c>
-      <c r="P312" t="s">
-        <v>661</v>
       </c>
       <c r="Q312" t="s">
         <v>47</v>
@@ -20173,7 +20173,7 @@
         <v>34</v>
       </c>
       <c r="E316" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="F316" t="s">
         <v>40</v>
@@ -20285,7 +20285,7 @@
         <v>34</v>
       </c>
       <c r="E318" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F318" t="s">
         <v>667</v>
@@ -20621,7 +20621,7 @@
         <v>34</v>
       </c>
       <c r="E324" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F324" t="s">
         <v>40</v>
@@ -20677,7 +20677,7 @@
         <v>34</v>
       </c>
       <c r="E325" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F325" t="s">
         <v>40</v>
@@ -20789,7 +20789,7 @@
         <v>34</v>
       </c>
       <c r="E327" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F327" t="s">
         <v>40</v>
@@ -20845,7 +20845,7 @@
         <v>34</v>
       </c>
       <c r="E328" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F328" t="s">
         <v>667</v>
@@ -20863,7 +20863,7 @@
         <v>90</v>
       </c>
       <c r="K328" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L328" t="s">
         <v>34</v>
@@ -21031,7 +21031,7 @@
         <v>680</v>
       </c>
       <c r="K331" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L331" t="s">
         <v>34</v>
@@ -21143,7 +21143,7 @@
         <v>686</v>
       </c>
       <c r="K333" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L333" t="s">
         <v>687</v>
@@ -21517,28 +21517,28 @@
         <v>33</v>
       </c>
       <c r="E340" t="s">
+        <v>673</v>
+      </c>
+      <c r="F340" t="s">
+        <v>40</v>
+      </c>
+      <c r="G340" t="s">
+        <v>41</v>
+      </c>
+      <c r="H340" t="s">
         <v>703</v>
-      </c>
-      <c r="F340" t="s">
-        <v>211</v>
-      </c>
-      <c r="G340" t="s">
-        <v>41</v>
-      </c>
-      <c r="H340" t="s">
-        <v>510</v>
       </c>
       <c r="I340" t="s">
         <v>704</v>
       </c>
       <c r="J340" t="s">
-        <v>474</v>
+        <v>686</v>
       </c>
       <c r="K340" t="s">
-        <v>229</v>
+        <v>45</v>
       </c>
       <c r="L340" t="s">
-        <v>34</v>
+        <v>705</v>
       </c>
       <c r="M340" t="s">
         <v>702</v>
@@ -21573,7 +21573,7 @@
         <v>34</v>
       </c>
       <c r="E341" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="F341" t="s">
         <v>211</v>
@@ -21582,16 +21582,16 @@
         <v>41</v>
       </c>
       <c r="H341" t="s">
-        <v>557</v>
+        <v>425</v>
       </c>
       <c r="I341" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="J341" t="s">
-        <v>461</v>
+        <v>474</v>
       </c>
       <c r="K341" t="s">
-        <v>229</v>
+        <v>178</v>
       </c>
       <c r="L341" t="s">
         <v>34</v>
@@ -21606,7 +21606,7 @@
         <v>48</v>
       </c>
       <c r="P341" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="Q341" t="s">
         <v>47</v>
@@ -21629,7 +21629,7 @@
         <v>34</v>
       </c>
       <c r="E342" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="F342" t="s">
         <v>211</v>
@@ -21638,16 +21638,16 @@
         <v>41</v>
       </c>
       <c r="H342" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="I342" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="J342" t="s">
         <v>474</v>
       </c>
       <c r="K342" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L342" t="s">
         <v>34</v>
@@ -21662,7 +21662,7 @@
         <v>48</v>
       </c>
       <c r="P342" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="Q342" t="s">
         <v>47</v>
@@ -21685,28 +21685,28 @@
         <v>34</v>
       </c>
       <c r="E343" t="s">
-        <v>673</v>
+        <v>711</v>
       </c>
       <c r="F343" t="s">
-        <v>40</v>
+        <v>211</v>
       </c>
       <c r="G343" t="s">
         <v>41</v>
       </c>
       <c r="H343" t="s">
-        <v>710</v>
+        <v>215</v>
       </c>
       <c r="I343" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="J343" t="s">
-        <v>335</v>
+        <v>474</v>
       </c>
       <c r="K343" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="L343" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="M343" t="s">
         <v>702</v>
@@ -21718,7 +21718,7 @@
         <v>48</v>
       </c>
       <c r="P343" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="Q343" t="s">
         <v>47</v>
@@ -21741,28 +21741,28 @@
         <v>34</v>
       </c>
       <c r="E344" t="s">
-        <v>673</v>
+        <v>714</v>
       </c>
       <c r="F344" t="s">
-        <v>40</v>
+        <v>211</v>
       </c>
       <c r="G344" t="s">
         <v>41</v>
       </c>
       <c r="H344" t="s">
-        <v>457</v>
+        <v>557</v>
       </c>
       <c r="I344" t="s">
-        <v>695</v>
+        <v>715</v>
       </c>
       <c r="J344" t="s">
-        <v>335</v>
+        <v>461</v>
       </c>
       <c r="K344" t="s">
-        <v>45</v>
+        <v>227</v>
       </c>
       <c r="L344" t="s">
-        <v>713</v>
+        <v>34</v>
       </c>
       <c r="M344" t="s">
         <v>702</v>
@@ -21774,7 +21774,7 @@
         <v>48</v>
       </c>
       <c r="P344" t="s">
-        <v>695</v>
+        <v>715</v>
       </c>
       <c r="Q344" t="s">
         <v>47</v>
@@ -21797,7 +21797,7 @@
         <v>34</v>
       </c>
       <c r="E345" t="s">
-        <v>175</v>
+        <v>673</v>
       </c>
       <c r="F345" t="s">
         <v>40</v>
@@ -21806,19 +21806,19 @@
         <v>41</v>
       </c>
       <c r="H345" t="s">
-        <v>513</v>
+        <v>716</v>
       </c>
       <c r="I345" t="s">
-        <v>695</v>
+        <v>717</v>
       </c>
       <c r="J345" t="s">
-        <v>70</v>
+        <v>686</v>
       </c>
       <c r="K345" t="s">
         <v>45</v>
       </c>
       <c r="L345" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="M345" t="s">
         <v>702</v>
@@ -21830,7 +21830,7 @@
         <v>48</v>
       </c>
       <c r="P345" t="s">
-        <v>695</v>
+        <v>717</v>
       </c>
       <c r="Q345" t="s">
         <v>47</v>
@@ -21853,28 +21853,28 @@
         <v>34</v>
       </c>
       <c r="E346" t="s">
-        <v>715</v>
+        <v>673</v>
       </c>
       <c r="F346" t="s">
-        <v>211</v>
+        <v>40</v>
       </c>
       <c r="G346" t="s">
         <v>41</v>
       </c>
       <c r="H346" t="s">
-        <v>557</v>
+        <v>719</v>
       </c>
       <c r="I346" t="s">
-        <v>695</v>
+        <v>720</v>
       </c>
       <c r="J346" t="s">
-        <v>474</v>
+        <v>686</v>
       </c>
       <c r="K346" t="s">
-        <v>122</v>
+        <v>45</v>
       </c>
       <c r="L346" t="s">
-        <v>34</v>
+        <v>721</v>
       </c>
       <c r="M346" t="s">
         <v>702</v>
@@ -21886,7 +21886,7 @@
         <v>48</v>
       </c>
       <c r="P346" t="s">
-        <v>695</v>
+        <v>720</v>
       </c>
       <c r="Q346" t="s">
         <v>47</v>
@@ -21909,28 +21909,28 @@
         <v>34</v>
       </c>
       <c r="E347" t="s">
-        <v>673</v>
+        <v>722</v>
       </c>
       <c r="F347" t="s">
-        <v>40</v>
+        <v>211</v>
       </c>
       <c r="G347" t="s">
         <v>41</v>
       </c>
       <c r="H347" t="s">
-        <v>716</v>
+        <v>557</v>
       </c>
       <c r="I347" t="s">
         <v>695</v>
       </c>
       <c r="J347" t="s">
-        <v>686</v>
+        <v>474</v>
       </c>
       <c r="K347" t="s">
-        <v>45</v>
+        <v>122</v>
       </c>
       <c r="L347" t="s">
-        <v>717</v>
+        <v>34</v>
       </c>
       <c r="M347" t="s">
         <v>702</v>
@@ -21965,28 +21965,28 @@
         <v>34</v>
       </c>
       <c r="E348" t="s">
-        <v>718</v>
+        <v>673</v>
       </c>
       <c r="F348" t="s">
-        <v>211</v>
+        <v>40</v>
       </c>
       <c r="G348" t="s">
         <v>41</v>
       </c>
       <c r="H348" t="s">
-        <v>215</v>
+        <v>723</v>
       </c>
       <c r="I348" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="J348" t="s">
-        <v>474</v>
+        <v>335</v>
       </c>
       <c r="K348" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="L348" t="s">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="M348" t="s">
         <v>702</v>
@@ -21998,7 +21998,7 @@
         <v>48</v>
       </c>
       <c r="P348" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="Q348" t="s">
         <v>47</v>
@@ -22021,28 +22021,28 @@
         <v>34</v>
       </c>
       <c r="E349" t="s">
-        <v>175</v>
+        <v>726</v>
       </c>
       <c r="F349" t="s">
-        <v>40</v>
+        <v>211</v>
       </c>
       <c r="G349" t="s">
         <v>41</v>
       </c>
       <c r="H349" t="s">
-        <v>447</v>
+        <v>508</v>
       </c>
       <c r="I349" t="s">
-        <v>155</v>
+        <v>727</v>
       </c>
       <c r="J349" t="s">
-        <v>122</v>
+        <v>474</v>
       </c>
       <c r="K349" t="s">
-        <v>45</v>
+        <v>227</v>
       </c>
       <c r="L349" t="s">
-        <v>721</v>
+        <v>34</v>
       </c>
       <c r="M349" t="s">
         <v>702</v>
@@ -22054,7 +22054,7 @@
         <v>48</v>
       </c>
       <c r="P349" t="s">
-        <v>155</v>
+        <v>727</v>
       </c>
       <c r="Q349" t="s">
         <v>47</v>
@@ -22086,10 +22086,10 @@
         <v>41</v>
       </c>
       <c r="H350" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="I350" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="J350" t="s">
         <v>686</v>
@@ -22098,7 +22098,7 @@
         <v>45</v>
       </c>
       <c r="L350" t="s">
-        <v>724</v>
+        <v>729</v>
       </c>
       <c r="M350" t="s">
         <v>702</v>
@@ -22110,7 +22110,7 @@
         <v>48</v>
       </c>
       <c r="P350" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="Q350" t="s">
         <v>47</v>
@@ -22133,7 +22133,7 @@
         <v>34</v>
       </c>
       <c r="E351" t="s">
-        <v>175</v>
+        <v>673</v>
       </c>
       <c r="F351" t="s">
         <v>40</v>
@@ -22142,19 +22142,19 @@
         <v>41</v>
       </c>
       <c r="H351" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="I351" t="s">
-        <v>155</v>
+        <v>731</v>
       </c>
       <c r="J351" t="s">
-        <v>122</v>
+        <v>686</v>
       </c>
       <c r="K351" t="s">
-        <v>122</v>
+        <v>45</v>
       </c>
       <c r="L351" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="M351" t="s">
         <v>702</v>
@@ -22166,7 +22166,7 @@
         <v>48</v>
       </c>
       <c r="P351" t="s">
-        <v>155</v>
+        <v>731</v>
       </c>
       <c r="Q351" t="s">
         <v>47</v>
@@ -22198,19 +22198,19 @@
         <v>41</v>
       </c>
       <c r="H352" t="s">
-        <v>727</v>
+        <v>457</v>
       </c>
       <c r="I352" t="s">
-        <v>728</v>
+        <v>695</v>
       </c>
       <c r="J352" t="s">
-        <v>686</v>
+        <v>335</v>
       </c>
       <c r="K352" t="s">
         <v>45</v>
       </c>
       <c r="L352" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="M352" t="s">
         <v>702</v>
@@ -22222,7 +22222,7 @@
         <v>48</v>
       </c>
       <c r="P352" t="s">
-        <v>728</v>
+        <v>695</v>
       </c>
       <c r="Q352" t="s">
         <v>47</v>
@@ -22245,7 +22245,7 @@
         <v>34</v>
       </c>
       <c r="E353" t="s">
-        <v>673</v>
+        <v>175</v>
       </c>
       <c r="F353" t="s">
         <v>40</v>
@@ -22254,19 +22254,19 @@
         <v>41</v>
       </c>
       <c r="H353" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="I353" t="s">
-        <v>723</v>
+        <v>155</v>
       </c>
       <c r="J353" t="s">
-        <v>686</v>
+        <v>122</v>
       </c>
       <c r="K353" t="s">
-        <v>45</v>
+        <v>122</v>
       </c>
       <c r="L353" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="M353" t="s">
         <v>702</v>
@@ -22278,7 +22278,7 @@
         <v>48</v>
       </c>
       <c r="P353" t="s">
-        <v>723</v>
+        <v>155</v>
       </c>
       <c r="Q353" t="s">
         <v>47</v>
@@ -22301,7 +22301,7 @@
         <v>34</v>
       </c>
       <c r="E354" t="s">
-        <v>673</v>
+        <v>175</v>
       </c>
       <c r="F354" t="s">
         <v>40</v>
@@ -22310,19 +22310,19 @@
         <v>41</v>
       </c>
       <c r="H354" t="s">
-        <v>732</v>
+        <v>447</v>
       </c>
       <c r="I354" t="s">
-        <v>733</v>
+        <v>155</v>
       </c>
       <c r="J354" t="s">
-        <v>686</v>
+        <v>122</v>
       </c>
       <c r="K354" t="s">
         <v>45</v>
       </c>
       <c r="L354" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="M354" t="s">
         <v>702</v>
@@ -22334,7 +22334,7 @@
         <v>48</v>
       </c>
       <c r="P354" t="s">
-        <v>733</v>
+        <v>155</v>
       </c>
       <c r="Q354" t="s">
         <v>47</v>
@@ -22366,10 +22366,10 @@
         <v>41</v>
       </c>
       <c r="H355" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="I355" t="s">
-        <v>736</v>
+        <v>695</v>
       </c>
       <c r="J355" t="s">
         <v>686</v>
@@ -22378,7 +22378,7 @@
         <v>45</v>
       </c>
       <c r="L355" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="M355" t="s">
         <v>702</v>
@@ -22390,7 +22390,7 @@
         <v>48</v>
       </c>
       <c r="P355" t="s">
-        <v>736</v>
+        <v>695</v>
       </c>
       <c r="Q355" t="s">
         <v>47</v>
@@ -22413,28 +22413,28 @@
         <v>34</v>
       </c>
       <c r="E356" t="s">
-        <v>738</v>
+        <v>175</v>
       </c>
       <c r="F356" t="s">
-        <v>211</v>
+        <v>40</v>
       </c>
       <c r="G356" t="s">
         <v>41</v>
       </c>
       <c r="H356" t="s">
-        <v>425</v>
+        <v>511</v>
       </c>
       <c r="I356" t="s">
+        <v>695</v>
+      </c>
+      <c r="J356" t="s">
+        <v>70</v>
+      </c>
+      <c r="K356" t="s">
+        <v>45</v>
+      </c>
+      <c r="L356" t="s">
         <v>739</v>
-      </c>
-      <c r="J356" t="s">
-        <v>474</v>
-      </c>
-      <c r="K356" t="s">
-        <v>178</v>
-      </c>
-      <c r="L356" t="s">
-        <v>34</v>
       </c>
       <c r="M356" t="s">
         <v>702</v>
@@ -22446,7 +22446,7 @@
         <v>48</v>
       </c>
       <c r="P356" t="s">
-        <v>739</v>
+        <v>695</v>
       </c>
       <c r="Q356" t="s">
         <v>47</v>
@@ -23271,7 +23271,7 @@
         <v>686</v>
       </c>
       <c r="K371" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L371" t="s">
         <v>774</v>
@@ -25997,7 +25997,7 @@
         <v>33</v>
       </c>
       <c r="E420" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F420" t="s">
         <v>218</v>
@@ -26109,7 +26109,7 @@
         <v>34</v>
       </c>
       <c r="E422" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="F422" t="s">
         <v>218</v>
@@ -26221,7 +26221,7 @@
         <v>34</v>
       </c>
       <c r="E424" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F424" t="s">
         <v>218</v>
@@ -26333,7 +26333,7 @@
         <v>34</v>
       </c>
       <c r="E426" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F426" t="s">
         <v>218</v>
@@ -26351,7 +26351,7 @@
         <v>90</v>
       </c>
       <c r="K426" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L426" t="s">
         <v>939</v>
@@ -26389,7 +26389,7 @@
         <v>34</v>
       </c>
       <c r="E427" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F427" t="s">
         <v>218</v>
@@ -26501,7 +26501,7 @@
         <v>34</v>
       </c>
       <c r="E429" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F429" t="s">
         <v>218</v>
